--- a/T07_BHXH, BHTN_2026.xlsx
+++ b/T07_BHXH, BHTN_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504" activeTab="6"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Thang 12" sheetId="5" r:id="rId1"/>
@@ -18,7 +18,10 @@
     <sheet name="Thang 4" sheetId="8" r:id="rId4"/>
     <sheet name="Thang 5" sheetId="9" r:id="rId5"/>
     <sheet name="Thang 6" sheetId="10" r:id="rId6"/>
-    <sheet name="Thang 7" sheetId="11" r:id="rId7"/>
+    <sheet name="Tháng 7" sheetId="11" r:id="rId7"/>
+    <sheet name="Tháng 8" sheetId="12" r:id="rId8"/>
+    <sheet name="Tháng 9" sheetId="13" r:id="rId9"/>
+    <sheet name="Tháng 10" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
@@ -56,8 +59,104 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Ngo Minh  Khoa</author>
+  </authors>
+  <commentList>
+    <comment ref="Z8" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>Ngo Minh  Khoa:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+Đã cập nhật số KH điều chỉnh</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Ngo Minh  Khoa</author>
+  </authors>
+  <commentList>
+    <comment ref="Z8" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>Ngo Minh  Khoa:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+Đã cập nhật số KH điều chỉnh</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Ngo Minh  Khoa</author>
+  </authors>
+  <commentList>
+    <comment ref="Z8" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>Ngo Minh  Khoa:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+Đã cập nhật số KH điều chỉnh</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="84">
   <si>
     <t>STT</t>
   </si>
@@ -294,6 +393,24 @@
   </si>
   <si>
     <t>Bảo hiểm xã hội cơ sở Cái Nước</t>
+  </si>
+  <si>
+    <t>BẢNG TỔNG HỢP SỐ NGƯỜI THAM GIA BHXH, BHTN, BHYT ĐẾN 31/8/2026</t>
+  </si>
+  <si>
+    <t>Tháng 8/2026</t>
+  </si>
+  <si>
+    <t>BẢNG TỔNG HỢP SỐ NGƯỜI THAM GIA BHXH, BHTN, BHYT ĐẾN 30/9/2026</t>
+  </si>
+  <si>
+    <t>Tháng 9/2026</t>
+  </si>
+  <si>
+    <t>Tháng 10/2026</t>
+  </si>
+  <si>
+    <t>BẢNG TỔNG HỢP SỐ NGƯỜI THAM GIA BHXH, BHTN, BHYT ĐẾN 31/10/2026</t>
   </si>
 </sst>
 </file>
@@ -695,7 +812,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -976,16 +1093,7 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -994,14 +1102,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1038,6 +1158,39 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1177,6 +1330,111 @@
         <a:xfrm>
           <a:off x="6512870" y="455295"/>
           <a:ext cx="1981849" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>520030</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>24765</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>64510</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>24765</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Straight Connector 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="923890" y="451485"/>
+          <a:ext cx="1800000" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9151620" y="455295"/>
+          <a:ext cx="3688080" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1832,6 +2090,216 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>520030</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>24765</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>64510</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>24765</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Straight Connector 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="923890" y="451485"/>
+          <a:ext cx="1800000" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9151620" y="455295"/>
+          <a:ext cx="3688080" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>520030</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>24765</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>64510</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>24765</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Straight Connector 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="923890" y="451485"/>
+          <a:ext cx="1800000" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9151620" y="455295"/>
+          <a:ext cx="3688080" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2149,11 +2617,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
       <c r="D1" s="20"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
@@ -2168,36 +2636,36 @@
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
-      <c r="R1" s="119" t="s">
+      <c r="R1" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="119"/>
-      <c r="AJ1" s="119"/>
-      <c r="AK1" s="117"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="137"/>
+      <c r="AA1" s="137"/>
+      <c r="AB1" s="137"/>
+      <c r="AC1" s="137"/>
+      <c r="AD1" s="137"/>
+      <c r="AE1" s="137"/>
+      <c r="AF1" s="137"/>
+      <c r="AG1" s="137"/>
+      <c r="AH1" s="137"/>
+      <c r="AI1" s="137"/>
+      <c r="AJ1" s="137"/>
+      <c r="AK1" s="135"/>
       <c r="AL1" s="20"/>
     </row>
     <row r="2" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
@@ -2212,36 +2680,36 @@
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
-      <c r="R2" s="120" t="s">
+      <c r="R2" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="120"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="120"/>
-      <c r="AA2" s="120"/>
-      <c r="AB2" s="120"/>
-      <c r="AC2" s="120"/>
-      <c r="AD2" s="120"/>
-      <c r="AE2" s="120"/>
-      <c r="AF2" s="120"/>
-      <c r="AG2" s="120"/>
-      <c r="AH2" s="120"/>
-      <c r="AI2" s="120"/>
-      <c r="AJ2" s="120"/>
-      <c r="AK2" s="117"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="138"/>
+      <c r="Y2" s="138"/>
+      <c r="Z2" s="138"/>
+      <c r="AA2" s="138"/>
+      <c r="AB2" s="138"/>
+      <c r="AC2" s="138"/>
+      <c r="AD2" s="138"/>
+      <c r="AE2" s="138"/>
+      <c r="AF2" s="138"/>
+      <c r="AG2" s="138"/>
+      <c r="AH2" s="138"/>
+      <c r="AI2" s="138"/>
+      <c r="AJ2" s="138"/>
+      <c r="AK2" s="135"/>
       <c r="AL2" s="20"/>
     </row>
     <row r="3" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
@@ -2319,87 +2787,87 @@
       <c r="AL4" s="20"/>
     </row>
     <row r="5" spans="1:40" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
-      <c r="L5" s="116"/>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="116"/>
-      <c r="R5" s="116"/>
-      <c r="S5" s="116"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="116"/>
-      <c r="W5" s="116"/>
-      <c r="X5" s="116"/>
-      <c r="Y5" s="116"/>
-      <c r="Z5" s="116"/>
-      <c r="AA5" s="116"/>
-      <c r="AB5" s="116"/>
-      <c r="AC5" s="116"/>
-      <c r="AD5" s="117"/>
-      <c r="AE5" s="117"/>
-      <c r="AF5" s="117"/>
-      <c r="AG5" s="117"/>
-      <c r="AH5" s="117"/>
-      <c r="AI5" s="117"/>
-      <c r="AJ5" s="117"/>
-      <c r="AK5" s="117"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="134"/>
+      <c r="T5" s="134"/>
+      <c r="U5" s="134"/>
+      <c r="V5" s="134"/>
+      <c r="W5" s="134"/>
+      <c r="X5" s="134"/>
+      <c r="Y5" s="134"/>
+      <c r="Z5" s="134"/>
+      <c r="AA5" s="134"/>
+      <c r="AB5" s="134"/>
+      <c r="AC5" s="134"/>
+      <c r="AD5" s="135"/>
+      <c r="AE5" s="135"/>
+      <c r="AF5" s="135"/>
+      <c r="AG5" s="135"/>
+      <c r="AH5" s="135"/>
+      <c r="AI5" s="135"/>
+      <c r="AJ5" s="135"/>
+      <c r="AK5" s="135"/>
       <c r="AL5" s="20"/>
     </row>
     <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="121" t="s">
+      <c r="A6" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="121"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="121"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="121"/>
-      <c r="M6" s="121"/>
-      <c r="N6" s="121"/>
-      <c r="O6" s="121"/>
-      <c r="P6" s="121"/>
-      <c r="Q6" s="121"/>
-      <c r="R6" s="121"/>
-      <c r="S6" s="121"/>
-      <c r="T6" s="121"/>
-      <c r="U6" s="121"/>
-      <c r="V6" s="121"/>
-      <c r="W6" s="121"/>
-      <c r="X6" s="121"/>
-      <c r="Y6" s="121"/>
-      <c r="Z6" s="121"/>
-      <c r="AA6" s="121"/>
-      <c r="AB6" s="121"/>
-      <c r="AC6" s="121"/>
-      <c r="AD6" s="122"/>
-      <c r="AE6" s="122"/>
-      <c r="AF6" s="122"/>
-      <c r="AG6" s="122"/>
-      <c r="AH6" s="122"/>
-      <c r="AI6" s="122"/>
-      <c r="AJ6" s="122"/>
-      <c r="AK6" s="122"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="122"/>
+      <c r="O6" s="122"/>
+      <c r="P6" s="122"/>
+      <c r="Q6" s="122"/>
+      <c r="R6" s="122"/>
+      <c r="S6" s="122"/>
+      <c r="T6" s="122"/>
+      <c r="U6" s="122"/>
+      <c r="V6" s="122"/>
+      <c r="W6" s="122"/>
+      <c r="X6" s="122"/>
+      <c r="Y6" s="122"/>
+      <c r="Z6" s="122"/>
+      <c r="AA6" s="122"/>
+      <c r="AB6" s="122"/>
+      <c r="AC6" s="122"/>
+      <c r="AD6" s="123"/>
+      <c r="AE6" s="123"/>
+      <c r="AF6" s="123"/>
+      <c r="AG6" s="123"/>
+      <c r="AH6" s="123"/>
+      <c r="AI6" s="123"/>
+      <c r="AJ6" s="123"/>
+      <c r="AK6" s="123"/>
       <c r="AL6" s="24"/>
     </row>
     <row r="7" spans="1:40" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2444,64 +2912,64 @@
       <c r="AL7" s="7"/>
     </row>
     <row r="8" spans="1:40" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="125" t="s">
+      <c r="A8" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="125" t="s">
+      <c r="B8" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="123" t="s">
+      <c r="C8" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="127" t="s">
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="128" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="128"/>
-      <c r="J8" s="128"/>
-      <c r="K8" s="128"/>
-      <c r="L8" s="128"/>
+      <c r="I8" s="129"/>
+      <c r="J8" s="129"/>
+      <c r="K8" s="129"/>
+      <c r="L8" s="129"/>
       <c r="M8" s="51"/>
-      <c r="N8" s="123" t="s">
+      <c r="N8" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="124"/>
-      <c r="P8" s="124"/>
-      <c r="Q8" s="124"/>
-      <c r="R8" s="124"/>
-      <c r="S8" s="124"/>
-      <c r="T8" s="129"/>
+      <c r="O8" s="125"/>
+      <c r="P8" s="125"/>
+      <c r="Q8" s="125"/>
+      <c r="R8" s="125"/>
+      <c r="S8" s="125"/>
+      <c r="T8" s="130"/>
       <c r="U8" s="52"/>
-      <c r="V8" s="123" t="s">
+      <c r="V8" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="W8" s="124"/>
-      <c r="X8" s="124"/>
-      <c r="Y8" s="124"/>
-      <c r="Z8" s="124"/>
-      <c r="AA8" s="124"/>
-      <c r="AB8" s="129"/>
+      <c r="W8" s="125"/>
+      <c r="X8" s="125"/>
+      <c r="Y8" s="125"/>
+      <c r="Z8" s="125"/>
+      <c r="AA8" s="125"/>
+      <c r="AB8" s="130"/>
       <c r="AC8" s="58"/>
-      <c r="AD8" s="130" t="s">
+      <c r="AD8" s="131" t="s">
         <v>11</v>
       </c>
-      <c r="AE8" s="131"/>
-      <c r="AF8" s="131"/>
-      <c r="AG8" s="131"/>
-      <c r="AH8" s="131"/>
-      <c r="AI8" s="131"/>
-      <c r="AJ8" s="132"/>
-      <c r="AK8" s="114" t="s">
+      <c r="AE8" s="132"/>
+      <c r="AF8" s="132"/>
+      <c r="AG8" s="132"/>
+      <c r="AH8" s="132"/>
+      <c r="AI8" s="132"/>
+      <c r="AJ8" s="133"/>
+      <c r="AK8" s="143" t="s">
         <v>8</v>
       </c>
       <c r="AL8" s="34"/>
     </row>
     <row r="9" spans="1:40" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="126"/>
-      <c r="B9" s="126"/>
+      <c r="A9" s="127"/>
+      <c r="B9" s="127"/>
       <c r="C9" s="42" t="s">
         <v>27</v>
       </c>
@@ -2604,7 +3072,7 @@
       <c r="AJ9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="AK9" s="115"/>
+      <c r="AK9" s="144"/>
       <c r="AL9" s="34"/>
       <c r="AM9" s="34"/>
     </row>
@@ -3259,10 +3727,10 @@
       <c r="AN16" s="10"/>
     </row>
     <row r="17" spans="1:40" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="112" t="s">
+      <c r="A17" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="112"/>
+      <c r="B17" s="141"/>
       <c r="C17" s="18">
         <f>SUM(C10:C16)</f>
         <v>227321</v>
@@ -3439,22 +3907,22 @@
     </row>
     <row r="19" spans="1:40" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="113" t="s">
+      <c r="B19" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="113"/>
-      <c r="D19" s="113"/>
-      <c r="E19" s="113"/>
-      <c r="F19" s="113"/>
-      <c r="G19" s="113"/>
-      <c r="H19" s="113"/>
-      <c r="I19" s="113"/>
-      <c r="J19" s="113"/>
-      <c r="K19" s="113"/>
-      <c r="L19" s="113"/>
-      <c r="M19" s="113"/>
-      <c r="N19" s="113"/>
-      <c r="O19" s="113"/>
+      <c r="C19" s="142"/>
+      <c r="D19" s="142"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="142"/>
+      <c r="G19" s="142"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="142"/>
+      <c r="J19" s="142"/>
+      <c r="K19" s="142"/>
+      <c r="L19" s="142"/>
+      <c r="M19" s="142"/>
+      <c r="N19" s="142"/>
+      <c r="O19" s="142"/>
       <c r="P19" s="49"/>
       <c r="Q19" s="49"/>
       <c r="R19" s="19"/>
@@ -3480,23 +3948,23 @@
       <c r="AL19" s="19"/>
     </row>
     <row r="20" spans="1:40" ht="18" x14ac:dyDescent="0.35">
-      <c r="B20" s="110"/>
-      <c r="C20" s="110"/>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="110"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="139"/>
+      <c r="N20" s="139"/>
+      <c r="O20" s="139"/>
+      <c r="P20" s="139"/>
+      <c r="Q20" s="139"/>
+      <c r="R20" s="139"/>
       <c r="S20" s="23"/>
       <c r="T20" s="23"/>
       <c r="U20" s="23"/>
@@ -3522,10 +3990,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="111"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="140"/>
+      <c r="G21" s="140"/>
       <c r="H21" s="21"/>
       <c r="I21" s="21"/>
       <c r="J21" s="21"/>
@@ -3649,6 +4117,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B20:R20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="B19:O19"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="R1:AK1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="R2:AK2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A6:AK6"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A8:A9"/>
@@ -3657,22 +4136,1506 @@
     <mergeCell ref="N8:T8"/>
     <mergeCell ref="V8:AB8"/>
     <mergeCell ref="AD8:AJ8"/>
-    <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="R1:AK1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="R2:AK2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="B20:R20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="B19:O19"/>
-    <mergeCell ref="AK8:AK9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AQ25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.88671875" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="4" width="13.5546875" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="10.88671875" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="10" width="10.33203125" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="9.21875" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="17" width="8.6640625" customWidth="1"/>
+    <col min="18" max="18" width="8" customWidth="1"/>
+    <col min="19" max="19" width="11.5546875" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="23" width="8.6640625" customWidth="1"/>
+    <col min="24" max="24" width="6.88671875" customWidth="1"/>
+    <col min="25" max="25" width="17" customWidth="1"/>
+    <col min="40" max="40" width="11.88671875" customWidth="1"/>
+    <col min="41" max="41" width="11.33203125" customWidth="1"/>
+    <col min="42" max="42" width="10.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="136" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
+      <c r="Y1" s="118"/>
+    </row>
+    <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="137" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
+      <c r="Y2" s="118"/>
+    </row>
+    <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+    </row>
+    <row r="4" spans="1:43" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="117"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="117"/>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118"/>
+      <c r="X4" s="118"/>
+      <c r="Y4" s="118"/>
+    </row>
+    <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="134" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
+      <c r="Y5" s="118"/>
+    </row>
+    <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y6" s="7"/>
+    </row>
+    <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="126" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="126" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="129" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y7" s="128" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z7" s="152" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA7" s="152"/>
+      <c r="AB7" s="152"/>
+      <c r="AC7" s="152"/>
+      <c r="AD7" s="152"/>
+      <c r="AE7" s="152"/>
+      <c r="AF7" s="152"/>
+      <c r="AG7" s="150" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH7" s="152" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI7" s="152"/>
+      <c r="AJ7" s="152"/>
+      <c r="AK7" s="152"/>
+      <c r="AL7" s="152"/>
+      <c r="AM7" s="152"/>
+      <c r="AN7" s="152"/>
+      <c r="AO7" s="152"/>
+      <c r="AP7" s="152"/>
+      <c r="AQ7" s="150"/>
+    </row>
+    <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="121" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="121" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="121" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="121" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="121" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="121" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="121" t="s">
+        <v>82</v>
+      </c>
+      <c r="N8" s="121" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="121" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="R8" s="121" t="s">
+        <v>33</v>
+      </c>
+      <c r="S8" s="121" t="s">
+        <v>82</v>
+      </c>
+      <c r="T8" s="121" t="s">
+        <v>30</v>
+      </c>
+      <c r="U8" s="121" t="s">
+        <v>46</v>
+      </c>
+      <c r="V8" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="W8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="X8" s="144"/>
+      <c r="Y8" s="128"/>
+      <c r="Z8" s="94" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA8" s="94" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB8" s="94" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC8" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD8" s="94" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE8" s="94" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF8" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG8" s="151"/>
+      <c r="AH8" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI8" s="105" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ8" s="105" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK8" s="105" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL8" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM8" s="96" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN8" s="94" t="s">
+        <v>67</v>
+      </c>
+      <c r="AO8" s="94" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP8" s="94" t="s">
+        <v>75</v>
+      </c>
+      <c r="AQ8" s="151"/>
+    </row>
+    <row r="9" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26">
+        <v>1</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="71">
+        <v>39379</v>
+      </c>
+      <c r="D9" s="72">
+        <v>39379</v>
+      </c>
+      <c r="E9" s="29">
+        <f t="shared" ref="E9:E16" si="0">D9/C9*100</f>
+        <v>100</v>
+      </c>
+      <c r="F9" s="59">
+        <v>1625</v>
+      </c>
+      <c r="G9" s="30"/>
+      <c r="H9" s="31">
+        <f>G9-'Tháng 7'!G9</f>
+        <v>-1528</v>
+      </c>
+      <c r="I9" s="31">
+        <f>G9-'Thang 12'!Q10</f>
+        <v>-1652</v>
+      </c>
+      <c r="J9" s="31">
+        <f t="shared" ref="J9:J15" si="1">F9-G9</f>
+        <v>1625</v>
+      </c>
+      <c r="K9" s="61">
+        <f t="shared" ref="K9:K16" si="2">G9/F9*100</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="31">
+        <v>1862</v>
+      </c>
+      <c r="M9" s="30"/>
+      <c r="N9" s="53">
+        <f>M9-'Tháng 7'!M9</f>
+        <v>-1624</v>
+      </c>
+      <c r="O9" s="53">
+        <f>M9-'Thang 12'!Y10</f>
+        <v>-1445</v>
+      </c>
+      <c r="P9" s="53">
+        <f>L9-M9</f>
+        <v>1862</v>
+      </c>
+      <c r="Q9" s="70">
+        <f>M9/L9*100</f>
+        <v>0</v>
+      </c>
+      <c r="R9" s="31">
+        <v>1420</v>
+      </c>
+      <c r="S9" s="31"/>
+      <c r="T9" s="53">
+        <f>S9-'Tháng 7'!S9</f>
+        <v>-1392</v>
+      </c>
+      <c r="U9" s="53">
+        <f>S9-'Thang 12'!AG10</f>
+        <v>-1670</v>
+      </c>
+      <c r="V9" s="53">
+        <f t="shared" ref="V9:V15" si="3">R9-S9</f>
+        <v>1420</v>
+      </c>
+      <c r="W9" s="61">
+        <f t="shared" ref="W9:W16" si="4">S9/R9*100</f>
+        <v>0</v>
+      </c>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="106" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z9" s="107">
+        <f>Z10+Z11+Z12+Z13</f>
+        <v>466144</v>
+      </c>
+      <c r="AA9" s="94">
+        <v>249318</v>
+      </c>
+      <c r="AB9" s="94">
+        <v>249318</v>
+      </c>
+      <c r="AC9" s="94">
+        <f>AA9-AB9</f>
+        <v>0</v>
+      </c>
+      <c r="AD9" s="94">
+        <f>AA9-AG9</f>
+        <v>-273397</v>
+      </c>
+      <c r="AE9" s="97">
+        <f>AA9/Z9*100</f>
+        <v>53.48518912610696</v>
+      </c>
+      <c r="AF9" s="98">
+        <f>Z9-AA9</f>
+        <v>216826</v>
+      </c>
+      <c r="AG9" s="104">
+        <v>522715</v>
+      </c>
+      <c r="AH9" s="99">
+        <f t="shared" ref="AH9" si="5">SUM(AI9:AL9)</f>
+        <v>48041</v>
+      </c>
+      <c r="AI9" s="100">
+        <v>2881</v>
+      </c>
+      <c r="AJ9" s="100">
+        <v>1394</v>
+      </c>
+      <c r="AK9" s="100">
+        <v>190</v>
+      </c>
+      <c r="AL9" s="101">
+        <v>43576</v>
+      </c>
+      <c r="AM9" s="102">
+        <f t="shared" ref="AM9" si="6">SUM(AJ9:AK9)</f>
+        <v>1584</v>
+      </c>
+      <c r="AN9" s="103">
+        <f>AM9/Z9*100</f>
+        <v>0.33980915768517883</v>
+      </c>
+      <c r="AO9" s="103">
+        <v>1.26</v>
+      </c>
+      <c r="AP9" s="103">
+        <f t="shared" ref="AP9" si="7">AO9-AN9</f>
+        <v>0.92019084231482118</v>
+      </c>
+      <c r="AQ9" s="104"/>
+    </row>
+    <row r="10" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26">
+        <v>2</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="71">
+        <v>29921</v>
+      </c>
+      <c r="D10" s="72">
+        <v>29921</v>
+      </c>
+      <c r="E10" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F10" s="59">
+        <v>815</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="31">
+        <f>G10-'Tháng 7'!G10</f>
+        <v>-496</v>
+      </c>
+      <c r="I10" s="31">
+        <f>G10-'Thang 12'!Q11</f>
+        <v>-487</v>
+      </c>
+      <c r="J10" s="31">
+        <f t="shared" si="1"/>
+        <v>815</v>
+      </c>
+      <c r="K10" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="31">
+        <v>1297</v>
+      </c>
+      <c r="M10" s="30"/>
+      <c r="N10" s="53">
+        <f>M10-'Tháng 7'!M10</f>
+        <v>-720</v>
+      </c>
+      <c r="O10" s="53">
+        <f>M10-'Thang 12'!Y11</f>
+        <v>-350</v>
+      </c>
+      <c r="P10" s="53">
+        <f t="shared" ref="P10:P15" si="8">L10-M10</f>
+        <v>1297</v>
+      </c>
+      <c r="Q10" s="70">
+        <f t="shared" ref="Q10:Q16" si="9">M10/L10*100</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="31">
+        <v>661</v>
+      </c>
+      <c r="S10" s="31"/>
+      <c r="T10" s="53">
+        <f>S10-'Tháng 7'!S10</f>
+        <v>-390</v>
+      </c>
+      <c r="U10" s="53">
+        <f>S10-'Thang 12'!AG11</f>
+        <v>-590</v>
+      </c>
+      <c r="V10" s="53">
+        <f t="shared" si="3"/>
+        <v>661</v>
+      </c>
+      <c r="W10" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="108" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z10" s="107">
+        <v>173399</v>
+      </c>
+      <c r="AA10" s="94">
+        <v>94017</v>
+      </c>
+      <c r="AB10" s="94">
+        <v>94017</v>
+      </c>
+      <c r="AC10" s="94">
+        <f t="shared" ref="AC10:AC14" si="10">AA10-AB10</f>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="94">
+        <f t="shared" ref="AD10:AD14" si="11">AA10-AG10</f>
+        <v>-97632</v>
+      </c>
+      <c r="AE10" s="97">
+        <f t="shared" ref="AE10:AE13" si="12">AA10/Z10*100</f>
+        <v>54.220035871025786</v>
+      </c>
+      <c r="AF10" s="98">
+        <f t="shared" ref="AF10:AF13" si="13">Z10-AA10</f>
+        <v>79382</v>
+      </c>
+      <c r="AG10" s="104">
+        <v>191649</v>
+      </c>
+      <c r="AH10" s="95"/>
+      <c r="AI10" s="105"/>
+      <c r="AJ10" s="105"/>
+      <c r="AK10" s="105"/>
+      <c r="AL10" s="96"/>
+      <c r="AM10" s="96"/>
+      <c r="AN10" s="94"/>
+      <c r="AO10" s="94"/>
+      <c r="AP10" s="94"/>
+      <c r="AQ10" s="104"/>
+    </row>
+    <row r="11" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="26">
+        <v>3</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="71">
+        <v>25763</v>
+      </c>
+      <c r="D11" s="72">
+        <v>25763</v>
+      </c>
+      <c r="E11" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F11" s="59">
+        <v>652</v>
+      </c>
+      <c r="G11" s="30"/>
+      <c r="H11" s="31">
+        <f>G11-'Tháng 7'!G11</f>
+        <v>-519</v>
+      </c>
+      <c r="I11" s="31">
+        <f>G11-'Thang 12'!Q12</f>
+        <v>-539</v>
+      </c>
+      <c r="J11" s="31">
+        <f t="shared" si="1"/>
+        <v>652</v>
+      </c>
+      <c r="K11" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="31">
+        <v>1117</v>
+      </c>
+      <c r="M11" s="30"/>
+      <c r="N11" s="53">
+        <f>M11-'Tháng 7'!M11</f>
+        <v>-770</v>
+      </c>
+      <c r="O11" s="53">
+        <f>M11-'Thang 12'!Y12</f>
+        <v>-397</v>
+      </c>
+      <c r="P11" s="53">
+        <f t="shared" si="8"/>
+        <v>1117</v>
+      </c>
+      <c r="Q11" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="31">
+        <v>565</v>
+      </c>
+      <c r="S11" s="31"/>
+      <c r="T11" s="53">
+        <f>S11-'Tháng 7'!S11</f>
+        <v>-434</v>
+      </c>
+      <c r="U11" s="53">
+        <f>S11-'Thang 12'!AG12</f>
+        <v>-816</v>
+      </c>
+      <c r="V11" s="53">
+        <f t="shared" si="3"/>
+        <v>565</v>
+      </c>
+      <c r="W11" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="28"/>
+      <c r="Y11" s="108" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z11" s="107">
+        <v>37255</v>
+      </c>
+      <c r="AA11" s="109">
+        <v>19221</v>
+      </c>
+      <c r="AB11" s="109">
+        <v>19221</v>
+      </c>
+      <c r="AC11" s="94">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="94">
+        <f t="shared" si="11"/>
+        <v>-16054</v>
+      </c>
+      <c r="AE11" s="97">
+        <f t="shared" si="12"/>
+        <v>51.593074755066439</v>
+      </c>
+      <c r="AF11" s="98">
+        <f t="shared" si="13"/>
+        <v>18034</v>
+      </c>
+      <c r="AG11" s="104">
+        <v>35275</v>
+      </c>
+      <c r="AH11" s="104"/>
+      <c r="AI11" s="104"/>
+      <c r="AJ11" s="104"/>
+      <c r="AK11" s="104"/>
+      <c r="AL11" s="104"/>
+      <c r="AM11" s="104"/>
+      <c r="AN11" s="104"/>
+      <c r="AO11" s="104"/>
+      <c r="AP11" s="104"/>
+      <c r="AQ11" s="104"/>
+    </row>
+    <row r="12" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="26">
+        <v>4</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="71">
+        <v>51742</v>
+      </c>
+      <c r="D12" s="72">
+        <v>51742</v>
+      </c>
+      <c r="E12" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F12" s="59">
+        <v>1151</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="31">
+        <f>G12-'Tháng 7'!G12</f>
+        <v>-1096</v>
+      </c>
+      <c r="I12" s="31">
+        <f>G12-'Thang 12'!Q13</f>
+        <v>-1101</v>
+      </c>
+      <c r="J12" s="31">
+        <f t="shared" si="1"/>
+        <v>1151</v>
+      </c>
+      <c r="K12" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="31">
+        <v>2043</v>
+      </c>
+      <c r="M12" s="30"/>
+      <c r="N12" s="53">
+        <f>M12-'Tháng 7'!M12</f>
+        <v>-1626</v>
+      </c>
+      <c r="O12" s="53">
+        <f>M12-'Thang 12'!Y13</f>
+        <v>-910</v>
+      </c>
+      <c r="P12" s="53">
+        <f t="shared" si="8"/>
+        <v>2043</v>
+      </c>
+      <c r="Q12" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="31">
+        <v>978</v>
+      </c>
+      <c r="S12" s="31"/>
+      <c r="T12" s="53">
+        <f>S12-'Tháng 7'!S12</f>
+        <v>-991</v>
+      </c>
+      <c r="U12" s="53">
+        <f>S12-'Thang 12'!AG13</f>
+        <v>-1451</v>
+      </c>
+      <c r="V12" s="53">
+        <f t="shared" si="3"/>
+        <v>978</v>
+      </c>
+      <c r="W12" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="108" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z12" s="107">
+        <v>10639</v>
+      </c>
+      <c r="AA12" s="109">
+        <v>6448</v>
+      </c>
+      <c r="AB12" s="109">
+        <v>6448</v>
+      </c>
+      <c r="AC12" s="94">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="94">
+        <f t="shared" si="11"/>
+        <v>-6661</v>
+      </c>
+      <c r="AE12" s="97">
+        <f t="shared" si="12"/>
+        <v>60.607199924804966</v>
+      </c>
+      <c r="AF12" s="98">
+        <f t="shared" si="13"/>
+        <v>4191</v>
+      </c>
+      <c r="AG12" s="104">
+        <v>13109</v>
+      </c>
+      <c r="AH12" s="104"/>
+      <c r="AI12" s="104"/>
+      <c r="AJ12" s="104"/>
+      <c r="AK12" s="104"/>
+      <c r="AL12" s="104"/>
+      <c r="AM12" s="104"/>
+      <c r="AN12" s="104"/>
+      <c r="AO12" s="104"/>
+      <c r="AP12" s="104"/>
+      <c r="AQ12" s="104"/>
+    </row>
+    <row r="13" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="26">
+        <v>5</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="71">
+        <v>27773</v>
+      </c>
+      <c r="D13" s="72">
+        <v>27773</v>
+      </c>
+      <c r="E13" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F13" s="59">
+        <v>1206</v>
+      </c>
+      <c r="G13" s="30"/>
+      <c r="H13" s="31">
+        <f>G13-'Tháng 7'!G13</f>
+        <v>-979</v>
+      </c>
+      <c r="I13" s="31">
+        <f>G13-'Thang 12'!Q14</f>
+        <v>-1008</v>
+      </c>
+      <c r="J13" s="31">
+        <f t="shared" si="1"/>
+        <v>1206</v>
+      </c>
+      <c r="K13" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="31">
+        <v>1204</v>
+      </c>
+      <c r="M13" s="30"/>
+      <c r="N13" s="53">
+        <f>M13-'Tháng 7'!M13</f>
+        <v>-972</v>
+      </c>
+      <c r="O13" s="53">
+        <f>M13-'Thang 12'!Y14</f>
+        <v>-914</v>
+      </c>
+      <c r="P13" s="53">
+        <f t="shared" si="8"/>
+        <v>1204</v>
+      </c>
+      <c r="Q13" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="31">
+        <v>1005</v>
+      </c>
+      <c r="S13" s="31"/>
+      <c r="T13" s="53">
+        <f>S13-'Tháng 7'!S13</f>
+        <v>-864</v>
+      </c>
+      <c r="U13" s="53">
+        <f>S13-'Thang 12'!AG14</f>
+        <v>-1007</v>
+      </c>
+      <c r="V13" s="53">
+        <f t="shared" si="3"/>
+        <v>1005</v>
+      </c>
+      <c r="W13" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="108" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z13" s="107">
+        <v>244851</v>
+      </c>
+      <c r="AA13" s="109">
+        <v>129490</v>
+      </c>
+      <c r="AB13" s="109">
+        <v>129490</v>
+      </c>
+      <c r="AC13" s="94">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="94">
+        <f t="shared" si="11"/>
+        <v>-153011</v>
+      </c>
+      <c r="AE13" s="97">
+        <f t="shared" si="12"/>
+        <v>52.88522407504972</v>
+      </c>
+      <c r="AF13" s="98">
+        <f t="shared" si="13"/>
+        <v>115361</v>
+      </c>
+      <c r="AG13" s="104">
+        <v>282501</v>
+      </c>
+      <c r="AH13" s="104"/>
+      <c r="AI13" s="104"/>
+      <c r="AJ13" s="104"/>
+      <c r="AK13" s="104"/>
+      <c r="AL13" s="104"/>
+      <c r="AM13" s="104"/>
+      <c r="AN13" s="104"/>
+      <c r="AO13" s="104"/>
+      <c r="AP13" s="104"/>
+      <c r="AQ13" s="104"/>
+    </row>
+    <row r="14" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="26">
+        <v>6</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="71">
+        <v>28987</v>
+      </c>
+      <c r="D14" s="72">
+        <v>28987</v>
+      </c>
+      <c r="E14" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F14" s="59">
+        <v>591</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="31">
+        <f>G14-'Tháng 7'!G14</f>
+        <v>-524</v>
+      </c>
+      <c r="I14" s="31">
+        <f>G14-'Thang 12'!Q15</f>
+        <v>-464</v>
+      </c>
+      <c r="J14" s="31">
+        <f t="shared" si="1"/>
+        <v>591</v>
+      </c>
+      <c r="K14" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="31">
+        <v>1257</v>
+      </c>
+      <c r="M14" s="30"/>
+      <c r="N14" s="53">
+        <f>M14-'Tháng 7'!M14</f>
+        <v>-1010</v>
+      </c>
+      <c r="O14" s="53">
+        <f>M14-'Thang 12'!Y15</f>
+        <v>-372</v>
+      </c>
+      <c r="P14" s="53">
+        <f t="shared" si="8"/>
+        <v>1257</v>
+      </c>
+      <c r="Q14" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="31">
+        <v>447</v>
+      </c>
+      <c r="S14" s="31"/>
+      <c r="T14" s="53">
+        <f>S14-'Tháng 7'!S14</f>
+        <v>-417</v>
+      </c>
+      <c r="U14" s="53">
+        <f>S14-'Thang 12'!AG15</f>
+        <v>-980</v>
+      </c>
+      <c r="V14" s="53">
+        <f t="shared" si="3"/>
+        <v>447</v>
+      </c>
+      <c r="W14" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X14" s="28"/>
+      <c r="Y14" s="108" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z14" s="109"/>
+      <c r="AA14" s="109">
+        <v>142</v>
+      </c>
+      <c r="AB14" s="109">
+        <v>142</v>
+      </c>
+      <c r="AC14" s="94">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="94">
+        <f t="shared" si="11"/>
+        <v>-39</v>
+      </c>
+      <c r="AE14" s="97"/>
+      <c r="AF14" s="104"/>
+      <c r="AG14" s="104">
+        <v>181</v>
+      </c>
+      <c r="AH14" s="104"/>
+      <c r="AI14" s="104"/>
+      <c r="AJ14" s="104"/>
+      <c r="AK14" s="104"/>
+      <c r="AL14" s="104"/>
+      <c r="AM14" s="104"/>
+      <c r="AN14" s="104"/>
+      <c r="AO14" s="104"/>
+      <c r="AP14" s="104"/>
+      <c r="AQ14" s="104"/>
+    </row>
+    <row r="15" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="26">
+        <v>7</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="71">
+        <v>24726</v>
+      </c>
+      <c r="D15" s="72">
+        <v>24726</v>
+      </c>
+      <c r="E15" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F15" s="59">
+        <v>541</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="31">
+        <f>G15-'Tháng 7'!G15</f>
+        <v>-536</v>
+      </c>
+      <c r="I15" s="31">
+        <f>G15-'Thang 12'!Q16</f>
+        <v>-461</v>
+      </c>
+      <c r="J15" s="31">
+        <f t="shared" si="1"/>
+        <v>541</v>
+      </c>
+      <c r="K15" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="31">
+        <v>1072</v>
+      </c>
+      <c r="M15" s="30"/>
+      <c r="N15" s="53">
+        <f>M15-'Tháng 7'!M15</f>
+        <v>-1068</v>
+      </c>
+      <c r="O15" s="53">
+        <f>M15-'Thang 12'!Y16</f>
+        <v>-383</v>
+      </c>
+      <c r="P15" s="53">
+        <f t="shared" si="8"/>
+        <v>1072</v>
+      </c>
+      <c r="Q15" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="31">
+        <v>439</v>
+      </c>
+      <c r="S15" s="31"/>
+      <c r="T15" s="53">
+        <f>S15-'Tháng 7'!S15</f>
+        <v>-441</v>
+      </c>
+      <c r="U15" s="53">
+        <f>S15-'Thang 12'!AG16</f>
+        <v>-1040</v>
+      </c>
+      <c r="V15" s="53">
+        <f t="shared" si="3"/>
+        <v>439</v>
+      </c>
+      <c r="W15" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10"/>
+      <c r="AB15" s="10"/>
+      <c r="AC15" s="10"/>
+    </row>
+    <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="141" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="141"/>
+      <c r="C16" s="18">
+        <f>SUM(C9:C15)</f>
+        <v>228291</v>
+      </c>
+      <c r="D16" s="18">
+        <f>SUM(D9:D15)</f>
+        <v>228291</v>
+      </c>
+      <c r="E16" s="32">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F16" s="60">
+        <f>SUM(F9:F15)</f>
+        <v>6581</v>
+      </c>
+      <c r="G16" s="50">
+        <f>SUM(G9:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="55">
+        <f>SUM(H9:H15)</f>
+        <v>-5678</v>
+      </c>
+      <c r="I16" s="55">
+        <f>G16-'Thang 12'!Q17</f>
+        <v>-5712</v>
+      </c>
+      <c r="J16" s="55">
+        <f>SUM(J9:J15)</f>
+        <v>6581</v>
+      </c>
+      <c r="K16" s="57">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="18">
+        <f>SUM(L9:L15)</f>
+        <v>9852</v>
+      </c>
+      <c r="M16" s="18">
+        <f>SUM(M9:M15)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="56">
+        <f>SUM(N9:N15)</f>
+        <v>-7790</v>
+      </c>
+      <c r="O16" s="56">
+        <f>M16-'Thang 12'!Y17</f>
+        <v>-4771</v>
+      </c>
+      <c r="P16" s="18">
+        <f t="shared" ref="P16" si="14">SUM(P9:P15)</f>
+        <v>9852</v>
+      </c>
+      <c r="Q16" s="69">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="55">
+        <f>SUM(R9:R15)</f>
+        <v>5515</v>
+      </c>
+      <c r="S16" s="18">
+        <f>SUM(S9:S15)</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="56">
+        <f>SUM(T9:T15)</f>
+        <v>-4929</v>
+      </c>
+      <c r="U16" s="56">
+        <f>S16-'Thang 12'!AG17</f>
+        <v>-7554</v>
+      </c>
+      <c r="V16" s="56">
+        <f>SUM(V9:V15)</f>
+        <v>5515</v>
+      </c>
+      <c r="W16" s="57">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="37"/>
+      <c r="Y16" s="36"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="25"/>
+    </row>
+    <row r="17" spans="1:25" ht="9.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="11"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+    </row>
+    <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="142" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19"/>
+      <c r="X18" s="19"/>
+      <c r="Y18" s="19"/>
+    </row>
+    <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+    </row>
+    <row r="21" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+    </row>
+    <row r="22" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+    </row>
+    <row r="23" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B23" s="5"/>
+      <c r="R23" s="31"/>
+    </row>
+    <row r="24" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B24" s="5"/>
+      <c r="R24" s="31"/>
+    </row>
+    <row r="25" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="R25" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AP7"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="L7:Q7"/>
+    <mergeCell ref="R7:W7"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -3706,12 +5669,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
@@ -3720,31 +5683,31 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
-      <c r="M1" s="119" t="s">
+      <c r="M1" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="117"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="135"/>
       <c r="AA1" s="20"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
@@ -3753,28 +5716,28 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="120" t="s">
+      <c r="M2" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="120"/>
-      <c r="O2" s="120"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="120"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="117"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="138"/>
+      <c r="Y2" s="138"/>
+      <c r="Z2" s="135"/>
       <c r="AA2" s="20"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
@@ -3830,63 +5793,63 @@
       <c r="AA4" s="20"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="134" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
-      <c r="L5" s="116"/>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="116"/>
-      <c r="R5" s="116"/>
-      <c r="S5" s="116"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="117"/>
-      <c r="W5" s="117"/>
-      <c r="X5" s="117"/>
-      <c r="Y5" s="117"/>
-      <c r="Z5" s="117"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="134"/>
+      <c r="T5" s="134"/>
+      <c r="U5" s="134"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
+      <c r="Y5" s="135"/>
+      <c r="Z5" s="135"/>
       <c r="AA5" s="20"/>
     </row>
     <row r="6" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="136"/>
-      <c r="B6" s="136"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="136"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="136"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="136"/>
-      <c r="O6" s="136"/>
-      <c r="P6" s="136"/>
-      <c r="Q6" s="136"/>
-      <c r="R6" s="136"/>
-      <c r="S6" s="136"/>
-      <c r="T6" s="136"/>
-      <c r="U6" s="136"/>
-      <c r="V6" s="137"/>
-      <c r="W6" s="137"/>
-      <c r="X6" s="137"/>
-      <c r="Y6" s="137"/>
-      <c r="Z6" s="137"/>
+      <c r="A6" s="148"/>
+      <c r="B6" s="148"/>
+      <c r="C6" s="148"/>
+      <c r="D6" s="148"/>
+      <c r="E6" s="148"/>
+      <c r="F6" s="148"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="148"/>
+      <c r="K6" s="148"/>
+      <c r="L6" s="148"/>
+      <c r="M6" s="148"/>
+      <c r="N6" s="148"/>
+      <c r="O6" s="148"/>
+      <c r="P6" s="148"/>
+      <c r="Q6" s="148"/>
+      <c r="R6" s="148"/>
+      <c r="S6" s="148"/>
+      <c r="T6" s="148"/>
+      <c r="U6" s="148"/>
+      <c r="V6" s="149"/>
+      <c r="W6" s="149"/>
+      <c r="X6" s="149"/>
+      <c r="Y6" s="149"/>
+      <c r="Z6" s="149"/>
       <c r="AA6" s="24"/>
     </row>
     <row r="7" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3920,53 +5883,53 @@
       <c r="AA7" s="7"/>
     </row>
     <row r="8" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="125" t="s">
+      <c r="A8" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="125" t="s">
+      <c r="B8" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="128" t="s">
+      <c r="C8" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="128"/>
-      <c r="E8" s="128"/>
+      <c r="D8" s="129"/>
+      <c r="E8" s="129"/>
       <c r="F8" s="51"/>
-      <c r="G8" s="133" t="s">
+      <c r="G8" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="134"/>
-      <c r="I8" s="134"/>
-      <c r="J8" s="135"/>
-      <c r="K8" s="123" t="s">
+      <c r="H8" s="146"/>
+      <c r="I8" s="146"/>
+      <c r="J8" s="147"/>
+      <c r="K8" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="124"/>
-      <c r="M8" s="124"/>
-      <c r="N8" s="124"/>
-      <c r="O8" s="129"/>
-      <c r="P8" s="123" t="s">
+      <c r="L8" s="125"/>
+      <c r="M8" s="125"/>
+      <c r="N8" s="125"/>
+      <c r="O8" s="130"/>
+      <c r="P8" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="Q8" s="124"/>
-      <c r="R8" s="124"/>
-      <c r="S8" s="124"/>
-      <c r="T8" s="129"/>
-      <c r="U8" s="123" t="s">
+      <c r="Q8" s="125"/>
+      <c r="R8" s="125"/>
+      <c r="S8" s="125"/>
+      <c r="T8" s="130"/>
+      <c r="U8" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="V8" s="124"/>
-      <c r="W8" s="124"/>
-      <c r="X8" s="124"/>
-      <c r="Y8" s="129"/>
-      <c r="Z8" s="114" t="s">
+      <c r="V8" s="125"/>
+      <c r="W8" s="125"/>
+      <c r="X8" s="125"/>
+      <c r="Y8" s="130"/>
+      <c r="Z8" s="143" t="s">
         <v>8</v>
       </c>
       <c r="AA8" s="34"/>
     </row>
     <row r="9" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="126"/>
-      <c r="B9" s="126"/>
+      <c r="A9" s="127"/>
+      <c r="B9" s="127"/>
       <c r="C9" s="42" t="s">
         <v>27</v>
       </c>
@@ -4034,7 +5997,7 @@
       <c r="Y9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="Z9" s="115"/>
+      <c r="Z9" s="144"/>
       <c r="AA9" s="34"/>
       <c r="AB9" s="34"/>
     </row>
@@ -4522,10 +6485,10 @@
       <c r="AC16" s="10"/>
     </row>
     <row r="17" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="112" t="s">
+      <c r="A17" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="112"/>
+      <c r="B17" s="141"/>
       <c r="C17" s="18">
         <f>SUM(C10:C16)</f>
         <v>227321</v>
@@ -4644,18 +6607,18 @@
     </row>
     <row r="19" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="113" t="s">
+      <c r="B19" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="113"/>
-      <c r="D19" s="113"/>
-      <c r="E19" s="113"/>
-      <c r="F19" s="113"/>
-      <c r="G19" s="113"/>
-      <c r="H19" s="113"/>
-      <c r="I19" s="113"/>
-      <c r="J19" s="113"/>
-      <c r="K19" s="113"/>
+      <c r="C19" s="142"/>
+      <c r="D19" s="142"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="142"/>
+      <c r="G19" s="142"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="142"/>
+      <c r="J19" s="142"/>
+      <c r="K19" s="142"/>
       <c r="L19" s="49"/>
       <c r="M19" s="19"/>
       <c r="N19" s="19"/>
@@ -4674,18 +6637,18 @@
       <c r="AA19" s="19"/>
     </row>
     <row r="20" spans="1:29" ht="18" x14ac:dyDescent="0.35">
-      <c r="B20" s="110"/>
-      <c r="C20" s="110"/>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="139"/>
       <c r="N20" s="23"/>
       <c r="O20" s="23"/>
       <c r="P20" s="23"/>
@@ -4704,8 +6667,8 @@
         <v>4</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
@@ -4792,6 +6755,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="M1:Z1"/>
+    <mergeCell ref="M2:Z2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A5:Z5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="A6:Z6"/>
@@ -4805,12 +6774,6 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="B19:K19"/>
     <mergeCell ref="B20:M20"/>
-    <mergeCell ref="M1:Z1"/>
-    <mergeCell ref="M2:Z2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A5:Z5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4852,12 +6815,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
@@ -4868,41 +6831,41 @@
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
-      <c r="O1" s="119" t="s">
+      <c r="O1" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="119"/>
-      <c r="AJ1" s="119"/>
-      <c r="AK1" s="119"/>
-      <c r="AL1" s="117"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="137"/>
+      <c r="AA1" s="137"/>
+      <c r="AB1" s="137"/>
+      <c r="AC1" s="137"/>
+      <c r="AD1" s="137"/>
+      <c r="AE1" s="137"/>
+      <c r="AF1" s="137"/>
+      <c r="AG1" s="137"/>
+      <c r="AH1" s="137"/>
+      <c r="AI1" s="137"/>
+      <c r="AJ1" s="137"/>
+      <c r="AK1" s="137"/>
+      <c r="AL1" s="135"/>
       <c r="AM1" s="20"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
@@ -4913,38 +6876,38 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
-      <c r="O2" s="120" t="s">
+      <c r="O2" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="120"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="120"/>
-      <c r="AA2" s="120"/>
-      <c r="AB2" s="120"/>
-      <c r="AC2" s="120"/>
-      <c r="AD2" s="120"/>
-      <c r="AE2" s="120"/>
-      <c r="AF2" s="120"/>
-      <c r="AG2" s="120"/>
-      <c r="AH2" s="120"/>
-      <c r="AI2" s="120"/>
-      <c r="AJ2" s="120"/>
-      <c r="AK2" s="120"/>
-      <c r="AL2" s="117"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="138"/>
+      <c r="Y2" s="138"/>
+      <c r="Z2" s="138"/>
+      <c r="AA2" s="138"/>
+      <c r="AB2" s="138"/>
+      <c r="AC2" s="138"/>
+      <c r="AD2" s="138"/>
+      <c r="AE2" s="138"/>
+      <c r="AF2" s="138"/>
+      <c r="AG2" s="138"/>
+      <c r="AH2" s="138"/>
+      <c r="AI2" s="138"/>
+      <c r="AJ2" s="138"/>
+      <c r="AK2" s="138"/>
+      <c r="AL2" s="135"/>
       <c r="AM2" s="20"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
@@ -5024,87 +6987,87 @@
       <c r="AM4" s="20"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="134" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
-      <c r="L5" s="116"/>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="116"/>
-      <c r="R5" s="116"/>
-      <c r="S5" s="116"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="116"/>
-      <c r="W5" s="116"/>
-      <c r="X5" s="116"/>
-      <c r="Y5" s="116"/>
-      <c r="Z5" s="116"/>
-      <c r="AA5" s="116"/>
-      <c r="AB5" s="116"/>
-      <c r="AC5" s="116"/>
-      <c r="AD5" s="116"/>
-      <c r="AE5" s="116"/>
-      <c r="AF5" s="117"/>
-      <c r="AG5" s="117"/>
-      <c r="AH5" s="117"/>
-      <c r="AI5" s="117"/>
-      <c r="AJ5" s="117"/>
-      <c r="AK5" s="117"/>
-      <c r="AL5" s="117"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="134"/>
+      <c r="T5" s="134"/>
+      <c r="U5" s="134"/>
+      <c r="V5" s="134"/>
+      <c r="W5" s="134"/>
+      <c r="X5" s="134"/>
+      <c r="Y5" s="134"/>
+      <c r="Z5" s="134"/>
+      <c r="AA5" s="134"/>
+      <c r="AB5" s="134"/>
+      <c r="AC5" s="134"/>
+      <c r="AD5" s="134"/>
+      <c r="AE5" s="134"/>
+      <c r="AF5" s="135"/>
+      <c r="AG5" s="135"/>
+      <c r="AH5" s="135"/>
+      <c r="AI5" s="135"/>
+      <c r="AJ5" s="135"/>
+      <c r="AK5" s="135"/>
+      <c r="AL5" s="135"/>
       <c r="AM5" s="20"/>
     </row>
     <row r="6" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="136"/>
-      <c r="B6" s="136"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="136"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="136"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="136"/>
-      <c r="O6" s="136"/>
-      <c r="P6" s="136"/>
-      <c r="Q6" s="136"/>
-      <c r="R6" s="136"/>
-      <c r="S6" s="136"/>
-      <c r="T6" s="136"/>
-      <c r="U6" s="136"/>
-      <c r="V6" s="136"/>
-      <c r="W6" s="136"/>
-      <c r="X6" s="136"/>
-      <c r="Y6" s="136"/>
-      <c r="Z6" s="136"/>
-      <c r="AA6" s="136"/>
-      <c r="AB6" s="136"/>
-      <c r="AC6" s="136"/>
-      <c r="AD6" s="136"/>
-      <c r="AE6" s="136"/>
-      <c r="AF6" s="137"/>
-      <c r="AG6" s="137"/>
-      <c r="AH6" s="137"/>
-      <c r="AI6" s="137"/>
-      <c r="AJ6" s="137"/>
-      <c r="AK6" s="137"/>
-      <c r="AL6" s="137"/>
+      <c r="A6" s="148"/>
+      <c r="B6" s="148"/>
+      <c r="C6" s="148"/>
+      <c r="D6" s="148"/>
+      <c r="E6" s="148"/>
+      <c r="F6" s="148"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="148"/>
+      <c r="K6" s="148"/>
+      <c r="L6" s="148"/>
+      <c r="M6" s="148"/>
+      <c r="N6" s="148"/>
+      <c r="O6" s="148"/>
+      <c r="P6" s="148"/>
+      <c r="Q6" s="148"/>
+      <c r="R6" s="148"/>
+      <c r="S6" s="148"/>
+      <c r="T6" s="148"/>
+      <c r="U6" s="148"/>
+      <c r="V6" s="148"/>
+      <c r="W6" s="148"/>
+      <c r="X6" s="148"/>
+      <c r="Y6" s="148"/>
+      <c r="Z6" s="148"/>
+      <c r="AA6" s="148"/>
+      <c r="AB6" s="148"/>
+      <c r="AC6" s="148"/>
+      <c r="AD6" s="148"/>
+      <c r="AE6" s="148"/>
+      <c r="AF6" s="149"/>
+      <c r="AG6" s="149"/>
+      <c r="AH6" s="149"/>
+      <c r="AI6" s="149"/>
+      <c r="AJ6" s="149"/>
+      <c r="AK6" s="149"/>
+      <c r="AL6" s="149"/>
       <c r="AM6" s="24"/>
     </row>
     <row r="7" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -5150,65 +7113,65 @@
       <c r="AM7" s="7"/>
     </row>
     <row r="8" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="125" t="s">
+      <c r="A8" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="125" t="s">
+      <c r="B8" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="128" t="s">
+      <c r="C8" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="128"/>
-      <c r="E8" s="128"/>
+      <c r="D8" s="129"/>
+      <c r="E8" s="129"/>
       <c r="F8" s="51"/>
-      <c r="G8" s="133" t="s">
+      <c r="G8" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="134"/>
-      <c r="I8" s="134"/>
-      <c r="J8" s="135"/>
-      <c r="K8" s="123" t="s">
+      <c r="H8" s="146"/>
+      <c r="I8" s="146"/>
+      <c r="J8" s="147"/>
+      <c r="K8" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="124"/>
-      <c r="M8" s="124"/>
-      <c r="N8" s="124"/>
-      <c r="O8" s="124"/>
-      <c r="P8" s="124"/>
-      <c r="Q8" s="124"/>
-      <c r="R8" s="124"/>
-      <c r="S8" s="129"/>
-      <c r="T8" s="123" t="s">
+      <c r="L8" s="125"/>
+      <c r="M8" s="125"/>
+      <c r="N8" s="125"/>
+      <c r="O8" s="125"/>
+      <c r="P8" s="125"/>
+      <c r="Q8" s="125"/>
+      <c r="R8" s="125"/>
+      <c r="S8" s="130"/>
+      <c r="T8" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="U8" s="124"/>
-      <c r="V8" s="124"/>
-      <c r="W8" s="124"/>
-      <c r="X8" s="124"/>
-      <c r="Y8" s="124"/>
-      <c r="Z8" s="124"/>
-      <c r="AA8" s="124"/>
-      <c r="AB8" s="129"/>
-      <c r="AC8" s="123" t="s">
+      <c r="U8" s="125"/>
+      <c r="V8" s="125"/>
+      <c r="W8" s="125"/>
+      <c r="X8" s="125"/>
+      <c r="Y8" s="125"/>
+      <c r="Z8" s="125"/>
+      <c r="AA8" s="125"/>
+      <c r="AB8" s="130"/>
+      <c r="AC8" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="AD8" s="124"/>
-      <c r="AE8" s="124"/>
-      <c r="AF8" s="124"/>
-      <c r="AG8" s="124"/>
-      <c r="AH8" s="124"/>
-      <c r="AI8" s="124"/>
-      <c r="AJ8" s="124"/>
-      <c r="AK8" s="129"/>
-      <c r="AL8" s="114" t="s">
+      <c r="AD8" s="125"/>
+      <c r="AE8" s="125"/>
+      <c r="AF8" s="125"/>
+      <c r="AG8" s="125"/>
+      <c r="AH8" s="125"/>
+      <c r="AI8" s="125"/>
+      <c r="AJ8" s="125"/>
+      <c r="AK8" s="130"/>
+      <c r="AL8" s="143" t="s">
         <v>8</v>
       </c>
       <c r="AM8" s="34"/>
     </row>
     <row r="9" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="126"/>
-      <c r="B9" s="126"/>
+      <c r="A9" s="127"/>
+      <c r="B9" s="127"/>
       <c r="C9" s="42" t="s">
         <v>27</v>
       </c>
@@ -5312,7 +7275,7 @@
       <c r="AK9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="AL9" s="115"/>
+      <c r="AL9" s="144"/>
       <c r="AM9" s="34"/>
       <c r="AN9" s="34"/>
     </row>
@@ -6101,10 +8064,10 @@
       <c r="AQ16" s="10"/>
     </row>
     <row r="17" spans="1:41" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="112" t="s">
+      <c r="A17" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="112"/>
+      <c r="B17" s="141"/>
       <c r="C17" s="18">
         <f>SUM(C10:C16)</f>
         <v>227321</v>
@@ -6283,18 +8246,18 @@
     </row>
     <row r="19" spans="1:41" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="113" t="s">
+      <c r="B19" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="113"/>
-      <c r="D19" s="113"/>
-      <c r="E19" s="113"/>
-      <c r="F19" s="113"/>
-      <c r="G19" s="113"/>
-      <c r="H19" s="113"/>
-      <c r="I19" s="113"/>
-      <c r="J19" s="113"/>
-      <c r="K19" s="113"/>
+      <c r="C19" s="142"/>
+      <c r="D19" s="142"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="142"/>
+      <c r="G19" s="142"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="142"/>
+      <c r="J19" s="142"/>
+      <c r="K19" s="142"/>
       <c r="L19" s="49"/>
       <c r="M19" s="49"/>
       <c r="N19" s="49"/>
@@ -6325,20 +8288,20 @@
       <c r="AM19" s="19"/>
     </row>
     <row r="20" spans="1:41" ht="18" x14ac:dyDescent="0.35">
-      <c r="B20" s="110"/>
-      <c r="C20" s="110"/>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="110"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="139"/>
+      <c r="N20" s="139"/>
+      <c r="O20" s="139"/>
       <c r="P20" s="23"/>
       <c r="Q20" s="23"/>
       <c r="R20" s="23"/>
@@ -6367,8 +8330,8 @@
         <v>4</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
@@ -6491,12 +8454,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A5:AL5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="O1:AL1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="O2:AL2"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="B19:K19"/>
     <mergeCell ref="B20:O20"/>
@@ -6510,6 +8467,12 @@
     <mergeCell ref="T8:AB8"/>
     <mergeCell ref="AC8:AK8"/>
     <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="A5:AL5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="O1:AL1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="O2:AL2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6542,67 +8505,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="63"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="117"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
       <c r="Y1" s="63"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="63"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="120"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="120"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="117"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
       <c r="Y2" s="63"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="63"/>
       <c r="E3" s="63"/>
       <c r="F3" s="17"/>
@@ -6654,32 +8617,32 @@
       <c r="Y4" s="63"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="134" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
-      <c r="L5" s="116"/>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="116"/>
-      <c r="R5" s="116"/>
-      <c r="S5" s="117"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="117"/>
-      <c r="W5" s="117"/>
-      <c r="X5" s="117"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
       <c r="Y5" s="63"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6711,49 +8674,49 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="125" t="s">
+      <c r="A7" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="125" t="s">
+      <c r="B7" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="128" t="s">
+      <c r="C7" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="123" t="s">
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="123" t="s">
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="124"/>
-      <c r="N7" s="124"/>
-      <c r="O7" s="124"/>
-      <c r="P7" s="124"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="123" t="s">
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="S7" s="124"/>
-      <c r="T7" s="124"/>
-      <c r="U7" s="124"/>
-      <c r="V7" s="124"/>
-      <c r="W7" s="129"/>
-      <c r="X7" s="114" t="s">
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
         <v>8</v>
       </c>
       <c r="Y7" s="34"/>
     </row>
     <row r="8" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="126"/>
-      <c r="B8" s="126"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="68" t="s">
         <v>27</v>
       </c>
@@ -6817,7 +8780,7 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="115"/>
+      <c r="X8" s="144"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
@@ -7467,10 +9430,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="112" t="s">
+      <c r="A16" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="112"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -7589,13 +9552,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="113" t="s">
+      <c r="B18" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="113"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="113"/>
-      <c r="F18" s="113"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="64"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -7617,12 +9580,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="110"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="110"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
       <c r="H19" s="65"/>
       <c r="I19" s="65"/>
       <c r="J19" s="65"/>
@@ -7645,8 +9608,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
       <c r="F20" s="66"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -7727,14 +9690,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
     <mergeCell ref="X7:X8"/>
@@ -7744,6 +9699,14 @@
     <mergeCell ref="H2:X2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7776,67 +9739,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="75"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="117"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
       <c r="Y1" s="75"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="75"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="120"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="120"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="117"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
       <c r="Y2" s="75"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="75"/>
       <c r="E3" s="75"/>
       <c r="F3" s="17"/>
@@ -7888,32 +9851,32 @@
       <c r="Y4" s="75"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="134" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
-      <c r="L5" s="116"/>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="116"/>
-      <c r="R5" s="116"/>
-      <c r="S5" s="117"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="117"/>
-      <c r="W5" s="117"/>
-      <c r="X5" s="117"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
       <c r="Y5" s="75"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7945,49 +9908,49 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="125" t="s">
+      <c r="A7" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="125" t="s">
+      <c r="B7" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="128" t="s">
+      <c r="C7" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="123" t="s">
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="123" t="s">
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="124"/>
-      <c r="N7" s="124"/>
-      <c r="O7" s="124"/>
-      <c r="P7" s="124"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="123" t="s">
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="S7" s="124"/>
-      <c r="T7" s="124"/>
-      <c r="U7" s="124"/>
-      <c r="V7" s="124"/>
-      <c r="W7" s="129"/>
-      <c r="X7" s="114" t="s">
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
         <v>8</v>
       </c>
       <c r="Y7" s="34"/>
     </row>
     <row r="8" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="126"/>
-      <c r="B8" s="126"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="73" t="s">
         <v>27</v>
       </c>
@@ -8051,7 +10014,7 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="115"/>
+      <c r="X8" s="144"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
@@ -8678,10 +10641,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="112" t="s">
+      <c r="A16" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="112"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -8800,13 +10763,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="113" t="s">
+      <c r="B18" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="113"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="113"/>
-      <c r="F18" s="113"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="78"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -8828,12 +10791,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="110"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="110"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
       <c r="H19" s="76"/>
       <c r="I19" s="76"/>
       <c r="J19" s="76"/>
@@ -8856,8 +10819,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
       <c r="F20" s="77"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -8938,6 +10901,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="X7:X8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
@@ -8949,12 +10918,6 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -8987,67 +10950,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="85"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="117"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
       <c r="Y1" s="85"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="85"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="120"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="120"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="117"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
       <c r="Y2" s="85"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="17"/>
@@ -9099,32 +11062,32 @@
       <c r="Y4" s="85"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="134" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
-      <c r="L5" s="116"/>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="116"/>
-      <c r="R5" s="116"/>
-      <c r="S5" s="117"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="117"/>
-      <c r="W5" s="117"/>
-      <c r="X5" s="117"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
       <c r="Y5" s="85"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9156,49 +11119,49 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="125" t="s">
+      <c r="A7" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="125" t="s">
+      <c r="B7" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="128" t="s">
+      <c r="C7" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="123" t="s">
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="123" t="s">
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="124"/>
-      <c r="N7" s="124"/>
-      <c r="O7" s="124"/>
-      <c r="P7" s="124"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="123" t="s">
-        <v>11</v>
-      </c>
-      <c r="S7" s="124"/>
-      <c r="T7" s="124"/>
-      <c r="U7" s="124"/>
-      <c r="V7" s="124"/>
-      <c r="W7" s="129"/>
-      <c r="X7" s="114" t="s">
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
         <v>8</v>
       </c>
       <c r="Y7" s="34"/>
     </row>
     <row r="8" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="126"/>
-      <c r="B8" s="126"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="86" t="s">
         <v>27</v>
       </c>
@@ -9262,7 +11225,7 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="115"/>
+      <c r="X8" s="144"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
@@ -9306,52 +11269,56 @@
         <v>96.92307692307692</v>
       </c>
       <c r="L9" s="31">
-        <v>1420.25</v>
-      </c>
-      <c r="M9" s="30">
-        <v>1393</v>
+        <v>1862.0796500000001</v>
+      </c>
+      <c r="M9" s="31">
+        <v>1606</v>
       </c>
       <c r="N9" s="53">
         <f>M9-'Thang 5'!M9</f>
-        <v>-23</v>
+        <v>190</v>
       </c>
       <c r="O9" s="53">
         <f>M9-'Thang 12'!Y10</f>
-        <v>-52</v>
+        <v>161</v>
       </c>
       <c r="P9" s="53">
         <f>L9-M9</f>
-        <v>27.25</v>
+        <v>256.07965000000013</v>
       </c>
       <c r="Q9" s="70">
         <f>M9/L9*100</f>
-        <v>98.081323710614328</v>
+        <v>86.247653262308077</v>
       </c>
       <c r="R9" s="31">
-        <v>1862.0796500000001</v>
-      </c>
-      <c r="S9" s="31">
-        <v>1606</v>
+        <v>1420.25</v>
+      </c>
+      <c r="S9" s="30">
+        <v>1393</v>
       </c>
       <c r="T9" s="53">
         <f>S9-'Thang 5'!S9</f>
-        <v>14</v>
+        <v>-199</v>
       </c>
       <c r="U9" s="53">
         <f>S9-'Thang 12'!AG10</f>
-        <v>-64</v>
+        <v>-277</v>
       </c>
       <c r="V9" s="53">
         <f t="shared" ref="V9:V15" si="3">R9-S9</f>
-        <v>256.07965000000013</v>
+        <v>27.25</v>
       </c>
       <c r="W9" s="61">
         <f t="shared" ref="W9:W16" si="4">S9/R9*100</f>
-        <v>86.247653262308077</v>
+        <v>98.081323710614328</v>
       </c>
       <c r="X9" s="28"/>
-      <c r="Y9" s="35"/>
-      <c r="Z9" s="10"/>
+      <c r="Y9" s="31">
+        <v>1862.0796500000001</v>
+      </c>
+      <c r="Z9" s="31">
+        <v>1606</v>
+      </c>
       <c r="AA9" s="10"/>
       <c r="AC9" s="10"/>
     </row>
@@ -9395,52 +11362,56 @@
         <v>62.453987730061343</v>
       </c>
       <c r="L10" s="31">
-        <v>661.1</v>
-      </c>
-      <c r="M10" s="30">
-        <v>390</v>
+        <v>1297.0753500000001</v>
+      </c>
+      <c r="M10" s="31">
+        <v>614</v>
       </c>
       <c r="N10" s="53">
         <f>M10-'Thang 5'!M10</f>
-        <v>-22</v>
+        <v>202</v>
       </c>
       <c r="O10" s="53">
         <f>M10-'Thang 12'!Y11</f>
-        <v>40</v>
+        <v>264</v>
       </c>
       <c r="P10" s="53">
         <f t="shared" ref="P10:P15" si="5">L10-M10</f>
-        <v>271.10000000000002</v>
+        <v>683.07535000000007</v>
       </c>
       <c r="Q10" s="70">
         <f t="shared" ref="Q10:Q16" si="6">M10/L10*100</f>
-        <v>58.992588110724554</v>
+        <v>47.337265333120385</v>
       </c>
       <c r="R10" s="31">
-        <v>1297.0753500000001</v>
-      </c>
-      <c r="S10" s="31">
-        <v>614</v>
+        <v>661.1</v>
+      </c>
+      <c r="S10" s="30">
+        <v>390</v>
       </c>
       <c r="T10" s="53">
         <f>S10-'Thang 5'!S10</f>
-        <v>5</v>
+        <v>-219</v>
       </c>
       <c r="U10" s="53">
         <f>S10-'Thang 12'!AG11</f>
-        <v>24</v>
+        <v>-200</v>
       </c>
       <c r="V10" s="53">
         <f t="shared" si="3"/>
-        <v>683.07535000000007</v>
+        <v>271.10000000000002</v>
       </c>
       <c r="W10" s="61">
         <f t="shared" si="4"/>
-        <v>47.337265333120385</v>
+        <v>58.992588110724554</v>
       </c>
       <c r="X10" s="28"/>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="10"/>
+      <c r="Y10" s="31">
+        <v>1297.0753500000001</v>
+      </c>
+      <c r="Z10" s="31">
+        <v>614</v>
+      </c>
       <c r="AA10" s="10"/>
       <c r="AC10" s="10"/>
     </row>
@@ -9484,52 +11455,56 @@
         <v>84.010424651234104</v>
       </c>
       <c r="L11" s="31">
-        <v>565.4</v>
-      </c>
-      <c r="M11" s="30">
-        <v>434</v>
+        <v>1116.8260500000001</v>
+      </c>
+      <c r="M11" s="31">
+        <v>777</v>
       </c>
       <c r="N11" s="53">
         <f>M11-'Thang 5'!M11</f>
-        <v>-14</v>
+        <v>329</v>
       </c>
       <c r="O11" s="53">
         <f>M11-'Thang 12'!Y12</f>
-        <v>37</v>
+        <v>380</v>
       </c>
       <c r="P11" s="53">
         <f t="shared" si="5"/>
-        <v>131.39999999999998</v>
+        <v>339.82605000000012</v>
       </c>
       <c r="Q11" s="70">
         <f t="shared" si="6"/>
-        <v>76.759816059426953</v>
+        <v>69.572159424469007</v>
       </c>
       <c r="R11" s="31">
-        <v>1116.8260500000001</v>
-      </c>
-      <c r="S11" s="31">
-        <v>777</v>
+        <v>565.4</v>
+      </c>
+      <c r="S11" s="30">
+        <v>434</v>
       </c>
       <c r="T11" s="53">
         <f>S11-'Thang 5'!S11</f>
-        <v>9</v>
+        <v>-334</v>
       </c>
       <c r="U11" s="53">
         <f>S11-'Thang 12'!AG12</f>
-        <v>-39</v>
+        <v>-382</v>
       </c>
       <c r="V11" s="53">
         <f t="shared" si="3"/>
-        <v>339.82605000000012</v>
+        <v>131.39999999999998</v>
       </c>
       <c r="W11" s="61">
         <f t="shared" si="4"/>
-        <v>69.572159424469007</v>
+        <v>76.759816059426953</v>
       </c>
       <c r="X11" s="28"/>
-      <c r="Y11" s="35"/>
-      <c r="Z11" s="10"/>
+      <c r="Y11" s="31">
+        <v>1116.8260500000001</v>
+      </c>
+      <c r="Z11" s="31">
+        <v>777</v>
+      </c>
       <c r="AA11" s="10"/>
       <c r="AC11" s="10"/>
     </row>
@@ -9573,52 +11548,56 @@
         <v>99.913119026933103</v>
       </c>
       <c r="L12" s="31">
-        <v>978</v>
-      </c>
-      <c r="M12" s="30">
-        <v>993</v>
+        <v>2043.0157000000004</v>
+      </c>
+      <c r="M12" s="31">
+        <v>1569</v>
       </c>
       <c r="N12" s="53">
         <f>M12-'Thang 5'!M12</f>
-        <v>-5</v>
+        <v>571</v>
       </c>
       <c r="O12" s="53">
         <f>M12-'Thang 12'!Y13</f>
-        <v>83</v>
+        <v>659</v>
       </c>
       <c r="P12" s="53">
         <f t="shared" si="5"/>
-        <v>-15</v>
+        <v>474.01570000000038</v>
       </c>
       <c r="Q12" s="70">
         <f t="shared" si="6"/>
-        <v>101.53374233128834</v>
+        <v>76.798235079642296</v>
       </c>
       <c r="R12" s="31">
-        <v>2043.0157000000004</v>
-      </c>
-      <c r="S12" s="31">
-        <v>1569</v>
+        <v>978</v>
+      </c>
+      <c r="S12" s="30">
+        <v>993</v>
       </c>
       <c r="T12" s="53">
         <f>S12-'Thang 5'!S12</f>
-        <v>19</v>
+        <v>-557</v>
       </c>
       <c r="U12" s="53">
         <f>S12-'Thang 12'!AG13</f>
-        <v>118</v>
+        <v>-458</v>
       </c>
       <c r="V12" s="53">
         <f t="shared" si="3"/>
-        <v>474.01570000000038</v>
+        <v>-15</v>
       </c>
       <c r="W12" s="61">
         <f t="shared" si="4"/>
-        <v>76.798235079642296</v>
+        <v>101.53374233128834</v>
       </c>
       <c r="X12" s="28"/>
-      <c r="Y12" s="35"/>
-      <c r="Z12" s="10"/>
+      <c r="Y12" s="31">
+        <v>2043.0157000000004</v>
+      </c>
+      <c r="Z12" s="31">
+        <v>1569</v>
+      </c>
       <c r="AA12" s="10"/>
       <c r="AC12" s="10"/>
     </row>
@@ -9662,52 +11641,56 @@
         <v>83.609820836098208</v>
       </c>
       <c r="L13" s="31">
-        <v>1005.4</v>
+        <v>1203.95955</v>
       </c>
       <c r="M13" s="54">
-        <v>864</v>
+        <v>963</v>
       </c>
       <c r="N13" s="53">
         <f>M13-'Thang 5'!M13</f>
-        <v>-1</v>
+        <v>98</v>
       </c>
       <c r="O13" s="53">
         <f>M13-'Thang 12'!Y14</f>
-        <v>-50</v>
+        <v>49</v>
       </c>
       <c r="P13" s="53">
         <f t="shared" si="5"/>
-        <v>141.39999999999998</v>
+        <v>240.95955000000004</v>
       </c>
       <c r="Q13" s="70">
         <f t="shared" si="6"/>
-        <v>85.935945892182218</v>
+        <v>79.986075944162735</v>
       </c>
       <c r="R13" s="31">
-        <v>1203.95955</v>
+        <v>1005.4</v>
       </c>
       <c r="S13" s="54">
-        <v>963</v>
+        <v>864</v>
       </c>
       <c r="T13" s="53">
         <f>S13-'Thang 5'!S13</f>
-        <v>11</v>
+        <v>-88</v>
       </c>
       <c r="U13" s="53">
         <f>S13-'Thang 12'!AG14</f>
-        <v>-44</v>
+        <v>-143</v>
       </c>
       <c r="V13" s="53">
         <f t="shared" si="3"/>
-        <v>240.95955000000004</v>
+        <v>141.39999999999998</v>
       </c>
       <c r="W13" s="61">
         <f t="shared" si="4"/>
-        <v>79.986075944162735</v>
+        <v>85.935945892182218</v>
       </c>
       <c r="X13" s="28"/>
-      <c r="Y13" s="35"/>
-      <c r="Z13" s="10"/>
+      <c r="Y13" s="31">
+        <v>1203.95955</v>
+      </c>
+      <c r="Z13" s="54">
+        <v>963</v>
+      </c>
       <c r="AA13" s="10"/>
       <c r="AC13" s="10"/>
     </row>
@@ -9751,52 +11734,56 @@
         <v>91.20135363790186</v>
       </c>
       <c r="L14" s="31">
-        <v>446.88</v>
+        <v>1256.5864500000002</v>
       </c>
       <c r="M14" s="54">
-        <v>417</v>
+        <v>945</v>
       </c>
       <c r="N14" s="53">
         <f>M14-'Thang 5'!M14</f>
-        <v>10</v>
+        <v>538</v>
       </c>
       <c r="O14" s="53">
         <f>M14-'Thang 12'!Y15</f>
-        <v>45</v>
+        <v>573</v>
       </c>
       <c r="P14" s="53">
         <f t="shared" si="5"/>
-        <v>29.879999999999995</v>
+        <v>311.58645000000024</v>
       </c>
       <c r="Q14" s="70">
         <f t="shared" si="6"/>
-        <v>93.313641245972079</v>
+        <v>75.203739464164983</v>
       </c>
       <c r="R14" s="31">
-        <v>1256.5864500000002</v>
+        <v>446.88</v>
       </c>
       <c r="S14" s="54">
-        <v>945</v>
+        <v>417</v>
       </c>
       <c r="T14" s="53">
         <f>S14-'Thang 5'!S14</f>
-        <v>11</v>
+        <v>-517</v>
       </c>
       <c r="U14" s="53">
         <f>S14-'Thang 12'!AG15</f>
-        <v>-35</v>
+        <v>-563</v>
       </c>
       <c r="V14" s="53">
         <f t="shared" si="3"/>
-        <v>311.58645000000024</v>
+        <v>29.879999999999995</v>
       </c>
       <c r="W14" s="61">
         <f t="shared" si="4"/>
-        <v>75.203739464164983</v>
+        <v>93.313641245972079</v>
       </c>
       <c r="X14" s="28"/>
-      <c r="Y14" s="35"/>
-      <c r="Z14" s="10"/>
+      <c r="Y14" s="31">
+        <v>1256.5864500000002</v>
+      </c>
+      <c r="Z14" s="54">
+        <v>945</v>
+      </c>
       <c r="AA14" s="10"/>
       <c r="AC14" s="10"/>
     </row>
@@ -9840,60 +11827,64 @@
         <v>101.10905730129389</v>
       </c>
       <c r="L15" s="31">
-        <v>439.04</v>
+        <v>1071.8721</v>
       </c>
       <c r="M15" s="54">
-        <v>441</v>
+        <v>1100</v>
       </c>
       <c r="N15" s="53">
         <f>M15-'Thang 5'!M15</f>
-        <v>7</v>
+        <v>666</v>
       </c>
       <c r="O15" s="53">
         <f>M15-'Thang 12'!Y16</f>
-        <v>58</v>
+        <v>717</v>
       </c>
       <c r="P15" s="53">
         <f t="shared" si="5"/>
-        <v>-1.9599999999999795</v>
+        <v>-28.127899999999954</v>
       </c>
       <c r="Q15" s="70">
         <f t="shared" si="6"/>
-        <v>100.44642857142856</v>
+        <v>102.62418435930928</v>
       </c>
       <c r="R15" s="31">
-        <v>1071.8721</v>
+        <v>439.04</v>
       </c>
       <c r="S15" s="54">
-        <v>1100</v>
+        <v>441</v>
       </c>
       <c r="T15" s="53">
         <f>S15-'Thang 5'!S15</f>
-        <v>61</v>
+        <v>-598</v>
       </c>
       <c r="U15" s="53">
         <f>S15-'Thang 12'!AG16</f>
-        <v>60</v>
+        <v>-599</v>
       </c>
       <c r="V15" s="53">
         <f t="shared" si="3"/>
-        <v>-28.127899999999954</v>
+        <v>-1.9599999999999795</v>
       </c>
       <c r="W15" s="61">
         <f t="shared" si="4"/>
-        <v>102.62418435930928</v>
+        <v>100.44642857142856</v>
       </c>
       <c r="X15" s="28"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="10"/>
+      <c r="Y15" s="31">
+        <v>1071.8721</v>
+      </c>
+      <c r="Z15" s="54">
+        <v>1100</v>
+      </c>
       <c r="AA15" s="10"/>
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="112" t="s">
+      <c r="A16" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="112"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -9932,51 +11923,51 @@
       </c>
       <c r="L16" s="18">
         <f>SUM(L9:L15)</f>
-        <v>5516.07</v>
+        <v>9851.414850000001</v>
       </c>
       <c r="M16" s="18">
         <f>SUM(M9:M15)</f>
-        <v>4932</v>
+        <v>7574</v>
       </c>
       <c r="N16" s="56">
         <f>SUM(N9:N15)</f>
-        <v>-48</v>
+        <v>2594</v>
       </c>
       <c r="O16" s="56">
         <f>M16-'Thang 12'!Y17</f>
-        <v>161</v>
+        <v>2803</v>
       </c>
       <c r="P16" s="18">
         <f t="shared" ref="P16" si="7">SUM(P9:P15)</f>
-        <v>584.06999999999994</v>
+        <v>2277.414850000001</v>
       </c>
       <c r="Q16" s="69">
         <f t="shared" si="6"/>
-        <v>89.41148317552171</v>
+        <v>76.882357664594736</v>
       </c>
       <c r="R16" s="55">
         <f>SUM(R9:R15)</f>
-        <v>9851.414850000001</v>
+        <v>5516.07</v>
       </c>
       <c r="S16" s="18">
         <f>SUM(S9:S15)</f>
-        <v>7574</v>
+        <v>4932</v>
       </c>
       <c r="T16" s="56">
         <f>SUM(T9:T15)</f>
-        <v>130</v>
+        <v>-2512</v>
       </c>
       <c r="U16" s="56">
         <f>S16-'Thang 12'!AG17</f>
-        <v>20</v>
+        <v>-2622</v>
       </c>
       <c r="V16" s="56">
         <f>SUM(V9:V15)</f>
-        <v>2277.414850000001</v>
+        <v>584.06999999999994</v>
       </c>
       <c r="W16" s="57">
         <f t="shared" si="4"/>
-        <v>76.882357664594736</v>
+        <v>89.41148317552171</v>
       </c>
       <c r="X16" s="37"/>
       <c r="Y16" s="36"/>
@@ -10012,13 +12003,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="113" t="s">
+      <c r="B18" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="113"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="113"/>
-      <c r="F18" s="113"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -10027,7 +12018,7 @@
       <c r="L18" s="19"/>
       <c r="M18" s="33">
         <f>4932-M16</f>
-        <v>0</v>
+        <v>-2642</v>
       </c>
       <c r="N18" s="33"/>
       <c r="O18" s="33"/>
@@ -10043,12 +12034,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="110"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="110"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
       <c r="H19" s="81"/>
       <c r="I19" s="81"/>
       <c r="J19" s="81"/>
@@ -10071,8 +12062,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
       <c r="F20" s="82"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -10153,12 +12144,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="X7:X8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
@@ -10170,6 +12155,12 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -10205,67 +12196,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="92"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="117"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
       <c r="Y1" s="92"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="92"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="120"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="120"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="117"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
       <c r="Y2" s="92"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="92"/>
       <c r="E3" s="92"/>
       <c r="F3" s="17"/>
@@ -10317,32 +12308,32 @@
       <c r="Y4" s="92"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="134" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
-      <c r="L5" s="116"/>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="116"/>
-      <c r="R5" s="116"/>
-      <c r="S5" s="117"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="117"/>
-      <c r="W5" s="117"/>
-      <c r="X5" s="117"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
       <c r="Y5" s="92"/>
     </row>
     <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10374,75 +12365,75 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="125" t="s">
+      <c r="A7" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="125" t="s">
+      <c r="B7" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="128" t="s">
+      <c r="C7" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="123" t="s">
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="123" t="s">
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="124"/>
-      <c r="N7" s="124"/>
-      <c r="O7" s="124"/>
-      <c r="P7" s="124"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="123" t="s">
-        <v>11</v>
-      </c>
-      <c r="S7" s="124"/>
-      <c r="T7" s="124"/>
-      <c r="U7" s="124"/>
-      <c r="V7" s="124"/>
-      <c r="W7" s="129"/>
-      <c r="X7" s="114" t="s">
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="127" t="s">
+      <c r="Y7" s="128" t="s">
         <v>77</v>
       </c>
-      <c r="Z7" s="140" t="s">
+      <c r="Z7" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="AA7" s="140"/>
-      <c r="AB7" s="140"/>
-      <c r="AC7" s="140"/>
-      <c r="AD7" s="140"/>
-      <c r="AE7" s="140"/>
-      <c r="AF7" s="140"/>
-      <c r="AG7" s="138" t="s">
+      <c r="AA7" s="152"/>
+      <c r="AB7" s="152"/>
+      <c r="AC7" s="152"/>
+      <c r="AD7" s="152"/>
+      <c r="AE7" s="152"/>
+      <c r="AF7" s="152"/>
+      <c r="AG7" s="150" t="s">
         <v>76</v>
       </c>
-      <c r="AH7" s="140" t="s">
+      <c r="AH7" s="152" t="s">
         <v>62</v>
       </c>
-      <c r="AI7" s="140"/>
-      <c r="AJ7" s="140"/>
-      <c r="AK7" s="140"/>
-      <c r="AL7" s="140"/>
-      <c r="AM7" s="140"/>
-      <c r="AN7" s="140"/>
-      <c r="AO7" s="140"/>
-      <c r="AP7" s="140"/>
-      <c r="AQ7" s="138"/>
+      <c r="AI7" s="152"/>
+      <c r="AJ7" s="152"/>
+      <c r="AK7" s="152"/>
+      <c r="AL7" s="152"/>
+      <c r="AM7" s="152"/>
+      <c r="AN7" s="152"/>
+      <c r="AO7" s="152"/>
+      <c r="AP7" s="152"/>
+      <c r="AQ7" s="150"/>
     </row>
     <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="126"/>
-      <c r="B8" s="126"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="93" t="s">
         <v>27</v>
       </c>
@@ -10506,8 +12497,8 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="115"/>
-      <c r="Y8" s="127"/>
+      <c r="X8" s="144"/>
+      <c r="Y8" s="128"/>
       <c r="Z8" s="94" t="s">
         <v>63</v>
       </c>
@@ -10529,7 +12520,7 @@
       <c r="AF8" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="AG8" s="139"/>
+      <c r="AG8" s="151"/>
       <c r="AH8" s="95" t="s">
         <v>69</v>
       </c>
@@ -10557,7 +12548,7 @@
       <c r="AP8" s="94" t="s">
         <v>75</v>
       </c>
-      <c r="AQ8" s="139"/>
+      <c r="AQ8" s="151"/>
     </row>
     <row r="9" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26">
@@ -10599,48 +12590,48 @@
         <v>94.030769230769224</v>
       </c>
       <c r="L9" s="31">
-        <v>1420</v>
-      </c>
-      <c r="M9" s="30">
-        <v>1392</v>
+        <v>1862</v>
+      </c>
+      <c r="M9" s="31">
+        <v>1624</v>
       </c>
       <c r="N9" s="53">
         <f>M9-'Thang 6'!M9</f>
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="O9" s="53">
         <f>M9-'Thang 12'!Y10</f>
-        <v>-53</v>
+        <v>179</v>
       </c>
       <c r="P9" s="53">
         <f>L9-M9</f>
-        <v>28</v>
+        <v>238</v>
       </c>
       <c r="Q9" s="70">
         <f>M9/L9*100</f>
-        <v>98.028169014084511</v>
+        <v>87.218045112781951</v>
       </c>
       <c r="R9" s="31">
-        <v>1862</v>
-      </c>
-      <c r="S9" s="31">
-        <v>1624</v>
+        <v>1420</v>
+      </c>
+      <c r="S9" s="30">
+        <v>1392</v>
       </c>
       <c r="T9" s="53">
         <f>S9-'Thang 6'!S9</f>
-        <v>18</v>
+        <v>-1</v>
       </c>
       <c r="U9" s="53">
         <f>S9-'Thang 12'!AG10</f>
-        <v>-46</v>
+        <v>-278</v>
       </c>
       <c r="V9" s="53">
         <f t="shared" ref="V9:V15" si="3">R9-S9</f>
-        <v>238</v>
+        <v>28</v>
       </c>
       <c r="W9" s="61">
         <f t="shared" ref="W9:W16" si="4">S9/R9*100</f>
-        <v>87.218045112781951</v>
+        <v>98.028169014084511</v>
       </c>
       <c r="X9" s="28"/>
       <c r="Y9" s="106" t="s">
@@ -10748,48 +12739,48 @@
         <v>60.858895705521476</v>
       </c>
       <c r="L10" s="31">
-        <v>661</v>
-      </c>
-      <c r="M10" s="30">
-        <v>390</v>
+        <v>1297</v>
+      </c>
+      <c r="M10" s="31">
+        <v>720</v>
       </c>
       <c r="N10" s="53">
         <f>M10-'Thang 6'!M10</f>
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="O10" s="53">
         <f>M10-'Thang 12'!Y11</f>
-        <v>40</v>
+        <v>370</v>
       </c>
       <c r="P10" s="53">
         <f t="shared" ref="P10:P15" si="8">L10-M10</f>
-        <v>271</v>
+        <v>577</v>
       </c>
       <c r="Q10" s="70">
         <f t="shared" ref="Q10:Q16" si="9">M10/L10*100</f>
-        <v>59.001512859304086</v>
+        <v>55.512721665381648</v>
       </c>
       <c r="R10" s="31">
-        <v>1297</v>
-      </c>
-      <c r="S10" s="31">
-        <v>720</v>
+        <v>661</v>
+      </c>
+      <c r="S10" s="30">
+        <v>390</v>
       </c>
       <c r="T10" s="53">
         <f>S10-'Thang 6'!S10</f>
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="U10" s="53">
         <f>S10-'Thang 12'!AG11</f>
-        <v>130</v>
+        <v>-200</v>
       </c>
       <c r="V10" s="53">
         <f t="shared" si="3"/>
-        <v>577</v>
+        <v>271</v>
       </c>
       <c r="W10" s="61">
         <f t="shared" si="4"/>
-        <v>55.512721665381648</v>
+        <v>59.001512859304086</v>
       </c>
       <c r="X10" s="28"/>
       <c r="Y10" s="108" t="s">
@@ -10874,48 +12865,48 @@
         <v>79.601226993865026</v>
       </c>
       <c r="L11" s="31">
-        <v>565</v>
-      </c>
-      <c r="M11" s="30">
-        <v>434</v>
+        <v>1117</v>
+      </c>
+      <c r="M11" s="31">
+        <v>770</v>
       </c>
       <c r="N11" s="53">
         <f>M11-'Thang 6'!M11</f>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="O11" s="53">
         <f>M11-'Thang 12'!Y12</f>
-        <v>37</v>
+        <v>373</v>
       </c>
       <c r="P11" s="53">
         <f t="shared" si="8"/>
-        <v>131</v>
+        <v>347</v>
       </c>
       <c r="Q11" s="70">
         <f t="shared" si="9"/>
-        <v>76.814159292035399</v>
+        <v>68.934646374216655</v>
       </c>
       <c r="R11" s="31">
-        <v>1117</v>
-      </c>
-      <c r="S11" s="31">
-        <v>770</v>
+        <v>565</v>
+      </c>
+      <c r="S11" s="30">
+        <v>434</v>
       </c>
       <c r="T11" s="53">
         <f>S11-'Thang 6'!S11</f>
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="U11" s="53">
         <f>S11-'Thang 12'!AG12</f>
-        <v>-46</v>
+        <v>-382</v>
       </c>
       <c r="V11" s="53">
         <f t="shared" si="3"/>
-        <v>347</v>
+        <v>131</v>
       </c>
       <c r="W11" s="61">
         <f t="shared" si="4"/>
-        <v>68.934646374216655</v>
+        <v>76.814159292035399</v>
       </c>
       <c r="X11" s="28"/>
       <c r="Y11" s="108" t="s">
@@ -11000,48 +12991,48 @@
         <v>95.221546481320601</v>
       </c>
       <c r="L12" s="31">
-        <v>978</v>
-      </c>
-      <c r="M12" s="30">
-        <v>991</v>
+        <v>2043</v>
+      </c>
+      <c r="M12" s="31">
+        <v>1626</v>
       </c>
       <c r="N12" s="53">
         <f>M12-'Thang 6'!M12</f>
-        <v>-2</v>
+        <v>57</v>
       </c>
       <c r="O12" s="53">
         <f>M12-'Thang 12'!Y13</f>
-        <v>81</v>
+        <v>716</v>
       </c>
       <c r="P12" s="53">
         <f t="shared" si="8"/>
-        <v>-13</v>
+        <v>417</v>
       </c>
       <c r="Q12" s="70">
         <f t="shared" si="9"/>
-        <v>101.32924335378324</v>
+        <v>79.588839941262847</v>
       </c>
       <c r="R12" s="31">
-        <v>2043</v>
-      </c>
-      <c r="S12" s="31">
-        <v>1626</v>
+        <v>978</v>
+      </c>
+      <c r="S12" s="30">
+        <v>991</v>
       </c>
       <c r="T12" s="53">
         <f>S12-'Thang 6'!S12</f>
-        <v>57</v>
+        <v>-2</v>
       </c>
       <c r="U12" s="53">
         <f>S12-'Thang 12'!AG13</f>
-        <v>175</v>
+        <v>-460</v>
       </c>
       <c r="V12" s="53">
         <f t="shared" si="3"/>
-        <v>417</v>
+        <v>-13</v>
       </c>
       <c r="W12" s="61">
         <f t="shared" si="4"/>
-        <v>79.588839941262847</v>
+        <v>101.32924335378324</v>
       </c>
       <c r="X12" s="28"/>
       <c r="Y12" s="108" t="s">
@@ -11126,48 +13117,48 @@
         <v>81.177446102819246</v>
       </c>
       <c r="L13" s="31">
-        <v>1005</v>
+        <v>1204</v>
       </c>
       <c r="M13" s="54">
-        <v>864</v>
+        <v>972</v>
       </c>
       <c r="N13" s="53">
         <f>M13-'Thang 6'!M13</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O13" s="53">
         <f>M13-'Thang 12'!Y14</f>
-        <v>-50</v>
+        <v>58</v>
       </c>
       <c r="P13" s="53">
         <f t="shared" si="8"/>
-        <v>141</v>
+        <v>232</v>
       </c>
       <c r="Q13" s="70">
         <f t="shared" si="9"/>
-        <v>85.970149253731336</v>
+        <v>80.730897009966768</v>
       </c>
       <c r="R13" s="31">
-        <v>1204</v>
+        <v>1005</v>
       </c>
       <c r="S13" s="54">
-        <v>972</v>
+        <v>864</v>
       </c>
       <c r="T13" s="53">
         <f>S13-'Thang 6'!S13</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U13" s="53">
         <f>S13-'Thang 12'!AG14</f>
-        <v>-35</v>
+        <v>-143</v>
       </c>
       <c r="V13" s="53">
         <f t="shared" si="3"/>
-        <v>232</v>
+        <v>141</v>
       </c>
       <c r="W13" s="61">
         <f t="shared" si="4"/>
-        <v>80.730897009966768</v>
+        <v>85.970149253731336</v>
       </c>
       <c r="X13" s="28"/>
       <c r="Y13" s="108" t="s">
@@ -11252,48 +13243,48 @@
         <v>88.663282571912021</v>
       </c>
       <c r="L14" s="31">
-        <v>447</v>
+        <v>1257</v>
       </c>
       <c r="M14" s="54">
-        <v>417</v>
+        <v>1010</v>
       </c>
       <c r="N14" s="53">
         <f>M14-'Thang 6'!M14</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="O14" s="53">
         <f>M14-'Thang 12'!Y15</f>
-        <v>45</v>
+        <v>638</v>
       </c>
       <c r="P14" s="53">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>247</v>
       </c>
       <c r="Q14" s="70">
         <f t="shared" si="9"/>
-        <v>93.288590604026851</v>
+        <v>80.350039777247417</v>
       </c>
       <c r="R14" s="31">
-        <v>1257</v>
+        <v>447</v>
       </c>
       <c r="S14" s="54">
-        <v>1010</v>
+        <v>417</v>
       </c>
       <c r="T14" s="53">
         <f>S14-'Thang 6'!S14</f>
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="U14" s="53">
         <f>S14-'Thang 12'!AG15</f>
-        <v>30</v>
+        <v>-563</v>
       </c>
       <c r="V14" s="53">
         <f t="shared" si="3"/>
-        <v>247</v>
+        <v>30</v>
       </c>
       <c r="W14" s="61">
         <f t="shared" si="4"/>
-        <v>80.350039777247417</v>
+        <v>93.288590604026851</v>
       </c>
       <c r="X14" s="28"/>
       <c r="Y14" s="108" t="s">
@@ -11370,48 +13361,48 @@
         <v>99.075785582255079</v>
       </c>
       <c r="L15" s="31">
-        <v>439</v>
+        <v>1072</v>
       </c>
       <c r="M15" s="54">
-        <v>441</v>
+        <v>1068</v>
       </c>
       <c r="N15" s="53">
         <f>M15-'Thang 6'!M15</f>
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="O15" s="53">
         <f>M15-'Thang 12'!Y16</f>
-        <v>58</v>
+        <v>685</v>
       </c>
       <c r="P15" s="53">
         <f t="shared" si="8"/>
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="70">
         <f t="shared" si="9"/>
-        <v>100.45558086560365</v>
+        <v>99.626865671641795</v>
       </c>
       <c r="R15" s="31">
-        <v>1072</v>
+        <v>439</v>
       </c>
       <c r="S15" s="54">
-        <v>1068</v>
+        <v>441</v>
       </c>
       <c r="T15" s="53">
         <f>S15-'Thang 6'!S15</f>
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="U15" s="53">
         <f>S15-'Thang 12'!AG16</f>
-        <v>28</v>
+        <v>-599</v>
       </c>
       <c r="V15" s="53">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="W15" s="61">
         <f t="shared" si="4"/>
-        <v>99.626865671641795</v>
+        <v>100.45558086560365</v>
       </c>
       <c r="X15" s="28"/>
       <c r="Y15" s="35"/>
@@ -11421,10 +13412,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="112" t="s">
+      <c r="A16" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="112"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -11463,51 +13454,51 @@
       </c>
       <c r="L16" s="18">
         <f>SUM(L9:L15)</f>
-        <v>5515</v>
+        <v>9852</v>
       </c>
       <c r="M16" s="18">
         <f>SUM(M9:M15)</f>
-        <v>4929</v>
+        <v>7790</v>
       </c>
       <c r="N16" s="56">
         <f>SUM(N9:N15)</f>
-        <v>-3</v>
+        <v>216</v>
       </c>
       <c r="O16" s="56">
         <f>M16-'Thang 12'!Y17</f>
-        <v>158</v>
+        <v>3019</v>
       </c>
       <c r="P16" s="18">
         <f t="shared" ref="P16" si="14">SUM(P9:P15)</f>
-        <v>586</v>
+        <v>2062</v>
       </c>
       <c r="Q16" s="69">
         <f t="shared" si="9"/>
-        <v>89.374433363553933</v>
+        <v>79.070239545269999</v>
       </c>
       <c r="R16" s="55">
         <f>SUM(R9:R15)</f>
-        <v>9852</v>
+        <v>5515</v>
       </c>
       <c r="S16" s="18">
         <f>SUM(S9:S15)</f>
-        <v>7790</v>
+        <v>4929</v>
       </c>
       <c r="T16" s="56">
         <f>SUM(T9:T15)</f>
-        <v>216</v>
+        <v>-3</v>
       </c>
       <c r="U16" s="56">
         <f>S16-'Thang 12'!AG17</f>
-        <v>236</v>
+        <v>-2625</v>
       </c>
       <c r="V16" s="56">
         <f>SUM(V9:V15)</f>
-        <v>2062</v>
+        <v>586</v>
       </c>
       <c r="W16" s="57">
         <f t="shared" si="4"/>
-        <v>79.070239545269999</v>
+        <v>89.374433363553933</v>
       </c>
       <c r="X16" s="37"/>
       <c r="Y16" s="36"/>
@@ -11543,13 +13534,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="113" t="s">
+      <c r="B18" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="113"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="113"/>
-      <c r="F18" s="113"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -11571,12 +13562,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="110"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="110"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
       <c r="H19" s="88"/>
       <c r="I19" s="88"/>
       <c r="J19" s="88"/>
@@ -11587,8 +13578,8 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="80"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
@@ -11599,8 +13590,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
       <c r="F20" s="89"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -11613,8 +13604,8 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
       <c r="V20" s="5"/>
@@ -11637,8 +13628,8 @@
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="31"/>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
       <c r="V21" s="5"/>
@@ -11661,8 +13652,8 @@
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
       <c r="V22" s="5"/>
@@ -11670,17 +13661,36 @@
     </row>
     <row r="23" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B23" s="5"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="54"/>
     </row>
     <row r="24" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B24" s="5"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="54"/>
     </row>
     <row r="25" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B25" s="5" t="s">
         <v>5</v>
       </c>
+      <c r="R25" s="31"/>
+      <c r="S25" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="Y7:Y8"/>
     <mergeCell ref="AQ7:AQ8"/>
     <mergeCell ref="Z7:AF7"/>
@@ -11690,19 +13700,3039 @@
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
     <mergeCell ref="AG7:AG8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AQ25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.88671875" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="4" width="13.5546875" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="10.88671875" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="10" width="10.33203125" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="9.21875" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="17" width="8.6640625" customWidth="1"/>
+    <col min="18" max="18" width="8" customWidth="1"/>
+    <col min="19" max="19" width="11.5546875" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="22" width="8.6640625" customWidth="1"/>
+    <col min="23" max="23" width="10.21875" customWidth="1"/>
+    <col min="24" max="24" width="6.88671875" customWidth="1"/>
+    <col min="25" max="25" width="17" customWidth="1"/>
+    <col min="40" max="40" width="11.88671875" customWidth="1"/>
+    <col min="41" max="41" width="11.33203125" customWidth="1"/>
+    <col min="42" max="42" width="10.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="136" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
+      <c r="Y1" s="114"/>
+    </row>
+    <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="137" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
+      <c r="Y2" s="114"/>
+    </row>
+    <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+    </row>
+    <row r="4" spans="1:43" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113"/>
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113"/>
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114"/>
+      <c r="V4" s="114"/>
+      <c r="W4" s="114"/>
+      <c r="X4" s="114"/>
+      <c r="Y4" s="114"/>
+    </row>
+    <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="134" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
+      <c r="Y5" s="114"/>
+    </row>
+    <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y6" s="7"/>
+    </row>
+    <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="126" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="126" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="129" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y7" s="128" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z7" s="152" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA7" s="152"/>
+      <c r="AB7" s="152"/>
+      <c r="AC7" s="152"/>
+      <c r="AD7" s="152"/>
+      <c r="AE7" s="152"/>
+      <c r="AF7" s="152"/>
+      <c r="AG7" s="150" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH7" s="152" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI7" s="152"/>
+      <c r="AJ7" s="152"/>
+      <c r="AK7" s="152"/>
+      <c r="AL7" s="152"/>
+      <c r="AM7" s="152"/>
+      <c r="AN7" s="152"/>
+      <c r="AO7" s="152"/>
+      <c r="AP7" s="152"/>
+      <c r="AQ7" s="150"/>
+    </row>
+    <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="112" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="112" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="112" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="112" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="112" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="112" t="s">
+        <v>79</v>
+      </c>
+      <c r="N8" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="112" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="R8" s="112" t="s">
+        <v>33</v>
+      </c>
+      <c r="S8" s="112" t="s">
+        <v>79</v>
+      </c>
+      <c r="T8" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="U8" s="112" t="s">
+        <v>46</v>
+      </c>
+      <c r="V8" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="W8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="X8" s="144"/>
+      <c r="Y8" s="128"/>
+      <c r="Z8" s="94" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA8" s="94" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB8" s="94" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC8" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD8" s="94" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE8" s="94" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF8" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG8" s="151"/>
+      <c r="AH8" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI8" s="105" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ8" s="105" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK8" s="105" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL8" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM8" s="96" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN8" s="94" t="s">
+        <v>67</v>
+      </c>
+      <c r="AO8" s="94" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP8" s="94" t="s">
+        <v>75</v>
+      </c>
+      <c r="AQ8" s="151"/>
+    </row>
+    <row r="9" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26">
+        <v>1</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="71">
+        <v>39379</v>
+      </c>
+      <c r="D9" s="72">
+        <v>39379</v>
+      </c>
+      <c r="E9" s="29">
+        <f t="shared" ref="E9:E16" si="0">D9/C9*100</f>
+        <v>100</v>
+      </c>
+      <c r="F9" s="59">
+        <v>1625</v>
+      </c>
+      <c r="G9" s="30">
+        <v>1549</v>
+      </c>
+      <c r="H9" s="31">
+        <f>G9-'Tháng 7'!G9</f>
+        <v>21</v>
+      </c>
+      <c r="I9" s="31">
+        <f>G9-'Thang 12'!Q10</f>
+        <v>-103</v>
+      </c>
+      <c r="J9" s="31">
+        <f t="shared" ref="J9:J15" si="1">F9-G9</f>
+        <v>76</v>
+      </c>
+      <c r="K9" s="61">
+        <f t="shared" ref="K9:K16" si="2">G9/F9*100</f>
+        <v>95.323076923076925</v>
+      </c>
+      <c r="L9" s="31">
+        <v>1862</v>
+      </c>
+      <c r="M9" s="30">
+        <v>1638</v>
+      </c>
+      <c r="N9" s="53">
+        <f>M9-'Tháng 7'!M9</f>
+        <v>14</v>
+      </c>
+      <c r="O9" s="53">
+        <f>M9-'Thang 12'!Y10</f>
+        <v>193</v>
+      </c>
+      <c r="P9" s="53">
+        <f>L9-M9</f>
+        <v>224</v>
+      </c>
+      <c r="Q9" s="70">
+        <f>M9/L9*100</f>
+        <v>87.969924812030072</v>
+      </c>
+      <c r="R9" s="31">
+        <v>1420</v>
+      </c>
+      <c r="S9" s="31">
+        <v>1427</v>
+      </c>
+      <c r="T9" s="53">
+        <f>S9-'Tháng 7'!S9</f>
+        <v>35</v>
+      </c>
+      <c r="U9" s="53">
+        <f>S9-'Thang 12'!AG10</f>
+        <v>-243</v>
+      </c>
+      <c r="V9" s="53">
+        <f t="shared" ref="V9:V15" si="3">R9-S9</f>
+        <v>-7</v>
+      </c>
+      <c r="W9" s="61">
+        <f t="shared" ref="W9:W16" si="4">S9/R9*100</f>
+        <v>100.49295774647888</v>
+      </c>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="106" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z9" s="107">
+        <f>Z10+Z11+Z12+Z13</f>
+        <v>466144</v>
+      </c>
+      <c r="AA9" s="94">
+        <v>277702</v>
+      </c>
+      <c r="AB9" s="94">
+        <v>249318</v>
+      </c>
+      <c r="AC9" s="94">
+        <f>AA9-AB9</f>
+        <v>28384</v>
+      </c>
+      <c r="AD9" s="94">
+        <f>AA9-AG9</f>
+        <v>-245013</v>
+      </c>
+      <c r="AE9" s="97">
+        <f>AA9/Z9*100</f>
+        <v>59.574294638566627</v>
+      </c>
+      <c r="AF9" s="98">
+        <f>Z9-AA9</f>
+        <v>188442</v>
+      </c>
+      <c r="AG9" s="104">
+        <v>522715</v>
+      </c>
+      <c r="AH9" s="99">
+        <f t="shared" ref="AH9" si="5">SUM(AI9:AL9)</f>
+        <v>68305</v>
+      </c>
+      <c r="AI9" s="100">
+        <v>2881</v>
+      </c>
+      <c r="AJ9" s="100">
+        <v>933</v>
+      </c>
+      <c r="AK9" s="100">
+        <v>190</v>
+      </c>
+      <c r="AL9" s="101">
+        <v>64301</v>
+      </c>
+      <c r="AM9" s="102">
+        <f t="shared" ref="AM9" si="6">SUM(AJ9:AK9)</f>
+        <v>1123</v>
+      </c>
+      <c r="AN9" s="103">
+        <f>AM9/Z9*100</f>
+        <v>0.2409126793437221</v>
+      </c>
+      <c r="AO9" s="103">
+        <v>1.26</v>
+      </c>
+      <c r="AP9" s="103">
+        <f t="shared" ref="AP9" si="7">AO9-AN9</f>
+        <v>1.0190873206562778</v>
+      </c>
+      <c r="AQ9" s="104"/>
+    </row>
+    <row r="10" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26">
+        <v>2</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="71">
+        <v>29921</v>
+      </c>
+      <c r="D10" s="72">
+        <v>29921</v>
+      </c>
+      <c r="E10" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F10" s="59">
+        <v>815</v>
+      </c>
+      <c r="G10" s="30">
+        <v>506</v>
+      </c>
+      <c r="H10" s="31">
+        <f>G10-'Tháng 7'!G10</f>
+        <v>10</v>
+      </c>
+      <c r="I10" s="31">
+        <f>G10-'Thang 12'!Q11</f>
+        <v>19</v>
+      </c>
+      <c r="J10" s="31">
+        <f t="shared" si="1"/>
+        <v>309</v>
+      </c>
+      <c r="K10" s="61">
+        <f t="shared" si="2"/>
+        <v>62.085889570552141</v>
+      </c>
+      <c r="L10" s="31">
+        <v>1297</v>
+      </c>
+      <c r="M10" s="30">
+        <v>785</v>
+      </c>
+      <c r="N10" s="53">
+        <f>M10-'Tháng 7'!M10</f>
+        <v>65</v>
+      </c>
+      <c r="O10" s="53">
+        <f>M10-'Thang 12'!Y11</f>
+        <v>435</v>
+      </c>
+      <c r="P10" s="53">
+        <f t="shared" ref="P10:P15" si="8">L10-M10</f>
+        <v>512</v>
+      </c>
+      <c r="Q10" s="70">
+        <f t="shared" ref="Q10:Q16" si="9">M10/L10*100</f>
+        <v>60.524286815728601</v>
+      </c>
+      <c r="R10" s="31">
+        <v>661</v>
+      </c>
+      <c r="S10" s="31">
+        <v>396</v>
+      </c>
+      <c r="T10" s="53">
+        <f>S10-'Tháng 7'!S10</f>
+        <v>6</v>
+      </c>
+      <c r="U10" s="53">
+        <f>S10-'Thang 12'!AG11</f>
+        <v>-194</v>
+      </c>
+      <c r="V10" s="53">
+        <f t="shared" si="3"/>
+        <v>265</v>
+      </c>
+      <c r="W10" s="61">
+        <f t="shared" si="4"/>
+        <v>59.909228441754912</v>
+      </c>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="108" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z10" s="107">
+        <v>173399</v>
+      </c>
+      <c r="AA10" s="94">
+        <v>111295</v>
+      </c>
+      <c r="AB10" s="94">
+        <v>94017</v>
+      </c>
+      <c r="AC10" s="94">
+        <f t="shared" ref="AC10:AC14" si="10">AA10-AB10</f>
+        <v>17278</v>
+      </c>
+      <c r="AD10" s="94">
+        <f t="shared" ref="AD10:AD14" si="11">AA10-AG10</f>
+        <v>-80354</v>
+      </c>
+      <c r="AE10" s="97">
+        <f t="shared" ref="AE10:AE13" si="12">AA10/Z10*100</f>
+        <v>64.184337856619706</v>
+      </c>
+      <c r="AF10" s="98">
+        <f t="shared" ref="AF10:AF13" si="13">Z10-AA10</f>
+        <v>62104</v>
+      </c>
+      <c r="AG10" s="104">
+        <v>191649</v>
+      </c>
+      <c r="AH10" s="95"/>
+      <c r="AI10" s="105"/>
+      <c r="AJ10" s="105"/>
+      <c r="AK10" s="105"/>
+      <c r="AL10" s="96"/>
+      <c r="AM10" s="96"/>
+      <c r="AN10" s="94"/>
+      <c r="AO10" s="94"/>
+      <c r="AP10" s="94"/>
+      <c r="AQ10" s="104"/>
+    </row>
+    <row r="11" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="26">
+        <v>3</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="71">
+        <v>25763</v>
+      </c>
+      <c r="D11" s="72">
+        <v>25763</v>
+      </c>
+      <c r="E11" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F11" s="59">
+        <v>652</v>
+      </c>
+      <c r="G11" s="30">
+        <v>515</v>
+      </c>
+      <c r="H11" s="31">
+        <f>G11-'Tháng 7'!G11</f>
+        <v>-4</v>
+      </c>
+      <c r="I11" s="31">
+        <f>G11-'Thang 12'!Q12</f>
+        <v>-24</v>
+      </c>
+      <c r="J11" s="31">
+        <f t="shared" si="1"/>
+        <v>137</v>
+      </c>
+      <c r="K11" s="61">
+        <f t="shared" si="2"/>
+        <v>78.987730061349694</v>
+      </c>
+      <c r="L11" s="31">
+        <v>1117</v>
+      </c>
+      <c r="M11" s="30">
+        <v>831</v>
+      </c>
+      <c r="N11" s="53">
+        <f>M11-'Tháng 7'!M11</f>
+        <v>61</v>
+      </c>
+      <c r="O11" s="53">
+        <f>M11-'Thang 12'!Y12</f>
+        <v>434</v>
+      </c>
+      <c r="P11" s="53">
+        <f t="shared" si="8"/>
+        <v>286</v>
+      </c>
+      <c r="Q11" s="70">
+        <f t="shared" si="9"/>
+        <v>74.395702775290957</v>
+      </c>
+      <c r="R11" s="31">
+        <v>565</v>
+      </c>
+      <c r="S11" s="31">
+        <v>425</v>
+      </c>
+      <c r="T11" s="53">
+        <f>S11-'Tháng 7'!S11</f>
+        <v>-9</v>
+      </c>
+      <c r="U11" s="53">
+        <f>S11-'Thang 12'!AG12</f>
+        <v>-391</v>
+      </c>
+      <c r="V11" s="53">
+        <f t="shared" si="3"/>
+        <v>140</v>
+      </c>
+      <c r="W11" s="61">
+        <f t="shared" si="4"/>
+        <v>75.221238938053091</v>
+      </c>
+      <c r="X11" s="28"/>
+      <c r="Y11" s="108" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z11" s="107">
+        <v>37255</v>
+      </c>
+      <c r="AA11" s="109">
+        <v>21156</v>
+      </c>
+      <c r="AB11" s="109">
+        <v>19221</v>
+      </c>
+      <c r="AC11" s="94">
+        <f t="shared" si="10"/>
+        <v>1935</v>
+      </c>
+      <c r="AD11" s="94">
+        <f t="shared" si="11"/>
+        <v>-14119</v>
+      </c>
+      <c r="AE11" s="97">
+        <f t="shared" si="12"/>
+        <v>56.787008455240908</v>
+      </c>
+      <c r="AF11" s="98">
+        <f t="shared" si="13"/>
+        <v>16099</v>
+      </c>
+      <c r="AG11" s="104">
+        <v>35275</v>
+      </c>
+      <c r="AH11" s="104"/>
+      <c r="AI11" s="104"/>
+      <c r="AJ11" s="104"/>
+      <c r="AK11" s="104"/>
+      <c r="AL11" s="104"/>
+      <c r="AM11" s="104"/>
+      <c r="AN11" s="104"/>
+      <c r="AO11" s="104"/>
+      <c r="AP11" s="104"/>
+      <c r="AQ11" s="104"/>
+    </row>
+    <row r="12" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="26">
+        <v>4</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="71">
+        <v>51742</v>
+      </c>
+      <c r="D12" s="72">
+        <v>51742</v>
+      </c>
+      <c r="E12" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F12" s="59">
+        <v>1151</v>
+      </c>
+      <c r="G12" s="30">
+        <v>1132</v>
+      </c>
+      <c r="H12" s="31">
+        <f>G12-'Tháng 7'!G12</f>
+        <v>36</v>
+      </c>
+      <c r="I12" s="31">
+        <f>G12-'Thang 12'!Q13</f>
+        <v>31</v>
+      </c>
+      <c r="J12" s="31">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="K12" s="61">
+        <f t="shared" si="2"/>
+        <v>98.34926151172894</v>
+      </c>
+      <c r="L12" s="31">
+        <v>2043</v>
+      </c>
+      <c r="M12" s="30">
+        <v>1719</v>
+      </c>
+      <c r="N12" s="53">
+        <f>M12-'Tháng 7'!M12</f>
+        <v>93</v>
+      </c>
+      <c r="O12" s="53">
+        <f>M12-'Thang 12'!Y13</f>
+        <v>809</v>
+      </c>
+      <c r="P12" s="53">
+        <f t="shared" si="8"/>
+        <v>324</v>
+      </c>
+      <c r="Q12" s="70">
+        <f t="shared" si="9"/>
+        <v>84.140969162995589</v>
+      </c>
+      <c r="R12" s="31">
+        <v>978</v>
+      </c>
+      <c r="S12" s="31">
+        <v>1026</v>
+      </c>
+      <c r="T12" s="53">
+        <f>S12-'Tháng 7'!S12</f>
+        <v>35</v>
+      </c>
+      <c r="U12" s="53">
+        <f>S12-'Thang 12'!AG13</f>
+        <v>-425</v>
+      </c>
+      <c r="V12" s="53">
+        <f t="shared" si="3"/>
+        <v>-48</v>
+      </c>
+      <c r="W12" s="61">
+        <f t="shared" si="4"/>
+        <v>104.9079754601227</v>
+      </c>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="108" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z12" s="107">
+        <v>10639</v>
+      </c>
+      <c r="AA12" s="109">
+        <v>7566</v>
+      </c>
+      <c r="AB12" s="109">
+        <v>6448</v>
+      </c>
+      <c r="AC12" s="94">
+        <f t="shared" si="10"/>
+        <v>1118</v>
+      </c>
+      <c r="AD12" s="94">
+        <f t="shared" si="11"/>
+        <v>-5543</v>
+      </c>
+      <c r="AE12" s="97">
+        <f t="shared" si="12"/>
+        <v>71.115706363380013</v>
+      </c>
+      <c r="AF12" s="98">
+        <f t="shared" si="13"/>
+        <v>3073</v>
+      </c>
+      <c r="AG12" s="104">
+        <v>13109</v>
+      </c>
+      <c r="AH12" s="104"/>
+      <c r="AI12" s="104"/>
+      <c r="AJ12" s="104"/>
+      <c r="AK12" s="104"/>
+      <c r="AL12" s="104"/>
+      <c r="AM12" s="104"/>
+      <c r="AN12" s="104"/>
+      <c r="AO12" s="104"/>
+      <c r="AP12" s="104"/>
+      <c r="AQ12" s="104"/>
+    </row>
+    <row r="13" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="26">
+        <v>5</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="71">
+        <v>27773</v>
+      </c>
+      <c r="D13" s="72">
+        <v>27773</v>
+      </c>
+      <c r="E13" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F13" s="59">
+        <v>1206</v>
+      </c>
+      <c r="G13" s="30">
+        <v>974</v>
+      </c>
+      <c r="H13" s="31">
+        <f>G13-'Tháng 7'!G13</f>
+        <v>-5</v>
+      </c>
+      <c r="I13" s="31">
+        <f>G13-'Thang 12'!Q14</f>
+        <v>-34</v>
+      </c>
+      <c r="J13" s="31">
+        <f t="shared" si="1"/>
+        <v>232</v>
+      </c>
+      <c r="K13" s="61">
+        <f t="shared" si="2"/>
+        <v>80.762852404643453</v>
+      </c>
+      <c r="L13" s="31">
+        <v>1204</v>
+      </c>
+      <c r="M13" s="30">
+        <v>1005</v>
+      </c>
+      <c r="N13" s="53">
+        <f>M13-'Tháng 7'!M13</f>
+        <v>33</v>
+      </c>
+      <c r="O13" s="53">
+        <f>M13-'Thang 12'!Y14</f>
+        <v>91</v>
+      </c>
+      <c r="P13" s="53">
+        <f t="shared" si="8"/>
+        <v>199</v>
+      </c>
+      <c r="Q13" s="70">
+        <f t="shared" si="9"/>
+        <v>83.471760797342199</v>
+      </c>
+      <c r="R13" s="31">
+        <v>1005</v>
+      </c>
+      <c r="S13" s="31">
+        <v>857</v>
+      </c>
+      <c r="T13" s="53">
+        <f>S13-'Tháng 7'!S13</f>
+        <v>-7</v>
+      </c>
+      <c r="U13" s="53">
+        <f>S13-'Thang 12'!AG14</f>
+        <v>-150</v>
+      </c>
+      <c r="V13" s="53">
+        <f t="shared" si="3"/>
+        <v>148</v>
+      </c>
+      <c r="W13" s="61">
+        <f t="shared" si="4"/>
+        <v>85.273631840796014</v>
+      </c>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="108" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z13" s="107">
+        <v>244851</v>
+      </c>
+      <c r="AA13" s="109">
+        <v>137467</v>
+      </c>
+      <c r="AB13" s="109">
+        <v>129490</v>
+      </c>
+      <c r="AC13" s="94">
+        <f t="shared" si="10"/>
+        <v>7977</v>
+      </c>
+      <c r="AD13" s="94">
+        <f t="shared" si="11"/>
+        <v>-145034</v>
+      </c>
+      <c r="AE13" s="97">
+        <f t="shared" si="12"/>
+        <v>56.143123777317641</v>
+      </c>
+      <c r="AF13" s="98">
+        <f t="shared" si="13"/>
+        <v>107384</v>
+      </c>
+      <c r="AG13" s="104">
+        <v>282501</v>
+      </c>
+      <c r="AH13" s="104"/>
+      <c r="AI13" s="104"/>
+      <c r="AJ13" s="104"/>
+      <c r="AK13" s="104"/>
+      <c r="AL13" s="104"/>
+      <c r="AM13" s="104"/>
+      <c r="AN13" s="104"/>
+      <c r="AO13" s="104"/>
+      <c r="AP13" s="104"/>
+      <c r="AQ13" s="104"/>
+    </row>
+    <row r="14" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="26">
+        <v>6</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="71">
+        <v>28987</v>
+      </c>
+      <c r="D14" s="72">
+        <v>28987</v>
+      </c>
+      <c r="E14" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F14" s="59">
+        <v>591</v>
+      </c>
+      <c r="G14" s="30">
+        <v>529</v>
+      </c>
+      <c r="H14" s="31">
+        <f>G14-'Tháng 7'!G14</f>
+        <v>5</v>
+      </c>
+      <c r="I14" s="31">
+        <f>G14-'Thang 12'!Q15</f>
+        <v>65</v>
+      </c>
+      <c r="J14" s="31">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+      <c r="K14" s="61">
+        <f t="shared" si="2"/>
+        <v>89.5093062605753</v>
+      </c>
+      <c r="L14" s="31">
+        <v>1257</v>
+      </c>
+      <c r="M14" s="30">
+        <v>1063</v>
+      </c>
+      <c r="N14" s="53">
+        <f>M14-'Tháng 7'!M14</f>
+        <v>53</v>
+      </c>
+      <c r="O14" s="53">
+        <f>M14-'Thang 12'!Y15</f>
+        <v>691</v>
+      </c>
+      <c r="P14" s="53">
+        <f t="shared" si="8"/>
+        <v>194</v>
+      </c>
+      <c r="Q14" s="70">
+        <f t="shared" si="9"/>
+        <v>84.566428003182182</v>
+      </c>
+      <c r="R14" s="31">
+        <v>447</v>
+      </c>
+      <c r="S14" s="31">
+        <v>417</v>
+      </c>
+      <c r="T14" s="53">
+        <f>S14-'Tháng 7'!S14</f>
+        <v>0</v>
+      </c>
+      <c r="U14" s="53">
+        <f>S14-'Thang 12'!AG15</f>
+        <v>-563</v>
+      </c>
+      <c r="V14" s="53">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="W14" s="61">
+        <f t="shared" si="4"/>
+        <v>93.288590604026851</v>
+      </c>
+      <c r="X14" s="28"/>
+      <c r="Y14" s="108" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z14" s="109"/>
+      <c r="AA14" s="109">
+        <v>218</v>
+      </c>
+      <c r="AB14" s="109">
+        <v>142</v>
+      </c>
+      <c r="AC14" s="94">
+        <f t="shared" si="10"/>
+        <v>76</v>
+      </c>
+      <c r="AD14" s="94">
+        <f t="shared" si="11"/>
+        <v>37</v>
+      </c>
+      <c r="AE14" s="97"/>
+      <c r="AF14" s="104"/>
+      <c r="AG14" s="104">
+        <v>181</v>
+      </c>
+      <c r="AH14" s="104"/>
+      <c r="AI14" s="104"/>
+      <c r="AJ14" s="104"/>
+      <c r="AK14" s="104"/>
+      <c r="AL14" s="104"/>
+      <c r="AM14" s="104"/>
+      <c r="AN14" s="104"/>
+      <c r="AO14" s="104"/>
+      <c r="AP14" s="104"/>
+      <c r="AQ14" s="104"/>
+    </row>
+    <row r="15" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="26">
+        <v>7</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="71">
+        <v>24726</v>
+      </c>
+      <c r="D15" s="72">
+        <v>24726</v>
+      </c>
+      <c r="E15" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F15" s="59">
+        <v>541</v>
+      </c>
+      <c r="G15" s="30">
+        <v>533</v>
+      </c>
+      <c r="H15" s="31">
+        <f>G15-'Tháng 7'!G15</f>
+        <v>-3</v>
+      </c>
+      <c r="I15" s="31">
+        <f>G15-'Thang 12'!Q16</f>
+        <v>72</v>
+      </c>
+      <c r="J15" s="31">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K15" s="61">
+        <f t="shared" si="2"/>
+        <v>98.521256931608136</v>
+      </c>
+      <c r="L15" s="31">
+        <v>1072</v>
+      </c>
+      <c r="M15" s="30">
+        <v>1025</v>
+      </c>
+      <c r="N15" s="53">
+        <f>M15-'Tháng 7'!M15</f>
+        <v>-43</v>
+      </c>
+      <c r="O15" s="53">
+        <f>M15-'Thang 12'!Y16</f>
+        <v>642</v>
+      </c>
+      <c r="P15" s="53">
+        <f t="shared" si="8"/>
+        <v>47</v>
+      </c>
+      <c r="Q15" s="70">
+        <f t="shared" si="9"/>
+        <v>95.615671641791039</v>
+      </c>
+      <c r="R15" s="31">
+        <v>439</v>
+      </c>
+      <c r="S15" s="31">
+        <v>435</v>
+      </c>
+      <c r="T15" s="53">
+        <f>S15-'Tháng 7'!S15</f>
+        <v>-6</v>
+      </c>
+      <c r="U15" s="53">
+        <f>S15-'Thang 12'!AG16</f>
+        <v>-605</v>
+      </c>
+      <c r="V15" s="53">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="W15" s="61">
+        <f t="shared" si="4"/>
+        <v>99.088838268792713</v>
+      </c>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10"/>
+      <c r="AB15" s="10"/>
+      <c r="AC15" s="10"/>
+    </row>
+    <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="141" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="141"/>
+      <c r="C16" s="18">
+        <f>SUM(C9:C15)</f>
+        <v>228291</v>
+      </c>
+      <c r="D16" s="18">
+        <f>SUM(D9:D15)</f>
+        <v>228291</v>
+      </c>
+      <c r="E16" s="32">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F16" s="60">
+        <f>SUM(F9:F15)</f>
+        <v>6581</v>
+      </c>
+      <c r="G16" s="50">
+        <f>SUM(G9:G15)</f>
+        <v>5738</v>
+      </c>
+      <c r="H16" s="55">
+        <f>SUM(H9:H15)</f>
+        <v>60</v>
+      </c>
+      <c r="I16" s="55">
+        <f>G16-'Thang 12'!Q17</f>
+        <v>26</v>
+      </c>
+      <c r="J16" s="55">
+        <f>SUM(J9:J15)</f>
+        <v>843</v>
+      </c>
+      <c r="K16" s="57">
+        <f t="shared" si="2"/>
+        <v>87.190396596261962</v>
+      </c>
+      <c r="L16" s="18">
+        <f>SUM(L9:L15)</f>
+        <v>9852</v>
+      </c>
+      <c r="M16" s="18">
+        <f>SUM(M9:M15)</f>
+        <v>8066</v>
+      </c>
+      <c r="N16" s="56">
+        <f>SUM(N9:N15)</f>
+        <v>276</v>
+      </c>
+      <c r="O16" s="56">
+        <f>M16-'Thang 12'!Y17</f>
+        <v>3295</v>
+      </c>
+      <c r="P16" s="18">
+        <f t="shared" ref="P16" si="14">SUM(P9:P15)</f>
+        <v>1786</v>
+      </c>
+      <c r="Q16" s="69">
+        <f t="shared" si="9"/>
+        <v>81.871701177425905</v>
+      </c>
+      <c r="R16" s="55">
+        <f>SUM(R9:R15)</f>
+        <v>5515</v>
+      </c>
+      <c r="S16" s="18">
+        <f>SUM(S9:S15)</f>
+        <v>4983</v>
+      </c>
+      <c r="T16" s="56">
+        <f>SUM(T9:T15)</f>
+        <v>54</v>
+      </c>
+      <c r="U16" s="56">
+        <f>S16-'Thang 12'!AG17</f>
+        <v>-2571</v>
+      </c>
+      <c r="V16" s="56">
+        <f>SUM(V9:V15)</f>
+        <v>532</v>
+      </c>
+      <c r="W16" s="57">
+        <f t="shared" si="4"/>
+        <v>90.353581142339081</v>
+      </c>
+      <c r="X16" s="37"/>
+      <c r="Y16" s="36"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="25"/>
+    </row>
+    <row r="17" spans="1:25" ht="9.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="11"/>
+      <c r="B17" s="110"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+    </row>
+    <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="142" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19"/>
+      <c r="X18" s="19"/>
+      <c r="Y18" s="19"/>
+    </row>
+    <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+    </row>
+    <row r="21" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+    </row>
+    <row r="22" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+    </row>
+    <row r="23" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B23" s="5"/>
+      <c r="R23" s="31"/>
+    </row>
+    <row r="24" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B24" s="5"/>
+      <c r="R24" s="31"/>
+    </row>
+    <row r="25" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="R25" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="L7:Q7"/>
+    <mergeCell ref="R7:W7"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AP7"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="A5:X5"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="H1:X1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="H2:X2"/>
     <mergeCell ref="A3:C3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AQ25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.88671875" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="4" width="13.5546875" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="10.88671875" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="10" width="10.33203125" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="9.21875" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="17" width="8.6640625" customWidth="1"/>
+    <col min="18" max="18" width="8" customWidth="1"/>
+    <col min="19" max="19" width="11.5546875" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="23" width="8.6640625" customWidth="1"/>
+    <col min="24" max="24" width="6.88671875" customWidth="1"/>
+    <col min="25" max="25" width="17" customWidth="1"/>
+    <col min="40" max="40" width="11.88671875" customWidth="1"/>
+    <col min="41" max="41" width="11.33203125" customWidth="1"/>
+    <col min="42" max="42" width="10.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="136" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
+      <c r="Y1" s="118"/>
+    </row>
+    <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="137" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
+      <c r="Y2" s="118"/>
+    </row>
+    <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+    </row>
+    <row r="4" spans="1:43" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="117"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="117"/>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118"/>
+      <c r="X4" s="118"/>
+      <c r="Y4" s="118"/>
+    </row>
+    <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="134" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
+      <c r="Y5" s="118"/>
+    </row>
+    <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y6" s="7"/>
+    </row>
+    <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="126" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="126" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="129" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y7" s="128" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z7" s="152" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA7" s="152"/>
+      <c r="AB7" s="152"/>
+      <c r="AC7" s="152"/>
+      <c r="AD7" s="152"/>
+      <c r="AE7" s="152"/>
+      <c r="AF7" s="152"/>
+      <c r="AG7" s="150" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH7" s="152" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI7" s="152"/>
+      <c r="AJ7" s="152"/>
+      <c r="AK7" s="152"/>
+      <c r="AL7" s="152"/>
+      <c r="AM7" s="152"/>
+      <c r="AN7" s="152"/>
+      <c r="AO7" s="152"/>
+      <c r="AP7" s="152"/>
+      <c r="AQ7" s="150"/>
+    </row>
+    <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="121" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="121" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="121" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="121" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="121" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="121" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="121" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" s="121" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="121" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="R8" s="121" t="s">
+        <v>33</v>
+      </c>
+      <c r="S8" s="121" t="s">
+        <v>81</v>
+      </c>
+      <c r="T8" s="121" t="s">
+        <v>30</v>
+      </c>
+      <c r="U8" s="121" t="s">
+        <v>46</v>
+      </c>
+      <c r="V8" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="W8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="X8" s="144"/>
+      <c r="Y8" s="128"/>
+      <c r="Z8" s="94" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA8" s="94" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB8" s="94" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC8" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD8" s="94" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE8" s="94" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF8" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG8" s="151"/>
+      <c r="AH8" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI8" s="105" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ8" s="105" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK8" s="105" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL8" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM8" s="96" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN8" s="94" t="s">
+        <v>67</v>
+      </c>
+      <c r="AO8" s="94" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP8" s="94" t="s">
+        <v>75</v>
+      </c>
+      <c r="AQ8" s="151"/>
+    </row>
+    <row r="9" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26">
+        <v>1</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="71">
+        <v>39379</v>
+      </c>
+      <c r="D9" s="72">
+        <v>39379</v>
+      </c>
+      <c r="E9" s="29">
+        <f t="shared" ref="E9:E16" si="0">D9/C9*100</f>
+        <v>100</v>
+      </c>
+      <c r="F9" s="59">
+        <v>1625</v>
+      </c>
+      <c r="G9" s="30"/>
+      <c r="H9" s="31">
+        <f>G9-'Tháng 7'!G9</f>
+        <v>-1528</v>
+      </c>
+      <c r="I9" s="31">
+        <f>G9-'Thang 12'!Q10</f>
+        <v>-1652</v>
+      </c>
+      <c r="J9" s="31">
+        <f t="shared" ref="J9:J15" si="1">F9-G9</f>
+        <v>1625</v>
+      </c>
+      <c r="K9" s="61">
+        <f t="shared" ref="K9:K16" si="2">G9/F9*100</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="31">
+        <v>1862</v>
+      </c>
+      <c r="M9" s="30"/>
+      <c r="N9" s="53">
+        <f>M9-'Tháng 7'!M9</f>
+        <v>-1624</v>
+      </c>
+      <c r="O9" s="53">
+        <f>M9-'Thang 12'!Y10</f>
+        <v>-1445</v>
+      </c>
+      <c r="P9" s="53">
+        <f>L9-M9</f>
+        <v>1862</v>
+      </c>
+      <c r="Q9" s="70">
+        <f>M9/L9*100</f>
+        <v>0</v>
+      </c>
+      <c r="R9" s="31">
+        <v>1420</v>
+      </c>
+      <c r="S9" s="31"/>
+      <c r="T9" s="53">
+        <f>S9-'Tháng 7'!S9</f>
+        <v>-1392</v>
+      </c>
+      <c r="U9" s="53">
+        <f>S9-'Thang 12'!AG10</f>
+        <v>-1670</v>
+      </c>
+      <c r="V9" s="53">
+        <f t="shared" ref="V9:V15" si="3">R9-S9</f>
+        <v>1420</v>
+      </c>
+      <c r="W9" s="61">
+        <f t="shared" ref="W9:W16" si="4">S9/R9*100</f>
+        <v>0</v>
+      </c>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="106" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z9" s="107">
+        <f>Z10+Z11+Z12+Z13</f>
+        <v>466144</v>
+      </c>
+      <c r="AA9" s="94">
+        <v>249318</v>
+      </c>
+      <c r="AB9" s="94">
+        <v>249318</v>
+      </c>
+      <c r="AC9" s="94">
+        <f>AA9-AB9</f>
+        <v>0</v>
+      </c>
+      <c r="AD9" s="94">
+        <f>AA9-AG9</f>
+        <v>-273397</v>
+      </c>
+      <c r="AE9" s="97">
+        <f>AA9/Z9*100</f>
+        <v>53.48518912610696</v>
+      </c>
+      <c r="AF9" s="98">
+        <f>Z9-AA9</f>
+        <v>216826</v>
+      </c>
+      <c r="AG9" s="104">
+        <v>522715</v>
+      </c>
+      <c r="AH9" s="99">
+        <f t="shared" ref="AH9" si="5">SUM(AI9:AL9)</f>
+        <v>48041</v>
+      </c>
+      <c r="AI9" s="100">
+        <v>2881</v>
+      </c>
+      <c r="AJ9" s="100">
+        <v>1394</v>
+      </c>
+      <c r="AK9" s="100">
+        <v>190</v>
+      </c>
+      <c r="AL9" s="101">
+        <v>43576</v>
+      </c>
+      <c r="AM9" s="102">
+        <f t="shared" ref="AM9" si="6">SUM(AJ9:AK9)</f>
+        <v>1584</v>
+      </c>
+      <c r="AN9" s="103">
+        <f>AM9/Z9*100</f>
+        <v>0.33980915768517883</v>
+      </c>
+      <c r="AO9" s="103">
+        <v>1.26</v>
+      </c>
+      <c r="AP9" s="103">
+        <f t="shared" ref="AP9" si="7">AO9-AN9</f>
+        <v>0.92019084231482118</v>
+      </c>
+      <c r="AQ9" s="104"/>
+    </row>
+    <row r="10" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26">
+        <v>2</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="71">
+        <v>29921</v>
+      </c>
+      <c r="D10" s="72">
+        <v>29921</v>
+      </c>
+      <c r="E10" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F10" s="59">
+        <v>815</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="31">
+        <f>G10-'Tháng 7'!G10</f>
+        <v>-496</v>
+      </c>
+      <c r="I10" s="31">
+        <f>G10-'Thang 12'!Q11</f>
+        <v>-487</v>
+      </c>
+      <c r="J10" s="31">
+        <f t="shared" si="1"/>
+        <v>815</v>
+      </c>
+      <c r="K10" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="31">
+        <v>1297</v>
+      </c>
+      <c r="M10" s="30"/>
+      <c r="N10" s="53">
+        <f>M10-'Tháng 7'!M10</f>
+        <v>-720</v>
+      </c>
+      <c r="O10" s="53">
+        <f>M10-'Thang 12'!Y11</f>
+        <v>-350</v>
+      </c>
+      <c r="P10" s="53">
+        <f t="shared" ref="P10:P15" si="8">L10-M10</f>
+        <v>1297</v>
+      </c>
+      <c r="Q10" s="70">
+        <f t="shared" ref="Q10:Q16" si="9">M10/L10*100</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="31">
+        <v>661</v>
+      </c>
+      <c r="S10" s="31"/>
+      <c r="T10" s="53">
+        <f>S10-'Tháng 7'!S10</f>
+        <v>-390</v>
+      </c>
+      <c r="U10" s="53">
+        <f>S10-'Thang 12'!AG11</f>
+        <v>-590</v>
+      </c>
+      <c r="V10" s="53">
+        <f t="shared" si="3"/>
+        <v>661</v>
+      </c>
+      <c r="W10" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="108" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z10" s="107">
+        <v>173399</v>
+      </c>
+      <c r="AA10" s="94">
+        <v>94017</v>
+      </c>
+      <c r="AB10" s="94">
+        <v>94017</v>
+      </c>
+      <c r="AC10" s="94">
+        <f t="shared" ref="AC10:AC14" si="10">AA10-AB10</f>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="94">
+        <f t="shared" ref="AD10:AD14" si="11">AA10-AG10</f>
+        <v>-97632</v>
+      </c>
+      <c r="AE10" s="97">
+        <f t="shared" ref="AE10:AE13" si="12">AA10/Z10*100</f>
+        <v>54.220035871025786</v>
+      </c>
+      <c r="AF10" s="98">
+        <f t="shared" ref="AF10:AF13" si="13">Z10-AA10</f>
+        <v>79382</v>
+      </c>
+      <c r="AG10" s="104">
+        <v>191649</v>
+      </c>
+      <c r="AH10" s="95"/>
+      <c r="AI10" s="105"/>
+      <c r="AJ10" s="105"/>
+      <c r="AK10" s="105"/>
+      <c r="AL10" s="96"/>
+      <c r="AM10" s="96"/>
+      <c r="AN10" s="94"/>
+      <c r="AO10" s="94"/>
+      <c r="AP10" s="94"/>
+      <c r="AQ10" s="104"/>
+    </row>
+    <row r="11" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="26">
+        <v>3</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="71">
+        <v>25763</v>
+      </c>
+      <c r="D11" s="72">
+        <v>25763</v>
+      </c>
+      <c r="E11" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F11" s="59">
+        <v>652</v>
+      </c>
+      <c r="G11" s="30"/>
+      <c r="H11" s="31">
+        <f>G11-'Tháng 7'!G11</f>
+        <v>-519</v>
+      </c>
+      <c r="I11" s="31">
+        <f>G11-'Thang 12'!Q12</f>
+        <v>-539</v>
+      </c>
+      <c r="J11" s="31">
+        <f t="shared" si="1"/>
+        <v>652</v>
+      </c>
+      <c r="K11" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="31">
+        <v>1117</v>
+      </c>
+      <c r="M11" s="30"/>
+      <c r="N11" s="53">
+        <f>M11-'Tháng 7'!M11</f>
+        <v>-770</v>
+      </c>
+      <c r="O11" s="53">
+        <f>M11-'Thang 12'!Y12</f>
+        <v>-397</v>
+      </c>
+      <c r="P11" s="53">
+        <f t="shared" si="8"/>
+        <v>1117</v>
+      </c>
+      <c r="Q11" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="31">
+        <v>565</v>
+      </c>
+      <c r="S11" s="31"/>
+      <c r="T11" s="53">
+        <f>S11-'Tháng 7'!S11</f>
+        <v>-434</v>
+      </c>
+      <c r="U11" s="53">
+        <f>S11-'Thang 12'!AG12</f>
+        <v>-816</v>
+      </c>
+      <c r="V11" s="53">
+        <f t="shared" si="3"/>
+        <v>565</v>
+      </c>
+      <c r="W11" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="28"/>
+      <c r="Y11" s="108" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z11" s="107">
+        <v>37255</v>
+      </c>
+      <c r="AA11" s="109">
+        <v>19221</v>
+      </c>
+      <c r="AB11" s="109">
+        <v>19221</v>
+      </c>
+      <c r="AC11" s="94">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="94">
+        <f t="shared" si="11"/>
+        <v>-16054</v>
+      </c>
+      <c r="AE11" s="97">
+        <f t="shared" si="12"/>
+        <v>51.593074755066439</v>
+      </c>
+      <c r="AF11" s="98">
+        <f t="shared" si="13"/>
+        <v>18034</v>
+      </c>
+      <c r="AG11" s="104">
+        <v>35275</v>
+      </c>
+      <c r="AH11" s="104"/>
+      <c r="AI11" s="104"/>
+      <c r="AJ11" s="104"/>
+      <c r="AK11" s="104"/>
+      <c r="AL11" s="104"/>
+      <c r="AM11" s="104"/>
+      <c r="AN11" s="104"/>
+      <c r="AO11" s="104"/>
+      <c r="AP11" s="104"/>
+      <c r="AQ11" s="104"/>
+    </row>
+    <row r="12" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="26">
+        <v>4</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="71">
+        <v>51742</v>
+      </c>
+      <c r="D12" s="72">
+        <v>51742</v>
+      </c>
+      <c r="E12" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F12" s="59">
+        <v>1151</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="31">
+        <f>G12-'Tháng 7'!G12</f>
+        <v>-1096</v>
+      </c>
+      <c r="I12" s="31">
+        <f>G12-'Thang 12'!Q13</f>
+        <v>-1101</v>
+      </c>
+      <c r="J12" s="31">
+        <f t="shared" si="1"/>
+        <v>1151</v>
+      </c>
+      <c r="K12" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="31">
+        <v>2043</v>
+      </c>
+      <c r="M12" s="30"/>
+      <c r="N12" s="53">
+        <f>M12-'Tháng 7'!M12</f>
+        <v>-1626</v>
+      </c>
+      <c r="O12" s="53">
+        <f>M12-'Thang 12'!Y13</f>
+        <v>-910</v>
+      </c>
+      <c r="P12" s="53">
+        <f t="shared" si="8"/>
+        <v>2043</v>
+      </c>
+      <c r="Q12" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="31">
+        <v>978</v>
+      </c>
+      <c r="S12" s="31"/>
+      <c r="T12" s="53">
+        <f>S12-'Tháng 7'!S12</f>
+        <v>-991</v>
+      </c>
+      <c r="U12" s="53">
+        <f>S12-'Thang 12'!AG13</f>
+        <v>-1451</v>
+      </c>
+      <c r="V12" s="53">
+        <f t="shared" si="3"/>
+        <v>978</v>
+      </c>
+      <c r="W12" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="108" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z12" s="107">
+        <v>10639</v>
+      </c>
+      <c r="AA12" s="109">
+        <v>6448</v>
+      </c>
+      <c r="AB12" s="109">
+        <v>6448</v>
+      </c>
+      <c r="AC12" s="94">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="94">
+        <f t="shared" si="11"/>
+        <v>-6661</v>
+      </c>
+      <c r="AE12" s="97">
+        <f t="shared" si="12"/>
+        <v>60.607199924804966</v>
+      </c>
+      <c r="AF12" s="98">
+        <f t="shared" si="13"/>
+        <v>4191</v>
+      </c>
+      <c r="AG12" s="104">
+        <v>13109</v>
+      </c>
+      <c r="AH12" s="104"/>
+      <c r="AI12" s="104"/>
+      <c r="AJ12" s="104"/>
+      <c r="AK12" s="104"/>
+      <c r="AL12" s="104"/>
+      <c r="AM12" s="104"/>
+      <c r="AN12" s="104"/>
+      <c r="AO12" s="104"/>
+      <c r="AP12" s="104"/>
+      <c r="AQ12" s="104"/>
+    </row>
+    <row r="13" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="26">
+        <v>5</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="71">
+        <v>27773</v>
+      </c>
+      <c r="D13" s="72">
+        <v>27773</v>
+      </c>
+      <c r="E13" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F13" s="59">
+        <v>1206</v>
+      </c>
+      <c r="G13" s="30"/>
+      <c r="H13" s="31">
+        <f>G13-'Tháng 7'!G13</f>
+        <v>-979</v>
+      </c>
+      <c r="I13" s="31">
+        <f>G13-'Thang 12'!Q14</f>
+        <v>-1008</v>
+      </c>
+      <c r="J13" s="31">
+        <f t="shared" si="1"/>
+        <v>1206</v>
+      </c>
+      <c r="K13" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="31">
+        <v>1204</v>
+      </c>
+      <c r="M13" s="30"/>
+      <c r="N13" s="53">
+        <f>M13-'Tháng 7'!M13</f>
+        <v>-972</v>
+      </c>
+      <c r="O13" s="53">
+        <f>M13-'Thang 12'!Y14</f>
+        <v>-914</v>
+      </c>
+      <c r="P13" s="53">
+        <f t="shared" si="8"/>
+        <v>1204</v>
+      </c>
+      <c r="Q13" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="31">
+        <v>1005</v>
+      </c>
+      <c r="S13" s="31"/>
+      <c r="T13" s="53">
+        <f>S13-'Tháng 7'!S13</f>
+        <v>-864</v>
+      </c>
+      <c r="U13" s="53">
+        <f>S13-'Thang 12'!AG14</f>
+        <v>-1007</v>
+      </c>
+      <c r="V13" s="53">
+        <f t="shared" si="3"/>
+        <v>1005</v>
+      </c>
+      <c r="W13" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="108" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z13" s="107">
+        <v>244851</v>
+      </c>
+      <c r="AA13" s="109">
+        <v>129490</v>
+      </c>
+      <c r="AB13" s="109">
+        <v>129490</v>
+      </c>
+      <c r="AC13" s="94">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="94">
+        <f t="shared" si="11"/>
+        <v>-153011</v>
+      </c>
+      <c r="AE13" s="97">
+        <f t="shared" si="12"/>
+        <v>52.88522407504972</v>
+      </c>
+      <c r="AF13" s="98">
+        <f t="shared" si="13"/>
+        <v>115361</v>
+      </c>
+      <c r="AG13" s="104">
+        <v>282501</v>
+      </c>
+      <c r="AH13" s="104"/>
+      <c r="AI13" s="104"/>
+      <c r="AJ13" s="104"/>
+      <c r="AK13" s="104"/>
+      <c r="AL13" s="104"/>
+      <c r="AM13" s="104"/>
+      <c r="AN13" s="104"/>
+      <c r="AO13" s="104"/>
+      <c r="AP13" s="104"/>
+      <c r="AQ13" s="104"/>
+    </row>
+    <row r="14" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="26">
+        <v>6</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="71">
+        <v>28987</v>
+      </c>
+      <c r="D14" s="72">
+        <v>28987</v>
+      </c>
+      <c r="E14" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F14" s="59">
+        <v>591</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="31">
+        <f>G14-'Tháng 7'!G14</f>
+        <v>-524</v>
+      </c>
+      <c r="I14" s="31">
+        <f>G14-'Thang 12'!Q15</f>
+        <v>-464</v>
+      </c>
+      <c r="J14" s="31">
+        <f t="shared" si="1"/>
+        <v>591</v>
+      </c>
+      <c r="K14" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="31">
+        <v>1257</v>
+      </c>
+      <c r="M14" s="30"/>
+      <c r="N14" s="53">
+        <f>M14-'Tháng 7'!M14</f>
+        <v>-1010</v>
+      </c>
+      <c r="O14" s="53">
+        <f>M14-'Thang 12'!Y15</f>
+        <v>-372</v>
+      </c>
+      <c r="P14" s="53">
+        <f t="shared" si="8"/>
+        <v>1257</v>
+      </c>
+      <c r="Q14" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="31">
+        <v>447</v>
+      </c>
+      <c r="S14" s="31"/>
+      <c r="T14" s="53">
+        <f>S14-'Tháng 7'!S14</f>
+        <v>-417</v>
+      </c>
+      <c r="U14" s="53">
+        <f>S14-'Thang 12'!AG15</f>
+        <v>-980</v>
+      </c>
+      <c r="V14" s="53">
+        <f t="shared" si="3"/>
+        <v>447</v>
+      </c>
+      <c r="W14" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X14" s="28"/>
+      <c r="Y14" s="108" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z14" s="109"/>
+      <c r="AA14" s="109">
+        <v>142</v>
+      </c>
+      <c r="AB14" s="109">
+        <v>142</v>
+      </c>
+      <c r="AC14" s="94">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="94">
+        <f t="shared" si="11"/>
+        <v>-39</v>
+      </c>
+      <c r="AE14" s="97"/>
+      <c r="AF14" s="104"/>
+      <c r="AG14" s="104">
+        <v>181</v>
+      </c>
+      <c r="AH14" s="104"/>
+      <c r="AI14" s="104"/>
+      <c r="AJ14" s="104"/>
+      <c r="AK14" s="104"/>
+      <c r="AL14" s="104"/>
+      <c r="AM14" s="104"/>
+      <c r="AN14" s="104"/>
+      <c r="AO14" s="104"/>
+      <c r="AP14" s="104"/>
+      <c r="AQ14" s="104"/>
+    </row>
+    <row r="15" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="26">
+        <v>7</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="71">
+        <v>24726</v>
+      </c>
+      <c r="D15" s="72">
+        <v>24726</v>
+      </c>
+      <c r="E15" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F15" s="59">
+        <v>541</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="31">
+        <f>G15-'Tháng 7'!G15</f>
+        <v>-536</v>
+      </c>
+      <c r="I15" s="31">
+        <f>G15-'Thang 12'!Q16</f>
+        <v>-461</v>
+      </c>
+      <c r="J15" s="31">
+        <f t="shared" si="1"/>
+        <v>541</v>
+      </c>
+      <c r="K15" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="31">
+        <v>1072</v>
+      </c>
+      <c r="M15" s="30"/>
+      <c r="N15" s="53">
+        <f>M15-'Tháng 7'!M15</f>
+        <v>-1068</v>
+      </c>
+      <c r="O15" s="53">
+        <f>M15-'Thang 12'!Y16</f>
+        <v>-383</v>
+      </c>
+      <c r="P15" s="53">
+        <f t="shared" si="8"/>
+        <v>1072</v>
+      </c>
+      <c r="Q15" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="31">
+        <v>439</v>
+      </c>
+      <c r="S15" s="31"/>
+      <c r="T15" s="53">
+        <f>S15-'Tháng 7'!S15</f>
+        <v>-441</v>
+      </c>
+      <c r="U15" s="53">
+        <f>S15-'Thang 12'!AG16</f>
+        <v>-1040</v>
+      </c>
+      <c r="V15" s="53">
+        <f t="shared" si="3"/>
+        <v>439</v>
+      </c>
+      <c r="W15" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10"/>
+      <c r="AB15" s="10"/>
+      <c r="AC15" s="10"/>
+    </row>
+    <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="141" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="141"/>
+      <c r="C16" s="18">
+        <f>SUM(C9:C15)</f>
+        <v>228291</v>
+      </c>
+      <c r="D16" s="18">
+        <f>SUM(D9:D15)</f>
+        <v>228291</v>
+      </c>
+      <c r="E16" s="32">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F16" s="60">
+        <f>SUM(F9:F15)</f>
+        <v>6581</v>
+      </c>
+      <c r="G16" s="50">
+        <f>SUM(G9:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="55">
+        <f>SUM(H9:H15)</f>
+        <v>-5678</v>
+      </c>
+      <c r="I16" s="55">
+        <f>G16-'Thang 12'!Q17</f>
+        <v>-5712</v>
+      </c>
+      <c r="J16" s="55">
+        <f>SUM(J9:J15)</f>
+        <v>6581</v>
+      </c>
+      <c r="K16" s="57">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="18">
+        <f>SUM(L9:L15)</f>
+        <v>9852</v>
+      </c>
+      <c r="M16" s="18">
+        <f>SUM(M9:M15)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="56">
+        <f>SUM(N9:N15)</f>
+        <v>-7790</v>
+      </c>
+      <c r="O16" s="56">
+        <f>M16-'Thang 12'!Y17</f>
+        <v>-4771</v>
+      </c>
+      <c r="P16" s="18">
+        <f t="shared" ref="P16" si="14">SUM(P9:P15)</f>
+        <v>9852</v>
+      </c>
+      <c r="Q16" s="69">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="55">
+        <f>SUM(R9:R15)</f>
+        <v>5515</v>
+      </c>
+      <c r="S16" s="18">
+        <f>SUM(S9:S15)</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="56">
+        <f>SUM(T9:T15)</f>
+        <v>-4929</v>
+      </c>
+      <c r="U16" s="56">
+        <f>S16-'Thang 12'!AG17</f>
+        <v>-7554</v>
+      </c>
+      <c r="V16" s="56">
+        <f>SUM(V9:V15)</f>
+        <v>5515</v>
+      </c>
+      <c r="W16" s="57">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="37"/>
+      <c r="Y16" s="36"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="25"/>
+    </row>
+    <row r="17" spans="1:25" ht="9.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="11"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+    </row>
+    <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="142" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19"/>
+      <c r="X18" s="19"/>
+      <c r="Y18" s="19"/>
+    </row>
+    <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+    </row>
+    <row r="21" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+    </row>
+    <row r="22" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+    </row>
+    <row r="23" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B23" s="5"/>
+      <c r="R23" s="31"/>
+    </row>
+    <row r="24" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B24" s="5"/>
+      <c r="R24" s="31"/>
+    </row>
+    <row r="25" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="R25" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AP7"/>
+    <mergeCell ref="AQ7:AQ8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="D20:E20"/>
+    <mergeCell ref="X7:X8"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="F7:K7"/>
+    <mergeCell ref="L7:Q7"/>
+    <mergeCell ref="R7:W7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/T07_BHXH, BHTN_2026.xlsx
+++ b/T07_BHXH, BHTN_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504" activeTab="7"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504" firstSheet="2" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Thang 12" sheetId="5" r:id="rId1"/>
@@ -18,10 +18,10 @@
     <sheet name="Thang 4" sheetId="8" r:id="rId4"/>
     <sheet name="Thang 5" sheetId="9" r:id="rId5"/>
     <sheet name="Thang 6" sheetId="10" r:id="rId6"/>
-    <sheet name="Tháng 7" sheetId="11" r:id="rId7"/>
-    <sheet name="Tháng 8" sheetId="12" r:id="rId8"/>
-    <sheet name="Tháng 9" sheetId="13" r:id="rId9"/>
-    <sheet name="Tháng 10" sheetId="14" r:id="rId10"/>
+    <sheet name="Tháng 7_2025" sheetId="11" r:id="rId7"/>
+    <sheet name="Tháng 8_2025" sheetId="12" r:id="rId8"/>
+    <sheet name="Tháng 9_2025" sheetId="13" r:id="rId9"/>
+    <sheet name="Tháng 10_2025" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
@@ -1123,6 +1123,39 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1158,39 +1191,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2617,11 +2617,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
       <c r="D1" s="20"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
@@ -2636,36 +2636,36 @@
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
-      <c r="R1" s="137" t="s">
+      <c r="R1" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="137"/>
-      <c r="Y1" s="137"/>
-      <c r="Z1" s="137"/>
-      <c r="AA1" s="137"/>
-      <c r="AB1" s="137"/>
-      <c r="AC1" s="137"/>
-      <c r="AD1" s="137"/>
-      <c r="AE1" s="137"/>
-      <c r="AF1" s="137"/>
-      <c r="AG1" s="137"/>
-      <c r="AH1" s="137"/>
-      <c r="AI1" s="137"/>
-      <c r="AJ1" s="137"/>
-      <c r="AK1" s="135"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="131"/>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="131"/>
+      <c r="Y1" s="131"/>
+      <c r="Z1" s="131"/>
+      <c r="AA1" s="131"/>
+      <c r="AB1" s="131"/>
+      <c r="AC1" s="131"/>
+      <c r="AD1" s="131"/>
+      <c r="AE1" s="131"/>
+      <c r="AF1" s="131"/>
+      <c r="AG1" s="131"/>
+      <c r="AH1" s="131"/>
+      <c r="AI1" s="131"/>
+      <c r="AJ1" s="131"/>
+      <c r="AK1" s="129"/>
       <c r="AL1" s="20"/>
     </row>
     <row r="2" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
@@ -2680,36 +2680,36 @@
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
-      <c r="R2" s="138" t="s">
+      <c r="R2" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="138"/>
-      <c r="Y2" s="138"/>
-      <c r="Z2" s="138"/>
-      <c r="AA2" s="138"/>
-      <c r="AB2" s="138"/>
-      <c r="AC2" s="138"/>
-      <c r="AD2" s="138"/>
-      <c r="AE2" s="138"/>
-      <c r="AF2" s="138"/>
-      <c r="AG2" s="138"/>
-      <c r="AH2" s="138"/>
-      <c r="AI2" s="138"/>
-      <c r="AJ2" s="138"/>
-      <c r="AK2" s="135"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="132"/>
+      <c r="Y2" s="132"/>
+      <c r="Z2" s="132"/>
+      <c r="AA2" s="132"/>
+      <c r="AB2" s="132"/>
+      <c r="AC2" s="132"/>
+      <c r="AD2" s="132"/>
+      <c r="AE2" s="132"/>
+      <c r="AF2" s="132"/>
+      <c r="AG2" s="132"/>
+      <c r="AH2" s="132"/>
+      <c r="AI2" s="132"/>
+      <c r="AJ2" s="132"/>
+      <c r="AK2" s="129"/>
       <c r="AL2" s="20"/>
     </row>
     <row r="3" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
@@ -2787,87 +2787,87 @@
       <c r="AL4" s="20"/>
     </row>
     <row r="5" spans="1:40" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="128" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="134"/>
-      <c r="T5" s="134"/>
-      <c r="U5" s="134"/>
-      <c r="V5" s="134"/>
-      <c r="W5" s="134"/>
-      <c r="X5" s="134"/>
-      <c r="Y5" s="134"/>
-      <c r="Z5" s="134"/>
-      <c r="AA5" s="134"/>
-      <c r="AB5" s="134"/>
-      <c r="AC5" s="134"/>
-      <c r="AD5" s="135"/>
-      <c r="AE5" s="135"/>
-      <c r="AF5" s="135"/>
-      <c r="AG5" s="135"/>
-      <c r="AH5" s="135"/>
-      <c r="AI5" s="135"/>
-      <c r="AJ5" s="135"/>
-      <c r="AK5" s="135"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="128"/>
+      <c r="S5" s="128"/>
+      <c r="T5" s="128"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="128"/>
+      <c r="W5" s="128"/>
+      <c r="X5" s="128"/>
+      <c r="Y5" s="128"/>
+      <c r="Z5" s="128"/>
+      <c r="AA5" s="128"/>
+      <c r="AB5" s="128"/>
+      <c r="AC5" s="128"/>
+      <c r="AD5" s="129"/>
+      <c r="AE5" s="129"/>
+      <c r="AF5" s="129"/>
+      <c r="AG5" s="129"/>
+      <c r="AH5" s="129"/>
+      <c r="AI5" s="129"/>
+      <c r="AJ5" s="129"/>
+      <c r="AK5" s="129"/>
       <c r="AL5" s="20"/>
     </row>
     <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="122"/>
-      <c r="O6" s="122"/>
-      <c r="P6" s="122"/>
-      <c r="Q6" s="122"/>
-      <c r="R6" s="122"/>
-      <c r="S6" s="122"/>
-      <c r="T6" s="122"/>
-      <c r="U6" s="122"/>
-      <c r="V6" s="122"/>
-      <c r="W6" s="122"/>
-      <c r="X6" s="122"/>
-      <c r="Y6" s="122"/>
-      <c r="Z6" s="122"/>
-      <c r="AA6" s="122"/>
-      <c r="AB6" s="122"/>
-      <c r="AC6" s="122"/>
-      <c r="AD6" s="123"/>
-      <c r="AE6" s="123"/>
-      <c r="AF6" s="123"/>
-      <c r="AG6" s="123"/>
-      <c r="AH6" s="123"/>
-      <c r="AI6" s="123"/>
-      <c r="AJ6" s="123"/>
-      <c r="AK6" s="123"/>
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="133"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
+      <c r="N6" s="133"/>
+      <c r="O6" s="133"/>
+      <c r="P6" s="133"/>
+      <c r="Q6" s="133"/>
+      <c r="R6" s="133"/>
+      <c r="S6" s="133"/>
+      <c r="T6" s="133"/>
+      <c r="U6" s="133"/>
+      <c r="V6" s="133"/>
+      <c r="W6" s="133"/>
+      <c r="X6" s="133"/>
+      <c r="Y6" s="133"/>
+      <c r="Z6" s="133"/>
+      <c r="AA6" s="133"/>
+      <c r="AB6" s="133"/>
+      <c r="AC6" s="133"/>
+      <c r="AD6" s="134"/>
+      <c r="AE6" s="134"/>
+      <c r="AF6" s="134"/>
+      <c r="AG6" s="134"/>
+      <c r="AH6" s="134"/>
+      <c r="AI6" s="134"/>
+      <c r="AJ6" s="134"/>
+      <c r="AK6" s="134"/>
       <c r="AL6" s="24"/>
     </row>
     <row r="7" spans="1:40" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2912,64 +2912,64 @@
       <c r="AL7" s="7"/>
     </row>
     <row r="8" spans="1:40" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="126" t="s">
+      <c r="B8" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="124" t="s">
+      <c r="C8" s="135" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="128" t="s">
+      <c r="D8" s="136"/>
+      <c r="E8" s="136"/>
+      <c r="F8" s="136"/>
+      <c r="G8" s="136"/>
+      <c r="H8" s="139" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="129"/>
-      <c r="J8" s="129"/>
-      <c r="K8" s="129"/>
-      <c r="L8" s="129"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140"/>
       <c r="M8" s="51"/>
-      <c r="N8" s="124" t="s">
+      <c r="N8" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="125"/>
-      <c r="P8" s="125"/>
-      <c r="Q8" s="125"/>
-      <c r="R8" s="125"/>
-      <c r="S8" s="125"/>
-      <c r="T8" s="130"/>
+      <c r="O8" s="136"/>
+      <c r="P8" s="136"/>
+      <c r="Q8" s="136"/>
+      <c r="R8" s="136"/>
+      <c r="S8" s="136"/>
+      <c r="T8" s="141"/>
       <c r="U8" s="52"/>
-      <c r="V8" s="124" t="s">
+      <c r="V8" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="W8" s="125"/>
-      <c r="X8" s="125"/>
-      <c r="Y8" s="125"/>
-      <c r="Z8" s="125"/>
-      <c r="AA8" s="125"/>
-      <c r="AB8" s="130"/>
+      <c r="W8" s="136"/>
+      <c r="X8" s="136"/>
+      <c r="Y8" s="136"/>
+      <c r="Z8" s="136"/>
+      <c r="AA8" s="136"/>
+      <c r="AB8" s="141"/>
       <c r="AC8" s="58"/>
-      <c r="AD8" s="131" t="s">
+      <c r="AD8" s="142" t="s">
         <v>11</v>
       </c>
-      <c r="AE8" s="132"/>
-      <c r="AF8" s="132"/>
-      <c r="AG8" s="132"/>
-      <c r="AH8" s="132"/>
-      <c r="AI8" s="132"/>
-      <c r="AJ8" s="133"/>
-      <c r="AK8" s="143" t="s">
+      <c r="AE8" s="143"/>
+      <c r="AF8" s="143"/>
+      <c r="AG8" s="143"/>
+      <c r="AH8" s="143"/>
+      <c r="AI8" s="143"/>
+      <c r="AJ8" s="144"/>
+      <c r="AK8" s="126" t="s">
         <v>8</v>
       </c>
       <c r="AL8" s="34"/>
     </row>
     <row r="9" spans="1:40" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="127"/>
-      <c r="B9" s="127"/>
+      <c r="A9" s="138"/>
+      <c r="B9" s="138"/>
       <c r="C9" s="42" t="s">
         <v>27</v>
       </c>
@@ -3072,7 +3072,7 @@
       <c r="AJ9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="AK9" s="144"/>
+      <c r="AK9" s="127"/>
       <c r="AL9" s="34"/>
       <c r="AM9" s="34"/>
     </row>
@@ -3727,10 +3727,10 @@
       <c r="AN16" s="10"/>
     </row>
     <row r="17" spans="1:40" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="141" t="s">
+      <c r="A17" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="141"/>
+      <c r="B17" s="124"/>
       <c r="C17" s="18">
         <f>SUM(C10:C16)</f>
         <v>227321</v>
@@ -3907,22 +3907,22 @@
     </row>
     <row r="19" spans="1:40" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="142" t="s">
+      <c r="B19" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="142"/>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="142"/>
-      <c r="G19" s="142"/>
-      <c r="H19" s="142"/>
-      <c r="I19" s="142"/>
-      <c r="J19" s="142"/>
-      <c r="K19" s="142"/>
-      <c r="L19" s="142"/>
-      <c r="M19" s="142"/>
-      <c r="N19" s="142"/>
-      <c r="O19" s="142"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="125"/>
+      <c r="K19" s="125"/>
+      <c r="L19" s="125"/>
+      <c r="M19" s="125"/>
+      <c r="N19" s="125"/>
+      <c r="O19" s="125"/>
       <c r="P19" s="49"/>
       <c r="Q19" s="49"/>
       <c r="R19" s="19"/>
@@ -3948,23 +3948,23 @@
       <c r="AL19" s="19"/>
     </row>
     <row r="20" spans="1:40" ht="18" x14ac:dyDescent="0.35">
-      <c r="B20" s="139"/>
-      <c r="C20" s="139"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="139"/>
-      <c r="I20" s="139"/>
-      <c r="J20" s="139"/>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="139"/>
-      <c r="N20" s="139"/>
-      <c r="O20" s="139"/>
-      <c r="P20" s="139"/>
-      <c r="Q20" s="139"/>
-      <c r="R20" s="139"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="122"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="122"/>
+      <c r="H20" s="122"/>
+      <c r="I20" s="122"/>
+      <c r="J20" s="122"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="122"/>
+      <c r="N20" s="122"/>
+      <c r="O20" s="122"/>
+      <c r="P20" s="122"/>
+      <c r="Q20" s="122"/>
+      <c r="R20" s="122"/>
       <c r="S20" s="23"/>
       <c r="T20" s="23"/>
       <c r="U20" s="23"/>
@@ -3990,10 +3990,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="140"/>
-      <c r="G21" s="140"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="123"/>
       <c r="H21" s="21"/>
       <c r="I21" s="21"/>
       <c r="J21" s="21"/>
@@ -4117,17 +4117,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B20:R20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="B19:O19"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="R1:AK1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="R2:AK2"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A6:AK6"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A8:A9"/>
@@ -4136,6 +4125,17 @@
     <mergeCell ref="N8:T8"/>
     <mergeCell ref="V8:AB8"/>
     <mergeCell ref="AD8:AJ8"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="R1:AK1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="R2:AK2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="B20:R20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="B19:O19"/>
+    <mergeCell ref="AK8:AK9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4171,67 +4171,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
       <c r="E1" s="118"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="131"/>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="129"/>
       <c r="Y1" s="118"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
       <c r="E2" s="118"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="129"/>
       <c r="Y2" s="118"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
       <c r="D3" s="118"/>
       <c r="E3" s="118"/>
       <c r="F3" s="17"/>
@@ -4283,32 +4283,32 @@
       <c r="Y4" s="118"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="128" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="128"/>
+      <c r="S5" s="129"/>
+      <c r="T5" s="129"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="129"/>
+      <c r="W5" s="129"/>
+      <c r="X5" s="129"/>
       <c r="Y5" s="118"/>
     </row>
     <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4340,45 +4340,45 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="136"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="141"/>
+      <c r="R7" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="136"/>
+      <c r="T7" s="136"/>
+      <c r="U7" s="136"/>
+      <c r="V7" s="136"/>
+      <c r="W7" s="141"/>
+      <c r="X7" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="128" t="s">
+      <c r="Y7" s="139" t="s">
         <v>77</v>
       </c>
       <c r="Z7" s="152" t="s">
@@ -4407,8 +4407,8 @@
       <c r="AQ7" s="150"/>
     </row>
     <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
+      <c r="A8" s="138"/>
+      <c r="B8" s="138"/>
       <c r="C8" s="116" t="s">
         <v>27</v>
       </c>
@@ -4472,8 +4472,8 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
-      <c r="Y8" s="128"/>
+      <c r="X8" s="127"/>
+      <c r="Y8" s="139"/>
       <c r="Z8" s="94" t="s">
         <v>63</v>
       </c>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G9" s="30"/>
       <c r="H9" s="31">
-        <f>G9-'Tháng 7'!G9</f>
+        <f>G9-'Tháng 7_2025'!G9</f>
         <v>-1528</v>
       </c>
       <c r="I9" s="31">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="M9" s="30"/>
       <c r="N9" s="53">
-        <f>M9-'Tháng 7'!M9</f>
+        <f>M9-'Tháng 7_2025'!M9</f>
         <v>-1624</v>
       </c>
       <c r="O9" s="53">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="S9" s="31"/>
       <c r="T9" s="53">
-        <f>S9-'Tháng 7'!S9</f>
+        <f>S9-'Tháng 7_2025'!S9</f>
         <v>-1392</v>
       </c>
       <c r="U9" s="53">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="G10" s="30"/>
       <c r="H10" s="31">
-        <f>G10-'Tháng 7'!G10</f>
+        <f>G10-'Tháng 7_2025'!G10</f>
         <v>-496</v>
       </c>
       <c r="I10" s="31">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="M10" s="30"/>
       <c r="N10" s="53">
-        <f>M10-'Tháng 7'!M10</f>
+        <f>M10-'Tháng 7_2025'!M10</f>
         <v>-720</v>
       </c>
       <c r="O10" s="53">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="S10" s="31"/>
       <c r="T10" s="53">
-        <f>S10-'Tháng 7'!S10</f>
+        <f>S10-'Tháng 7_2025'!S10</f>
         <v>-390</v>
       </c>
       <c r="U10" s="53">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="31">
-        <f>G11-'Tháng 7'!G11</f>
+        <f>G11-'Tháng 7_2025'!G11</f>
         <v>-519</v>
       </c>
       <c r="I11" s="31">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="M11" s="30"/>
       <c r="N11" s="53">
-        <f>M11-'Tháng 7'!M11</f>
+        <f>M11-'Tháng 7_2025'!M11</f>
         <v>-770</v>
       </c>
       <c r="O11" s="53">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="S11" s="31"/>
       <c r="T11" s="53">
-        <f>S11-'Tháng 7'!S11</f>
+        <f>S11-'Tháng 7_2025'!S11</f>
         <v>-434</v>
       </c>
       <c r="U11" s="53">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31">
-        <f>G12-'Tháng 7'!G12</f>
+        <f>G12-'Tháng 7_2025'!G12</f>
         <v>-1096</v>
       </c>
       <c r="I12" s="31">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="M12" s="30"/>
       <c r="N12" s="53">
-        <f>M12-'Tháng 7'!M12</f>
+        <f>M12-'Tháng 7_2025'!M12</f>
         <v>-1626</v>
       </c>
       <c r="O12" s="53">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="S12" s="31"/>
       <c r="T12" s="53">
-        <f>S12-'Tháng 7'!S12</f>
+        <f>S12-'Tháng 7_2025'!S12</f>
         <v>-991</v>
       </c>
       <c r="U12" s="53">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="G13" s="30"/>
       <c r="H13" s="31">
-        <f>G13-'Tháng 7'!G13</f>
+        <f>G13-'Tháng 7_2025'!G13</f>
         <v>-979</v>
       </c>
       <c r="I13" s="31">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="M13" s="30"/>
       <c r="N13" s="53">
-        <f>M13-'Tháng 7'!M13</f>
+        <f>M13-'Tháng 7_2025'!M13</f>
         <v>-972</v>
       </c>
       <c r="O13" s="53">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="S13" s="31"/>
       <c r="T13" s="53">
-        <f>S13-'Tháng 7'!S13</f>
+        <f>S13-'Tháng 7_2025'!S13</f>
         <v>-864</v>
       </c>
       <c r="U13" s="53">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="G14" s="30"/>
       <c r="H14" s="31">
-        <f>G14-'Tháng 7'!G14</f>
+        <f>G14-'Tháng 7_2025'!G14</f>
         <v>-524</v>
       </c>
       <c r="I14" s="31">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="M14" s="30"/>
       <c r="N14" s="53">
-        <f>M14-'Tháng 7'!M14</f>
+        <f>M14-'Tháng 7_2025'!M14</f>
         <v>-1010</v>
       </c>
       <c r="O14" s="53">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="S14" s="31"/>
       <c r="T14" s="53">
-        <f>S14-'Tháng 7'!S14</f>
+        <f>S14-'Tháng 7_2025'!S14</f>
         <v>-417</v>
       </c>
       <c r="U14" s="53">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="G15" s="30"/>
       <c r="H15" s="31">
-        <f>G15-'Tháng 7'!G15</f>
+        <f>G15-'Tháng 7_2025'!G15</f>
         <v>-536</v>
       </c>
       <c r="I15" s="31">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="M15" s="30"/>
       <c r="N15" s="53">
-        <f>M15-'Tháng 7'!M15</f>
+        <f>M15-'Tháng 7_2025'!M15</f>
         <v>-1068</v>
       </c>
       <c r="O15" s="53">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="S15" s="31"/>
       <c r="T15" s="53">
-        <f>S15-'Tháng 7'!S15</f>
+        <f>S15-'Tháng 7_2025'!S15</f>
         <v>-441</v>
       </c>
       <c r="U15" s="53">
@@ -5345,10 +5345,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="124"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -5467,13 +5467,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -5495,12 +5495,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
       <c r="H19" s="119"/>
       <c r="I19" s="119"/>
       <c r="J19" s="119"/>
@@ -5523,8 +5523,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
       <c r="F20" s="120"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -5608,17 +5608,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AH7:AP7"/>
-    <mergeCell ref="AQ7:AQ8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:G19"/>
@@ -5630,6 +5619,17 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AP7"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5669,12 +5669,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
@@ -5683,31 +5683,31 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
-      <c r="M1" s="137" t="s">
+      <c r="M1" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="137"/>
-      <c r="Y1" s="137"/>
-      <c r="Z1" s="135"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="131"/>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="131"/>
+      <c r="Y1" s="131"/>
+      <c r="Z1" s="129"/>
       <c r="AA1" s="20"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
@@ -5716,28 +5716,28 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="138" t="s">
+      <c r="M2" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="138"/>
-      <c r="Y2" s="138"/>
-      <c r="Z2" s="135"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="132"/>
+      <c r="Y2" s="132"/>
+      <c r="Z2" s="129"/>
       <c r="AA2" s="20"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
@@ -5793,34 +5793,34 @@
       <c r="AA4" s="20"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="134"/>
-      <c r="T5" s="134"/>
-      <c r="U5" s="134"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
-      <c r="Y5" s="135"/>
-      <c r="Z5" s="135"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="128"/>
+      <c r="S5" s="128"/>
+      <c r="T5" s="128"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="129"/>
+      <c r="W5" s="129"/>
+      <c r="X5" s="129"/>
+      <c r="Y5" s="129"/>
+      <c r="Z5" s="129"/>
       <c r="AA5" s="20"/>
     </row>
     <row r="6" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5883,17 +5883,17 @@
       <c r="AA7" s="7"/>
     </row>
     <row r="8" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="126" t="s">
+      <c r="B8" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="129" t="s">
+      <c r="C8" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="129"/>
-      <c r="E8" s="129"/>
+      <c r="D8" s="140"/>
+      <c r="E8" s="140"/>
       <c r="F8" s="51"/>
       <c r="G8" s="145" t="s">
         <v>32</v>
@@ -5901,35 +5901,35 @@
       <c r="H8" s="146"/>
       <c r="I8" s="146"/>
       <c r="J8" s="147"/>
-      <c r="K8" s="124" t="s">
+      <c r="K8" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="125"/>
-      <c r="M8" s="125"/>
-      <c r="N8" s="125"/>
-      <c r="O8" s="130"/>
-      <c r="P8" s="124" t="s">
+      <c r="L8" s="136"/>
+      <c r="M8" s="136"/>
+      <c r="N8" s="136"/>
+      <c r="O8" s="141"/>
+      <c r="P8" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="Q8" s="125"/>
-      <c r="R8" s="125"/>
-      <c r="S8" s="125"/>
-      <c r="T8" s="130"/>
-      <c r="U8" s="124" t="s">
+      <c r="Q8" s="136"/>
+      <c r="R8" s="136"/>
+      <c r="S8" s="136"/>
+      <c r="T8" s="141"/>
+      <c r="U8" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V8" s="125"/>
-      <c r="W8" s="125"/>
-      <c r="X8" s="125"/>
-      <c r="Y8" s="130"/>
-      <c r="Z8" s="143" t="s">
+      <c r="V8" s="136"/>
+      <c r="W8" s="136"/>
+      <c r="X8" s="136"/>
+      <c r="Y8" s="141"/>
+      <c r="Z8" s="126" t="s">
         <v>8</v>
       </c>
       <c r="AA8" s="34"/>
     </row>
     <row r="9" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="127"/>
-      <c r="B9" s="127"/>
+      <c r="A9" s="138"/>
+      <c r="B9" s="138"/>
       <c r="C9" s="42" t="s">
         <v>27</v>
       </c>
@@ -5997,7 +5997,7 @@
       <c r="Y9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="Z9" s="144"/>
+      <c r="Z9" s="127"/>
       <c r="AA9" s="34"/>
       <c r="AB9" s="34"/>
     </row>
@@ -6485,10 +6485,10 @@
       <c r="AC16" s="10"/>
     </row>
     <row r="17" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="141" t="s">
+      <c r="A17" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="141"/>
+      <c r="B17" s="124"/>
       <c r="C17" s="18">
         <f>SUM(C10:C16)</f>
         <v>227321</v>
@@ -6607,18 +6607,18 @@
     </row>
     <row r="19" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="142" t="s">
+      <c r="B19" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="142"/>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="142"/>
-      <c r="G19" s="142"/>
-      <c r="H19" s="142"/>
-      <c r="I19" s="142"/>
-      <c r="J19" s="142"/>
-      <c r="K19" s="142"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="125"/>
+      <c r="K19" s="125"/>
       <c r="L19" s="49"/>
       <c r="M19" s="19"/>
       <c r="N19" s="19"/>
@@ -6637,18 +6637,18 @@
       <c r="AA19" s="19"/>
     </row>
     <row r="20" spans="1:29" ht="18" x14ac:dyDescent="0.35">
-      <c r="B20" s="139"/>
-      <c r="C20" s="139"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="139"/>
-      <c r="I20" s="139"/>
-      <c r="J20" s="139"/>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="139"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="122"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="122"/>
+      <c r="H20" s="122"/>
+      <c r="I20" s="122"/>
+      <c r="J20" s="122"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="122"/>
       <c r="N20" s="23"/>
       <c r="O20" s="23"/>
       <c r="P20" s="23"/>
@@ -6667,8 +6667,8 @@
         <v>4</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
@@ -6755,12 +6755,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="M1:Z1"/>
-    <mergeCell ref="M2:Z2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A5:Z5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="A6:Z6"/>
@@ -6774,6 +6768,12 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="B19:K19"/>
     <mergeCell ref="B20:M20"/>
+    <mergeCell ref="M1:Z1"/>
+    <mergeCell ref="M2:Z2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A5:Z5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6815,12 +6815,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
@@ -6831,41 +6831,41 @@
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
-      <c r="O1" s="137" t="s">
+      <c r="O1" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="137"/>
-      <c r="Y1" s="137"/>
-      <c r="Z1" s="137"/>
-      <c r="AA1" s="137"/>
-      <c r="AB1" s="137"/>
-      <c r="AC1" s="137"/>
-      <c r="AD1" s="137"/>
-      <c r="AE1" s="137"/>
-      <c r="AF1" s="137"/>
-      <c r="AG1" s="137"/>
-      <c r="AH1" s="137"/>
-      <c r="AI1" s="137"/>
-      <c r="AJ1" s="137"/>
-      <c r="AK1" s="137"/>
-      <c r="AL1" s="135"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="131"/>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="131"/>
+      <c r="Y1" s="131"/>
+      <c r="Z1" s="131"/>
+      <c r="AA1" s="131"/>
+      <c r="AB1" s="131"/>
+      <c r="AC1" s="131"/>
+      <c r="AD1" s="131"/>
+      <c r="AE1" s="131"/>
+      <c r="AF1" s="131"/>
+      <c r="AG1" s="131"/>
+      <c r="AH1" s="131"/>
+      <c r="AI1" s="131"/>
+      <c r="AJ1" s="131"/>
+      <c r="AK1" s="131"/>
+      <c r="AL1" s="129"/>
       <c r="AM1" s="20"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
@@ -6876,38 +6876,38 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
-      <c r="O2" s="138" t="s">
+      <c r="O2" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="138"/>
-      <c r="Y2" s="138"/>
-      <c r="Z2" s="138"/>
-      <c r="AA2" s="138"/>
-      <c r="AB2" s="138"/>
-      <c r="AC2" s="138"/>
-      <c r="AD2" s="138"/>
-      <c r="AE2" s="138"/>
-      <c r="AF2" s="138"/>
-      <c r="AG2" s="138"/>
-      <c r="AH2" s="138"/>
-      <c r="AI2" s="138"/>
-      <c r="AJ2" s="138"/>
-      <c r="AK2" s="138"/>
-      <c r="AL2" s="135"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="132"/>
+      <c r="Y2" s="132"/>
+      <c r="Z2" s="132"/>
+      <c r="AA2" s="132"/>
+      <c r="AB2" s="132"/>
+      <c r="AC2" s="132"/>
+      <c r="AD2" s="132"/>
+      <c r="AE2" s="132"/>
+      <c r="AF2" s="132"/>
+      <c r="AG2" s="132"/>
+      <c r="AH2" s="132"/>
+      <c r="AI2" s="132"/>
+      <c r="AJ2" s="132"/>
+      <c r="AK2" s="132"/>
+      <c r="AL2" s="129"/>
       <c r="AM2" s="20"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
@@ -6987,46 +6987,46 @@
       <c r="AM4" s="20"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="134"/>
-      <c r="T5" s="134"/>
-      <c r="U5" s="134"/>
-      <c r="V5" s="134"/>
-      <c r="W5" s="134"/>
-      <c r="X5" s="134"/>
-      <c r="Y5" s="134"/>
-      <c r="Z5" s="134"/>
-      <c r="AA5" s="134"/>
-      <c r="AB5" s="134"/>
-      <c r="AC5" s="134"/>
-      <c r="AD5" s="134"/>
-      <c r="AE5" s="134"/>
-      <c r="AF5" s="135"/>
-      <c r="AG5" s="135"/>
-      <c r="AH5" s="135"/>
-      <c r="AI5" s="135"/>
-      <c r="AJ5" s="135"/>
-      <c r="AK5" s="135"/>
-      <c r="AL5" s="135"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="128"/>
+      <c r="S5" s="128"/>
+      <c r="T5" s="128"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="128"/>
+      <c r="W5" s="128"/>
+      <c r="X5" s="128"/>
+      <c r="Y5" s="128"/>
+      <c r="Z5" s="128"/>
+      <c r="AA5" s="128"/>
+      <c r="AB5" s="128"/>
+      <c r="AC5" s="128"/>
+      <c r="AD5" s="128"/>
+      <c r="AE5" s="128"/>
+      <c r="AF5" s="129"/>
+      <c r="AG5" s="129"/>
+      <c r="AH5" s="129"/>
+      <c r="AI5" s="129"/>
+      <c r="AJ5" s="129"/>
+      <c r="AK5" s="129"/>
+      <c r="AL5" s="129"/>
       <c r="AM5" s="20"/>
     </row>
     <row r="6" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7113,17 +7113,17 @@
       <c r="AM7" s="7"/>
     </row>
     <row r="8" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="126" t="s">
+      <c r="B8" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="129" t="s">
+      <c r="C8" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="129"/>
-      <c r="E8" s="129"/>
+      <c r="D8" s="140"/>
+      <c r="E8" s="140"/>
       <c r="F8" s="51"/>
       <c r="G8" s="145" t="s">
         <v>32</v>
@@ -7131,47 +7131,47 @@
       <c r="H8" s="146"/>
       <c r="I8" s="146"/>
       <c r="J8" s="147"/>
-      <c r="K8" s="124" t="s">
+      <c r="K8" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="125"/>
-      <c r="M8" s="125"/>
-      <c r="N8" s="125"/>
-      <c r="O8" s="125"/>
-      <c r="P8" s="125"/>
-      <c r="Q8" s="125"/>
-      <c r="R8" s="125"/>
-      <c r="S8" s="130"/>
-      <c r="T8" s="124" t="s">
+      <c r="L8" s="136"/>
+      <c r="M8" s="136"/>
+      <c r="N8" s="136"/>
+      <c r="O8" s="136"/>
+      <c r="P8" s="136"/>
+      <c r="Q8" s="136"/>
+      <c r="R8" s="136"/>
+      <c r="S8" s="141"/>
+      <c r="T8" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="U8" s="125"/>
-      <c r="V8" s="125"/>
-      <c r="W8" s="125"/>
-      <c r="X8" s="125"/>
-      <c r="Y8" s="125"/>
-      <c r="Z8" s="125"/>
-      <c r="AA8" s="125"/>
-      <c r="AB8" s="130"/>
-      <c r="AC8" s="124" t="s">
+      <c r="U8" s="136"/>
+      <c r="V8" s="136"/>
+      <c r="W8" s="136"/>
+      <c r="X8" s="136"/>
+      <c r="Y8" s="136"/>
+      <c r="Z8" s="136"/>
+      <c r="AA8" s="136"/>
+      <c r="AB8" s="141"/>
+      <c r="AC8" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="AD8" s="125"/>
-      <c r="AE8" s="125"/>
-      <c r="AF8" s="125"/>
-      <c r="AG8" s="125"/>
-      <c r="AH8" s="125"/>
-      <c r="AI8" s="125"/>
-      <c r="AJ8" s="125"/>
-      <c r="AK8" s="130"/>
-      <c r="AL8" s="143" t="s">
+      <c r="AD8" s="136"/>
+      <c r="AE8" s="136"/>
+      <c r="AF8" s="136"/>
+      <c r="AG8" s="136"/>
+      <c r="AH8" s="136"/>
+      <c r="AI8" s="136"/>
+      <c r="AJ8" s="136"/>
+      <c r="AK8" s="141"/>
+      <c r="AL8" s="126" t="s">
         <v>8</v>
       </c>
       <c r="AM8" s="34"/>
     </row>
     <row r="9" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="127"/>
-      <c r="B9" s="127"/>
+      <c r="A9" s="138"/>
+      <c r="B9" s="138"/>
       <c r="C9" s="42" t="s">
         <v>27</v>
       </c>
@@ -7275,7 +7275,7 @@
       <c r="AK9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="AL9" s="144"/>
+      <c r="AL9" s="127"/>
       <c r="AM9" s="34"/>
       <c r="AN9" s="34"/>
     </row>
@@ -8064,10 +8064,10 @@
       <c r="AQ16" s="10"/>
     </row>
     <row r="17" spans="1:41" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="141" t="s">
+      <c r="A17" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="141"/>
+      <c r="B17" s="124"/>
       <c r="C17" s="18">
         <f>SUM(C10:C16)</f>
         <v>227321</v>
@@ -8246,18 +8246,18 @@
     </row>
     <row r="19" spans="1:41" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="142" t="s">
+      <c r="B19" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="142"/>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="142"/>
-      <c r="G19" s="142"/>
-      <c r="H19" s="142"/>
-      <c r="I19" s="142"/>
-      <c r="J19" s="142"/>
-      <c r="K19" s="142"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="125"/>
+      <c r="K19" s="125"/>
       <c r="L19" s="49"/>
       <c r="M19" s="49"/>
       <c r="N19" s="49"/>
@@ -8288,20 +8288,20 @@
       <c r="AM19" s="19"/>
     </row>
     <row r="20" spans="1:41" ht="18" x14ac:dyDescent="0.35">
-      <c r="B20" s="139"/>
-      <c r="C20" s="139"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="139"/>
-      <c r="I20" s="139"/>
-      <c r="J20" s="139"/>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="139"/>
-      <c r="N20" s="139"/>
-      <c r="O20" s="139"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="122"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="122"/>
+      <c r="H20" s="122"/>
+      <c r="I20" s="122"/>
+      <c r="J20" s="122"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="122"/>
+      <c r="N20" s="122"/>
+      <c r="O20" s="122"/>
       <c r="P20" s="23"/>
       <c r="Q20" s="23"/>
       <c r="R20" s="23"/>
@@ -8330,8 +8330,8 @@
         <v>4</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
@@ -8454,6 +8454,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A5:AL5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="O1:AL1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="O2:AL2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="B19:K19"/>
     <mergeCell ref="B20:O20"/>
@@ -8467,12 +8473,6 @@
     <mergeCell ref="T8:AB8"/>
     <mergeCell ref="AC8:AK8"/>
     <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="A5:AL5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="O1:AL1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="O2:AL2"/>
-    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -8505,67 +8505,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
       <c r="E1" s="63"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="131"/>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="129"/>
       <c r="Y1" s="63"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
       <c r="E2" s="63"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="129"/>
       <c r="Y2" s="63"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
       <c r="D3" s="63"/>
       <c r="E3" s="63"/>
       <c r="F3" s="17"/>
@@ -8617,32 +8617,32 @@
       <c r="Y4" s="63"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="128" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="128"/>
+      <c r="S5" s="129"/>
+      <c r="T5" s="129"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="129"/>
+      <c r="W5" s="129"/>
+      <c r="X5" s="129"/>
       <c r="Y5" s="63"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8674,49 +8674,49 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="136"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="141"/>
+      <c r="R7" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="136"/>
+      <c r="T7" s="136"/>
+      <c r="U7" s="136"/>
+      <c r="V7" s="136"/>
+      <c r="W7" s="141"/>
+      <c r="X7" s="126" t="s">
         <v>8</v>
       </c>
       <c r="Y7" s="34"/>
     </row>
     <row r="8" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
+      <c r="A8" s="138"/>
+      <c r="B8" s="138"/>
       <c r="C8" s="68" t="s">
         <v>27</v>
       </c>
@@ -8780,7 +8780,7 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
+      <c r="X8" s="127"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
@@ -9430,10 +9430,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="124"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -9552,13 +9552,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
       <c r="G18" s="64"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -9580,12 +9580,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
       <c r="H19" s="65"/>
       <c r="I19" s="65"/>
       <c r="J19" s="65"/>
@@ -9608,8 +9608,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
       <c r="F20" s="66"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -9690,6 +9690,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
     <mergeCell ref="X7:X8"/>
@@ -9699,14 +9707,6 @@
     <mergeCell ref="H2:X2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -9739,67 +9739,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
       <c r="E1" s="75"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="131"/>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="129"/>
       <c r="Y1" s="75"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
       <c r="E2" s="75"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="129"/>
       <c r="Y2" s="75"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
       <c r="D3" s="75"/>
       <c r="E3" s="75"/>
       <c r="F3" s="17"/>
@@ -9851,32 +9851,32 @@
       <c r="Y4" s="75"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="128" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="128"/>
+      <c r="S5" s="129"/>
+      <c r="T5" s="129"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="129"/>
+      <c r="W5" s="129"/>
+      <c r="X5" s="129"/>
       <c r="Y5" s="75"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9908,49 +9908,49 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="136"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="141"/>
+      <c r="R7" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="136"/>
+      <c r="T7" s="136"/>
+      <c r="U7" s="136"/>
+      <c r="V7" s="136"/>
+      <c r="W7" s="141"/>
+      <c r="X7" s="126" t="s">
         <v>8</v>
       </c>
       <c r="Y7" s="34"/>
     </row>
     <row r="8" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
+      <c r="A8" s="138"/>
+      <c r="B8" s="138"/>
       <c r="C8" s="73" t="s">
         <v>27</v>
       </c>
@@ -10014,7 +10014,7 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
+      <c r="X8" s="127"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
@@ -10641,10 +10641,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="124"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -10763,13 +10763,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
       <c r="G18" s="78"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -10791,12 +10791,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
       <c r="H19" s="76"/>
       <c r="I19" s="76"/>
       <c r="J19" s="76"/>
@@ -10819,8 +10819,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
       <c r="F20" s="77"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -10901,12 +10901,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="X7:X8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
@@ -10918,6 +10912,12 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -10950,67 +10950,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
       <c r="E1" s="85"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="131"/>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="129"/>
       <c r="Y1" s="85"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
       <c r="E2" s="85"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="129"/>
       <c r="Y2" s="85"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="17"/>
@@ -11062,32 +11062,32 @@
       <c r="Y4" s="85"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="128"/>
+      <c r="S5" s="129"/>
+      <c r="T5" s="129"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="129"/>
+      <c r="W5" s="129"/>
+      <c r="X5" s="129"/>
       <c r="Y5" s="85"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11119,49 +11119,49 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="136"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="141"/>
+      <c r="R7" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="136"/>
+      <c r="T7" s="136"/>
+      <c r="U7" s="136"/>
+      <c r="V7" s="136"/>
+      <c r="W7" s="141"/>
+      <c r="X7" s="126" t="s">
         <v>8</v>
       </c>
       <c r="Y7" s="34"/>
     </row>
     <row r="8" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
+      <c r="A8" s="138"/>
+      <c r="B8" s="138"/>
       <c r="C8" s="86" t="s">
         <v>27</v>
       </c>
@@ -11225,7 +11225,7 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
+      <c r="X8" s="127"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
@@ -11881,10 +11881,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="124"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -12003,13 +12003,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -12034,12 +12034,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
       <c r="H19" s="81"/>
       <c r="I19" s="81"/>
       <c r="J19" s="81"/>
@@ -12062,8 +12062,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
       <c r="F20" s="82"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -12144,6 +12144,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="X7:X8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
@@ -12155,12 +12161,6 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -12196,67 +12196,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
       <c r="E1" s="92"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="131"/>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="129"/>
       <c r="Y1" s="92"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
       <c r="E2" s="92"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="129"/>
       <c r="Y2" s="92"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
       <c r="D3" s="92"/>
       <c r="E3" s="92"/>
       <c r="F3" s="17"/>
@@ -12308,32 +12308,32 @@
       <c r="Y4" s="92"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="128" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="128"/>
+      <c r="S5" s="129"/>
+      <c r="T5" s="129"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="129"/>
+      <c r="W5" s="129"/>
+      <c r="X5" s="129"/>
       <c r="Y5" s="92"/>
     </row>
     <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12365,45 +12365,45 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="136"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="141"/>
+      <c r="R7" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="136"/>
+      <c r="T7" s="136"/>
+      <c r="U7" s="136"/>
+      <c r="V7" s="136"/>
+      <c r="W7" s="141"/>
+      <c r="X7" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="128" t="s">
+      <c r="Y7" s="139" t="s">
         <v>77</v>
       </c>
       <c r="Z7" s="152" t="s">
@@ -12432,8 +12432,8 @@
       <c r="AQ7" s="150"/>
     </row>
     <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
+      <c r="A8" s="138"/>
+      <c r="B8" s="138"/>
       <c r="C8" s="93" t="s">
         <v>27</v>
       </c>
@@ -12497,8 +12497,8 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
-      <c r="Y8" s="128"/>
+      <c r="X8" s="127"/>
+      <c r="Y8" s="139"/>
       <c r="Z8" s="94" t="s">
         <v>63</v>
       </c>
@@ -13412,10 +13412,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="124"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -13534,13 +13534,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -13562,12 +13562,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
       <c r="H19" s="88"/>
       <c r="I19" s="88"/>
       <c r="J19" s="88"/>
@@ -13590,8 +13590,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
       <c r="F20" s="89"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -13678,19 +13678,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:K7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="Y7:Y8"/>
     <mergeCell ref="AQ7:AQ8"/>
     <mergeCell ref="Z7:AF7"/>
@@ -13700,6 +13687,19 @@
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
     <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13737,67 +13737,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
       <c r="E1" s="114"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="131"/>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="129"/>
       <c r="Y1" s="114"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
       <c r="E2" s="114"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="129"/>
       <c r="Y2" s="114"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
       <c r="D3" s="114"/>
       <c r="E3" s="114"/>
       <c r="F3" s="17"/>
@@ -13849,32 +13849,32 @@
       <c r="Y4" s="114"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="128" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="128"/>
+      <c r="S5" s="129"/>
+      <c r="T5" s="129"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="129"/>
+      <c r="W5" s="129"/>
+      <c r="X5" s="129"/>
       <c r="Y5" s="114"/>
     </row>
     <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13906,45 +13906,45 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="136"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="141"/>
+      <c r="R7" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="136"/>
+      <c r="T7" s="136"/>
+      <c r="U7" s="136"/>
+      <c r="V7" s="136"/>
+      <c r="W7" s="141"/>
+      <c r="X7" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="128" t="s">
+      <c r="Y7" s="139" t="s">
         <v>77</v>
       </c>
       <c r="Z7" s="152" t="s">
@@ -13973,8 +13973,8 @@
       <c r="AQ7" s="150"/>
     </row>
     <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
+      <c r="A8" s="138"/>
+      <c r="B8" s="138"/>
       <c r="C8" s="115" t="s">
         <v>27</v>
       </c>
@@ -14038,8 +14038,8 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
-      <c r="Y8" s="128"/>
+      <c r="X8" s="127"/>
+      <c r="Y8" s="139"/>
       <c r="Z8" s="94" t="s">
         <v>63</v>
       </c>
@@ -14115,7 +14115,7 @@
         <v>1549</v>
       </c>
       <c r="H9" s="31">
-        <f>G9-'Tháng 7'!G9</f>
+        <f>G9-'Tháng 7_2025'!G9</f>
         <v>21</v>
       </c>
       <c r="I9" s="31">
@@ -14137,7 +14137,7 @@
         <v>1638</v>
       </c>
       <c r="N9" s="53">
-        <f>M9-'Tháng 7'!M9</f>
+        <f>M9-'Tháng 7_2025'!M9</f>
         <v>14</v>
       </c>
       <c r="O9" s="53">
@@ -14159,7 +14159,7 @@
         <v>1427</v>
       </c>
       <c r="T9" s="53">
-        <f>S9-'Tháng 7'!S9</f>
+        <f>S9-'Tháng 7_2025'!S9</f>
         <v>35</v>
       </c>
       <c r="U9" s="53">
@@ -14264,7 +14264,7 @@
         <v>506</v>
       </c>
       <c r="H10" s="31">
-        <f>G10-'Tháng 7'!G10</f>
+        <f>G10-'Tháng 7_2025'!G10</f>
         <v>10</v>
       </c>
       <c r="I10" s="31">
@@ -14286,7 +14286,7 @@
         <v>785</v>
       </c>
       <c r="N10" s="53">
-        <f>M10-'Tháng 7'!M10</f>
+        <f>M10-'Tháng 7_2025'!M10</f>
         <v>65</v>
       </c>
       <c r="O10" s="53">
@@ -14308,7 +14308,7 @@
         <v>396</v>
       </c>
       <c r="T10" s="53">
-        <f>S10-'Tháng 7'!S10</f>
+        <f>S10-'Tháng 7_2025'!S10</f>
         <v>6</v>
       </c>
       <c r="U10" s="53">
@@ -14390,7 +14390,7 @@
         <v>515</v>
       </c>
       <c r="H11" s="31">
-        <f>G11-'Tháng 7'!G11</f>
+        <f>G11-'Tháng 7_2025'!G11</f>
         <v>-4</v>
       </c>
       <c r="I11" s="31">
@@ -14412,7 +14412,7 @@
         <v>831</v>
       </c>
       <c r="N11" s="53">
-        <f>M11-'Tháng 7'!M11</f>
+        <f>M11-'Tháng 7_2025'!M11</f>
         <v>61</v>
       </c>
       <c r="O11" s="53">
@@ -14434,7 +14434,7 @@
         <v>425</v>
       </c>
       <c r="T11" s="53">
-        <f>S11-'Tháng 7'!S11</f>
+        <f>S11-'Tháng 7_2025'!S11</f>
         <v>-9</v>
       </c>
       <c r="U11" s="53">
@@ -14516,7 +14516,7 @@
         <v>1132</v>
       </c>
       <c r="H12" s="31">
-        <f>G12-'Tháng 7'!G12</f>
+        <f>G12-'Tháng 7_2025'!G12</f>
         <v>36</v>
       </c>
       <c r="I12" s="31">
@@ -14538,7 +14538,7 @@
         <v>1719</v>
       </c>
       <c r="N12" s="53">
-        <f>M12-'Tháng 7'!M12</f>
+        <f>M12-'Tháng 7_2025'!M12</f>
         <v>93</v>
       </c>
       <c r="O12" s="53">
@@ -14560,7 +14560,7 @@
         <v>1026</v>
       </c>
       <c r="T12" s="53">
-        <f>S12-'Tháng 7'!S12</f>
+        <f>S12-'Tháng 7_2025'!S12</f>
         <v>35</v>
       </c>
       <c r="U12" s="53">
@@ -14642,7 +14642,7 @@
         <v>974</v>
       </c>
       <c r="H13" s="31">
-        <f>G13-'Tháng 7'!G13</f>
+        <f>G13-'Tháng 7_2025'!G13</f>
         <v>-5</v>
       </c>
       <c r="I13" s="31">
@@ -14664,7 +14664,7 @@
         <v>1005</v>
       </c>
       <c r="N13" s="53">
-        <f>M13-'Tháng 7'!M13</f>
+        <f>M13-'Tháng 7_2025'!M13</f>
         <v>33</v>
       </c>
       <c r="O13" s="53">
@@ -14686,7 +14686,7 @@
         <v>857</v>
       </c>
       <c r="T13" s="53">
-        <f>S13-'Tháng 7'!S13</f>
+        <f>S13-'Tháng 7_2025'!S13</f>
         <v>-7</v>
       </c>
       <c r="U13" s="53">
@@ -14768,7 +14768,7 @@
         <v>529</v>
       </c>
       <c r="H14" s="31">
-        <f>G14-'Tháng 7'!G14</f>
+        <f>G14-'Tháng 7_2025'!G14</f>
         <v>5</v>
       </c>
       <c r="I14" s="31">
@@ -14790,7 +14790,7 @@
         <v>1063</v>
       </c>
       <c r="N14" s="53">
-        <f>M14-'Tháng 7'!M14</f>
+        <f>M14-'Tháng 7_2025'!M14</f>
         <v>53</v>
       </c>
       <c r="O14" s="53">
@@ -14812,7 +14812,7 @@
         <v>417</v>
       </c>
       <c r="T14" s="53">
-        <f>S14-'Tháng 7'!S14</f>
+        <f>S14-'Tháng 7_2025'!S14</f>
         <v>0</v>
       </c>
       <c r="U14" s="53">
@@ -14886,7 +14886,7 @@
         <v>533</v>
       </c>
       <c r="H15" s="31">
-        <f>G15-'Tháng 7'!G15</f>
+        <f>G15-'Tháng 7_2025'!G15</f>
         <v>-3</v>
       </c>
       <c r="I15" s="31">
@@ -14908,7 +14908,7 @@
         <v>1025</v>
       </c>
       <c r="N15" s="53">
-        <f>M15-'Tháng 7'!M15</f>
+        <f>M15-'Tháng 7_2025'!M15</f>
         <v>-43</v>
       </c>
       <c r="O15" s="53">
@@ -14930,7 +14930,7 @@
         <v>435</v>
       </c>
       <c r="T15" s="53">
-        <f>S15-'Tháng 7'!S15</f>
+        <f>S15-'Tháng 7_2025'!S15</f>
         <v>-6</v>
       </c>
       <c r="U15" s="53">
@@ -14953,10 +14953,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="124"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -15075,13 +15075,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -15103,12 +15103,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
       <c r="H19" s="110"/>
       <c r="I19" s="110"/>
       <c r="J19" s="110"/>
@@ -15131,8 +15131,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
       <c r="F20" s="111"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -15216,6 +15216,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AP7"/>
+    <mergeCell ref="AQ7:AQ8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:G19"/>
@@ -15227,17 +15238,6 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AH7:AP7"/>
-    <mergeCell ref="AQ7:AQ8"/>
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -15274,67 +15274,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
       <c r="E1" s="118"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="131"/>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="129"/>
       <c r="Y1" s="118"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
       <c r="E2" s="118"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="132"/>
+      <c r="X2" s="129"/>
       <c r="Y2" s="118"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
       <c r="D3" s="118"/>
       <c r="E3" s="118"/>
       <c r="F3" s="17"/>
@@ -15386,32 +15386,32 @@
       <c r="Y4" s="118"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="128" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="128"/>
+      <c r="S5" s="129"/>
+      <c r="T5" s="129"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="129"/>
+      <c r="W5" s="129"/>
+      <c r="X5" s="129"/>
       <c r="Y5" s="118"/>
     </row>
     <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15443,45 +15443,45 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="136"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="141"/>
+      <c r="R7" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="136"/>
+      <c r="T7" s="136"/>
+      <c r="U7" s="136"/>
+      <c r="V7" s="136"/>
+      <c r="W7" s="141"/>
+      <c r="X7" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="128" t="s">
+      <c r="Y7" s="139" t="s">
         <v>77</v>
       </c>
       <c r="Z7" s="152" t="s">
@@ -15510,8 +15510,8 @@
       <c r="AQ7" s="150"/>
     </row>
     <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
+      <c r="A8" s="138"/>
+      <c r="B8" s="138"/>
       <c r="C8" s="116" t="s">
         <v>27</v>
       </c>
@@ -15575,8 +15575,8 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
-      <c r="Y8" s="128"/>
+      <c r="X8" s="127"/>
+      <c r="Y8" s="139"/>
       <c r="Z8" s="94" t="s">
         <v>63</v>
       </c>
@@ -15650,7 +15650,7 @@
       </c>
       <c r="G9" s="30"/>
       <c r="H9" s="31">
-        <f>G9-'Tháng 7'!G9</f>
+        <f>G9-'Tháng 7_2025'!G9</f>
         <v>-1528</v>
       </c>
       <c r="I9" s="31">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="M9" s="30"/>
       <c r="N9" s="53">
-        <f>M9-'Tháng 7'!M9</f>
+        <f>M9-'Tháng 7_2025'!M9</f>
         <v>-1624</v>
       </c>
       <c r="O9" s="53">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="S9" s="31"/>
       <c r="T9" s="53">
-        <f>S9-'Tháng 7'!S9</f>
+        <f>S9-'Tháng 7_2025'!S9</f>
         <v>-1392</v>
       </c>
       <c r="U9" s="53">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="G10" s="30"/>
       <c r="H10" s="31">
-        <f>G10-'Tháng 7'!G10</f>
+        <f>G10-'Tháng 7_2025'!G10</f>
         <v>-496</v>
       </c>
       <c r="I10" s="31">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="M10" s="30"/>
       <c r="N10" s="53">
-        <f>M10-'Tháng 7'!M10</f>
+        <f>M10-'Tháng 7_2025'!M10</f>
         <v>-720</v>
       </c>
       <c r="O10" s="53">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="S10" s="31"/>
       <c r="T10" s="53">
-        <f>S10-'Tháng 7'!S10</f>
+        <f>S10-'Tháng 7_2025'!S10</f>
         <v>-390</v>
       </c>
       <c r="U10" s="53">
@@ -15913,7 +15913,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="31">
-        <f>G11-'Tháng 7'!G11</f>
+        <f>G11-'Tháng 7_2025'!G11</f>
         <v>-519</v>
       </c>
       <c r="I11" s="31">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="M11" s="30"/>
       <c r="N11" s="53">
-        <f>M11-'Tháng 7'!M11</f>
+        <f>M11-'Tháng 7_2025'!M11</f>
         <v>-770</v>
       </c>
       <c r="O11" s="53">
@@ -15953,7 +15953,7 @@
       </c>
       <c r="S11" s="31"/>
       <c r="T11" s="53">
-        <f>S11-'Tháng 7'!S11</f>
+        <f>S11-'Tháng 7_2025'!S11</f>
         <v>-434</v>
       </c>
       <c r="U11" s="53">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31">
-        <f>G12-'Tháng 7'!G12</f>
+        <f>G12-'Tháng 7_2025'!G12</f>
         <v>-1096</v>
       </c>
       <c r="I12" s="31">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="M12" s="30"/>
       <c r="N12" s="53">
-        <f>M12-'Tháng 7'!M12</f>
+        <f>M12-'Tháng 7_2025'!M12</f>
         <v>-1626</v>
       </c>
       <c r="O12" s="53">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="S12" s="31"/>
       <c r="T12" s="53">
-        <f>S12-'Tháng 7'!S12</f>
+        <f>S12-'Tháng 7_2025'!S12</f>
         <v>-991</v>
       </c>
       <c r="U12" s="53">
@@ -16153,7 +16153,7 @@
       </c>
       <c r="G13" s="30"/>
       <c r="H13" s="31">
-        <f>G13-'Tháng 7'!G13</f>
+        <f>G13-'Tháng 7_2025'!G13</f>
         <v>-979</v>
       </c>
       <c r="I13" s="31">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="M13" s="30"/>
       <c r="N13" s="53">
-        <f>M13-'Tháng 7'!M13</f>
+        <f>M13-'Tháng 7_2025'!M13</f>
         <v>-972</v>
       </c>
       <c r="O13" s="53">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="S13" s="31"/>
       <c r="T13" s="53">
-        <f>S13-'Tháng 7'!S13</f>
+        <f>S13-'Tháng 7_2025'!S13</f>
         <v>-864</v>
       </c>
       <c r="U13" s="53">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="G14" s="30"/>
       <c r="H14" s="31">
-        <f>G14-'Tháng 7'!G14</f>
+        <f>G14-'Tháng 7_2025'!G14</f>
         <v>-524</v>
       </c>
       <c r="I14" s="31">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="M14" s="30"/>
       <c r="N14" s="53">
-        <f>M14-'Tháng 7'!M14</f>
+        <f>M14-'Tháng 7_2025'!M14</f>
         <v>-1010</v>
       </c>
       <c r="O14" s="53">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="S14" s="31"/>
       <c r="T14" s="53">
-        <f>S14-'Tháng 7'!S14</f>
+        <f>S14-'Tháng 7_2025'!S14</f>
         <v>-417</v>
       </c>
       <c r="U14" s="53">
@@ -16385,7 +16385,7 @@
       </c>
       <c r="G15" s="30"/>
       <c r="H15" s="31">
-        <f>G15-'Tháng 7'!G15</f>
+        <f>G15-'Tháng 7_2025'!G15</f>
         <v>-536</v>
       </c>
       <c r="I15" s="31">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="M15" s="30"/>
       <c r="N15" s="53">
-        <f>M15-'Tháng 7'!M15</f>
+        <f>M15-'Tháng 7_2025'!M15</f>
         <v>-1068</v>
       </c>
       <c r="O15" s="53">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="S15" s="31"/>
       <c r="T15" s="53">
-        <f>S15-'Tháng 7'!S15</f>
+        <f>S15-'Tháng 7_2025'!S15</f>
         <v>-441</v>
       </c>
       <c r="U15" s="53">
@@ -16448,10 +16448,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="124"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -16570,13 +16570,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -16598,12 +16598,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
       <c r="H19" s="119"/>
       <c r="I19" s="119"/>
       <c r="J19" s="119"/>
@@ -16626,8 +16626,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
       <c r="F20" s="120"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -16711,17 +16711,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AH7:AP7"/>
-    <mergeCell ref="AQ7:AQ8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:G19"/>
@@ -16733,6 +16722,17 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AP7"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/T07_BHXH, BHTN_2026.xlsx
+++ b/T07_BHXH, BHTN_2026.xlsx
@@ -1123,39 +1123,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1191,6 +1158,39 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2617,11 +2617,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
       <c r="D1" s="20"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
@@ -2636,36 +2636,36 @@
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
-      <c r="R1" s="131" t="s">
+      <c r="R1" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
-      <c r="U1" s="131"/>
-      <c r="V1" s="131"/>
-      <c r="W1" s="131"/>
-      <c r="X1" s="131"/>
-      <c r="Y1" s="131"/>
-      <c r="Z1" s="131"/>
-      <c r="AA1" s="131"/>
-      <c r="AB1" s="131"/>
-      <c r="AC1" s="131"/>
-      <c r="AD1" s="131"/>
-      <c r="AE1" s="131"/>
-      <c r="AF1" s="131"/>
-      <c r="AG1" s="131"/>
-      <c r="AH1" s="131"/>
-      <c r="AI1" s="131"/>
-      <c r="AJ1" s="131"/>
-      <c r="AK1" s="129"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="137"/>
+      <c r="AA1" s="137"/>
+      <c r="AB1" s="137"/>
+      <c r="AC1" s="137"/>
+      <c r="AD1" s="137"/>
+      <c r="AE1" s="137"/>
+      <c r="AF1" s="137"/>
+      <c r="AG1" s="137"/>
+      <c r="AH1" s="137"/>
+      <c r="AI1" s="137"/>
+      <c r="AJ1" s="137"/>
+      <c r="AK1" s="135"/>
       <c r="AL1" s="20"/>
     </row>
     <row r="2" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
@@ -2680,36 +2680,36 @@
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
-      <c r="R2" s="132" t="s">
+      <c r="R2" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="132"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="132"/>
-      <c r="Y2" s="132"/>
-      <c r="Z2" s="132"/>
-      <c r="AA2" s="132"/>
-      <c r="AB2" s="132"/>
-      <c r="AC2" s="132"/>
-      <c r="AD2" s="132"/>
-      <c r="AE2" s="132"/>
-      <c r="AF2" s="132"/>
-      <c r="AG2" s="132"/>
-      <c r="AH2" s="132"/>
-      <c r="AI2" s="132"/>
-      <c r="AJ2" s="132"/>
-      <c r="AK2" s="129"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="138"/>
+      <c r="Y2" s="138"/>
+      <c r="Z2" s="138"/>
+      <c r="AA2" s="138"/>
+      <c r="AB2" s="138"/>
+      <c r="AC2" s="138"/>
+      <c r="AD2" s="138"/>
+      <c r="AE2" s="138"/>
+      <c r="AF2" s="138"/>
+      <c r="AG2" s="138"/>
+      <c r="AH2" s="138"/>
+      <c r="AI2" s="138"/>
+      <c r="AJ2" s="138"/>
+      <c r="AK2" s="135"/>
       <c r="AL2" s="20"/>
     </row>
     <row r="3" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
@@ -2787,87 +2787,87 @@
       <c r="AL4" s="20"/>
     </row>
     <row r="5" spans="1:40" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="128"/>
-      <c r="T5" s="128"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="128"/>
-      <c r="W5" s="128"/>
-      <c r="X5" s="128"/>
-      <c r="Y5" s="128"/>
-      <c r="Z5" s="128"/>
-      <c r="AA5" s="128"/>
-      <c r="AB5" s="128"/>
-      <c r="AC5" s="128"/>
-      <c r="AD5" s="129"/>
-      <c r="AE5" s="129"/>
-      <c r="AF5" s="129"/>
-      <c r="AG5" s="129"/>
-      <c r="AH5" s="129"/>
-      <c r="AI5" s="129"/>
-      <c r="AJ5" s="129"/>
-      <c r="AK5" s="129"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="134"/>
+      <c r="T5" s="134"/>
+      <c r="U5" s="134"/>
+      <c r="V5" s="134"/>
+      <c r="W5" s="134"/>
+      <c r="X5" s="134"/>
+      <c r="Y5" s="134"/>
+      <c r="Z5" s="134"/>
+      <c r="AA5" s="134"/>
+      <c r="AB5" s="134"/>
+      <c r="AC5" s="134"/>
+      <c r="AD5" s="135"/>
+      <c r="AE5" s="135"/>
+      <c r="AF5" s="135"/>
+      <c r="AG5" s="135"/>
+      <c r="AH5" s="135"/>
+      <c r="AI5" s="135"/>
+      <c r="AJ5" s="135"/>
+      <c r="AK5" s="135"/>
       <c r="AL5" s="20"/>
     </row>
     <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="133" t="s">
+      <c r="A6" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="133"/>
-      <c r="K6" s="133"/>
-      <c r="L6" s="133"/>
-      <c r="M6" s="133"/>
-      <c r="N6" s="133"/>
-      <c r="O6" s="133"/>
-      <c r="P6" s="133"/>
-      <c r="Q6" s="133"/>
-      <c r="R6" s="133"/>
-      <c r="S6" s="133"/>
-      <c r="T6" s="133"/>
-      <c r="U6" s="133"/>
-      <c r="V6" s="133"/>
-      <c r="W6" s="133"/>
-      <c r="X6" s="133"/>
-      <c r="Y6" s="133"/>
-      <c r="Z6" s="133"/>
-      <c r="AA6" s="133"/>
-      <c r="AB6" s="133"/>
-      <c r="AC6" s="133"/>
-      <c r="AD6" s="134"/>
-      <c r="AE6" s="134"/>
-      <c r="AF6" s="134"/>
-      <c r="AG6" s="134"/>
-      <c r="AH6" s="134"/>
-      <c r="AI6" s="134"/>
-      <c r="AJ6" s="134"/>
-      <c r="AK6" s="134"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="122"/>
+      <c r="O6" s="122"/>
+      <c r="P6" s="122"/>
+      <c r="Q6" s="122"/>
+      <c r="R6" s="122"/>
+      <c r="S6" s="122"/>
+      <c r="T6" s="122"/>
+      <c r="U6" s="122"/>
+      <c r="V6" s="122"/>
+      <c r="W6" s="122"/>
+      <c r="X6" s="122"/>
+      <c r="Y6" s="122"/>
+      <c r="Z6" s="122"/>
+      <c r="AA6" s="122"/>
+      <c r="AB6" s="122"/>
+      <c r="AC6" s="122"/>
+      <c r="AD6" s="123"/>
+      <c r="AE6" s="123"/>
+      <c r="AF6" s="123"/>
+      <c r="AG6" s="123"/>
+      <c r="AH6" s="123"/>
+      <c r="AI6" s="123"/>
+      <c r="AJ6" s="123"/>
+      <c r="AK6" s="123"/>
       <c r="AL6" s="24"/>
     </row>
     <row r="7" spans="1:40" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2912,64 +2912,64 @@
       <c r="AL7" s="7"/>
     </row>
     <row r="8" spans="1:40" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="135" t="s">
+      <c r="C8" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="136"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="136"/>
-      <c r="H8" s="139" t="s">
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="128" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
+      <c r="I8" s="129"/>
+      <c r="J8" s="129"/>
+      <c r="K8" s="129"/>
+      <c r="L8" s="129"/>
       <c r="M8" s="51"/>
-      <c r="N8" s="135" t="s">
+      <c r="N8" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="136"/>
-      <c r="P8" s="136"/>
-      <c r="Q8" s="136"/>
-      <c r="R8" s="136"/>
-      <c r="S8" s="136"/>
-      <c r="T8" s="141"/>
+      <c r="O8" s="125"/>
+      <c r="P8" s="125"/>
+      <c r="Q8" s="125"/>
+      <c r="R8" s="125"/>
+      <c r="S8" s="125"/>
+      <c r="T8" s="130"/>
       <c r="U8" s="52"/>
-      <c r="V8" s="135" t="s">
+      <c r="V8" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="W8" s="136"/>
-      <c r="X8" s="136"/>
-      <c r="Y8" s="136"/>
-      <c r="Z8" s="136"/>
-      <c r="AA8" s="136"/>
-      <c r="AB8" s="141"/>
+      <c r="W8" s="125"/>
+      <c r="X8" s="125"/>
+      <c r="Y8" s="125"/>
+      <c r="Z8" s="125"/>
+      <c r="AA8" s="125"/>
+      <c r="AB8" s="130"/>
       <c r="AC8" s="58"/>
-      <c r="AD8" s="142" t="s">
+      <c r="AD8" s="131" t="s">
         <v>11</v>
       </c>
-      <c r="AE8" s="143"/>
-      <c r="AF8" s="143"/>
-      <c r="AG8" s="143"/>
-      <c r="AH8" s="143"/>
-      <c r="AI8" s="143"/>
-      <c r="AJ8" s="144"/>
-      <c r="AK8" s="126" t="s">
+      <c r="AE8" s="132"/>
+      <c r="AF8" s="132"/>
+      <c r="AG8" s="132"/>
+      <c r="AH8" s="132"/>
+      <c r="AI8" s="132"/>
+      <c r="AJ8" s="133"/>
+      <c r="AK8" s="143" t="s">
         <v>8</v>
       </c>
       <c r="AL8" s="34"/>
     </row>
     <row r="9" spans="1:40" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="138"/>
-      <c r="B9" s="138"/>
+      <c r="A9" s="127"/>
+      <c r="B9" s="127"/>
       <c r="C9" s="42" t="s">
         <v>27</v>
       </c>
@@ -3072,7 +3072,7 @@
       <c r="AJ9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="AK9" s="127"/>
+      <c r="AK9" s="144"/>
       <c r="AL9" s="34"/>
       <c r="AM9" s="34"/>
     </row>
@@ -3727,10 +3727,10 @@
       <c r="AN16" s="10"/>
     </row>
     <row r="17" spans="1:40" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="124" t="s">
+      <c r="A17" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="124"/>
+      <c r="B17" s="141"/>
       <c r="C17" s="18">
         <f>SUM(C10:C16)</f>
         <v>227321</v>
@@ -3907,22 +3907,22 @@
     </row>
     <row r="19" spans="1:40" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="125" t="s">
+      <c r="B19" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="125"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="125"/>
-      <c r="I19" s="125"/>
-      <c r="J19" s="125"/>
-      <c r="K19" s="125"/>
-      <c r="L19" s="125"/>
-      <c r="M19" s="125"/>
-      <c r="N19" s="125"/>
-      <c r="O19" s="125"/>
+      <c r="C19" s="142"/>
+      <c r="D19" s="142"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="142"/>
+      <c r="G19" s="142"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="142"/>
+      <c r="J19" s="142"/>
+      <c r="K19" s="142"/>
+      <c r="L19" s="142"/>
+      <c r="M19" s="142"/>
+      <c r="N19" s="142"/>
+      <c r="O19" s="142"/>
       <c r="P19" s="49"/>
       <c r="Q19" s="49"/>
       <c r="R19" s="19"/>
@@ -3948,23 +3948,23 @@
       <c r="AL19" s="19"/>
     </row>
     <row r="20" spans="1:40" ht="18" x14ac:dyDescent="0.35">
-      <c r="B20" s="122"/>
-      <c r="C20" s="122"/>
-      <c r="D20" s="122"/>
-      <c r="E20" s="122"/>
-      <c r="F20" s="122"/>
-      <c r="G20" s="122"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="122"/>
-      <c r="J20" s="122"/>
-      <c r="K20" s="122"/>
-      <c r="L20" s="122"/>
-      <c r="M20" s="122"/>
-      <c r="N20" s="122"/>
-      <c r="O20" s="122"/>
-      <c r="P20" s="122"/>
-      <c r="Q20" s="122"/>
-      <c r="R20" s="122"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="139"/>
+      <c r="N20" s="139"/>
+      <c r="O20" s="139"/>
+      <c r="P20" s="139"/>
+      <c r="Q20" s="139"/>
+      <c r="R20" s="139"/>
       <c r="S20" s="23"/>
       <c r="T20" s="23"/>
       <c r="U20" s="23"/>
@@ -3990,10 +3990,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="123"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="140"/>
+      <c r="G21" s="140"/>
       <c r="H21" s="21"/>
       <c r="I21" s="21"/>
       <c r="J21" s="21"/>
@@ -4117,6 +4117,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B20:R20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="B19:O19"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="R1:AK1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="R2:AK2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A6:AK6"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A8:A9"/>
@@ -4125,17 +4136,6 @@
     <mergeCell ref="N8:T8"/>
     <mergeCell ref="V8:AB8"/>
     <mergeCell ref="AD8:AJ8"/>
-    <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="R1:AK1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="R2:AK2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="B20:R20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="B19:O19"/>
-    <mergeCell ref="AK8:AK9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4171,67 +4171,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="118"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
-      <c r="U1" s="131"/>
-      <c r="V1" s="131"/>
-      <c r="W1" s="131"/>
-      <c r="X1" s="129"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
       <c r="Y1" s="118"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="118"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="129"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
       <c r="Y2" s="118"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131"/>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="118"/>
       <c r="E3" s="118"/>
       <c r="F3" s="17"/>
@@ -4283,32 +4283,32 @@
       <c r="Y4" s="118"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="134" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="129"/>
-      <c r="T5" s="129"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="129"/>
-      <c r="W5" s="129"/>
-      <c r="X5" s="129"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
       <c r="Y5" s="118"/>
     </row>
     <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4340,45 +4340,45 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="140" t="s">
+      <c r="C7" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="135" t="s">
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="135" t="s">
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="136"/>
-      <c r="P7" s="136"/>
-      <c r="Q7" s="141"/>
-      <c r="R7" s="135" t="s">
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="136"/>
-      <c r="T7" s="136"/>
-      <c r="U7" s="136"/>
-      <c r="V7" s="136"/>
-      <c r="W7" s="141"/>
-      <c r="X7" s="126" t="s">
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="139" t="s">
+      <c r="Y7" s="128" t="s">
         <v>77</v>
       </c>
       <c r="Z7" s="152" t="s">
@@ -4407,8 +4407,8 @@
       <c r="AQ7" s="150"/>
     </row>
     <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="138"/>
-      <c r="B8" s="138"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="116" t="s">
         <v>27</v>
       </c>
@@ -4472,8 +4472,8 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="127"/>
-      <c r="Y8" s="139"/>
+      <c r="X8" s="144"/>
+      <c r="Y8" s="128"/>
       <c r="Z8" s="94" t="s">
         <v>63</v>
       </c>
@@ -4571,8 +4571,8 @@
         <v>-1624</v>
       </c>
       <c r="O9" s="53">
-        <f>M9-'Thang 12'!Y10</f>
-        <v>-1445</v>
+        <f>M9-'Thang 12'!AG10</f>
+        <v>-1670</v>
       </c>
       <c r="P9" s="53">
         <f>L9-M9</f>
@@ -4591,8 +4591,8 @@
         <v>-1392</v>
       </c>
       <c r="U9" s="53">
-        <f>S9-'Thang 12'!AG10</f>
-        <v>-1670</v>
+        <f>S9-'Thang 12'!Y10</f>
+        <v>-1445</v>
       </c>
       <c r="V9" s="53">
         <f t="shared" ref="V9:V15" si="3">R9-S9</f>
@@ -4714,8 +4714,8 @@
         <v>-720</v>
       </c>
       <c r="O10" s="53">
-        <f>M10-'Thang 12'!Y11</f>
-        <v>-350</v>
+        <f>M10-'Thang 12'!AG11</f>
+        <v>-590</v>
       </c>
       <c r="P10" s="53">
         <f t="shared" ref="P10:P15" si="8">L10-M10</f>
@@ -4734,8 +4734,8 @@
         <v>-390</v>
       </c>
       <c r="U10" s="53">
-        <f>S10-'Thang 12'!AG11</f>
-        <v>-590</v>
+        <f>S10-'Thang 12'!Y11</f>
+        <v>-350</v>
       </c>
       <c r="V10" s="53">
         <f t="shared" si="3"/>
@@ -4834,8 +4834,8 @@
         <v>-770</v>
       </c>
       <c r="O11" s="53">
-        <f>M11-'Thang 12'!Y12</f>
-        <v>-397</v>
+        <f>M11-'Thang 12'!AG12</f>
+        <v>-816</v>
       </c>
       <c r="P11" s="53">
         <f t="shared" si="8"/>
@@ -4854,8 +4854,8 @@
         <v>-434</v>
       </c>
       <c r="U11" s="53">
-        <f>S11-'Thang 12'!AG12</f>
-        <v>-816</v>
+        <f>S11-'Thang 12'!Y12</f>
+        <v>-397</v>
       </c>
       <c r="V11" s="53">
         <f t="shared" si="3"/>
@@ -4954,8 +4954,8 @@
         <v>-1626</v>
       </c>
       <c r="O12" s="53">
-        <f>M12-'Thang 12'!Y13</f>
-        <v>-910</v>
+        <f>M12-'Thang 12'!AG13</f>
+        <v>-1451</v>
       </c>
       <c r="P12" s="53">
         <f t="shared" si="8"/>
@@ -4974,8 +4974,8 @@
         <v>-991</v>
       </c>
       <c r="U12" s="53">
-        <f>S12-'Thang 12'!AG13</f>
-        <v>-1451</v>
+        <f>S12-'Thang 12'!Y13</f>
+        <v>-910</v>
       </c>
       <c r="V12" s="53">
         <f t="shared" si="3"/>
@@ -5074,8 +5074,8 @@
         <v>-972</v>
       </c>
       <c r="O13" s="53">
-        <f>M13-'Thang 12'!Y14</f>
-        <v>-914</v>
+        <f>M13-'Thang 12'!AG14</f>
+        <v>-1007</v>
       </c>
       <c r="P13" s="53">
         <f t="shared" si="8"/>
@@ -5094,8 +5094,8 @@
         <v>-864</v>
       </c>
       <c r="U13" s="53">
-        <f>S13-'Thang 12'!AG14</f>
-        <v>-1007</v>
+        <f>S13-'Thang 12'!Y14</f>
+        <v>-914</v>
       </c>
       <c r="V13" s="53">
         <f t="shared" si="3"/>
@@ -5194,8 +5194,8 @@
         <v>-1010</v>
       </c>
       <c r="O14" s="53">
-        <f>M14-'Thang 12'!Y15</f>
-        <v>-372</v>
+        <f>M14-'Thang 12'!AG15</f>
+        <v>-980</v>
       </c>
       <c r="P14" s="53">
         <f t="shared" si="8"/>
@@ -5214,8 +5214,8 @@
         <v>-417</v>
       </c>
       <c r="U14" s="53">
-        <f>S14-'Thang 12'!AG15</f>
-        <v>-980</v>
+        <f>S14-'Thang 12'!Y15</f>
+        <v>-372</v>
       </c>
       <c r="V14" s="53">
         <f t="shared" si="3"/>
@@ -5306,8 +5306,8 @@
         <v>-1068</v>
       </c>
       <c r="O15" s="53">
-        <f>M15-'Thang 12'!Y16</f>
-        <v>-383</v>
+        <f>M15-'Thang 12'!AG16</f>
+        <v>-1040</v>
       </c>
       <c r="P15" s="53">
         <f t="shared" si="8"/>
@@ -5326,8 +5326,8 @@
         <v>-441</v>
       </c>
       <c r="U15" s="53">
-        <f>S15-'Thang 12'!AG16</f>
-        <v>-1040</v>
+        <f>S15-'Thang 12'!Y16</f>
+        <v>-383</v>
       </c>
       <c r="V15" s="53">
         <f t="shared" si="3"/>
@@ -5345,10 +5345,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="124"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -5398,8 +5398,8 @@
         <v>-7790</v>
       </c>
       <c r="O16" s="56">
-        <f>M16-'Thang 12'!Y17</f>
-        <v>-4771</v>
+        <f>SUM(O9:O15)</f>
+        <v>-7554</v>
       </c>
       <c r="P16" s="18">
         <f t="shared" ref="P16" si="14">SUM(P9:P15)</f>
@@ -5422,8 +5422,8 @@
         <v>-4929</v>
       </c>
       <c r="U16" s="56">
-        <f>S16-'Thang 12'!AG17</f>
-        <v>-7554</v>
+        <f>SUM(U9:U15)</f>
+        <v>-4771</v>
       </c>
       <c r="V16" s="56">
         <f>SUM(V9:V15)</f>
@@ -5467,13 +5467,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="125" t="s">
+      <c r="B18" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -5495,12 +5495,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="122"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
       <c r="H19" s="119"/>
       <c r="I19" s="119"/>
       <c r="J19" s="119"/>
@@ -5523,8 +5523,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="123"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
       <c r="F20" s="120"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -5608,6 +5608,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AP7"/>
+    <mergeCell ref="AQ7:AQ8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:G19"/>
@@ -5619,17 +5630,6 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AH7:AP7"/>
-    <mergeCell ref="AQ7:AQ8"/>
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5669,12 +5669,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
@@ -5683,31 +5683,31 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
-      <c r="M1" s="131" t="s">
+      <c r="M1" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
-      <c r="U1" s="131"/>
-      <c r="V1" s="131"/>
-      <c r="W1" s="131"/>
-      <c r="X1" s="131"/>
-      <c r="Y1" s="131"/>
-      <c r="Z1" s="129"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="135"/>
       <c r="AA1" s="20"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
@@ -5716,28 +5716,28 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="132" t="s">
+      <c r="M2" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="132"/>
-      <c r="Y2" s="132"/>
-      <c r="Z2" s="129"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="138"/>
+      <c r="Y2" s="138"/>
+      <c r="Z2" s="135"/>
       <c r="AA2" s="20"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131"/>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
@@ -5793,34 +5793,34 @@
       <c r="AA4" s="20"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="134" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="128"/>
-      <c r="T5" s="128"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="129"/>
-      <c r="W5" s="129"/>
-      <c r="X5" s="129"/>
-      <c r="Y5" s="129"/>
-      <c r="Z5" s="129"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="134"/>
+      <c r="T5" s="134"/>
+      <c r="U5" s="134"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
+      <c r="Y5" s="135"/>
+      <c r="Z5" s="135"/>
       <c r="AA5" s="20"/>
     </row>
     <row r="6" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5883,17 +5883,17 @@
       <c r="AA7" s="7"/>
     </row>
     <row r="8" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="140" t="s">
+      <c r="C8" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="140"/>
-      <c r="E8" s="140"/>
+      <c r="D8" s="129"/>
+      <c r="E8" s="129"/>
       <c r="F8" s="51"/>
       <c r="G8" s="145" t="s">
         <v>32</v>
@@ -5901,35 +5901,35 @@
       <c r="H8" s="146"/>
       <c r="I8" s="146"/>
       <c r="J8" s="147"/>
-      <c r="K8" s="135" t="s">
+      <c r="K8" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="136"/>
-      <c r="M8" s="136"/>
-      <c r="N8" s="136"/>
-      <c r="O8" s="141"/>
-      <c r="P8" s="135" t="s">
+      <c r="L8" s="125"/>
+      <c r="M8" s="125"/>
+      <c r="N8" s="125"/>
+      <c r="O8" s="130"/>
+      <c r="P8" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="Q8" s="136"/>
-      <c r="R8" s="136"/>
-      <c r="S8" s="136"/>
-      <c r="T8" s="141"/>
-      <c r="U8" s="135" t="s">
+      <c r="Q8" s="125"/>
+      <c r="R8" s="125"/>
+      <c r="S8" s="125"/>
+      <c r="T8" s="130"/>
+      <c r="U8" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="V8" s="136"/>
-      <c r="W8" s="136"/>
-      <c r="X8" s="136"/>
-      <c r="Y8" s="141"/>
-      <c r="Z8" s="126" t="s">
+      <c r="V8" s="125"/>
+      <c r="W8" s="125"/>
+      <c r="X8" s="125"/>
+      <c r="Y8" s="130"/>
+      <c r="Z8" s="143" t="s">
         <v>8</v>
       </c>
       <c r="AA8" s="34"/>
     </row>
     <row r="9" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="138"/>
-      <c r="B9" s="138"/>
+      <c r="A9" s="127"/>
+      <c r="B9" s="127"/>
       <c r="C9" s="42" t="s">
         <v>27</v>
       </c>
@@ -5997,7 +5997,7 @@
       <c r="Y9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="Z9" s="127"/>
+      <c r="Z9" s="144"/>
       <c r="AA9" s="34"/>
       <c r="AB9" s="34"/>
     </row>
@@ -6485,10 +6485,10 @@
       <c r="AC16" s="10"/>
     </row>
     <row r="17" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="124" t="s">
+      <c r="A17" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="124"/>
+      <c r="B17" s="141"/>
       <c r="C17" s="18">
         <f>SUM(C10:C16)</f>
         <v>227321</v>
@@ -6607,18 +6607,18 @@
     </row>
     <row r="19" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="125" t="s">
+      <c r="B19" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="125"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="125"/>
-      <c r="I19" s="125"/>
-      <c r="J19" s="125"/>
-      <c r="K19" s="125"/>
+      <c r="C19" s="142"/>
+      <c r="D19" s="142"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="142"/>
+      <c r="G19" s="142"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="142"/>
+      <c r="J19" s="142"/>
+      <c r="K19" s="142"/>
       <c r="L19" s="49"/>
       <c r="M19" s="19"/>
       <c r="N19" s="19"/>
@@ -6637,18 +6637,18 @@
       <c r="AA19" s="19"/>
     </row>
     <row r="20" spans="1:29" ht="18" x14ac:dyDescent="0.35">
-      <c r="B20" s="122"/>
-      <c r="C20" s="122"/>
-      <c r="D20" s="122"/>
-      <c r="E20" s="122"/>
-      <c r="F20" s="122"/>
-      <c r="G20" s="122"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="122"/>
-      <c r="J20" s="122"/>
-      <c r="K20" s="122"/>
-      <c r="L20" s="122"/>
-      <c r="M20" s="122"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="139"/>
       <c r="N20" s="23"/>
       <c r="O20" s="23"/>
       <c r="P20" s="23"/>
@@ -6667,8 +6667,8 @@
         <v>4</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
@@ -6755,6 +6755,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="M1:Z1"/>
+    <mergeCell ref="M2:Z2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A5:Z5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="A6:Z6"/>
@@ -6768,12 +6774,6 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="B19:K19"/>
     <mergeCell ref="B20:M20"/>
-    <mergeCell ref="M1:Z1"/>
-    <mergeCell ref="M2:Z2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A5:Z5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6815,12 +6815,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
@@ -6831,41 +6831,41 @@
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
-      <c r="O1" s="131" t="s">
+      <c r="O1" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
-      <c r="U1" s="131"/>
-      <c r="V1" s="131"/>
-      <c r="W1" s="131"/>
-      <c r="X1" s="131"/>
-      <c r="Y1" s="131"/>
-      <c r="Z1" s="131"/>
-      <c r="AA1" s="131"/>
-      <c r="AB1" s="131"/>
-      <c r="AC1" s="131"/>
-      <c r="AD1" s="131"/>
-      <c r="AE1" s="131"/>
-      <c r="AF1" s="131"/>
-      <c r="AG1" s="131"/>
-      <c r="AH1" s="131"/>
-      <c r="AI1" s="131"/>
-      <c r="AJ1" s="131"/>
-      <c r="AK1" s="131"/>
-      <c r="AL1" s="129"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="137"/>
+      <c r="AA1" s="137"/>
+      <c r="AB1" s="137"/>
+      <c r="AC1" s="137"/>
+      <c r="AD1" s="137"/>
+      <c r="AE1" s="137"/>
+      <c r="AF1" s="137"/>
+      <c r="AG1" s="137"/>
+      <c r="AH1" s="137"/>
+      <c r="AI1" s="137"/>
+      <c r="AJ1" s="137"/>
+      <c r="AK1" s="137"/>
+      <c r="AL1" s="135"/>
       <c r="AM1" s="20"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
@@ -6876,38 +6876,38 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
-      <c r="O2" s="132" t="s">
+      <c r="O2" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="132"/>
-      <c r="Y2" s="132"/>
-      <c r="Z2" s="132"/>
-      <c r="AA2" s="132"/>
-      <c r="AB2" s="132"/>
-      <c r="AC2" s="132"/>
-      <c r="AD2" s="132"/>
-      <c r="AE2" s="132"/>
-      <c r="AF2" s="132"/>
-      <c r="AG2" s="132"/>
-      <c r="AH2" s="132"/>
-      <c r="AI2" s="132"/>
-      <c r="AJ2" s="132"/>
-      <c r="AK2" s="132"/>
-      <c r="AL2" s="129"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="138"/>
+      <c r="Y2" s="138"/>
+      <c r="Z2" s="138"/>
+      <c r="AA2" s="138"/>
+      <c r="AB2" s="138"/>
+      <c r="AC2" s="138"/>
+      <c r="AD2" s="138"/>
+      <c r="AE2" s="138"/>
+      <c r="AF2" s="138"/>
+      <c r="AG2" s="138"/>
+      <c r="AH2" s="138"/>
+      <c r="AI2" s="138"/>
+      <c r="AJ2" s="138"/>
+      <c r="AK2" s="138"/>
+      <c r="AL2" s="135"/>
       <c r="AM2" s="20"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131"/>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
@@ -6987,46 +6987,46 @@
       <c r="AM4" s="20"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="134" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="128"/>
-      <c r="T5" s="128"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="128"/>
-      <c r="W5" s="128"/>
-      <c r="X5" s="128"/>
-      <c r="Y5" s="128"/>
-      <c r="Z5" s="128"/>
-      <c r="AA5" s="128"/>
-      <c r="AB5" s="128"/>
-      <c r="AC5" s="128"/>
-      <c r="AD5" s="128"/>
-      <c r="AE5" s="128"/>
-      <c r="AF5" s="129"/>
-      <c r="AG5" s="129"/>
-      <c r="AH5" s="129"/>
-      <c r="AI5" s="129"/>
-      <c r="AJ5" s="129"/>
-      <c r="AK5" s="129"/>
-      <c r="AL5" s="129"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="134"/>
+      <c r="T5" s="134"/>
+      <c r="U5" s="134"/>
+      <c r="V5" s="134"/>
+      <c r="W5" s="134"/>
+      <c r="X5" s="134"/>
+      <c r="Y5" s="134"/>
+      <c r="Z5" s="134"/>
+      <c r="AA5" s="134"/>
+      <c r="AB5" s="134"/>
+      <c r="AC5" s="134"/>
+      <c r="AD5" s="134"/>
+      <c r="AE5" s="134"/>
+      <c r="AF5" s="135"/>
+      <c r="AG5" s="135"/>
+      <c r="AH5" s="135"/>
+      <c r="AI5" s="135"/>
+      <c r="AJ5" s="135"/>
+      <c r="AK5" s="135"/>
+      <c r="AL5" s="135"/>
       <c r="AM5" s="20"/>
     </row>
     <row r="6" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7113,17 +7113,17 @@
       <c r="AM7" s="7"/>
     </row>
     <row r="8" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="140" t="s">
+      <c r="C8" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="140"/>
-      <c r="E8" s="140"/>
+      <c r="D8" s="129"/>
+      <c r="E8" s="129"/>
       <c r="F8" s="51"/>
       <c r="G8" s="145" t="s">
         <v>32</v>
@@ -7131,47 +7131,47 @@
       <c r="H8" s="146"/>
       <c r="I8" s="146"/>
       <c r="J8" s="147"/>
-      <c r="K8" s="135" t="s">
+      <c r="K8" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="136"/>
-      <c r="M8" s="136"/>
-      <c r="N8" s="136"/>
-      <c r="O8" s="136"/>
-      <c r="P8" s="136"/>
-      <c r="Q8" s="136"/>
-      <c r="R8" s="136"/>
-      <c r="S8" s="141"/>
-      <c r="T8" s="135" t="s">
+      <c r="L8" s="125"/>
+      <c r="M8" s="125"/>
+      <c r="N8" s="125"/>
+      <c r="O8" s="125"/>
+      <c r="P8" s="125"/>
+      <c r="Q8" s="125"/>
+      <c r="R8" s="125"/>
+      <c r="S8" s="130"/>
+      <c r="T8" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="U8" s="136"/>
-      <c r="V8" s="136"/>
-      <c r="W8" s="136"/>
-      <c r="X8" s="136"/>
-      <c r="Y8" s="136"/>
-      <c r="Z8" s="136"/>
-      <c r="AA8" s="136"/>
-      <c r="AB8" s="141"/>
-      <c r="AC8" s="135" t="s">
+      <c r="U8" s="125"/>
+      <c r="V8" s="125"/>
+      <c r="W8" s="125"/>
+      <c r="X8" s="125"/>
+      <c r="Y8" s="125"/>
+      <c r="Z8" s="125"/>
+      <c r="AA8" s="125"/>
+      <c r="AB8" s="130"/>
+      <c r="AC8" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="AD8" s="136"/>
-      <c r="AE8" s="136"/>
-      <c r="AF8" s="136"/>
-      <c r="AG8" s="136"/>
-      <c r="AH8" s="136"/>
-      <c r="AI8" s="136"/>
-      <c r="AJ8" s="136"/>
-      <c r="AK8" s="141"/>
-      <c r="AL8" s="126" t="s">
+      <c r="AD8" s="125"/>
+      <c r="AE8" s="125"/>
+      <c r="AF8" s="125"/>
+      <c r="AG8" s="125"/>
+      <c r="AH8" s="125"/>
+      <c r="AI8" s="125"/>
+      <c r="AJ8" s="125"/>
+      <c r="AK8" s="130"/>
+      <c r="AL8" s="143" t="s">
         <v>8</v>
       </c>
       <c r="AM8" s="34"/>
     </row>
     <row r="9" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="138"/>
-      <c r="B9" s="138"/>
+      <c r="A9" s="127"/>
+      <c r="B9" s="127"/>
       <c r="C9" s="42" t="s">
         <v>27</v>
       </c>
@@ -7275,7 +7275,7 @@
       <c r="AK9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="AL9" s="127"/>
+      <c r="AL9" s="144"/>
       <c r="AM9" s="34"/>
       <c r="AN9" s="34"/>
     </row>
@@ -8064,10 +8064,10 @@
       <c r="AQ16" s="10"/>
     </row>
     <row r="17" spans="1:41" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="124" t="s">
+      <c r="A17" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="124"/>
+      <c r="B17" s="141"/>
       <c r="C17" s="18">
         <f>SUM(C10:C16)</f>
         <v>227321</v>
@@ -8246,18 +8246,18 @@
     </row>
     <row r="19" spans="1:41" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="125" t="s">
+      <c r="B19" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="125"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="125"/>
-      <c r="I19" s="125"/>
-      <c r="J19" s="125"/>
-      <c r="K19" s="125"/>
+      <c r="C19" s="142"/>
+      <c r="D19" s="142"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="142"/>
+      <c r="G19" s="142"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="142"/>
+      <c r="J19" s="142"/>
+      <c r="K19" s="142"/>
       <c r="L19" s="49"/>
       <c r="M19" s="49"/>
       <c r="N19" s="49"/>
@@ -8288,20 +8288,20 @@
       <c r="AM19" s="19"/>
     </row>
     <row r="20" spans="1:41" ht="18" x14ac:dyDescent="0.35">
-      <c r="B20" s="122"/>
-      <c r="C20" s="122"/>
-      <c r="D20" s="122"/>
-      <c r="E20" s="122"/>
-      <c r="F20" s="122"/>
-      <c r="G20" s="122"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="122"/>
-      <c r="J20" s="122"/>
-      <c r="K20" s="122"/>
-      <c r="L20" s="122"/>
-      <c r="M20" s="122"/>
-      <c r="N20" s="122"/>
-      <c r="O20" s="122"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="139"/>
+      <c r="N20" s="139"/>
+      <c r="O20" s="139"/>
       <c r="P20" s="23"/>
       <c r="Q20" s="23"/>
       <c r="R20" s="23"/>
@@ -8330,8 +8330,8 @@
         <v>4</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
@@ -8454,12 +8454,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A5:AL5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="O1:AL1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="O2:AL2"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="B19:K19"/>
     <mergeCell ref="B20:O20"/>
@@ -8473,6 +8467,12 @@
     <mergeCell ref="T8:AB8"/>
     <mergeCell ref="AC8:AK8"/>
     <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="A5:AL5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="O1:AL1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="O2:AL2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -8505,67 +8505,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="63"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
-      <c r="U1" s="131"/>
-      <c r="V1" s="131"/>
-      <c r="W1" s="131"/>
-      <c r="X1" s="129"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
       <c r="Y1" s="63"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="63"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="129"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
       <c r="Y2" s="63"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131"/>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="63"/>
       <c r="E3" s="63"/>
       <c r="F3" s="17"/>
@@ -8617,32 +8617,32 @@
       <c r="Y4" s="63"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="134" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="129"/>
-      <c r="T5" s="129"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="129"/>
-      <c r="W5" s="129"/>
-      <c r="X5" s="129"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
       <c r="Y5" s="63"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8674,49 +8674,49 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="140" t="s">
+      <c r="C7" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="135" t="s">
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="135" t="s">
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="136"/>
-      <c r="P7" s="136"/>
-      <c r="Q7" s="141"/>
-      <c r="R7" s="135" t="s">
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="S7" s="136"/>
-      <c r="T7" s="136"/>
-      <c r="U7" s="136"/>
-      <c r="V7" s="136"/>
-      <c r="W7" s="141"/>
-      <c r="X7" s="126" t="s">
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
         <v>8</v>
       </c>
       <c r="Y7" s="34"/>
     </row>
     <row r="8" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="138"/>
-      <c r="B8" s="138"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="68" t="s">
         <v>27</v>
       </c>
@@ -8780,7 +8780,7 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="127"/>
+      <c r="X8" s="144"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
@@ -9430,10 +9430,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="124"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -9552,13 +9552,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="125" t="s">
+      <c r="B18" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="64"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -9580,12 +9580,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="122"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
       <c r="H19" s="65"/>
       <c r="I19" s="65"/>
       <c r="J19" s="65"/>
@@ -9608,8 +9608,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="123"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
       <c r="F20" s="66"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -9690,14 +9690,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
     <mergeCell ref="X7:X8"/>
@@ -9707,6 +9699,14 @@
     <mergeCell ref="H2:X2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -9739,67 +9739,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="75"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
-      <c r="U1" s="131"/>
-      <c r="V1" s="131"/>
-      <c r="W1" s="131"/>
-      <c r="X1" s="129"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
       <c r="Y1" s="75"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="75"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="129"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
       <c r="Y2" s="75"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131"/>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="75"/>
       <c r="E3" s="75"/>
       <c r="F3" s="17"/>
@@ -9851,32 +9851,32 @@
       <c r="Y4" s="75"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="134" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="129"/>
-      <c r="T5" s="129"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="129"/>
-      <c r="W5" s="129"/>
-      <c r="X5" s="129"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
       <c r="Y5" s="75"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9908,49 +9908,49 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="140" t="s">
+      <c r="C7" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="135" t="s">
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="135" t="s">
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="136"/>
-      <c r="P7" s="136"/>
-      <c r="Q7" s="141"/>
-      <c r="R7" s="135" t="s">
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="S7" s="136"/>
-      <c r="T7" s="136"/>
-      <c r="U7" s="136"/>
-      <c r="V7" s="136"/>
-      <c r="W7" s="141"/>
-      <c r="X7" s="126" t="s">
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
         <v>8</v>
       </c>
       <c r="Y7" s="34"/>
     </row>
     <row r="8" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="138"/>
-      <c r="B8" s="138"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="73" t="s">
         <v>27</v>
       </c>
@@ -10014,7 +10014,7 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="127"/>
+      <c r="X8" s="144"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
@@ -10641,10 +10641,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="124"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -10763,13 +10763,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="125" t="s">
+      <c r="B18" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="78"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -10791,12 +10791,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="122"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
       <c r="H19" s="76"/>
       <c r="I19" s="76"/>
       <c r="J19" s="76"/>
@@ -10819,8 +10819,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="123"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
       <c r="F20" s="77"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -10901,6 +10901,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="X7:X8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
@@ -10912,12 +10918,6 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -10950,67 +10950,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="85"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
-      <c r="U1" s="131"/>
-      <c r="V1" s="131"/>
-      <c r="W1" s="131"/>
-      <c r="X1" s="129"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
       <c r="Y1" s="85"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="85"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="129"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
       <c r="Y2" s="85"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131"/>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="17"/>
@@ -11062,32 +11062,32 @@
       <c r="Y4" s="85"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="134" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="129"/>
-      <c r="T5" s="129"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="129"/>
-      <c r="W5" s="129"/>
-      <c r="X5" s="129"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
       <c r="Y5" s="85"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11119,49 +11119,49 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="140" t="s">
+      <c r="C7" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="135" t="s">
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="135" t="s">
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="136"/>
-      <c r="P7" s="136"/>
-      <c r="Q7" s="141"/>
-      <c r="R7" s="135" t="s">
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="136"/>
-      <c r="T7" s="136"/>
-      <c r="U7" s="136"/>
-      <c r="V7" s="136"/>
-      <c r="W7" s="141"/>
-      <c r="X7" s="126" t="s">
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
         <v>8</v>
       </c>
       <c r="Y7" s="34"/>
     </row>
     <row r="8" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="138"/>
-      <c r="B8" s="138"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="86" t="s">
         <v>27</v>
       </c>
@@ -11225,7 +11225,7 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="127"/>
+      <c r="X8" s="144"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
@@ -11881,10 +11881,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="124"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -12003,13 +12003,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="125" t="s">
+      <c r="B18" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -12034,12 +12034,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="122"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
       <c r="H19" s="81"/>
       <c r="I19" s="81"/>
       <c r="J19" s="81"/>
@@ -12062,8 +12062,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="123"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
       <c r="F20" s="82"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -12144,12 +12144,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="X7:X8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
@@ -12161,6 +12155,12 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -12196,67 +12196,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="92"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
-      <c r="U1" s="131"/>
-      <c r="V1" s="131"/>
-      <c r="W1" s="131"/>
-      <c r="X1" s="129"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
       <c r="Y1" s="92"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="92"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="129"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
       <c r="Y2" s="92"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131"/>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="92"/>
       <c r="E3" s="92"/>
       <c r="F3" s="17"/>
@@ -12308,32 +12308,32 @@
       <c r="Y4" s="92"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="134" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="129"/>
-      <c r="T5" s="129"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="129"/>
-      <c r="W5" s="129"/>
-      <c r="X5" s="129"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
       <c r="Y5" s="92"/>
     </row>
     <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12365,45 +12365,45 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="140" t="s">
+      <c r="C7" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="135" t="s">
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="135" t="s">
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="136"/>
-      <c r="P7" s="136"/>
-      <c r="Q7" s="141"/>
-      <c r="R7" s="135" t="s">
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="136"/>
-      <c r="T7" s="136"/>
-      <c r="U7" s="136"/>
-      <c r="V7" s="136"/>
-      <c r="W7" s="141"/>
-      <c r="X7" s="126" t="s">
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="139" t="s">
+      <c r="Y7" s="128" t="s">
         <v>77</v>
       </c>
       <c r="Z7" s="152" t="s">
@@ -12432,8 +12432,8 @@
       <c r="AQ7" s="150"/>
     </row>
     <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="138"/>
-      <c r="B8" s="138"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="93" t="s">
         <v>27</v>
       </c>
@@ -12497,8 +12497,8 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="127"/>
-      <c r="Y8" s="139"/>
+      <c r="X8" s="144"/>
+      <c r="Y8" s="128"/>
       <c r="Z8" s="94" t="s">
         <v>63</v>
       </c>
@@ -12600,8 +12600,8 @@
         <v>18</v>
       </c>
       <c r="O9" s="53">
-        <f>M9-'Thang 12'!Y10</f>
-        <v>179</v>
+        <f>M9-'Thang 12'!AG10</f>
+        <v>-46</v>
       </c>
       <c r="P9" s="53">
         <f>L9-M9</f>
@@ -12622,8 +12622,8 @@
         <v>-1</v>
       </c>
       <c r="U9" s="53">
-        <f>S9-'Thang 12'!AG10</f>
-        <v>-278</v>
+        <f>S9-'Thang 12'!Y10</f>
+        <v>-53</v>
       </c>
       <c r="V9" s="53">
         <f t="shared" ref="V9:V15" si="3">R9-S9</f>
@@ -12749,8 +12749,8 @@
         <v>106</v>
       </c>
       <c r="O10" s="53">
-        <f>M10-'Thang 12'!Y11</f>
-        <v>370</v>
+        <f>M10-'Thang 12'!AG11</f>
+        <v>130</v>
       </c>
       <c r="P10" s="53">
         <f t="shared" ref="P10:P15" si="8">L10-M10</f>
@@ -12771,8 +12771,8 @@
         <v>0</v>
       </c>
       <c r="U10" s="53">
-        <f>S10-'Thang 12'!AG11</f>
-        <v>-200</v>
+        <f>S10-'Thang 12'!Y11</f>
+        <v>40</v>
       </c>
       <c r="V10" s="53">
         <f t="shared" si="3"/>
@@ -12875,8 +12875,8 @@
         <v>-7</v>
       </c>
       <c r="O11" s="53">
-        <f>M11-'Thang 12'!Y12</f>
-        <v>373</v>
+        <f>M11-'Thang 12'!AG12</f>
+        <v>-46</v>
       </c>
       <c r="P11" s="53">
         <f t="shared" si="8"/>
@@ -12897,8 +12897,8 @@
         <v>0</v>
       </c>
       <c r="U11" s="53">
-        <f>S11-'Thang 12'!AG12</f>
-        <v>-382</v>
+        <f>S11-'Thang 12'!Y12</f>
+        <v>37</v>
       </c>
       <c r="V11" s="53">
         <f t="shared" si="3"/>
@@ -13001,8 +13001,8 @@
         <v>57</v>
       </c>
       <c r="O12" s="53">
-        <f>M12-'Thang 12'!Y13</f>
-        <v>716</v>
+        <f>M12-'Thang 12'!AG13</f>
+        <v>175</v>
       </c>
       <c r="P12" s="53">
         <f t="shared" si="8"/>
@@ -13023,8 +13023,8 @@
         <v>-2</v>
       </c>
       <c r="U12" s="53">
-        <f>S12-'Thang 12'!AG13</f>
-        <v>-460</v>
+        <f>S12-'Thang 12'!Y13</f>
+        <v>81</v>
       </c>
       <c r="V12" s="53">
         <f t="shared" si="3"/>
@@ -13127,8 +13127,8 @@
         <v>9</v>
       </c>
       <c r="O13" s="53">
-        <f>M13-'Thang 12'!Y14</f>
-        <v>58</v>
+        <f>M13-'Thang 12'!AG14</f>
+        <v>-35</v>
       </c>
       <c r="P13" s="53">
         <f t="shared" si="8"/>
@@ -13149,8 +13149,8 @@
         <v>0</v>
       </c>
       <c r="U13" s="53">
-        <f>S13-'Thang 12'!AG14</f>
-        <v>-143</v>
+        <f>S13-'Thang 12'!Y14</f>
+        <v>-50</v>
       </c>
       <c r="V13" s="53">
         <f t="shared" si="3"/>
@@ -13253,8 +13253,8 @@
         <v>65</v>
       </c>
       <c r="O14" s="53">
-        <f>M14-'Thang 12'!Y15</f>
-        <v>638</v>
+        <f>M14-'Thang 12'!AG15</f>
+        <v>30</v>
       </c>
       <c r="P14" s="53">
         <f t="shared" si="8"/>
@@ -13275,8 +13275,8 @@
         <v>0</v>
       </c>
       <c r="U14" s="53">
-        <f>S14-'Thang 12'!AG15</f>
-        <v>-563</v>
+        <f>S14-'Thang 12'!Y15</f>
+        <v>45</v>
       </c>
       <c r="V14" s="53">
         <f t="shared" si="3"/>
@@ -13371,8 +13371,8 @@
         <v>-32</v>
       </c>
       <c r="O15" s="53">
-        <f>M15-'Thang 12'!Y16</f>
-        <v>685</v>
+        <f>M15-'Thang 12'!AG16</f>
+        <v>28</v>
       </c>
       <c r="P15" s="53">
         <f t="shared" si="8"/>
@@ -13393,8 +13393,8 @@
         <v>0</v>
       </c>
       <c r="U15" s="53">
-        <f>S15-'Thang 12'!AG16</f>
-        <v>-599</v>
+        <f>S15-'Thang 12'!Y16</f>
+        <v>58</v>
       </c>
       <c r="V15" s="53">
         <f t="shared" si="3"/>
@@ -13412,10 +13412,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="124"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -13465,8 +13465,8 @@
         <v>216</v>
       </c>
       <c r="O16" s="56">
-        <f>M16-'Thang 12'!Y17</f>
-        <v>3019</v>
+        <f>SUM(O9:O15)</f>
+        <v>236</v>
       </c>
       <c r="P16" s="18">
         <f t="shared" ref="P16" si="14">SUM(P9:P15)</f>
@@ -13489,8 +13489,8 @@
         <v>-3</v>
       </c>
       <c r="U16" s="56">
-        <f>S16-'Thang 12'!AG17</f>
-        <v>-2625</v>
+        <f>SUM(U9:U15)</f>
+        <v>158</v>
       </c>
       <c r="V16" s="56">
         <f>SUM(V9:V15)</f>
@@ -13534,13 +13534,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="125" t="s">
+      <c r="B18" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -13562,12 +13562,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="122"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
       <c r="H19" s="88"/>
       <c r="I19" s="88"/>
       <c r="J19" s="88"/>
@@ -13590,8 +13590,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="123"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
       <c r="F20" s="89"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -13678,6 +13678,19 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="Y7:Y8"/>
     <mergeCell ref="AQ7:AQ8"/>
     <mergeCell ref="Z7:AF7"/>
@@ -13687,19 +13700,6 @@
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
     <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13737,67 +13737,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="114"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
-      <c r="U1" s="131"/>
-      <c r="V1" s="131"/>
-      <c r="W1" s="131"/>
-      <c r="X1" s="129"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
       <c r="Y1" s="114"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="114"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="129"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
       <c r="Y2" s="114"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131"/>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="114"/>
       <c r="E3" s="114"/>
       <c r="F3" s="17"/>
@@ -13849,32 +13849,32 @@
       <c r="Y4" s="114"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="134" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="129"/>
-      <c r="T5" s="129"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="129"/>
-      <c r="W5" s="129"/>
-      <c r="X5" s="129"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
       <c r="Y5" s="114"/>
     </row>
     <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13906,45 +13906,45 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="140" t="s">
+      <c r="C7" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="135" t="s">
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="135" t="s">
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="136"/>
-      <c r="P7" s="136"/>
-      <c r="Q7" s="141"/>
-      <c r="R7" s="135" t="s">
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="136"/>
-      <c r="T7" s="136"/>
-      <c r="U7" s="136"/>
-      <c r="V7" s="136"/>
-      <c r="W7" s="141"/>
-      <c r="X7" s="126" t="s">
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="139" t="s">
+      <c r="Y7" s="128" t="s">
         <v>77</v>
       </c>
       <c r="Z7" s="152" t="s">
@@ -13973,8 +13973,8 @@
       <c r="AQ7" s="150"/>
     </row>
     <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="138"/>
-      <c r="B8" s="138"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="115" t="s">
         <v>27</v>
       </c>
@@ -14038,8 +14038,8 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="127"/>
-      <c r="Y8" s="139"/>
+      <c r="X8" s="144"/>
+      <c r="Y8" s="128"/>
       <c r="Z8" s="94" t="s">
         <v>63</v>
       </c>
@@ -14141,8 +14141,8 @@
         <v>14</v>
       </c>
       <c r="O9" s="53">
-        <f>M9-'Thang 12'!Y10</f>
-        <v>193</v>
+        <f>M9-'Thang 12'!AG10</f>
+        <v>-32</v>
       </c>
       <c r="P9" s="53">
         <f>L9-M9</f>
@@ -14163,8 +14163,8 @@
         <v>35</v>
       </c>
       <c r="U9" s="53">
-        <f>S9-'Thang 12'!AG10</f>
-        <v>-243</v>
+        <f>S9-'Thang 12'!Y10</f>
+        <v>-18</v>
       </c>
       <c r="V9" s="53">
         <f t="shared" ref="V9:V15" si="3">R9-S9</f>
@@ -14290,8 +14290,8 @@
         <v>65</v>
       </c>
       <c r="O10" s="53">
-        <f>M10-'Thang 12'!Y11</f>
-        <v>435</v>
+        <f>M10-'Thang 12'!AG11</f>
+        <v>195</v>
       </c>
       <c r="P10" s="53">
         <f t="shared" ref="P10:P15" si="8">L10-M10</f>
@@ -14312,8 +14312,8 @@
         <v>6</v>
       </c>
       <c r="U10" s="53">
-        <f>S10-'Thang 12'!AG11</f>
-        <v>-194</v>
+        <f>S10-'Thang 12'!Y11</f>
+        <v>46</v>
       </c>
       <c r="V10" s="53">
         <f t="shared" si="3"/>
@@ -14416,8 +14416,8 @@
         <v>61</v>
       </c>
       <c r="O11" s="53">
-        <f>M11-'Thang 12'!Y12</f>
-        <v>434</v>
+        <f>M11-'Thang 12'!AG12</f>
+        <v>15</v>
       </c>
       <c r="P11" s="53">
         <f t="shared" si="8"/>
@@ -14438,8 +14438,8 @@
         <v>-9</v>
       </c>
       <c r="U11" s="53">
-        <f>S11-'Thang 12'!AG12</f>
-        <v>-391</v>
+        <f>S11-'Thang 12'!Y12</f>
+        <v>28</v>
       </c>
       <c r="V11" s="53">
         <f t="shared" si="3"/>
@@ -14542,8 +14542,8 @@
         <v>93</v>
       </c>
       <c r="O12" s="53">
-        <f>M12-'Thang 12'!Y13</f>
-        <v>809</v>
+        <f>M12-'Thang 12'!AG13</f>
+        <v>268</v>
       </c>
       <c r="P12" s="53">
         <f t="shared" si="8"/>
@@ -14564,8 +14564,8 @@
         <v>35</v>
       </c>
       <c r="U12" s="53">
-        <f>S12-'Thang 12'!AG13</f>
-        <v>-425</v>
+        <f>S12-'Thang 12'!Y13</f>
+        <v>116</v>
       </c>
       <c r="V12" s="53">
         <f t="shared" si="3"/>
@@ -14668,8 +14668,8 @@
         <v>33</v>
       </c>
       <c r="O13" s="53">
-        <f>M13-'Thang 12'!Y14</f>
-        <v>91</v>
+        <f>M13-'Thang 12'!AG14</f>
+        <v>-2</v>
       </c>
       <c r="P13" s="53">
         <f t="shared" si="8"/>
@@ -14690,8 +14690,8 @@
         <v>-7</v>
       </c>
       <c r="U13" s="53">
-        <f>S13-'Thang 12'!AG14</f>
-        <v>-150</v>
+        <f>S13-'Thang 12'!Y14</f>
+        <v>-57</v>
       </c>
       <c r="V13" s="53">
         <f t="shared" si="3"/>
@@ -14794,8 +14794,8 @@
         <v>53</v>
       </c>
       <c r="O14" s="53">
-        <f>M14-'Thang 12'!Y15</f>
-        <v>691</v>
+        <f>M14-'Thang 12'!AG15</f>
+        <v>83</v>
       </c>
       <c r="P14" s="53">
         <f t="shared" si="8"/>
@@ -14816,8 +14816,8 @@
         <v>0</v>
       </c>
       <c r="U14" s="53">
-        <f>S14-'Thang 12'!AG15</f>
-        <v>-563</v>
+        <f>S14-'Thang 12'!Y15</f>
+        <v>45</v>
       </c>
       <c r="V14" s="53">
         <f t="shared" si="3"/>
@@ -14912,8 +14912,8 @@
         <v>-43</v>
       </c>
       <c r="O15" s="53">
-        <f>M15-'Thang 12'!Y16</f>
-        <v>642</v>
+        <f>M15-'Thang 12'!AG16</f>
+        <v>-15</v>
       </c>
       <c r="P15" s="53">
         <f t="shared" si="8"/>
@@ -14934,8 +14934,8 @@
         <v>-6</v>
       </c>
       <c r="U15" s="53">
-        <f>S15-'Thang 12'!AG16</f>
-        <v>-605</v>
+        <f>S15-'Thang 12'!Y16</f>
+        <v>52</v>
       </c>
       <c r="V15" s="53">
         <f t="shared" si="3"/>
@@ -14953,10 +14953,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="124"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -15006,8 +15006,8 @@
         <v>276</v>
       </c>
       <c r="O16" s="56">
-        <f>M16-'Thang 12'!Y17</f>
-        <v>3295</v>
+        <f>SUM(O9:O15)</f>
+        <v>512</v>
       </c>
       <c r="P16" s="18">
         <f t="shared" ref="P16" si="14">SUM(P9:P15)</f>
@@ -15030,8 +15030,8 @@
         <v>54</v>
       </c>
       <c r="U16" s="56">
-        <f>S16-'Thang 12'!AG17</f>
-        <v>-2571</v>
+        <f>SUM(U9:U15)</f>
+        <v>212</v>
       </c>
       <c r="V16" s="56">
         <f>SUM(V9:V15)</f>
@@ -15075,13 +15075,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="125" t="s">
+      <c r="B18" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -15103,12 +15103,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="122"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
       <c r="H19" s="110"/>
       <c r="I19" s="110"/>
       <c r="J19" s="110"/>
@@ -15131,8 +15131,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="123"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
       <c r="F20" s="111"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -15216,17 +15216,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AH7:AP7"/>
-    <mergeCell ref="AQ7:AQ8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:G19"/>
@@ -15238,6 +15227,17 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AP7"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -15274,67 +15274,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
       <c r="E1" s="118"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
-      <c r="U1" s="131"/>
-      <c r="V1" s="131"/>
-      <c r="W1" s="131"/>
-      <c r="X1" s="129"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="135"/>
       <c r="Y1" s="118"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
       <c r="E2" s="118"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="129"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="135"/>
       <c r="Y2" s="118"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131"/>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
       <c r="D3" s="118"/>
       <c r="E3" s="118"/>
       <c r="F3" s="17"/>
@@ -15386,32 +15386,32 @@
       <c r="Y4" s="118"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="134" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="129"/>
-      <c r="T5" s="129"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="129"/>
-      <c r="W5" s="129"/>
-      <c r="X5" s="129"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="135"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="X5" s="135"/>
       <c r="Y5" s="118"/>
     </row>
     <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15443,45 +15443,45 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="140" t="s">
+      <c r="C7" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="135" t="s">
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="135" t="s">
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="136"/>
-      <c r="P7" s="136"/>
-      <c r="Q7" s="141"/>
-      <c r="R7" s="135" t="s">
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="125"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="136"/>
-      <c r="T7" s="136"/>
-      <c r="U7" s="136"/>
-      <c r="V7" s="136"/>
-      <c r="W7" s="141"/>
-      <c r="X7" s="126" t="s">
+      <c r="S7" s="125"/>
+      <c r="T7" s="125"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="139" t="s">
+      <c r="Y7" s="128" t="s">
         <v>77</v>
       </c>
       <c r="Z7" s="152" t="s">
@@ -15510,8 +15510,8 @@
       <c r="AQ7" s="150"/>
     </row>
     <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="138"/>
-      <c r="B8" s="138"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="116" t="s">
         <v>27</v>
       </c>
@@ -15575,8 +15575,8 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="127"/>
-      <c r="Y8" s="139"/>
+      <c r="X8" s="144"/>
+      <c r="Y8" s="128"/>
       <c r="Z8" s="94" t="s">
         <v>63</v>
       </c>
@@ -15674,8 +15674,8 @@
         <v>-1624</v>
       </c>
       <c r="O9" s="53">
-        <f>M9-'Thang 12'!Y10</f>
-        <v>-1445</v>
+        <f>M9-'Thang 12'!AG10</f>
+        <v>-1670</v>
       </c>
       <c r="P9" s="53">
         <f>L9-M9</f>
@@ -15694,8 +15694,8 @@
         <v>-1392</v>
       </c>
       <c r="U9" s="53">
-        <f>S9-'Thang 12'!AG10</f>
-        <v>-1670</v>
+        <f>S9-'Thang 12'!Y10</f>
+        <v>-1445</v>
       </c>
       <c r="V9" s="53">
         <f t="shared" ref="V9:V15" si="3">R9-S9</f>
@@ -15817,8 +15817,8 @@
         <v>-720</v>
       </c>
       <c r="O10" s="53">
-        <f>M10-'Thang 12'!Y11</f>
-        <v>-350</v>
+        <f>M10-'Thang 12'!AG11</f>
+        <v>-590</v>
       </c>
       <c r="P10" s="53">
         <f t="shared" ref="P10:P15" si="8">L10-M10</f>
@@ -15837,8 +15837,8 @@
         <v>-390</v>
       </c>
       <c r="U10" s="53">
-        <f>S10-'Thang 12'!AG11</f>
-        <v>-590</v>
+        <f>S10-'Thang 12'!Y11</f>
+        <v>-350</v>
       </c>
       <c r="V10" s="53">
         <f t="shared" si="3"/>
@@ -15937,8 +15937,8 @@
         <v>-770</v>
       </c>
       <c r="O11" s="53">
-        <f>M11-'Thang 12'!Y12</f>
-        <v>-397</v>
+        <f>M11-'Thang 12'!AG12</f>
+        <v>-816</v>
       </c>
       <c r="P11" s="53">
         <f t="shared" si="8"/>
@@ -15957,8 +15957,8 @@
         <v>-434</v>
       </c>
       <c r="U11" s="53">
-        <f>S11-'Thang 12'!AG12</f>
-        <v>-816</v>
+        <f>S11-'Thang 12'!Y12</f>
+        <v>-397</v>
       </c>
       <c r="V11" s="53">
         <f t="shared" si="3"/>
@@ -16057,8 +16057,8 @@
         <v>-1626</v>
       </c>
       <c r="O12" s="53">
-        <f>M12-'Thang 12'!Y13</f>
-        <v>-910</v>
+        <f>M12-'Thang 12'!AG13</f>
+        <v>-1451</v>
       </c>
       <c r="P12" s="53">
         <f t="shared" si="8"/>
@@ -16077,8 +16077,8 @@
         <v>-991</v>
       </c>
       <c r="U12" s="53">
-        <f>S12-'Thang 12'!AG13</f>
-        <v>-1451</v>
+        <f>S12-'Thang 12'!Y13</f>
+        <v>-910</v>
       </c>
       <c r="V12" s="53">
         <f t="shared" si="3"/>
@@ -16177,8 +16177,8 @@
         <v>-972</v>
       </c>
       <c r="O13" s="53">
-        <f>M13-'Thang 12'!Y14</f>
-        <v>-914</v>
+        <f>M13-'Thang 12'!AG14</f>
+        <v>-1007</v>
       </c>
       <c r="P13" s="53">
         <f t="shared" si="8"/>
@@ -16197,8 +16197,8 @@
         <v>-864</v>
       </c>
       <c r="U13" s="53">
-        <f>S13-'Thang 12'!AG14</f>
-        <v>-1007</v>
+        <f>S13-'Thang 12'!Y14</f>
+        <v>-914</v>
       </c>
       <c r="V13" s="53">
         <f t="shared" si="3"/>
@@ -16297,8 +16297,8 @@
         <v>-1010</v>
       </c>
       <c r="O14" s="53">
-        <f>M14-'Thang 12'!Y15</f>
-        <v>-372</v>
+        <f>M14-'Thang 12'!AG15</f>
+        <v>-980</v>
       </c>
       <c r="P14" s="53">
         <f t="shared" si="8"/>
@@ -16317,8 +16317,8 @@
         <v>-417</v>
       </c>
       <c r="U14" s="53">
-        <f>S14-'Thang 12'!AG15</f>
-        <v>-980</v>
+        <f>S14-'Thang 12'!Y15</f>
+        <v>-372</v>
       </c>
       <c r="V14" s="53">
         <f t="shared" si="3"/>
@@ -16409,8 +16409,8 @@
         <v>-1068</v>
       </c>
       <c r="O15" s="53">
-        <f>M15-'Thang 12'!Y16</f>
-        <v>-383</v>
+        <f>M15-'Thang 12'!AG16</f>
+        <v>-1040</v>
       </c>
       <c r="P15" s="53">
         <f t="shared" si="8"/>
@@ -16429,8 +16429,8 @@
         <v>-441</v>
       </c>
       <c r="U15" s="53">
-        <f>S15-'Thang 12'!AG16</f>
-        <v>-1040</v>
+        <f>S15-'Thang 12'!Y16</f>
+        <v>-383</v>
       </c>
       <c r="V15" s="53">
         <f t="shared" si="3"/>
@@ -16448,10 +16448,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="124"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -16501,8 +16501,8 @@
         <v>-7790</v>
       </c>
       <c r="O16" s="56">
-        <f>M16-'Thang 12'!Y17</f>
-        <v>-4771</v>
+        <f>SUM(O9:O15)</f>
+        <v>-7554</v>
       </c>
       <c r="P16" s="18">
         <f t="shared" ref="P16" si="14">SUM(P9:P15)</f>
@@ -16525,8 +16525,8 @@
         <v>-4929</v>
       </c>
       <c r="U16" s="56">
-        <f>S16-'Thang 12'!AG17</f>
-        <v>-7554</v>
+        <f>SUM(U9:U15)</f>
+        <v>-4771</v>
       </c>
       <c r="V16" s="56">
         <f>SUM(V9:V15)</f>
@@ -16570,13 +16570,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="125" t="s">
+      <c r="B18" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -16598,12 +16598,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="122"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="122"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
       <c r="H19" s="119"/>
       <c r="I19" s="119"/>
       <c r="J19" s="119"/>
@@ -16626,8 +16626,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="123"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
       <c r="F20" s="120"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -16711,6 +16711,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AP7"/>
+    <mergeCell ref="AQ7:AQ8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:G19"/>
@@ -16722,17 +16733,6 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AH7:AP7"/>
-    <mergeCell ref="AQ7:AQ8"/>
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/T07_BHXH, BHTN_2026.xlsx
+++ b/T07_BHXH, BHTN_2026.xlsx
@@ -18,10 +18,10 @@
     <sheet name="Thang 4" sheetId="8" r:id="rId4"/>
     <sheet name="Thang 5" sheetId="9" r:id="rId5"/>
     <sheet name="Thang 6" sheetId="10" r:id="rId6"/>
-    <sheet name="Tháng 7_2025" sheetId="11" r:id="rId7"/>
-    <sheet name="Tháng 8_2025" sheetId="12" r:id="rId8"/>
-    <sheet name="Tháng 9_2025" sheetId="13" r:id="rId9"/>
-    <sheet name="Tháng 10_2025" sheetId="14" r:id="rId10"/>
+    <sheet name="Tháng 7_2026" sheetId="11" r:id="rId7"/>
+    <sheet name="Tháng 8_2026" sheetId="12" r:id="rId8"/>
+    <sheet name="Tháng 9_2026" sheetId="13" r:id="rId9"/>
+    <sheet name="Tháng 10_2026" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="84">
   <si>
     <t>STT</t>
   </si>
@@ -812,7 +812,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1030,9 +1030,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1090,9 +1087,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1117,11 +1111,41 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1158,39 +1182,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2617,11 +2608,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
       <c r="D1" s="20"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
@@ -2636,36 +2627,36 @@
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
-      <c r="R1" s="137" t="s">
+      <c r="R1" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="137"/>
-      <c r="Y1" s="137"/>
-      <c r="Z1" s="137"/>
-      <c r="AA1" s="137"/>
-      <c r="AB1" s="137"/>
-      <c r="AC1" s="137"/>
-      <c r="AD1" s="137"/>
-      <c r="AE1" s="137"/>
-      <c r="AF1" s="137"/>
-      <c r="AG1" s="137"/>
-      <c r="AH1" s="137"/>
-      <c r="AI1" s="137"/>
-      <c r="AJ1" s="137"/>
-      <c r="AK1" s="135"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="128"/>
+      <c r="Y1" s="128"/>
+      <c r="Z1" s="128"/>
+      <c r="AA1" s="128"/>
+      <c r="AB1" s="128"/>
+      <c r="AC1" s="128"/>
+      <c r="AD1" s="128"/>
+      <c r="AE1" s="128"/>
+      <c r="AF1" s="128"/>
+      <c r="AG1" s="128"/>
+      <c r="AH1" s="128"/>
+      <c r="AI1" s="128"/>
+      <c r="AJ1" s="128"/>
+      <c r="AK1" s="126"/>
       <c r="AL1" s="20"/>
     </row>
     <row r="2" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
@@ -2680,36 +2671,36 @@
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
-      <c r="R2" s="138" t="s">
+      <c r="R2" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="138"/>
-      <c r="Y2" s="138"/>
-      <c r="Z2" s="138"/>
-      <c r="AA2" s="138"/>
-      <c r="AB2" s="138"/>
-      <c r="AC2" s="138"/>
-      <c r="AD2" s="138"/>
-      <c r="AE2" s="138"/>
-      <c r="AF2" s="138"/>
-      <c r="AG2" s="138"/>
-      <c r="AH2" s="138"/>
-      <c r="AI2" s="138"/>
-      <c r="AJ2" s="138"/>
-      <c r="AK2" s="135"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
+      <c r="Y2" s="129"/>
+      <c r="Z2" s="129"/>
+      <c r="AA2" s="129"/>
+      <c r="AB2" s="129"/>
+      <c r="AC2" s="129"/>
+      <c r="AD2" s="129"/>
+      <c r="AE2" s="129"/>
+      <c r="AF2" s="129"/>
+      <c r="AG2" s="129"/>
+      <c r="AH2" s="129"/>
+      <c r="AI2" s="129"/>
+      <c r="AJ2" s="129"/>
+      <c r="AK2" s="126"/>
       <c r="AL2" s="20"/>
     </row>
     <row r="3" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
@@ -2787,87 +2778,87 @@
       <c r="AL4" s="20"/>
     </row>
     <row r="5" spans="1:40" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="134"/>
-      <c r="T5" s="134"/>
-      <c r="U5" s="134"/>
-      <c r="V5" s="134"/>
-      <c r="W5" s="134"/>
-      <c r="X5" s="134"/>
-      <c r="Y5" s="134"/>
-      <c r="Z5" s="134"/>
-      <c r="AA5" s="134"/>
-      <c r="AB5" s="134"/>
-      <c r="AC5" s="134"/>
-      <c r="AD5" s="135"/>
-      <c r="AE5" s="135"/>
-      <c r="AF5" s="135"/>
-      <c r="AG5" s="135"/>
-      <c r="AH5" s="135"/>
-      <c r="AI5" s="135"/>
-      <c r="AJ5" s="135"/>
-      <c r="AK5" s="135"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="125"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="125"/>
+      <c r="W5" s="125"/>
+      <c r="X5" s="125"/>
+      <c r="Y5" s="125"/>
+      <c r="Z5" s="125"/>
+      <c r="AA5" s="125"/>
+      <c r="AB5" s="125"/>
+      <c r="AC5" s="125"/>
+      <c r="AD5" s="126"/>
+      <c r="AE5" s="126"/>
+      <c r="AF5" s="126"/>
+      <c r="AG5" s="126"/>
+      <c r="AH5" s="126"/>
+      <c r="AI5" s="126"/>
+      <c r="AJ5" s="126"/>
+      <c r="AK5" s="126"/>
       <c r="AL5" s="20"/>
     </row>
     <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="130" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="122"/>
-      <c r="O6" s="122"/>
-      <c r="P6" s="122"/>
-      <c r="Q6" s="122"/>
-      <c r="R6" s="122"/>
-      <c r="S6" s="122"/>
-      <c r="T6" s="122"/>
-      <c r="U6" s="122"/>
-      <c r="V6" s="122"/>
-      <c r="W6" s="122"/>
-      <c r="X6" s="122"/>
-      <c r="Y6" s="122"/>
-      <c r="Z6" s="122"/>
-      <c r="AA6" s="122"/>
-      <c r="AB6" s="122"/>
-      <c r="AC6" s="122"/>
-      <c r="AD6" s="123"/>
-      <c r="AE6" s="123"/>
-      <c r="AF6" s="123"/>
-      <c r="AG6" s="123"/>
-      <c r="AH6" s="123"/>
-      <c r="AI6" s="123"/>
-      <c r="AJ6" s="123"/>
-      <c r="AK6" s="123"/>
+      <c r="B6" s="130"/>
+      <c r="C6" s="130"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
+      <c r="J6" s="130"/>
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
+      <c r="M6" s="130"/>
+      <c r="N6" s="130"/>
+      <c r="O6" s="130"/>
+      <c r="P6" s="130"/>
+      <c r="Q6" s="130"/>
+      <c r="R6" s="130"/>
+      <c r="S6" s="130"/>
+      <c r="T6" s="130"/>
+      <c r="U6" s="130"/>
+      <c r="V6" s="130"/>
+      <c r="W6" s="130"/>
+      <c r="X6" s="130"/>
+      <c r="Y6" s="130"/>
+      <c r="Z6" s="130"/>
+      <c r="AA6" s="130"/>
+      <c r="AB6" s="130"/>
+      <c r="AC6" s="130"/>
+      <c r="AD6" s="131"/>
+      <c r="AE6" s="131"/>
+      <c r="AF6" s="131"/>
+      <c r="AG6" s="131"/>
+      <c r="AH6" s="131"/>
+      <c r="AI6" s="131"/>
+      <c r="AJ6" s="131"/>
+      <c r="AK6" s="131"/>
       <c r="AL6" s="24"/>
     </row>
     <row r="7" spans="1:40" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2912,64 +2903,64 @@
       <c r="AL7" s="7"/>
     </row>
     <row r="8" spans="1:40" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="126" t="s">
+      <c r="B8" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="124" t="s">
+      <c r="C8" s="132" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="128" t="s">
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="136" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="129"/>
-      <c r="J8" s="129"/>
-      <c r="K8" s="129"/>
-      <c r="L8" s="129"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="137"/>
+      <c r="K8" s="137"/>
+      <c r="L8" s="137"/>
       <c r="M8" s="51"/>
-      <c r="N8" s="124" t="s">
+      <c r="N8" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="125"/>
-      <c r="P8" s="125"/>
-      <c r="Q8" s="125"/>
-      <c r="R8" s="125"/>
-      <c r="S8" s="125"/>
-      <c r="T8" s="130"/>
+      <c r="O8" s="133"/>
+      <c r="P8" s="133"/>
+      <c r="Q8" s="133"/>
+      <c r="R8" s="133"/>
+      <c r="S8" s="133"/>
+      <c r="T8" s="138"/>
       <c r="U8" s="52"/>
-      <c r="V8" s="124" t="s">
+      <c r="V8" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="W8" s="125"/>
-      <c r="X8" s="125"/>
-      <c r="Y8" s="125"/>
-      <c r="Z8" s="125"/>
-      <c r="AA8" s="125"/>
-      <c r="AB8" s="130"/>
+      <c r="W8" s="133"/>
+      <c r="X8" s="133"/>
+      <c r="Y8" s="133"/>
+      <c r="Z8" s="133"/>
+      <c r="AA8" s="133"/>
+      <c r="AB8" s="138"/>
       <c r="AC8" s="58"/>
-      <c r="AD8" s="131" t="s">
+      <c r="AD8" s="139" t="s">
         <v>11</v>
       </c>
-      <c r="AE8" s="132"/>
-      <c r="AF8" s="132"/>
-      <c r="AG8" s="132"/>
-      <c r="AH8" s="132"/>
-      <c r="AI8" s="132"/>
-      <c r="AJ8" s="133"/>
-      <c r="AK8" s="143" t="s">
+      <c r="AE8" s="140"/>
+      <c r="AF8" s="140"/>
+      <c r="AG8" s="140"/>
+      <c r="AH8" s="140"/>
+      <c r="AI8" s="140"/>
+      <c r="AJ8" s="141"/>
+      <c r="AK8" s="123" t="s">
         <v>8</v>
       </c>
       <c r="AL8" s="34"/>
     </row>
     <row r="9" spans="1:40" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="127"/>
-      <c r="B9" s="127"/>
+      <c r="A9" s="135"/>
+      <c r="B9" s="135"/>
       <c r="C9" s="42" t="s">
         <v>27</v>
       </c>
@@ -3072,7 +3063,7 @@
       <c r="AJ9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="AK9" s="144"/>
+      <c r="AK9" s="124"/>
       <c r="AL9" s="34"/>
       <c r="AM9" s="34"/>
     </row>
@@ -3727,10 +3718,10 @@
       <c r="AN16" s="10"/>
     </row>
     <row r="17" spans="1:40" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="141" t="s">
+      <c r="A17" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="141"/>
+      <c r="B17" s="121"/>
       <c r="C17" s="18">
         <f>SUM(C10:C16)</f>
         <v>227321</v>
@@ -3907,22 +3898,22 @@
     </row>
     <row r="19" spans="1:40" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="142" t="s">
+      <c r="B19" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="142"/>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="142"/>
-      <c r="G19" s="142"/>
-      <c r="H19" s="142"/>
-      <c r="I19" s="142"/>
-      <c r="J19" s="142"/>
-      <c r="K19" s="142"/>
-      <c r="L19" s="142"/>
-      <c r="M19" s="142"/>
-      <c r="N19" s="142"/>
-      <c r="O19" s="142"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="122"/>
+      <c r="J19" s="122"/>
+      <c r="K19" s="122"/>
+      <c r="L19" s="122"/>
+      <c r="M19" s="122"/>
+      <c r="N19" s="122"/>
+      <c r="O19" s="122"/>
       <c r="P19" s="49"/>
       <c r="Q19" s="49"/>
       <c r="R19" s="19"/>
@@ -3948,23 +3939,23 @@
       <c r="AL19" s="19"/>
     </row>
     <row r="20" spans="1:40" ht="18" x14ac:dyDescent="0.35">
-      <c r="B20" s="139"/>
-      <c r="C20" s="139"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="139"/>
-      <c r="I20" s="139"/>
-      <c r="J20" s="139"/>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="139"/>
-      <c r="N20" s="139"/>
-      <c r="O20" s="139"/>
-      <c r="P20" s="139"/>
-      <c r="Q20" s="139"/>
-      <c r="R20" s="139"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="119"/>
+      <c r="N20" s="119"/>
+      <c r="O20" s="119"/>
+      <c r="P20" s="119"/>
+      <c r="Q20" s="119"/>
+      <c r="R20" s="119"/>
       <c r="S20" s="23"/>
       <c r="T20" s="23"/>
       <c r="U20" s="23"/>
@@ -3990,10 +3981,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="140"/>
-      <c r="G21" s="140"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="120"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="120"/>
       <c r="H21" s="21"/>
       <c r="I21" s="21"/>
       <c r="J21" s="21"/>
@@ -4117,17 +4108,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B20:R20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="B19:O19"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="R1:AK1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="R2:AK2"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A6:AK6"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A8:A9"/>
@@ -4136,6 +4116,17 @@
     <mergeCell ref="N8:T8"/>
     <mergeCell ref="V8:AB8"/>
     <mergeCell ref="AD8:AJ8"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="R1:AK1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="R2:AK2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="B20:R20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="B19:O19"/>
+    <mergeCell ref="AK8:AK9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4146,7 +4137,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ25"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.88671875" customWidth="1"/>
@@ -4171,69 +4162,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="118"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="116"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="118"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="116"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="118"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="116"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
-      <c r="Y2" s="118"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="126"/>
+      <c r="Y2" s="116"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
       <c r="F3" s="17"/>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
@@ -4256,60 +4247,60 @@
       <c r="Y3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="117"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="117"/>
-      <c r="O4" s="117"/>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="118"/>
-      <c r="X4" s="118"/>
-      <c r="Y4" s="118"/>
+      <c r="A4" s="115"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="115"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
+      <c r="N4" s="115"/>
+      <c r="O4" s="115"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116"/>
+      <c r="V4" s="116"/>
+      <c r="W4" s="116"/>
+      <c r="X4" s="116"/>
+      <c r="Y4" s="116"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="125" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
-      <c r="Y5" s="118"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="126"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="126"/>
+      <c r="W5" s="126"/>
+      <c r="X5" s="126"/>
+      <c r="Y5" s="116"/>
     </row>
     <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
@@ -4340,190 +4331,190 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="133"/>
+      <c r="T7" s="133"/>
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="128" t="s">
+      <c r="Y7" s="136" t="s">
         <v>77</v>
       </c>
-      <c r="Z7" s="152" t="s">
+      <c r="Z7" s="149" t="s">
         <v>61</v>
       </c>
-      <c r="AA7" s="152"/>
-      <c r="AB7" s="152"/>
-      <c r="AC7" s="152"/>
-      <c r="AD7" s="152"/>
-      <c r="AE7" s="152"/>
-      <c r="AF7" s="152"/>
-      <c r="AG7" s="150" t="s">
+      <c r="AA7" s="149"/>
+      <c r="AB7" s="149"/>
+      <c r="AC7" s="149"/>
+      <c r="AD7" s="149"/>
+      <c r="AE7" s="149"/>
+      <c r="AF7" s="149"/>
+      <c r="AG7" s="147" t="s">
         <v>76</v>
       </c>
-      <c r="AH7" s="152" t="s">
+      <c r="AH7" s="149" t="s">
         <v>62</v>
       </c>
-      <c r="AI7" s="152"/>
-      <c r="AJ7" s="152"/>
-      <c r="AK7" s="152"/>
-      <c r="AL7" s="152"/>
-      <c r="AM7" s="152"/>
-      <c r="AN7" s="152"/>
-      <c r="AO7" s="152"/>
-      <c r="AP7" s="152"/>
-      <c r="AQ7" s="150"/>
+      <c r="AI7" s="149"/>
+      <c r="AJ7" s="149"/>
+      <c r="AK7" s="149"/>
+      <c r="AL7" s="149"/>
+      <c r="AM7" s="149"/>
+      <c r="AN7" s="149"/>
+      <c r="AO7" s="149"/>
+      <c r="AP7" s="149"/>
+      <c r="AQ7" s="147"/>
     </row>
     <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
-      <c r="C8" s="116" t="s">
+      <c r="A8" s="135"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="114" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="121" t="s">
+      <c r="D8" s="118" t="s">
         <v>82</v>
       </c>
       <c r="E8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="121" t="s">
+      <c r="F8" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="121" t="s">
+      <c r="G8" s="118" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="121" t="s">
+      <c r="H8" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="121" t="s">
+      <c r="I8" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="121" t="s">
+      <c r="J8" s="118" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="121" t="s">
+      <c r="L8" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="121" t="s">
+      <c r="M8" s="118" t="s">
         <v>82</v>
       </c>
-      <c r="N8" s="121" t="s">
+      <c r="N8" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="O8" s="121" t="s">
+      <c r="O8" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="P8" s="121" t="s">
+      <c r="P8" s="118" t="s">
         <v>34</v>
       </c>
       <c r="Q8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="R8" s="121" t="s">
+      <c r="R8" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="S8" s="121" t="s">
+      <c r="S8" s="118" t="s">
         <v>82</v>
       </c>
-      <c r="T8" s="121" t="s">
+      <c r="T8" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="U8" s="121" t="s">
+      <c r="U8" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="V8" s="121" t="s">
+      <c r="V8" s="118" t="s">
         <v>34</v>
       </c>
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
-      <c r="Y8" s="128"/>
-      <c r="Z8" s="94" t="s">
+      <c r="X8" s="124"/>
+      <c r="Y8" s="136"/>
+      <c r="Z8" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="AA8" s="94" t="s">
+      <c r="AA8" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="AB8" s="94" t="s">
+      <c r="AB8" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="AC8" s="94" t="s">
+      <c r="AC8" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="AD8" s="94" t="s">
+      <c r="AD8" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="AE8" s="94" t="s">
+      <c r="AE8" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="AF8" s="95" t="s">
+      <c r="AF8" s="94" t="s">
         <v>68</v>
       </c>
-      <c r="AG8" s="151"/>
-      <c r="AH8" s="95" t="s">
+      <c r="AG8" s="148"/>
+      <c r="AH8" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="AI8" s="105" t="s">
+      <c r="AI8" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="AJ8" s="105" t="s">
+      <c r="AJ8" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="AK8" s="105" t="s">
+      <c r="AK8" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="AL8" s="96" t="s">
+      <c r="AL8" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="AM8" s="96" t="s">
+      <c r="AM8" s="95" t="s">
         <v>74</v>
       </c>
-      <c r="AN8" s="94" t="s">
+      <c r="AN8" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="AO8" s="94" t="s">
+      <c r="AO8" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="AP8" s="94" t="s">
+      <c r="AP8" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="AQ8" s="151"/>
+      <c r="AQ8" s="148"/>
     </row>
     <row r="9" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26">
@@ -4547,7 +4538,7 @@
       </c>
       <c r="G9" s="30"/>
       <c r="H9" s="31">
-        <f>G9-'Tháng 7_2025'!G9</f>
+        <f>G9-'Tháng 7_2026'!G9</f>
         <v>-1528</v>
       </c>
       <c r="I9" s="31">
@@ -4567,7 +4558,7 @@
       </c>
       <c r="M9" s="30"/>
       <c r="N9" s="53">
-        <f>M9-'Tháng 7_2025'!M9</f>
+        <f>M9-'Tháng 7_2026'!M9</f>
         <v>-1624</v>
       </c>
       <c r="O9" s="53">
@@ -4587,7 +4578,7 @@
       </c>
       <c r="S9" s="31"/>
       <c r="T9" s="53">
-        <f>S9-'Tháng 7_2025'!S9</f>
+        <f>S9-'Tháng 7_2026'!S9</f>
         <v>-1392</v>
       </c>
       <c r="U9" s="53">
@@ -4603,70 +4594,70 @@
         <v>0</v>
       </c>
       <c r="X9" s="28"/>
-      <c r="Y9" s="106" t="s">
+      <c r="Y9" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="Z9" s="107">
+      <c r="Z9" s="106">
         <f>Z10+Z11+Z12+Z13</f>
         <v>466144</v>
       </c>
-      <c r="AA9" s="94">
+      <c r="AA9" s="93">
         <v>249318</v>
       </c>
-      <c r="AB9" s="94">
+      <c r="AB9" s="93">
         <v>249318</v>
       </c>
-      <c r="AC9" s="94">
+      <c r="AC9" s="93">
         <f>AA9-AB9</f>
         <v>0</v>
       </c>
-      <c r="AD9" s="94">
+      <c r="AD9" s="93">
         <f>AA9-AG9</f>
         <v>-273397</v>
       </c>
-      <c r="AE9" s="97">
+      <c r="AE9" s="96">
         <f>AA9/Z9*100</f>
         <v>53.48518912610696</v>
       </c>
-      <c r="AF9" s="98">
+      <c r="AF9" s="97">
         <f>Z9-AA9</f>
         <v>216826</v>
       </c>
-      <c r="AG9" s="104">
+      <c r="AG9" s="103">
         <v>522715</v>
       </c>
-      <c r="AH9" s="99">
+      <c r="AH9" s="98">
         <f t="shared" ref="AH9" si="5">SUM(AI9:AL9)</f>
         <v>48041</v>
       </c>
-      <c r="AI9" s="100">
+      <c r="AI9" s="99">
         <v>2881</v>
       </c>
-      <c r="AJ9" s="100">
+      <c r="AJ9" s="99">
         <v>1394</v>
       </c>
-      <c r="AK9" s="100">
+      <c r="AK9" s="99">
         <v>190</v>
       </c>
-      <c r="AL9" s="101">
+      <c r="AL9" s="100">
         <v>43576</v>
       </c>
-      <c r="AM9" s="102">
+      <c r="AM9" s="101">
         <f t="shared" ref="AM9" si="6">SUM(AJ9:AK9)</f>
         <v>1584</v>
       </c>
-      <c r="AN9" s="103">
+      <c r="AN9" s="102">
         <f>AM9/Z9*100</f>
         <v>0.33980915768517883</v>
       </c>
-      <c r="AO9" s="103">
+      <c r="AO9" s="102">
         <v>1.26</v>
       </c>
-      <c r="AP9" s="103">
+      <c r="AP9" s="102">
         <f t="shared" ref="AP9" si="7">AO9-AN9</f>
         <v>0.92019084231482118</v>
       </c>
-      <c r="AQ9" s="104"/>
+      <c r="AQ9" s="103"/>
     </row>
     <row r="10" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A10" s="26">
@@ -4690,7 +4681,7 @@
       </c>
       <c r="G10" s="30"/>
       <c r="H10" s="31">
-        <f>G10-'Tháng 7_2025'!G10</f>
+        <f>G10-'Tháng 7_2026'!G10</f>
         <v>-496</v>
       </c>
       <c r="I10" s="31">
@@ -4710,7 +4701,7 @@
       </c>
       <c r="M10" s="30"/>
       <c r="N10" s="53">
-        <f>M10-'Tháng 7_2025'!M10</f>
+        <f>M10-'Tháng 7_2026'!M10</f>
         <v>-720</v>
       </c>
       <c r="O10" s="53">
@@ -4730,7 +4721,7 @@
       </c>
       <c r="S10" s="31"/>
       <c r="T10" s="53">
-        <f>S10-'Tháng 7_2025'!S10</f>
+        <f>S10-'Tháng 7_2026'!S10</f>
         <v>-390</v>
       </c>
       <c r="U10" s="53">
@@ -4746,47 +4737,47 @@
         <v>0</v>
       </c>
       <c r="X10" s="28"/>
-      <c r="Y10" s="108" t="s">
+      <c r="Y10" s="107" t="s">
         <v>56</v>
       </c>
-      <c r="Z10" s="107">
+      <c r="Z10" s="106">
         <v>173399</v>
       </c>
-      <c r="AA10" s="94">
+      <c r="AA10" s="93">
         <v>94017</v>
       </c>
-      <c r="AB10" s="94">
+      <c r="AB10" s="93">
         <v>94017</v>
       </c>
-      <c r="AC10" s="94">
+      <c r="AC10" s="93">
         <f t="shared" ref="AC10:AC14" si="10">AA10-AB10</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="94">
+      <c r="AD10" s="93">
         <f t="shared" ref="AD10:AD14" si="11">AA10-AG10</f>
         <v>-97632</v>
       </c>
-      <c r="AE10" s="97">
+      <c r="AE10" s="96">
         <f t="shared" ref="AE10:AE13" si="12">AA10/Z10*100</f>
         <v>54.220035871025786</v>
       </c>
-      <c r="AF10" s="98">
+      <c r="AF10" s="97">
         <f t="shared" ref="AF10:AF13" si="13">Z10-AA10</f>
         <v>79382</v>
       </c>
-      <c r="AG10" s="104">
+      <c r="AG10" s="103">
         <v>191649</v>
       </c>
-      <c r="AH10" s="95"/>
-      <c r="AI10" s="105"/>
-      <c r="AJ10" s="105"/>
-      <c r="AK10" s="105"/>
-      <c r="AL10" s="96"/>
-      <c r="AM10" s="96"/>
-      <c r="AN10" s="94"/>
-      <c r="AO10" s="94"/>
-      <c r="AP10" s="94"/>
-      <c r="AQ10" s="104"/>
+      <c r="AH10" s="94"/>
+      <c r="AI10" s="104"/>
+      <c r="AJ10" s="104"/>
+      <c r="AK10" s="104"/>
+      <c r="AL10" s="95"/>
+      <c r="AM10" s="95"/>
+      <c r="AN10" s="93"/>
+      <c r="AO10" s="93"/>
+      <c r="AP10" s="93"/>
+      <c r="AQ10" s="103"/>
     </row>
     <row r="11" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A11" s="26">
@@ -4810,7 +4801,7 @@
       </c>
       <c r="G11" s="30"/>
       <c r="H11" s="31">
-        <f>G11-'Tháng 7_2025'!G11</f>
+        <f>G11-'Tháng 7_2026'!G11</f>
         <v>-519</v>
       </c>
       <c r="I11" s="31">
@@ -4830,7 +4821,7 @@
       </c>
       <c r="M11" s="30"/>
       <c r="N11" s="53">
-        <f>M11-'Tháng 7_2025'!M11</f>
+        <f>M11-'Tháng 7_2026'!M11</f>
         <v>-770</v>
       </c>
       <c r="O11" s="53">
@@ -4850,7 +4841,7 @@
       </c>
       <c r="S11" s="31"/>
       <c r="T11" s="53">
-        <f>S11-'Tháng 7_2025'!S11</f>
+        <f>S11-'Tháng 7_2026'!S11</f>
         <v>-434</v>
       </c>
       <c r="U11" s="53">
@@ -4866,47 +4857,47 @@
         <v>0</v>
       </c>
       <c r="X11" s="28"/>
-      <c r="Y11" s="108" t="s">
+      <c r="Y11" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="Z11" s="107">
+      <c r="Z11" s="106">
         <v>37255</v>
       </c>
-      <c r="AA11" s="109">
+      <c r="AA11" s="108">
         <v>19221</v>
       </c>
-      <c r="AB11" s="109">
+      <c r="AB11" s="108">
         <v>19221</v>
       </c>
-      <c r="AC11" s="94">
+      <c r="AC11" s="93">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AD11" s="94">
+      <c r="AD11" s="93">
         <f t="shared" si="11"/>
         <v>-16054</v>
       </c>
-      <c r="AE11" s="97">
+      <c r="AE11" s="96">
         <f t="shared" si="12"/>
         <v>51.593074755066439</v>
       </c>
-      <c r="AF11" s="98">
+      <c r="AF11" s="97">
         <f t="shared" si="13"/>
         <v>18034</v>
       </c>
-      <c r="AG11" s="104">
+      <c r="AG11" s="103">
         <v>35275</v>
       </c>
-      <c r="AH11" s="104"/>
-      <c r="AI11" s="104"/>
-      <c r="AJ11" s="104"/>
-      <c r="AK11" s="104"/>
-      <c r="AL11" s="104"/>
-      <c r="AM11" s="104"/>
-      <c r="AN11" s="104"/>
-      <c r="AO11" s="104"/>
-      <c r="AP11" s="104"/>
-      <c r="AQ11" s="104"/>
+      <c r="AH11" s="103"/>
+      <c r="AI11" s="103"/>
+      <c r="AJ11" s="103"/>
+      <c r="AK11" s="103"/>
+      <c r="AL11" s="103"/>
+      <c r="AM11" s="103"/>
+      <c r="AN11" s="103"/>
+      <c r="AO11" s="103"/>
+      <c r="AP11" s="103"/>
+      <c r="AQ11" s="103"/>
     </row>
     <row r="12" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="26">
@@ -4930,7 +4921,7 @@
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="31">
-        <f>G12-'Tháng 7_2025'!G12</f>
+        <f>G12-'Tháng 7_2026'!G12</f>
         <v>-1096</v>
       </c>
       <c r="I12" s="31">
@@ -4950,7 +4941,7 @@
       </c>
       <c r="M12" s="30"/>
       <c r="N12" s="53">
-        <f>M12-'Tháng 7_2025'!M12</f>
+        <f>M12-'Tháng 7_2026'!M12</f>
         <v>-1626</v>
       </c>
       <c r="O12" s="53">
@@ -4970,7 +4961,7 @@
       </c>
       <c r="S12" s="31"/>
       <c r="T12" s="53">
-        <f>S12-'Tháng 7_2025'!S12</f>
+        <f>S12-'Tháng 7_2026'!S12</f>
         <v>-991</v>
       </c>
       <c r="U12" s="53">
@@ -4986,47 +4977,47 @@
         <v>0</v>
       </c>
       <c r="X12" s="28"/>
-      <c r="Y12" s="108" t="s">
+      <c r="Y12" s="107" t="s">
         <v>58</v>
       </c>
-      <c r="Z12" s="107">
+      <c r="Z12" s="106">
         <v>10639</v>
       </c>
-      <c r="AA12" s="109">
+      <c r="AA12" s="108">
         <v>6448</v>
       </c>
-      <c r="AB12" s="109">
+      <c r="AB12" s="108">
         <v>6448</v>
       </c>
-      <c r="AC12" s="94">
+      <c r="AC12" s="93">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AD12" s="94">
+      <c r="AD12" s="93">
         <f t="shared" si="11"/>
         <v>-6661</v>
       </c>
-      <c r="AE12" s="97">
+      <c r="AE12" s="96">
         <f t="shared" si="12"/>
         <v>60.607199924804966</v>
       </c>
-      <c r="AF12" s="98">
+      <c r="AF12" s="97">
         <f t="shared" si="13"/>
         <v>4191</v>
       </c>
-      <c r="AG12" s="104">
+      <c r="AG12" s="103">
         <v>13109</v>
       </c>
-      <c r="AH12" s="104"/>
-      <c r="AI12" s="104"/>
-      <c r="AJ12" s="104"/>
-      <c r="AK12" s="104"/>
-      <c r="AL12" s="104"/>
-      <c r="AM12" s="104"/>
-      <c r="AN12" s="104"/>
-      <c r="AO12" s="104"/>
-      <c r="AP12" s="104"/>
-      <c r="AQ12" s="104"/>
+      <c r="AH12" s="103"/>
+      <c r="AI12" s="103"/>
+      <c r="AJ12" s="103"/>
+      <c r="AK12" s="103"/>
+      <c r="AL12" s="103"/>
+      <c r="AM12" s="103"/>
+      <c r="AN12" s="103"/>
+      <c r="AO12" s="103"/>
+      <c r="AP12" s="103"/>
+      <c r="AQ12" s="103"/>
     </row>
     <row r="13" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="26">
@@ -5050,7 +5041,7 @@
       </c>
       <c r="G13" s="30"/>
       <c r="H13" s="31">
-        <f>G13-'Tháng 7_2025'!G13</f>
+        <f>G13-'Tháng 7_2026'!G13</f>
         <v>-979</v>
       </c>
       <c r="I13" s="31">
@@ -5070,7 +5061,7 @@
       </c>
       <c r="M13" s="30"/>
       <c r="N13" s="53">
-        <f>M13-'Tháng 7_2025'!M13</f>
+        <f>M13-'Tháng 7_2026'!M13</f>
         <v>-972</v>
       </c>
       <c r="O13" s="53">
@@ -5090,7 +5081,7 @@
       </c>
       <c r="S13" s="31"/>
       <c r="T13" s="53">
-        <f>S13-'Tháng 7_2025'!S13</f>
+        <f>S13-'Tháng 7_2026'!S13</f>
         <v>-864</v>
       </c>
       <c r="U13" s="53">
@@ -5106,47 +5097,47 @@
         <v>0</v>
       </c>
       <c r="X13" s="28"/>
-      <c r="Y13" s="108" t="s">
+      <c r="Y13" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="Z13" s="107">
+      <c r="Z13" s="106">
         <v>244851</v>
       </c>
-      <c r="AA13" s="109">
+      <c r="AA13" s="108">
         <v>129490</v>
       </c>
-      <c r="AB13" s="109">
+      <c r="AB13" s="108">
         <v>129490</v>
       </c>
-      <c r="AC13" s="94">
+      <c r="AC13" s="93">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AD13" s="94">
+      <c r="AD13" s="93">
         <f t="shared" si="11"/>
         <v>-153011</v>
       </c>
-      <c r="AE13" s="97">
+      <c r="AE13" s="96">
         <f t="shared" si="12"/>
         <v>52.88522407504972</v>
       </c>
-      <c r="AF13" s="98">
+      <c r="AF13" s="97">
         <f t="shared" si="13"/>
         <v>115361</v>
       </c>
-      <c r="AG13" s="104">
+      <c r="AG13" s="103">
         <v>282501</v>
       </c>
-      <c r="AH13" s="104"/>
-      <c r="AI13" s="104"/>
-      <c r="AJ13" s="104"/>
-      <c r="AK13" s="104"/>
-      <c r="AL13" s="104"/>
-      <c r="AM13" s="104"/>
-      <c r="AN13" s="104"/>
-      <c r="AO13" s="104"/>
-      <c r="AP13" s="104"/>
-      <c r="AQ13" s="104"/>
+      <c r="AH13" s="103"/>
+      <c r="AI13" s="103"/>
+      <c r="AJ13" s="103"/>
+      <c r="AK13" s="103"/>
+      <c r="AL13" s="103"/>
+      <c r="AM13" s="103"/>
+      <c r="AN13" s="103"/>
+      <c r="AO13" s="103"/>
+      <c r="AP13" s="103"/>
+      <c r="AQ13" s="103"/>
     </row>
     <row r="14" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A14" s="26">
@@ -5170,7 +5161,7 @@
       </c>
       <c r="G14" s="30"/>
       <c r="H14" s="31">
-        <f>G14-'Tháng 7_2025'!G14</f>
+        <f>G14-'Tháng 7_2026'!G14</f>
         <v>-524</v>
       </c>
       <c r="I14" s="31">
@@ -5190,7 +5181,7 @@
       </c>
       <c r="M14" s="30"/>
       <c r="N14" s="53">
-        <f>M14-'Tháng 7_2025'!M14</f>
+        <f>M14-'Tháng 7_2026'!M14</f>
         <v>-1010</v>
       </c>
       <c r="O14" s="53">
@@ -5210,7 +5201,7 @@
       </c>
       <c r="S14" s="31"/>
       <c r="T14" s="53">
-        <f>S14-'Tháng 7_2025'!S14</f>
+        <f>S14-'Tháng 7_2026'!S14</f>
         <v>-417</v>
       </c>
       <c r="U14" s="53">
@@ -5226,39 +5217,39 @@
         <v>0</v>
       </c>
       <c r="X14" s="28"/>
-      <c r="Y14" s="108" t="s">
+      <c r="Y14" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="Z14" s="109"/>
-      <c r="AA14" s="109">
+      <c r="Z14" s="108"/>
+      <c r="AA14" s="108">
         <v>142</v>
       </c>
-      <c r="AB14" s="109">
+      <c r="AB14" s="108">
         <v>142</v>
       </c>
-      <c r="AC14" s="94">
+      <c r="AC14" s="93">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AD14" s="94">
+      <c r="AD14" s="93">
         <f t="shared" si="11"/>
         <v>-39</v>
       </c>
-      <c r="AE14" s="97"/>
-      <c r="AF14" s="104"/>
-      <c r="AG14" s="104">
+      <c r="AE14" s="96"/>
+      <c r="AF14" s="103"/>
+      <c r="AG14" s="103">
         <v>181</v>
       </c>
-      <c r="AH14" s="104"/>
-      <c r="AI14" s="104"/>
-      <c r="AJ14" s="104"/>
-      <c r="AK14" s="104"/>
-      <c r="AL14" s="104"/>
-      <c r="AM14" s="104"/>
-      <c r="AN14" s="104"/>
-      <c r="AO14" s="104"/>
-      <c r="AP14" s="104"/>
-      <c r="AQ14" s="104"/>
+      <c r="AH14" s="103"/>
+      <c r="AI14" s="103"/>
+      <c r="AJ14" s="103"/>
+      <c r="AK14" s="103"/>
+      <c r="AL14" s="103"/>
+      <c r="AM14" s="103"/>
+      <c r="AN14" s="103"/>
+      <c r="AO14" s="103"/>
+      <c r="AP14" s="103"/>
+      <c r="AQ14" s="103"/>
     </row>
     <row r="15" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="26">
@@ -5282,7 +5273,7 @@
       </c>
       <c r="G15" s="30"/>
       <c r="H15" s="31">
-        <f>G15-'Tháng 7_2025'!G15</f>
+        <f>G15-'Tháng 7_2026'!G15</f>
         <v>-536</v>
       </c>
       <c r="I15" s="31">
@@ -5302,7 +5293,7 @@
       </c>
       <c r="M15" s="30"/>
       <c r="N15" s="53">
-        <f>M15-'Tháng 7_2025'!M15</f>
+        <f>M15-'Tháng 7_2026'!M15</f>
         <v>-1068</v>
       </c>
       <c r="O15" s="53">
@@ -5322,7 +5313,7 @@
       </c>
       <c r="S15" s="31"/>
       <c r="T15" s="53">
-        <f>S15-'Tháng 7_2025'!S15</f>
+        <f>S15-'Tháng 7_2026'!S15</f>
         <v>-441</v>
       </c>
       <c r="U15" s="53">
@@ -5345,10 +5336,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="121"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -5440,7 +5431,7 @@
     </row>
     <row r="17" spans="1:25" ht="9.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
-      <c r="B17" s="119"/>
+      <c r="B17" s="117"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
@@ -5465,164 +5456,9 @@
       <c r="X17" s="15"/>
       <c r="Y17" s="15"/>
     </row>
-    <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="19"/>
-    </row>
-    <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="119"/>
-      <c r="J19" s="119"/>
-      <c r="K19" s="119"/>
-      <c r="L19" s="119"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="80"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B20" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-    </row>
-    <row r="21" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="120"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-    </row>
-    <row r="22" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-    </row>
-    <row r="23" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B23" s="5"/>
-      <c r="R23" s="31"/>
-    </row>
-    <row r="24" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B24" s="5"/>
-      <c r="R24" s="31"/>
-    </row>
-    <row r="25" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="R25" s="31"/>
-    </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AH7:AP7"/>
-    <mergeCell ref="AQ7:AQ8"/>
+  <mergeCells count="19">
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D20:E20"/>
     <mergeCell ref="X7:X8"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
@@ -5630,6 +5466,17 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AP7"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5669,12 +5516,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
@@ -5683,31 +5530,31 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
-      <c r="M1" s="137" t="s">
+      <c r="M1" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="137"/>
-      <c r="Y1" s="137"/>
-      <c r="Z1" s="135"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="128"/>
+      <c r="Y1" s="128"/>
+      <c r="Z1" s="126"/>
       <c r="AA1" s="20"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
@@ -5716,28 +5563,28 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="138" t="s">
+      <c r="M2" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="138"/>
-      <c r="Y2" s="138"/>
-      <c r="Z2" s="135"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
+      <c r="Y2" s="129"/>
+      <c r="Z2" s="126"/>
       <c r="AA2" s="20"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
@@ -5793,63 +5640,63 @@
       <c r="AA4" s="20"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="134"/>
-      <c r="T5" s="134"/>
-      <c r="U5" s="134"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
-      <c r="Y5" s="135"/>
-      <c r="Z5" s="135"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="125"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="126"/>
+      <c r="W5" s="126"/>
+      <c r="X5" s="126"/>
+      <c r="Y5" s="126"/>
+      <c r="Z5" s="126"/>
       <c r="AA5" s="20"/>
     </row>
     <row r="6" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="148"/>
-      <c r="B6" s="148"/>
-      <c r="C6" s="148"/>
-      <c r="D6" s="148"/>
-      <c r="E6" s="148"/>
-      <c r="F6" s="148"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="148"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="148"/>
-      <c r="K6" s="148"/>
-      <c r="L6" s="148"/>
-      <c r="M6" s="148"/>
-      <c r="N6" s="148"/>
-      <c r="O6" s="148"/>
-      <c r="P6" s="148"/>
-      <c r="Q6" s="148"/>
-      <c r="R6" s="148"/>
-      <c r="S6" s="148"/>
-      <c r="T6" s="148"/>
-      <c r="U6" s="148"/>
-      <c r="V6" s="149"/>
-      <c r="W6" s="149"/>
-      <c r="X6" s="149"/>
-      <c r="Y6" s="149"/>
-      <c r="Z6" s="149"/>
+      <c r="A6" s="145"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="145"/>
+      <c r="I6" s="145"/>
+      <c r="J6" s="145"/>
+      <c r="K6" s="145"/>
+      <c r="L6" s="145"/>
+      <c r="M6" s="145"/>
+      <c r="N6" s="145"/>
+      <c r="O6" s="145"/>
+      <c r="P6" s="145"/>
+      <c r="Q6" s="145"/>
+      <c r="R6" s="145"/>
+      <c r="S6" s="145"/>
+      <c r="T6" s="145"/>
+      <c r="U6" s="145"/>
+      <c r="V6" s="146"/>
+      <c r="W6" s="146"/>
+      <c r="X6" s="146"/>
+      <c r="Y6" s="146"/>
+      <c r="Z6" s="146"/>
       <c r="AA6" s="24"/>
     </row>
     <row r="7" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -5883,53 +5730,53 @@
       <c r="AA7" s="7"/>
     </row>
     <row r="8" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="126" t="s">
+      <c r="B8" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="129" t="s">
+      <c r="C8" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="129"/>
-      <c r="E8" s="129"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
       <c r="F8" s="51"/>
-      <c r="G8" s="145" t="s">
+      <c r="G8" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="146"/>
-      <c r="I8" s="146"/>
-      <c r="J8" s="147"/>
-      <c r="K8" s="124" t="s">
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="125"/>
-      <c r="M8" s="125"/>
-      <c r="N8" s="125"/>
-      <c r="O8" s="130"/>
-      <c r="P8" s="124" t="s">
+      <c r="L8" s="133"/>
+      <c r="M8" s="133"/>
+      <c r="N8" s="133"/>
+      <c r="O8" s="138"/>
+      <c r="P8" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="Q8" s="125"/>
-      <c r="R8" s="125"/>
-      <c r="S8" s="125"/>
-      <c r="T8" s="130"/>
-      <c r="U8" s="124" t="s">
+      <c r="Q8" s="133"/>
+      <c r="R8" s="133"/>
+      <c r="S8" s="133"/>
+      <c r="T8" s="138"/>
+      <c r="U8" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="V8" s="125"/>
-      <c r="W8" s="125"/>
-      <c r="X8" s="125"/>
-      <c r="Y8" s="130"/>
-      <c r="Z8" s="143" t="s">
+      <c r="V8" s="133"/>
+      <c r="W8" s="133"/>
+      <c r="X8" s="133"/>
+      <c r="Y8" s="138"/>
+      <c r="Z8" s="123" t="s">
         <v>8</v>
       </c>
       <c r="AA8" s="34"/>
     </row>
     <row r="9" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="127"/>
-      <c r="B9" s="127"/>
+      <c r="A9" s="135"/>
+      <c r="B9" s="135"/>
       <c r="C9" s="42" t="s">
         <v>27</v>
       </c>
@@ -5997,7 +5844,7 @@
       <c r="Y9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="Z9" s="144"/>
+      <c r="Z9" s="124"/>
       <c r="AA9" s="34"/>
       <c r="AB9" s="34"/>
     </row>
@@ -6485,10 +6332,10 @@
       <c r="AC16" s="10"/>
     </row>
     <row r="17" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="141" t="s">
+      <c r="A17" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="141"/>
+      <c r="B17" s="121"/>
       <c r="C17" s="18">
         <f>SUM(C10:C16)</f>
         <v>227321</v>
@@ -6607,18 +6454,18 @@
     </row>
     <row r="19" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="142" t="s">
+      <c r="B19" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="142"/>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="142"/>
-      <c r="G19" s="142"/>
-      <c r="H19" s="142"/>
-      <c r="I19" s="142"/>
-      <c r="J19" s="142"/>
-      <c r="K19" s="142"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="122"/>
+      <c r="J19" s="122"/>
+      <c r="K19" s="122"/>
       <c r="L19" s="49"/>
       <c r="M19" s="19"/>
       <c r="N19" s="19"/>
@@ -6637,18 +6484,18 @@
       <c r="AA19" s="19"/>
     </row>
     <row r="20" spans="1:29" ht="18" x14ac:dyDescent="0.35">
-      <c r="B20" s="139"/>
-      <c r="C20" s="139"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="139"/>
-      <c r="I20" s="139"/>
-      <c r="J20" s="139"/>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="139"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="119"/>
       <c r="N20" s="23"/>
       <c r="O20" s="23"/>
       <c r="P20" s="23"/>
@@ -6667,8 +6514,8 @@
         <v>4</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="120"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
@@ -6755,12 +6602,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="M1:Z1"/>
-    <mergeCell ref="M2:Z2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A5:Z5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="A6:Z6"/>
@@ -6774,6 +6615,12 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="B19:K19"/>
     <mergeCell ref="B20:M20"/>
+    <mergeCell ref="M1:Z1"/>
+    <mergeCell ref="M2:Z2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A5:Z5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6815,12 +6662,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
@@ -6831,41 +6678,41 @@
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
-      <c r="O1" s="137" t="s">
+      <c r="O1" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="137"/>
-      <c r="Y1" s="137"/>
-      <c r="Z1" s="137"/>
-      <c r="AA1" s="137"/>
-      <c r="AB1" s="137"/>
-      <c r="AC1" s="137"/>
-      <c r="AD1" s="137"/>
-      <c r="AE1" s="137"/>
-      <c r="AF1" s="137"/>
-      <c r="AG1" s="137"/>
-      <c r="AH1" s="137"/>
-      <c r="AI1" s="137"/>
-      <c r="AJ1" s="137"/>
-      <c r="AK1" s="137"/>
-      <c r="AL1" s="135"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="128"/>
+      <c r="Y1" s="128"/>
+      <c r="Z1" s="128"/>
+      <c r="AA1" s="128"/>
+      <c r="AB1" s="128"/>
+      <c r="AC1" s="128"/>
+      <c r="AD1" s="128"/>
+      <c r="AE1" s="128"/>
+      <c r="AF1" s="128"/>
+      <c r="AG1" s="128"/>
+      <c r="AH1" s="128"/>
+      <c r="AI1" s="128"/>
+      <c r="AJ1" s="128"/>
+      <c r="AK1" s="128"/>
+      <c r="AL1" s="126"/>
       <c r="AM1" s="20"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
@@ -6876,38 +6723,38 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
-      <c r="O2" s="138" t="s">
+      <c r="O2" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="138"/>
-      <c r="Y2" s="138"/>
-      <c r="Z2" s="138"/>
-      <c r="AA2" s="138"/>
-      <c r="AB2" s="138"/>
-      <c r="AC2" s="138"/>
-      <c r="AD2" s="138"/>
-      <c r="AE2" s="138"/>
-      <c r="AF2" s="138"/>
-      <c r="AG2" s="138"/>
-      <c r="AH2" s="138"/>
-      <c r="AI2" s="138"/>
-      <c r="AJ2" s="138"/>
-      <c r="AK2" s="138"/>
-      <c r="AL2" s="135"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
+      <c r="Y2" s="129"/>
+      <c r="Z2" s="129"/>
+      <c r="AA2" s="129"/>
+      <c r="AB2" s="129"/>
+      <c r="AC2" s="129"/>
+      <c r="AD2" s="129"/>
+      <c r="AE2" s="129"/>
+      <c r="AF2" s="129"/>
+      <c r="AG2" s="129"/>
+      <c r="AH2" s="129"/>
+      <c r="AI2" s="129"/>
+      <c r="AJ2" s="129"/>
+      <c r="AK2" s="129"/>
+      <c r="AL2" s="126"/>
       <c r="AM2" s="20"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
@@ -6987,87 +6834,87 @@
       <c r="AM4" s="20"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="134"/>
-      <c r="T5" s="134"/>
-      <c r="U5" s="134"/>
-      <c r="V5" s="134"/>
-      <c r="W5" s="134"/>
-      <c r="X5" s="134"/>
-      <c r="Y5" s="134"/>
-      <c r="Z5" s="134"/>
-      <c r="AA5" s="134"/>
-      <c r="AB5" s="134"/>
-      <c r="AC5" s="134"/>
-      <c r="AD5" s="134"/>
-      <c r="AE5" s="134"/>
-      <c r="AF5" s="135"/>
-      <c r="AG5" s="135"/>
-      <c r="AH5" s="135"/>
-      <c r="AI5" s="135"/>
-      <c r="AJ5" s="135"/>
-      <c r="AK5" s="135"/>
-      <c r="AL5" s="135"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="125"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="125"/>
+      <c r="W5" s="125"/>
+      <c r="X5" s="125"/>
+      <c r="Y5" s="125"/>
+      <c r="Z5" s="125"/>
+      <c r="AA5" s="125"/>
+      <c r="AB5" s="125"/>
+      <c r="AC5" s="125"/>
+      <c r="AD5" s="125"/>
+      <c r="AE5" s="125"/>
+      <c r="AF5" s="126"/>
+      <c r="AG5" s="126"/>
+      <c r="AH5" s="126"/>
+      <c r="AI5" s="126"/>
+      <c r="AJ5" s="126"/>
+      <c r="AK5" s="126"/>
+      <c r="AL5" s="126"/>
       <c r="AM5" s="20"/>
     </row>
     <row r="6" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="148"/>
-      <c r="B6" s="148"/>
-      <c r="C6" s="148"/>
-      <c r="D6" s="148"/>
-      <c r="E6" s="148"/>
-      <c r="F6" s="148"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="148"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="148"/>
-      <c r="K6" s="148"/>
-      <c r="L6" s="148"/>
-      <c r="M6" s="148"/>
-      <c r="N6" s="148"/>
-      <c r="O6" s="148"/>
-      <c r="P6" s="148"/>
-      <c r="Q6" s="148"/>
-      <c r="R6" s="148"/>
-      <c r="S6" s="148"/>
-      <c r="T6" s="148"/>
-      <c r="U6" s="148"/>
-      <c r="V6" s="148"/>
-      <c r="W6" s="148"/>
-      <c r="X6" s="148"/>
-      <c r="Y6" s="148"/>
-      <c r="Z6" s="148"/>
-      <c r="AA6" s="148"/>
-      <c r="AB6" s="148"/>
-      <c r="AC6" s="148"/>
-      <c r="AD6" s="148"/>
-      <c r="AE6" s="148"/>
-      <c r="AF6" s="149"/>
-      <c r="AG6" s="149"/>
-      <c r="AH6" s="149"/>
-      <c r="AI6" s="149"/>
-      <c r="AJ6" s="149"/>
-      <c r="AK6" s="149"/>
-      <c r="AL6" s="149"/>
+      <c r="A6" s="145"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="145"/>
+      <c r="I6" s="145"/>
+      <c r="J6" s="145"/>
+      <c r="K6" s="145"/>
+      <c r="L6" s="145"/>
+      <c r="M6" s="145"/>
+      <c r="N6" s="145"/>
+      <c r="O6" s="145"/>
+      <c r="P6" s="145"/>
+      <c r="Q6" s="145"/>
+      <c r="R6" s="145"/>
+      <c r="S6" s="145"/>
+      <c r="T6" s="145"/>
+      <c r="U6" s="145"/>
+      <c r="V6" s="145"/>
+      <c r="W6" s="145"/>
+      <c r="X6" s="145"/>
+      <c r="Y6" s="145"/>
+      <c r="Z6" s="145"/>
+      <c r="AA6" s="145"/>
+      <c r="AB6" s="145"/>
+      <c r="AC6" s="145"/>
+      <c r="AD6" s="145"/>
+      <c r="AE6" s="145"/>
+      <c r="AF6" s="146"/>
+      <c r="AG6" s="146"/>
+      <c r="AH6" s="146"/>
+      <c r="AI6" s="146"/>
+      <c r="AJ6" s="146"/>
+      <c r="AK6" s="146"/>
+      <c r="AL6" s="146"/>
       <c r="AM6" s="24"/>
     </row>
     <row r="7" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7113,65 +6960,65 @@
       <c r="AM7" s="7"/>
     </row>
     <row r="8" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="126" t="s">
+      <c r="B8" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="129" t="s">
+      <c r="C8" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="129"/>
-      <c r="E8" s="129"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
       <c r="F8" s="51"/>
-      <c r="G8" s="145" t="s">
+      <c r="G8" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="146"/>
-      <c r="I8" s="146"/>
-      <c r="J8" s="147"/>
-      <c r="K8" s="124" t="s">
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="125"/>
-      <c r="M8" s="125"/>
-      <c r="N8" s="125"/>
-      <c r="O8" s="125"/>
-      <c r="P8" s="125"/>
-      <c r="Q8" s="125"/>
-      <c r="R8" s="125"/>
-      <c r="S8" s="130"/>
-      <c r="T8" s="124" t="s">
+      <c r="L8" s="133"/>
+      <c r="M8" s="133"/>
+      <c r="N8" s="133"/>
+      <c r="O8" s="133"/>
+      <c r="P8" s="133"/>
+      <c r="Q8" s="133"/>
+      <c r="R8" s="133"/>
+      <c r="S8" s="138"/>
+      <c r="T8" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="U8" s="125"/>
-      <c r="V8" s="125"/>
-      <c r="W8" s="125"/>
-      <c r="X8" s="125"/>
-      <c r="Y8" s="125"/>
-      <c r="Z8" s="125"/>
-      <c r="AA8" s="125"/>
-      <c r="AB8" s="130"/>
-      <c r="AC8" s="124" t="s">
+      <c r="U8" s="133"/>
+      <c r="V8" s="133"/>
+      <c r="W8" s="133"/>
+      <c r="X8" s="133"/>
+      <c r="Y8" s="133"/>
+      <c r="Z8" s="133"/>
+      <c r="AA8" s="133"/>
+      <c r="AB8" s="138"/>
+      <c r="AC8" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="AD8" s="125"/>
-      <c r="AE8" s="125"/>
-      <c r="AF8" s="125"/>
-      <c r="AG8" s="125"/>
-      <c r="AH8" s="125"/>
-      <c r="AI8" s="125"/>
-      <c r="AJ8" s="125"/>
-      <c r="AK8" s="130"/>
-      <c r="AL8" s="143" t="s">
+      <c r="AD8" s="133"/>
+      <c r="AE8" s="133"/>
+      <c r="AF8" s="133"/>
+      <c r="AG8" s="133"/>
+      <c r="AH8" s="133"/>
+      <c r="AI8" s="133"/>
+      <c r="AJ8" s="133"/>
+      <c r="AK8" s="138"/>
+      <c r="AL8" s="123" t="s">
         <v>8</v>
       </c>
       <c r="AM8" s="34"/>
     </row>
     <row r="9" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="127"/>
-      <c r="B9" s="127"/>
+      <c r="A9" s="135"/>
+      <c r="B9" s="135"/>
       <c r="C9" s="42" t="s">
         <v>27</v>
       </c>
@@ -7275,7 +7122,7 @@
       <c r="AK9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="AL9" s="144"/>
+      <c r="AL9" s="124"/>
       <c r="AM9" s="34"/>
       <c r="AN9" s="34"/>
     </row>
@@ -8064,10 +7911,10 @@
       <c r="AQ16" s="10"/>
     </row>
     <row r="17" spans="1:41" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="141" t="s">
+      <c r="A17" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="141"/>
+      <c r="B17" s="121"/>
       <c r="C17" s="18">
         <f>SUM(C10:C16)</f>
         <v>227321</v>
@@ -8246,18 +8093,18 @@
     </row>
     <row r="19" spans="1:41" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="142" t="s">
+      <c r="B19" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="142"/>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="142"/>
-      <c r="G19" s="142"/>
-      <c r="H19" s="142"/>
-      <c r="I19" s="142"/>
-      <c r="J19" s="142"/>
-      <c r="K19" s="142"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="122"/>
+      <c r="J19" s="122"/>
+      <c r="K19" s="122"/>
       <c r="L19" s="49"/>
       <c r="M19" s="49"/>
       <c r="N19" s="49"/>
@@ -8288,20 +8135,20 @@
       <c r="AM19" s="19"/>
     </row>
     <row r="20" spans="1:41" ht="18" x14ac:dyDescent="0.35">
-      <c r="B20" s="139"/>
-      <c r="C20" s="139"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="139"/>
-      <c r="I20" s="139"/>
-      <c r="J20" s="139"/>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="139"/>
-      <c r="N20" s="139"/>
-      <c r="O20" s="139"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="119"/>
+      <c r="N20" s="119"/>
+      <c r="O20" s="119"/>
       <c r="P20" s="23"/>
       <c r="Q20" s="23"/>
       <c r="R20" s="23"/>
@@ -8330,8 +8177,8 @@
         <v>4</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="120"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
@@ -8454,6 +8301,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A5:AL5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="O1:AL1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="O2:AL2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="B19:K19"/>
     <mergeCell ref="B20:O20"/>
@@ -8467,12 +8320,6 @@
     <mergeCell ref="T8:AB8"/>
     <mergeCell ref="AC8:AK8"/>
     <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="A5:AL5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="O1:AL1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="O2:AL2"/>
-    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -8505,67 +8352,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
       <c r="E1" s="63"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="126"/>
       <c r="Y1" s="63"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
       <c r="E2" s="63"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="126"/>
       <c r="Y2" s="63"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
       <c r="D3" s="63"/>
       <c r="E3" s="63"/>
       <c r="F3" s="17"/>
@@ -8617,32 +8464,32 @@
       <c r="Y4" s="63"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="126"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="126"/>
+      <c r="W5" s="126"/>
+      <c r="X5" s="126"/>
       <c r="Y5" s="63"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8674,49 +8521,49 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="133"/>
+      <c r="T7" s="133"/>
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="123" t="s">
         <v>8</v>
       </c>
       <c r="Y7" s="34"/>
     </row>
     <row r="8" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
+      <c r="A8" s="135"/>
+      <c r="B8" s="135"/>
       <c r="C8" s="68" t="s">
         <v>27</v>
       </c>
@@ -8780,7 +8627,7 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
+      <c r="X8" s="124"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
@@ -9430,10 +9277,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="121"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -9552,13 +9399,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
       <c r="G18" s="64"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -9580,12 +9427,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
       <c r="H19" s="65"/>
       <c r="I19" s="65"/>
       <c r="J19" s="65"/>
@@ -9608,8 +9455,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
       <c r="F20" s="66"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -9690,6 +9537,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
     <mergeCell ref="X7:X8"/>
@@ -9699,14 +9554,6 @@
     <mergeCell ref="H2:X2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -9739,67 +9586,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
       <c r="E1" s="75"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="126"/>
       <c r="Y1" s="75"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
       <c r="E2" s="75"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="126"/>
       <c r="Y2" s="75"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
       <c r="D3" s="75"/>
       <c r="E3" s="75"/>
       <c r="F3" s="17"/>
@@ -9851,32 +9698,32 @@
       <c r="Y4" s="75"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="125" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="126"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="126"/>
+      <c r="W5" s="126"/>
+      <c r="X5" s="126"/>
       <c r="Y5" s="75"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9908,49 +9755,49 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="133"/>
+      <c r="T7" s="133"/>
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="123" t="s">
         <v>8</v>
       </c>
       <c r="Y7" s="34"/>
     </row>
     <row r="8" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
+      <c r="A8" s="135"/>
+      <c r="B8" s="135"/>
       <c r="C8" s="73" t="s">
         <v>27</v>
       </c>
@@ -10014,7 +9861,7 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
+      <c r="X8" s="124"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
@@ -10641,10 +10488,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="121"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -10763,13 +10610,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
       <c r="G18" s="78"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -10791,12 +10638,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
       <c r="H19" s="76"/>
       <c r="I19" s="76"/>
       <c r="J19" s="76"/>
@@ -10819,8 +10666,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
       <c r="F20" s="77"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -10901,12 +10748,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="X7:X8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
@@ -10918,6 +10759,12 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -10950,67 +10797,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
       <c r="E1" s="85"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="126"/>
       <c r="Y1" s="85"/>
     </row>
     <row r="2" spans="1:29" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
       <c r="E2" s="85"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="126"/>
       <c r="Y2" s="85"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="17"/>
@@ -11062,32 +10909,32 @@
       <c r="Y4" s="85"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="125" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="126"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="126"/>
+      <c r="W5" s="126"/>
+      <c r="X5" s="126"/>
       <c r="Y5" s="85"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11119,49 +10966,49 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="133"/>
+      <c r="T7" s="133"/>
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="123" t="s">
         <v>8</v>
       </c>
       <c r="Y7" s="34"/>
     </row>
     <row r="8" spans="1:29" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
+      <c r="A8" s="135"/>
+      <c r="B8" s="135"/>
       <c r="C8" s="86" t="s">
         <v>27</v>
       </c>
@@ -11225,7 +11072,7 @@
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
+      <c r="X8" s="124"/>
       <c r="Y8" s="34"/>
       <c r="Z8" s="34"/>
     </row>
@@ -11881,10 +11728,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:29" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="121"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -12003,13 +11850,13 @@
     </row>
     <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
       <c r="G18" s="87"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -12034,12 +11881,12 @@
       <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
       <c r="H19" s="81"/>
       <c r="I19" s="81"/>
       <c r="J19" s="81"/>
@@ -12062,8 +11909,8 @@
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
       <c r="F20" s="82"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -12144,6 +11991,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="X7:X8"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="B18:F18"/>
@@ -12155,12 +12008,6 @@
     <mergeCell ref="F7:K7"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -12171,7 +12018,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ25"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.88671875" customWidth="1"/>
@@ -12196,69 +12043,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="92"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="91"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="92"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="91"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="92"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="91"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
-      <c r="Y2" s="92"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="126"/>
+      <c r="Y2" s="91"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
       <c r="F3" s="17"/>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
@@ -12281,60 +12128,60 @@
       <c r="Y3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="91"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="91"/>
-      <c r="S4" s="92"/>
-      <c r="T4" s="92"/>
-      <c r="U4" s="92"/>
-      <c r="V4" s="92"/>
-      <c r="W4" s="92"/>
-      <c r="X4" s="92"/>
-      <c r="Y4" s="92"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
+      <c r="N4" s="90"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="90"/>
+      <c r="Q4" s="90"/>
+      <c r="R4" s="90"/>
+      <c r="S4" s="91"/>
+      <c r="T4" s="91"/>
+      <c r="U4" s="91"/>
+      <c r="V4" s="91"/>
+      <c r="W4" s="91"/>
+      <c r="X4" s="91"/>
+      <c r="Y4" s="91"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="125" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
-      <c r="Y5" s="92"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="126"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="126"/>
+      <c r="W5" s="126"/>
+      <c r="X5" s="126"/>
+      <c r="Y5" s="91"/>
     </row>
     <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
@@ -12365,190 +12212,190 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="133"/>
+      <c r="T7" s="133"/>
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="128" t="s">
+      <c r="Y7" s="136" t="s">
         <v>77</v>
       </c>
-      <c r="Z7" s="152" t="s">
+      <c r="Z7" s="149" t="s">
         <v>61</v>
       </c>
-      <c r="AA7" s="152"/>
-      <c r="AB7" s="152"/>
-      <c r="AC7" s="152"/>
-      <c r="AD7" s="152"/>
-      <c r="AE7" s="152"/>
-      <c r="AF7" s="152"/>
-      <c r="AG7" s="150" t="s">
+      <c r="AA7" s="149"/>
+      <c r="AB7" s="149"/>
+      <c r="AC7" s="149"/>
+      <c r="AD7" s="149"/>
+      <c r="AE7" s="149"/>
+      <c r="AF7" s="149"/>
+      <c r="AG7" s="147" t="s">
         <v>76</v>
       </c>
-      <c r="AH7" s="152" t="s">
+      <c r="AH7" s="149" t="s">
         <v>62</v>
       </c>
-      <c r="AI7" s="152"/>
-      <c r="AJ7" s="152"/>
-      <c r="AK7" s="152"/>
-      <c r="AL7" s="152"/>
-      <c r="AM7" s="152"/>
-      <c r="AN7" s="152"/>
-      <c r="AO7" s="152"/>
-      <c r="AP7" s="152"/>
-      <c r="AQ7" s="150"/>
+      <c r="AI7" s="149"/>
+      <c r="AJ7" s="149"/>
+      <c r="AK7" s="149"/>
+      <c r="AL7" s="149"/>
+      <c r="AM7" s="149"/>
+      <c r="AN7" s="149"/>
+      <c r="AO7" s="149"/>
+      <c r="AP7" s="149"/>
+      <c r="AQ7" s="147"/>
     </row>
     <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
-      <c r="C8" s="93" t="s">
+      <c r="A8" s="135"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="90" t="s">
+      <c r="D8" s="89" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="90" t="s">
+      <c r="F8" s="89" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="90" t="s">
+      <c r="G8" s="89" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="90" t="s">
+      <c r="H8" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="90" t="s">
+      <c r="I8" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="90" t="s">
+      <c r="J8" s="89" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="90" t="s">
+      <c r="L8" s="89" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="90" t="s">
+      <c r="M8" s="89" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="90" t="s">
+      <c r="N8" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="O8" s="90" t="s">
+      <c r="O8" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="P8" s="90" t="s">
+      <c r="P8" s="89" t="s">
         <v>34</v>
       </c>
       <c r="Q8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="R8" s="90" t="s">
+      <c r="R8" s="89" t="s">
         <v>33</v>
       </c>
-      <c r="S8" s="90" t="s">
+      <c r="S8" s="89" t="s">
         <v>54</v>
       </c>
-      <c r="T8" s="90" t="s">
+      <c r="T8" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="U8" s="90" t="s">
+      <c r="U8" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="V8" s="90" t="s">
+      <c r="V8" s="89" t="s">
         <v>34</v>
       </c>
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
-      <c r="Y8" s="128"/>
-      <c r="Z8" s="94" t="s">
+      <c r="X8" s="124"/>
+      <c r="Y8" s="136"/>
+      <c r="Z8" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="AA8" s="94" t="s">
+      <c r="AA8" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="AB8" s="94" t="s">
+      <c r="AB8" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="AC8" s="94" t="s">
+      <c r="AC8" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="AD8" s="94" t="s">
+      <c r="AD8" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="AE8" s="94" t="s">
+      <c r="AE8" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="AF8" s="95" t="s">
+      <c r="AF8" s="94" t="s">
         <v>68</v>
       </c>
-      <c r="AG8" s="151"/>
-      <c r="AH8" s="95" t="s">
+      <c r="AG8" s="148"/>
+      <c r="AH8" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="AI8" s="105" t="s">
+      <c r="AI8" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="AJ8" s="105" t="s">
+      <c r="AJ8" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="AK8" s="105" t="s">
+      <c r="AK8" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="AL8" s="96" t="s">
+      <c r="AL8" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="AM8" s="96" t="s">
+      <c r="AM8" s="95" t="s">
         <v>74</v>
       </c>
-      <c r="AN8" s="94" t="s">
+      <c r="AN8" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="AO8" s="94" t="s">
+      <c r="AO8" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="AP8" s="94" t="s">
+      <c r="AP8" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="AQ8" s="151"/>
+      <c r="AQ8" s="148"/>
     </row>
     <row r="9" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26">
@@ -12634,70 +12481,70 @@
         <v>98.028169014084511</v>
       </c>
       <c r="X9" s="28"/>
-      <c r="Y9" s="106" t="s">
+      <c r="Y9" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="Z9" s="107">
+      <c r="Z9" s="106">
         <f>Z10+Z11+Z12+Z13</f>
         <v>466144</v>
       </c>
-      <c r="AA9" s="94">
+      <c r="AA9" s="93">
         <v>249318</v>
       </c>
-      <c r="AB9" s="94">
+      <c r="AB9" s="93">
         <v>228211</v>
       </c>
-      <c r="AC9" s="94">
+      <c r="AC9" s="93">
         <f>AA9-AB9</f>
         <v>21107</v>
       </c>
-      <c r="AD9" s="94">
+      <c r="AD9" s="93">
         <f>AA9-AG9</f>
         <v>-273397</v>
       </c>
-      <c r="AE9" s="97">
+      <c r="AE9" s="96">
         <f>AA9/Z9*100</f>
         <v>53.48518912610696</v>
       </c>
-      <c r="AF9" s="98">
+      <c r="AF9" s="97">
         <f>Z9-AA9</f>
         <v>216826</v>
       </c>
-      <c r="AG9" s="104">
+      <c r="AG9" s="103">
         <v>522715</v>
       </c>
-      <c r="AH9" s="99">
+      <c r="AH9" s="98">
         <f t="shared" ref="AH9" si="5">SUM(AI9:AL9)</f>
         <v>48041</v>
       </c>
-      <c r="AI9" s="100">
+      <c r="AI9" s="99">
         <v>2881</v>
       </c>
-      <c r="AJ9" s="100">
+      <c r="AJ9" s="99">
         <v>1394</v>
       </c>
-      <c r="AK9" s="100">
+      <c r="AK9" s="99">
         <v>190</v>
       </c>
-      <c r="AL9" s="101">
+      <c r="AL9" s="100">
         <v>43576</v>
       </c>
-      <c r="AM9" s="102">
+      <c r="AM9" s="101">
         <f t="shared" ref="AM9" si="6">SUM(AJ9:AK9)</f>
         <v>1584</v>
       </c>
-      <c r="AN9" s="103">
+      <c r="AN9" s="102">
         <f>AM9/Z9*100</f>
         <v>0.33980915768517883</v>
       </c>
-      <c r="AO9" s="103">
+      <c r="AO9" s="102">
         <v>1.26</v>
       </c>
-      <c r="AP9" s="103">
+      <c r="AP9" s="102">
         <f t="shared" ref="AP9" si="7">AO9-AN9</f>
         <v>0.92019084231482118</v>
       </c>
-      <c r="AQ9" s="104"/>
+      <c r="AQ9" s="103"/>
     </row>
     <row r="10" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A10" s="26">
@@ -12783,47 +12630,47 @@
         <v>59.001512859304086</v>
       </c>
       <c r="X10" s="28"/>
-      <c r="Y10" s="108" t="s">
+      <c r="Y10" s="107" t="s">
         <v>56</v>
       </c>
-      <c r="Z10" s="107">
+      <c r="Z10" s="106">
         <v>173399</v>
       </c>
-      <c r="AA10" s="94">
+      <c r="AA10" s="93">
         <v>94017</v>
       </c>
-      <c r="AB10" s="94">
+      <c r="AB10" s="93">
         <v>79425</v>
       </c>
-      <c r="AC10" s="94">
+      <c r="AC10" s="93">
         <f t="shared" ref="AC10:AC14" si="10">AA10-AB10</f>
         <v>14592</v>
       </c>
-      <c r="AD10" s="94">
+      <c r="AD10" s="93">
         <f t="shared" ref="AD10:AD14" si="11">AA10-AG10</f>
         <v>-97632</v>
       </c>
-      <c r="AE10" s="97">
+      <c r="AE10" s="96">
         <f t="shared" ref="AE10:AE13" si="12">AA10/Z10*100</f>
         <v>54.220035871025786</v>
       </c>
-      <c r="AF10" s="98">
+      <c r="AF10" s="97">
         <f t="shared" ref="AF10:AF13" si="13">Z10-AA10</f>
         <v>79382</v>
       </c>
-      <c r="AG10" s="104">
+      <c r="AG10" s="103">
         <v>191649</v>
       </c>
-      <c r="AH10" s="95"/>
-      <c r="AI10" s="105"/>
-      <c r="AJ10" s="105"/>
-      <c r="AK10" s="105"/>
-      <c r="AL10" s="96"/>
-      <c r="AM10" s="96"/>
-      <c r="AN10" s="94"/>
-      <c r="AO10" s="94"/>
-      <c r="AP10" s="94"/>
-      <c r="AQ10" s="104"/>
+      <c r="AH10" s="94"/>
+      <c r="AI10" s="104"/>
+      <c r="AJ10" s="104"/>
+      <c r="AK10" s="104"/>
+      <c r="AL10" s="95"/>
+      <c r="AM10" s="95"/>
+      <c r="AN10" s="93"/>
+      <c r="AO10" s="93"/>
+      <c r="AP10" s="93"/>
+      <c r="AQ10" s="103"/>
     </row>
     <row r="11" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A11" s="26">
@@ -12909,47 +12756,47 @@
         <v>76.814159292035399</v>
       </c>
       <c r="X11" s="28"/>
-      <c r="Y11" s="108" t="s">
+      <c r="Y11" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="Z11" s="107">
+      <c r="Z11" s="106">
         <v>37255</v>
       </c>
-      <c r="AA11" s="109">
+      <c r="AA11" s="108">
         <v>19221</v>
       </c>
-      <c r="AB11" s="109">
+      <c r="AB11" s="108">
         <v>15595</v>
       </c>
-      <c r="AC11" s="94">
+      <c r="AC11" s="93">
         <f t="shared" si="10"/>
         <v>3626</v>
       </c>
-      <c r="AD11" s="94">
+      <c r="AD11" s="93">
         <f t="shared" si="11"/>
         <v>-16054</v>
       </c>
-      <c r="AE11" s="97">
+      <c r="AE11" s="96">
         <f t="shared" si="12"/>
         <v>51.593074755066439</v>
       </c>
-      <c r="AF11" s="98">
+      <c r="AF11" s="97">
         <f t="shared" si="13"/>
         <v>18034</v>
       </c>
-      <c r="AG11" s="104">
+      <c r="AG11" s="103">
         <v>35275</v>
       </c>
-      <c r="AH11" s="104"/>
-      <c r="AI11" s="104"/>
-      <c r="AJ11" s="104"/>
-      <c r="AK11" s="104"/>
-      <c r="AL11" s="104"/>
-      <c r="AM11" s="104"/>
-      <c r="AN11" s="104"/>
-      <c r="AO11" s="104"/>
-      <c r="AP11" s="104"/>
-      <c r="AQ11" s="104"/>
+      <c r="AH11" s="103"/>
+      <c r="AI11" s="103"/>
+      <c r="AJ11" s="103"/>
+      <c r="AK11" s="103"/>
+      <c r="AL11" s="103"/>
+      <c r="AM11" s="103"/>
+      <c r="AN11" s="103"/>
+      <c r="AO11" s="103"/>
+      <c r="AP11" s="103"/>
+      <c r="AQ11" s="103"/>
     </row>
     <row r="12" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="26">
@@ -13035,47 +12882,47 @@
         <v>101.32924335378324</v>
       </c>
       <c r="X12" s="28"/>
-      <c r="Y12" s="108" t="s">
+      <c r="Y12" s="107" t="s">
         <v>58</v>
       </c>
-      <c r="Z12" s="107">
+      <c r="Z12" s="106">
         <v>10639</v>
       </c>
-      <c r="AA12" s="109">
+      <c r="AA12" s="108">
         <v>6448</v>
       </c>
-      <c r="AB12" s="109">
+      <c r="AB12" s="108">
         <v>5407</v>
       </c>
-      <c r="AC12" s="94">
+      <c r="AC12" s="93">
         <f t="shared" si="10"/>
         <v>1041</v>
       </c>
-      <c r="AD12" s="94">
+      <c r="AD12" s="93">
         <f t="shared" si="11"/>
         <v>-6661</v>
       </c>
-      <c r="AE12" s="97">
+      <c r="AE12" s="96">
         <f t="shared" si="12"/>
         <v>60.607199924804966</v>
       </c>
-      <c r="AF12" s="98">
+      <c r="AF12" s="97">
         <f t="shared" si="13"/>
         <v>4191</v>
       </c>
-      <c r="AG12" s="104">
+      <c r="AG12" s="103">
         <v>13109</v>
       </c>
-      <c r="AH12" s="104"/>
-      <c r="AI12" s="104"/>
-      <c r="AJ12" s="104"/>
-      <c r="AK12" s="104"/>
-      <c r="AL12" s="104"/>
-      <c r="AM12" s="104"/>
-      <c r="AN12" s="104"/>
-      <c r="AO12" s="104"/>
-      <c r="AP12" s="104"/>
-      <c r="AQ12" s="104"/>
+      <c r="AH12" s="103"/>
+      <c r="AI12" s="103"/>
+      <c r="AJ12" s="103"/>
+      <c r="AK12" s="103"/>
+      <c r="AL12" s="103"/>
+      <c r="AM12" s="103"/>
+      <c r="AN12" s="103"/>
+      <c r="AO12" s="103"/>
+      <c r="AP12" s="103"/>
+      <c r="AQ12" s="103"/>
     </row>
     <row r="13" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="26">
@@ -13161,47 +13008,47 @@
         <v>85.970149253731336</v>
       </c>
       <c r="X13" s="28"/>
-      <c r="Y13" s="108" t="s">
+      <c r="Y13" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="Z13" s="107">
+      <c r="Z13" s="106">
         <v>244851</v>
       </c>
-      <c r="AA13" s="109">
+      <c r="AA13" s="108">
         <v>129490</v>
       </c>
-      <c r="AB13" s="109">
+      <c r="AB13" s="108">
         <v>127670</v>
       </c>
-      <c r="AC13" s="94">
+      <c r="AC13" s="93">
         <f t="shared" si="10"/>
         <v>1820</v>
       </c>
-      <c r="AD13" s="94">
+      <c r="AD13" s="93">
         <f t="shared" si="11"/>
         <v>-153011</v>
       </c>
-      <c r="AE13" s="97">
+      <c r="AE13" s="96">
         <f t="shared" si="12"/>
         <v>52.88522407504972</v>
       </c>
-      <c r="AF13" s="98">
+      <c r="AF13" s="97">
         <f t="shared" si="13"/>
         <v>115361</v>
       </c>
-      <c r="AG13" s="104">
+      <c r="AG13" s="103">
         <v>282501</v>
       </c>
-      <c r="AH13" s="104"/>
-      <c r="AI13" s="104"/>
-      <c r="AJ13" s="104"/>
-      <c r="AK13" s="104"/>
-      <c r="AL13" s="104"/>
-      <c r="AM13" s="104"/>
-      <c r="AN13" s="104"/>
-      <c r="AO13" s="104"/>
-      <c r="AP13" s="104"/>
-      <c r="AQ13" s="104"/>
+      <c r="AH13" s="103"/>
+      <c r="AI13" s="103"/>
+      <c r="AJ13" s="103"/>
+      <c r="AK13" s="103"/>
+      <c r="AL13" s="103"/>
+      <c r="AM13" s="103"/>
+      <c r="AN13" s="103"/>
+      <c r="AO13" s="103"/>
+      <c r="AP13" s="103"/>
+      <c r="AQ13" s="103"/>
     </row>
     <row r="14" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A14" s="26">
@@ -13287,39 +13134,39 @@
         <v>93.288590604026851</v>
       </c>
       <c r="X14" s="28"/>
-      <c r="Y14" s="108" t="s">
+      <c r="Y14" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="Z14" s="109"/>
-      <c r="AA14" s="109">
+      <c r="Z14" s="108"/>
+      <c r="AA14" s="108">
         <v>142</v>
       </c>
-      <c r="AB14" s="109">
+      <c r="AB14" s="108">
         <v>114</v>
       </c>
-      <c r="AC14" s="94">
+      <c r="AC14" s="93">
         <f t="shared" si="10"/>
         <v>28</v>
       </c>
-      <c r="AD14" s="94">
+      <c r="AD14" s="93">
         <f t="shared" si="11"/>
         <v>-39</v>
       </c>
-      <c r="AE14" s="97"/>
-      <c r="AF14" s="104"/>
-      <c r="AG14" s="104">
+      <c r="AE14" s="96"/>
+      <c r="AF14" s="103"/>
+      <c r="AG14" s="103">
         <v>181</v>
       </c>
-      <c r="AH14" s="104"/>
-      <c r="AI14" s="104"/>
-      <c r="AJ14" s="104"/>
-      <c r="AK14" s="104"/>
-      <c r="AL14" s="104"/>
-      <c r="AM14" s="104"/>
-      <c r="AN14" s="104"/>
-      <c r="AO14" s="104"/>
-      <c r="AP14" s="104"/>
-      <c r="AQ14" s="104"/>
+      <c r="AH14" s="103"/>
+      <c r="AI14" s="103"/>
+      <c r="AJ14" s="103"/>
+      <c r="AK14" s="103"/>
+      <c r="AL14" s="103"/>
+      <c r="AM14" s="103"/>
+      <c r="AN14" s="103"/>
+      <c r="AO14" s="103"/>
+      <c r="AP14" s="103"/>
+      <c r="AQ14" s="103"/>
     </row>
     <row r="15" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="26">
@@ -13412,10 +13259,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="121"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -13532,165 +13379,8 @@
       <c r="X17" s="15"/>
       <c r="Y17" s="15"/>
     </row>
-    <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="19"/>
-    </row>
-    <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="88"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="31"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B20" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-    </row>
-    <row r="21" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="31"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-    </row>
-    <row r="22" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-    </row>
-    <row r="23" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B23" s="5"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="54"/>
-    </row>
-    <row r="24" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B24" s="5"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="54"/>
-    </row>
-    <row r="25" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="R25" s="31"/>
-      <c r="S25" s="54"/>
-    </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:K7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
+  <mergeCells count="19">
     <mergeCell ref="Y7:Y8"/>
     <mergeCell ref="AQ7:AQ8"/>
     <mergeCell ref="Z7:AF7"/>
@@ -13700,6 +13390,16 @@
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="R7:W7"/>
     <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13711,7 +13411,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ25"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.88671875" customWidth="1"/>
@@ -13737,69 +13437,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="114"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="112"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="114"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="112"/>
     </row>
     <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="114"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="112"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
-      <c r="Y2" s="114"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="126"/>
+      <c r="Y2" s="112"/>
     </row>
     <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
       <c r="F3" s="17"/>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
@@ -13822,60 +13522,60 @@
       <c r="Y3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="113"/>
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113"/>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113"/>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114"/>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="114"/>
+      <c r="A4" s="111"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111"/>
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
     </row>
     <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="125" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
-      <c r="Y5" s="114"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="126"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="126"/>
+      <c r="W5" s="126"/>
+      <c r="X5" s="126"/>
+      <c r="Y5" s="112"/>
     </row>
     <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
@@ -13906,190 +13606,190 @@
       <c r="Y6" s="7"/>
     </row>
     <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="C7" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
+      <c r="S7" s="133"/>
+      <c r="T7" s="133"/>
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="128" t="s">
+      <c r="Y7" s="136" t="s">
         <v>77</v>
       </c>
-      <c r="Z7" s="152" t="s">
+      <c r="Z7" s="149" t="s">
         <v>61</v>
       </c>
-      <c r="AA7" s="152"/>
-      <c r="AB7" s="152"/>
-      <c r="AC7" s="152"/>
-      <c r="AD7" s="152"/>
-      <c r="AE7" s="152"/>
-      <c r="AF7" s="152"/>
-      <c r="AG7" s="150" t="s">
+      <c r="AA7" s="149"/>
+      <c r="AB7" s="149"/>
+      <c r="AC7" s="149"/>
+      <c r="AD7" s="149"/>
+      <c r="AE7" s="149"/>
+      <c r="AF7" s="149"/>
+      <c r="AG7" s="147" t="s">
         <v>76</v>
       </c>
-      <c r="AH7" s="152" t="s">
+      <c r="AH7" s="149" t="s">
         <v>62</v>
       </c>
-      <c r="AI7" s="152"/>
-      <c r="AJ7" s="152"/>
-      <c r="AK7" s="152"/>
-      <c r="AL7" s="152"/>
-      <c r="AM7" s="152"/>
-      <c r="AN7" s="152"/>
-      <c r="AO7" s="152"/>
-      <c r="AP7" s="152"/>
-      <c r="AQ7" s="150"/>
+      <c r="AI7" s="149"/>
+      <c r="AJ7" s="149"/>
+      <c r="AK7" s="149"/>
+      <c r="AL7" s="149"/>
+      <c r="AM7" s="149"/>
+      <c r="AN7" s="149"/>
+      <c r="AO7" s="149"/>
+      <c r="AP7" s="149"/>
+      <c r="AQ7" s="147"/>
     </row>
     <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
-      <c r="C8" s="115" t="s">
+      <c r="A8" s="135"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="112" t="s">
+      <c r="D8" s="110" t="s">
         <v>79</v>
       </c>
       <c r="E8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="112" t="s">
+      <c r="F8" s="110" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="112" t="s">
+      <c r="G8" s="110" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="112" t="s">
+      <c r="H8" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="112" t="s">
+      <c r="I8" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="112" t="s">
+      <c r="J8" s="110" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="112" t="s">
+      <c r="L8" s="110" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="112" t="s">
+      <c r="M8" s="110" t="s">
         <v>79</v>
       </c>
-      <c r="N8" s="112" t="s">
+      <c r="N8" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="O8" s="112" t="s">
+      <c r="O8" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="P8" s="112" t="s">
+      <c r="P8" s="110" t="s">
         <v>34</v>
       </c>
       <c r="Q8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="R8" s="112" t="s">
+      <c r="R8" s="110" t="s">
         <v>33</v>
       </c>
-      <c r="S8" s="112" t="s">
+      <c r="S8" s="110" t="s">
         <v>79</v>
       </c>
-      <c r="T8" s="112" t="s">
+      <c r="T8" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="U8" s="112" t="s">
+      <c r="U8" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="V8" s="112" t="s">
+      <c r="V8" s="110" t="s">
         <v>34</v>
       </c>
       <c r="W8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="X8" s="144"/>
-      <c r="Y8" s="128"/>
-      <c r="Z8" s="94" t="s">
+      <c r="X8" s="124"/>
+      <c r="Y8" s="136"/>
+      <c r="Z8" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="AA8" s="94" t="s">
+      <c r="AA8" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="AB8" s="94" t="s">
+      <c r="AB8" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="AC8" s="94" t="s">
+      <c r="AC8" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="AD8" s="94" t="s">
+      <c r="AD8" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="AE8" s="94" t="s">
+      <c r="AE8" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="AF8" s="95" t="s">
+      <c r="AF8" s="94" t="s">
         <v>68</v>
       </c>
-      <c r="AG8" s="151"/>
-      <c r="AH8" s="95" t="s">
+      <c r="AG8" s="148"/>
+      <c r="AH8" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="AI8" s="105" t="s">
+      <c r="AI8" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="AJ8" s="105" t="s">
+      <c r="AJ8" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="AK8" s="105" t="s">
+      <c r="AK8" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="AL8" s="96" t="s">
+      <c r="AL8" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="AM8" s="96" t="s">
+      <c r="AM8" s="95" t="s">
         <v>74</v>
       </c>
-      <c r="AN8" s="94" t="s">
+      <c r="AN8" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="AO8" s="94" t="s">
+      <c r="AO8" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="AP8" s="94" t="s">
+      <c r="AP8" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="AQ8" s="151"/>
+      <c r="AQ8" s="148"/>
     </row>
     <row r="9" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26">
@@ -14115,7 +13815,7 @@
         <v>1549</v>
       </c>
       <c r="H9" s="31">
-        <f>G9-'Tháng 7_2025'!G9</f>
+        <f>G9-'Tháng 7_2026'!G9</f>
         <v>21</v>
       </c>
       <c r="I9" s="31">
@@ -14137,7 +13837,7 @@
         <v>1638</v>
       </c>
       <c r="N9" s="53">
-        <f>M9-'Tháng 7_2025'!M9</f>
+        <f>M9-'Tháng 7_2026'!M9</f>
         <v>14</v>
       </c>
       <c r="O9" s="53">
@@ -14159,7 +13859,7 @@
         <v>1427</v>
       </c>
       <c r="T9" s="53">
-        <f>S9-'Tháng 7_2025'!S9</f>
+        <f>S9-'Tháng 7_2026'!S9</f>
         <v>35</v>
       </c>
       <c r="U9" s="53">
@@ -14175,70 +13875,70 @@
         <v>100.49295774647888</v>
       </c>
       <c r="X9" s="28"/>
-      <c r="Y9" s="106" t="s">
+      <c r="Y9" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="Z9" s="107">
+      <c r="Z9" s="106">
         <f>Z10+Z11+Z12+Z13</f>
         <v>466144</v>
       </c>
-      <c r="AA9" s="94">
+      <c r="AA9" s="93">
         <v>277702</v>
       </c>
-      <c r="AB9" s="94">
+      <c r="AB9" s="93">
         <v>249318</v>
       </c>
-      <c r="AC9" s="94">
+      <c r="AC9" s="93">
         <f>AA9-AB9</f>
         <v>28384</v>
       </c>
-      <c r="AD9" s="94">
+      <c r="AD9" s="93">
         <f>AA9-AG9</f>
         <v>-245013</v>
       </c>
-      <c r="AE9" s="97">
+      <c r="AE9" s="96">
         <f>AA9/Z9*100</f>
         <v>59.574294638566627</v>
       </c>
-      <c r="AF9" s="98">
+      <c r="AF9" s="97">
         <f>Z9-AA9</f>
         <v>188442</v>
       </c>
-      <c r="AG9" s="104">
+      <c r="AG9" s="103">
         <v>522715</v>
       </c>
-      <c r="AH9" s="99">
+      <c r="AH9" s="98">
         <f t="shared" ref="AH9" si="5">SUM(AI9:AL9)</f>
         <v>68305</v>
       </c>
-      <c r="AI9" s="100">
+      <c r="AI9" s="99">
         <v>2881</v>
       </c>
-      <c r="AJ9" s="100">
+      <c r="AJ9" s="99">
         <v>933</v>
       </c>
-      <c r="AK9" s="100">
+      <c r="AK9" s="99">
         <v>190</v>
       </c>
-      <c r="AL9" s="101">
+      <c r="AL9" s="100">
         <v>64301</v>
       </c>
-      <c r="AM9" s="102">
+      <c r="AM9" s="101">
         <f t="shared" ref="AM9" si="6">SUM(AJ9:AK9)</f>
         <v>1123</v>
       </c>
-      <c r="AN9" s="103">
+      <c r="AN9" s="102">
         <f>AM9/Z9*100</f>
         <v>0.2409126793437221</v>
       </c>
-      <c r="AO9" s="103">
+      <c r="AO9" s="102">
         <v>1.26</v>
       </c>
-      <c r="AP9" s="103">
+      <c r="AP9" s="102">
         <f t="shared" ref="AP9" si="7">AO9-AN9</f>
         <v>1.0190873206562778</v>
       </c>
-      <c r="AQ9" s="104"/>
+      <c r="AQ9" s="103"/>
     </row>
     <row r="10" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A10" s="26">
@@ -14264,7 +13964,7 @@
         <v>506</v>
       </c>
       <c r="H10" s="31">
-        <f>G10-'Tháng 7_2025'!G10</f>
+        <f>G10-'Tháng 7_2026'!G10</f>
         <v>10</v>
       </c>
       <c r="I10" s="31">
@@ -14286,7 +13986,7 @@
         <v>785</v>
       </c>
       <c r="N10" s="53">
-        <f>M10-'Tháng 7_2025'!M10</f>
+        <f>M10-'Tháng 7_2026'!M10</f>
         <v>65</v>
       </c>
       <c r="O10" s="53">
@@ -14308,7 +14008,7 @@
         <v>396</v>
       </c>
       <c r="T10" s="53">
-        <f>S10-'Tháng 7_2025'!S10</f>
+        <f>S10-'Tháng 7_2026'!S10</f>
         <v>6</v>
       </c>
       <c r="U10" s="53">
@@ -14324,47 +14024,47 @@
         <v>59.909228441754912</v>
       </c>
       <c r="X10" s="28"/>
-      <c r="Y10" s="108" t="s">
+      <c r="Y10" s="107" t="s">
         <v>56</v>
       </c>
-      <c r="Z10" s="107">
+      <c r="Z10" s="106">
         <v>173399</v>
       </c>
-      <c r="AA10" s="94">
+      <c r="AA10" s="93">
         <v>111295</v>
       </c>
-      <c r="AB10" s="94">
+      <c r="AB10" s="93">
         <v>94017</v>
       </c>
-      <c r="AC10" s="94">
+      <c r="AC10" s="93">
         <f t="shared" ref="AC10:AC14" si="10">AA10-AB10</f>
         <v>17278</v>
       </c>
-      <c r="AD10" s="94">
+      <c r="AD10" s="93">
         <f t="shared" ref="AD10:AD14" si="11">AA10-AG10</f>
         <v>-80354</v>
       </c>
-      <c r="AE10" s="97">
+      <c r="AE10" s="96">
         <f t="shared" ref="AE10:AE13" si="12">AA10/Z10*100</f>
         <v>64.184337856619706</v>
       </c>
-      <c r="AF10" s="98">
+      <c r="AF10" s="97">
         <f t="shared" ref="AF10:AF13" si="13">Z10-AA10</f>
         <v>62104</v>
       </c>
-      <c r="AG10" s="104">
+      <c r="AG10" s="103">
         <v>191649</v>
       </c>
-      <c r="AH10" s="95"/>
-      <c r="AI10" s="105"/>
-      <c r="AJ10" s="105"/>
-      <c r="AK10" s="105"/>
-      <c r="AL10" s="96"/>
-      <c r="AM10" s="96"/>
-      <c r="AN10" s="94"/>
-      <c r="AO10" s="94"/>
-      <c r="AP10" s="94"/>
-      <c r="AQ10" s="104"/>
+      <c r="AH10" s="94"/>
+      <c r="AI10" s="104"/>
+      <c r="AJ10" s="104"/>
+      <c r="AK10" s="104"/>
+      <c r="AL10" s="95"/>
+      <c r="AM10" s="95"/>
+      <c r="AN10" s="93"/>
+      <c r="AO10" s="93"/>
+      <c r="AP10" s="93"/>
+      <c r="AQ10" s="103"/>
     </row>
     <row r="11" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A11" s="26">
@@ -14390,7 +14090,7 @@
         <v>515</v>
       </c>
       <c r="H11" s="31">
-        <f>G11-'Tháng 7_2025'!G11</f>
+        <f>G11-'Tháng 7_2026'!G11</f>
         <v>-4</v>
       </c>
       <c r="I11" s="31">
@@ -14412,7 +14112,7 @@
         <v>831</v>
       </c>
       <c r="N11" s="53">
-        <f>M11-'Tháng 7_2025'!M11</f>
+        <f>M11-'Tháng 7_2026'!M11</f>
         <v>61</v>
       </c>
       <c r="O11" s="53">
@@ -14434,7 +14134,7 @@
         <v>425</v>
       </c>
       <c r="T11" s="53">
-        <f>S11-'Tháng 7_2025'!S11</f>
+        <f>S11-'Tháng 7_2026'!S11</f>
         <v>-9</v>
       </c>
       <c r="U11" s="53">
@@ -14450,47 +14150,47 @@
         <v>75.221238938053091</v>
       </c>
       <c r="X11" s="28"/>
-      <c r="Y11" s="108" t="s">
+      <c r="Y11" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="Z11" s="107">
+      <c r="Z11" s="106">
         <v>37255</v>
       </c>
-      <c r="AA11" s="109">
+      <c r="AA11" s="108">
         <v>21156</v>
       </c>
-      <c r="AB11" s="109">
+      <c r="AB11" s="108">
         <v>19221</v>
       </c>
-      <c r="AC11" s="94">
+      <c r="AC11" s="93">
         <f t="shared" si="10"/>
         <v>1935</v>
       </c>
-      <c r="AD11" s="94">
+      <c r="AD11" s="93">
         <f t="shared" si="11"/>
         <v>-14119</v>
       </c>
-      <c r="AE11" s="97">
+      <c r="AE11" s="96">
         <f t="shared" si="12"/>
         <v>56.787008455240908</v>
       </c>
-      <c r="AF11" s="98">
+      <c r="AF11" s="97">
         <f t="shared" si="13"/>
         <v>16099</v>
       </c>
-      <c r="AG11" s="104">
+      <c r="AG11" s="103">
         <v>35275</v>
       </c>
-      <c r="AH11" s="104"/>
-      <c r="AI11" s="104"/>
-      <c r="AJ11" s="104"/>
-      <c r="AK11" s="104"/>
-      <c r="AL11" s="104"/>
-      <c r="AM11" s="104"/>
-      <c r="AN11" s="104"/>
-      <c r="AO11" s="104"/>
-      <c r="AP11" s="104"/>
-      <c r="AQ11" s="104"/>
+      <c r="AH11" s="103"/>
+      <c r="AI11" s="103"/>
+      <c r="AJ11" s="103"/>
+      <c r="AK11" s="103"/>
+      <c r="AL11" s="103"/>
+      <c r="AM11" s="103"/>
+      <c r="AN11" s="103"/>
+      <c r="AO11" s="103"/>
+      <c r="AP11" s="103"/>
+      <c r="AQ11" s="103"/>
     </row>
     <row r="12" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="26">
@@ -14516,7 +14216,7 @@
         <v>1132</v>
       </c>
       <c r="H12" s="31">
-        <f>G12-'Tháng 7_2025'!G12</f>
+        <f>G12-'Tháng 7_2026'!G12</f>
         <v>36</v>
       </c>
       <c r="I12" s="31">
@@ -14538,7 +14238,7 @@
         <v>1719</v>
       </c>
       <c r="N12" s="53">
-        <f>M12-'Tháng 7_2025'!M12</f>
+        <f>M12-'Tháng 7_2026'!M12</f>
         <v>93</v>
       </c>
       <c r="O12" s="53">
@@ -14560,7 +14260,7 @@
         <v>1026</v>
       </c>
       <c r="T12" s="53">
-        <f>S12-'Tháng 7_2025'!S12</f>
+        <f>S12-'Tháng 7_2026'!S12</f>
         <v>35</v>
       </c>
       <c r="U12" s="53">
@@ -14576,47 +14276,47 @@
         <v>104.9079754601227</v>
       </c>
       <c r="X12" s="28"/>
-      <c r="Y12" s="108" t="s">
+      <c r="Y12" s="107" t="s">
         <v>58</v>
       </c>
-      <c r="Z12" s="107">
+      <c r="Z12" s="106">
         <v>10639</v>
       </c>
-      <c r="AA12" s="109">
+      <c r="AA12" s="108">
         <v>7566</v>
       </c>
-      <c r="AB12" s="109">
+      <c r="AB12" s="108">
         <v>6448</v>
       </c>
-      <c r="AC12" s="94">
+      <c r="AC12" s="93">
         <f t="shared" si="10"/>
         <v>1118</v>
       </c>
-      <c r="AD12" s="94">
+      <c r="AD12" s="93">
         <f t="shared" si="11"/>
         <v>-5543</v>
       </c>
-      <c r="AE12" s="97">
+      <c r="AE12" s="96">
         <f t="shared" si="12"/>
         <v>71.115706363380013</v>
       </c>
-      <c r="AF12" s="98">
+      <c r="AF12" s="97">
         <f t="shared" si="13"/>
         <v>3073</v>
       </c>
-      <c r="AG12" s="104">
+      <c r="AG12" s="103">
         <v>13109</v>
       </c>
-      <c r="AH12" s="104"/>
-      <c r="AI12" s="104"/>
-      <c r="AJ12" s="104"/>
-      <c r="AK12" s="104"/>
-      <c r="AL12" s="104"/>
-      <c r="AM12" s="104"/>
-      <c r="AN12" s="104"/>
-      <c r="AO12" s="104"/>
-      <c r="AP12" s="104"/>
-      <c r="AQ12" s="104"/>
+      <c r="AH12" s="103"/>
+      <c r="AI12" s="103"/>
+      <c r="AJ12" s="103"/>
+      <c r="AK12" s="103"/>
+      <c r="AL12" s="103"/>
+      <c r="AM12" s="103"/>
+      <c r="AN12" s="103"/>
+      <c r="AO12" s="103"/>
+      <c r="AP12" s="103"/>
+      <c r="AQ12" s="103"/>
     </row>
     <row r="13" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="26">
@@ -14642,7 +14342,7 @@
         <v>974</v>
       </c>
       <c r="H13" s="31">
-        <f>G13-'Tháng 7_2025'!G13</f>
+        <f>G13-'Tháng 7_2026'!G13</f>
         <v>-5</v>
       </c>
       <c r="I13" s="31">
@@ -14664,7 +14364,7 @@
         <v>1005</v>
       </c>
       <c r="N13" s="53">
-        <f>M13-'Tháng 7_2025'!M13</f>
+        <f>M13-'Tháng 7_2026'!M13</f>
         <v>33</v>
       </c>
       <c r="O13" s="53">
@@ -14686,7 +14386,7 @@
         <v>857</v>
       </c>
       <c r="T13" s="53">
-        <f>S13-'Tháng 7_2025'!S13</f>
+        <f>S13-'Tháng 7_2026'!S13</f>
         <v>-7</v>
       </c>
       <c r="U13" s="53">
@@ -14702,47 +14402,47 @@
         <v>85.273631840796014</v>
       </c>
       <c r="X13" s="28"/>
-      <c r="Y13" s="108" t="s">
+      <c r="Y13" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="Z13" s="107">
+      <c r="Z13" s="106">
         <v>244851</v>
       </c>
-      <c r="AA13" s="109">
+      <c r="AA13" s="108">
         <v>137467</v>
       </c>
-      <c r="AB13" s="109">
+      <c r="AB13" s="108">
         <v>129490</v>
       </c>
-      <c r="AC13" s="94">
+      <c r="AC13" s="93">
         <f t="shared" si="10"/>
         <v>7977</v>
       </c>
-      <c r="AD13" s="94">
+      <c r="AD13" s="93">
         <f t="shared" si="11"/>
         <v>-145034</v>
       </c>
-      <c r="AE13" s="97">
+      <c r="AE13" s="96">
         <f t="shared" si="12"/>
         <v>56.143123777317641</v>
       </c>
-      <c r="AF13" s="98">
+      <c r="AF13" s="97">
         <f t="shared" si="13"/>
         <v>107384</v>
       </c>
-      <c r="AG13" s="104">
+      <c r="AG13" s="103">
         <v>282501</v>
       </c>
-      <c r="AH13" s="104"/>
-      <c r="AI13" s="104"/>
-      <c r="AJ13" s="104"/>
-      <c r="AK13" s="104"/>
-      <c r="AL13" s="104"/>
-      <c r="AM13" s="104"/>
-      <c r="AN13" s="104"/>
-      <c r="AO13" s="104"/>
-      <c r="AP13" s="104"/>
-      <c r="AQ13" s="104"/>
+      <c r="AH13" s="103"/>
+      <c r="AI13" s="103"/>
+      <c r="AJ13" s="103"/>
+      <c r="AK13" s="103"/>
+      <c r="AL13" s="103"/>
+      <c r="AM13" s="103"/>
+      <c r="AN13" s="103"/>
+      <c r="AO13" s="103"/>
+      <c r="AP13" s="103"/>
+      <c r="AQ13" s="103"/>
     </row>
     <row r="14" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A14" s="26">
@@ -14768,7 +14468,7 @@
         <v>529</v>
       </c>
       <c r="H14" s="31">
-        <f>G14-'Tháng 7_2025'!G14</f>
+        <f>G14-'Tháng 7_2026'!G14</f>
         <v>5</v>
       </c>
       <c r="I14" s="31">
@@ -14790,7 +14490,7 @@
         <v>1063</v>
       </c>
       <c r="N14" s="53">
-        <f>M14-'Tháng 7_2025'!M14</f>
+        <f>M14-'Tháng 7_2026'!M14</f>
         <v>53</v>
       </c>
       <c r="O14" s="53">
@@ -14812,7 +14512,7 @@
         <v>417</v>
       </c>
       <c r="T14" s="53">
-        <f>S14-'Tháng 7_2025'!S14</f>
+        <f>S14-'Tháng 7_2026'!S14</f>
         <v>0</v>
       </c>
       <c r="U14" s="53">
@@ -14828,39 +14528,39 @@
         <v>93.288590604026851</v>
       </c>
       <c r="X14" s="28"/>
-      <c r="Y14" s="108" t="s">
+      <c r="Y14" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="Z14" s="109"/>
-      <c r="AA14" s="109">
+      <c r="Z14" s="108"/>
+      <c r="AA14" s="108">
         <v>218</v>
       </c>
-      <c r="AB14" s="109">
+      <c r="AB14" s="108">
         <v>142</v>
       </c>
-      <c r="AC14" s="94">
+      <c r="AC14" s="93">
         <f t="shared" si="10"/>
         <v>76</v>
       </c>
-      <c r="AD14" s="94">
+      <c r="AD14" s="93">
         <f t="shared" si="11"/>
         <v>37</v>
       </c>
-      <c r="AE14" s="97"/>
-      <c r="AF14" s="104"/>
-      <c r="AG14" s="104">
+      <c r="AE14" s="96"/>
+      <c r="AF14" s="103"/>
+      <c r="AG14" s="103">
         <v>181</v>
       </c>
-      <c r="AH14" s="104"/>
-      <c r="AI14" s="104"/>
-      <c r="AJ14" s="104"/>
-      <c r="AK14" s="104"/>
-      <c r="AL14" s="104"/>
-      <c r="AM14" s="104"/>
-      <c r="AN14" s="104"/>
-      <c r="AO14" s="104"/>
-      <c r="AP14" s="104"/>
-      <c r="AQ14" s="104"/>
+      <c r="AH14" s="103"/>
+      <c r="AI14" s="103"/>
+      <c r="AJ14" s="103"/>
+      <c r="AK14" s="103"/>
+      <c r="AL14" s="103"/>
+      <c r="AM14" s="103"/>
+      <c r="AN14" s="103"/>
+      <c r="AO14" s="103"/>
+      <c r="AP14" s="103"/>
+      <c r="AQ14" s="103"/>
     </row>
     <row r="15" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="26">
@@ -14886,7 +14586,7 @@
         <v>533</v>
       </c>
       <c r="H15" s="31">
-        <f>G15-'Tháng 7_2025'!G15</f>
+        <f>G15-'Tháng 7_2026'!G15</f>
         <v>-3</v>
       </c>
       <c r="I15" s="31">
@@ -14908,7 +14608,7 @@
         <v>1025</v>
       </c>
       <c r="N15" s="53">
-        <f>M15-'Tháng 7_2025'!M15</f>
+        <f>M15-'Tháng 7_2026'!M15</f>
         <v>-43</v>
       </c>
       <c r="O15" s="53">
@@ -14930,7 +14630,7 @@
         <v>435</v>
       </c>
       <c r="T15" s="53">
-        <f>S15-'Tháng 7_2025'!S15</f>
+        <f>S15-'Tháng 7_2026'!S15</f>
         <v>-6</v>
       </c>
       <c r="U15" s="53">
@@ -14953,10 +14653,10 @@
       <c r="AC15" s="10"/>
     </row>
     <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="121"/>
       <c r="C16" s="18">
         <f>SUM(C9:C15)</f>
         <v>228291</v>
@@ -15048,7 +14748,7 @@
     </row>
     <row r="17" spans="1:25" ht="9.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
-      <c r="B17" s="110"/>
+      <c r="B17" s="109"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
@@ -15073,153 +14773,1360 @@
       <c r="X17" s="15"/>
       <c r="Y17" s="15"/>
     </row>
-    <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="19"/>
-    </row>
-    <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="80"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B20" s="5" t="s">
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:X1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="H2:X2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:AF7"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AP7"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="L7:Q7"/>
+    <mergeCell ref="R7:W7"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AQ17"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.88671875" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="4" width="13.5546875" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="10.88671875" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="10" width="10.33203125" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="9.21875" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="17" width="8.6640625" customWidth="1"/>
+    <col min="18" max="18" width="8" customWidth="1"/>
+    <col min="19" max="19" width="11.5546875" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="23" width="8.6640625" customWidth="1"/>
+    <col min="24" max="24" width="6.88671875" customWidth="1"/>
+    <col min="25" max="25" width="17" customWidth="1"/>
+    <col min="40" max="40" width="11.88671875" customWidth="1"/>
+    <col min="41" max="41" width="11.33203125" customWidth="1"/>
+    <col min="42" max="42" width="10.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="127" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="116"/>
+    </row>
+    <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="128" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="126"/>
+      <c r="Y2" s="116"/>
+    </row>
+    <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="128"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+    </row>
+    <row r="4" spans="1:43" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="115"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="115"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
+      <c r="N4" s="115"/>
+      <c r="O4" s="115"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116"/>
+      <c r="V4" s="116"/>
+      <c r="W4" s="116"/>
+      <c r="X4" s="116"/>
+      <c r="Y4" s="116"/>
+    </row>
+    <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="125" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="125"/>
+      <c r="N5" s="125"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="126"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="126"/>
+      <c r="W5" s="126"/>
+      <c r="X5" s="126"/>
+      <c r="Y5" s="116"/>
+    </row>
+    <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y6" s="7"/>
+    </row>
+    <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="134" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="134" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="137" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="132" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="132" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="133"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="132" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="133"/>
+      <c r="T7" s="133"/>
+      <c r="U7" s="133"/>
+      <c r="V7" s="133"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="123" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y7" s="136" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z7" s="149" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA7" s="149"/>
+      <c r="AB7" s="149"/>
+      <c r="AC7" s="149"/>
+      <c r="AD7" s="149"/>
+      <c r="AE7" s="149"/>
+      <c r="AF7" s="149"/>
+      <c r="AG7" s="147" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH7" s="149" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI7" s="149"/>
+      <c r="AJ7" s="149"/>
+      <c r="AK7" s="149"/>
+      <c r="AL7" s="149"/>
+      <c r="AM7" s="149"/>
+      <c r="AN7" s="149"/>
+      <c r="AO7" s="149"/>
+      <c r="AP7" s="149"/>
+      <c r="AQ7" s="147"/>
+    </row>
+    <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="135"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="118" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="118" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="118" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="118" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="118" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="118" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="118" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="118" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" s="118" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="118" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" s="118" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="R8" s="118" t="s">
+        <v>33</v>
+      </c>
+      <c r="S8" s="118" t="s">
+        <v>81</v>
+      </c>
+      <c r="T8" s="118" t="s">
+        <v>30</v>
+      </c>
+      <c r="U8" s="118" t="s">
+        <v>46</v>
+      </c>
+      <c r="V8" s="118" t="s">
+        <v>34</v>
+      </c>
+      <c r="W8" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="X8" s="124"/>
+      <c r="Y8" s="136"/>
+      <c r="Z8" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA8" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB8" s="93" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC8" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD8" s="93" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE8" s="93" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF8" s="94" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG8" s="148"/>
+      <c r="AH8" s="94" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI8" s="104" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ8" s="104" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK8" s="104" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL8" s="95" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM8" s="95" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN8" s="93" t="s">
+        <v>67</v>
+      </c>
+      <c r="AO8" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP8" s="93" t="s">
+        <v>75</v>
+      </c>
+      <c r="AQ8" s="148"/>
+    </row>
+    <row r="9" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26">
+        <v>1</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="71">
+        <v>39379</v>
+      </c>
+      <c r="D9" s="72">
+        <v>39379</v>
+      </c>
+      <c r="E9" s="29">
+        <f t="shared" ref="E9:E16" si="0">D9/C9*100</f>
+        <v>100</v>
+      </c>
+      <c r="F9" s="59">
+        <v>1625</v>
+      </c>
+      <c r="G9" s="30"/>
+      <c r="H9" s="31">
+        <f>G9-'Tháng 7_2026'!G9</f>
+        <v>-1528</v>
+      </c>
+      <c r="I9" s="31">
+        <f>G9-'Thang 12'!Q10</f>
+        <v>-1652</v>
+      </c>
+      <c r="J9" s="31">
+        <f t="shared" ref="J9:J15" si="1">F9-G9</f>
+        <v>1625</v>
+      </c>
+      <c r="K9" s="61">
+        <f t="shared" ref="K9:K16" si="2">G9/F9*100</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="31">
+        <v>1862</v>
+      </c>
+      <c r="M9" s="30"/>
+      <c r="N9" s="53">
+        <f>M9-'Tháng 7_2026'!M9</f>
+        <v>-1624</v>
+      </c>
+      <c r="O9" s="53">
+        <f>M9-'Thang 12'!AG10</f>
+        <v>-1670</v>
+      </c>
+      <c r="P9" s="53">
+        <f>L9-M9</f>
+        <v>1862</v>
+      </c>
+      <c r="Q9" s="70">
+        <f>M9/L9*100</f>
+        <v>0</v>
+      </c>
+      <c r="R9" s="31">
+        <v>1420</v>
+      </c>
+      <c r="S9" s="31"/>
+      <c r="T9" s="53">
+        <f>S9-'Tháng 7_2026'!S9</f>
+        <v>-1392</v>
+      </c>
+      <c r="U9" s="53">
+        <f>S9-'Thang 12'!Y10</f>
+        <v>-1445</v>
+      </c>
+      <c r="V9" s="53">
+        <f t="shared" ref="V9:V15" si="3">R9-S9</f>
+        <v>1420</v>
+      </c>
+      <c r="W9" s="61">
+        <f t="shared" ref="W9:W16" si="4">S9/R9*100</f>
+        <v>0</v>
+      </c>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="105" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z9" s="106">
+        <f>Z10+Z11+Z12+Z13</f>
+        <v>466144</v>
+      </c>
+      <c r="AA9" s="93">
+        <v>249318</v>
+      </c>
+      <c r="AB9" s="93">
+        <v>249318</v>
+      </c>
+      <c r="AC9" s="93">
+        <f>AA9-AB9</f>
+        <v>0</v>
+      </c>
+      <c r="AD9" s="93">
+        <f>AA9-AG9</f>
+        <v>-273397</v>
+      </c>
+      <c r="AE9" s="96">
+        <f>AA9/Z9*100</f>
+        <v>53.48518912610696</v>
+      </c>
+      <c r="AF9" s="97">
+        <f>Z9-AA9</f>
+        <v>216826</v>
+      </c>
+      <c r="AG9" s="103">
+        <v>522715</v>
+      </c>
+      <c r="AH9" s="98">
+        <f t="shared" ref="AH9" si="5">SUM(AI9:AL9)</f>
+        <v>48041</v>
+      </c>
+      <c r="AI9" s="99">
+        <v>2881</v>
+      </c>
+      <c r="AJ9" s="99">
+        <v>1394</v>
+      </c>
+      <c r="AK9" s="99">
+        <v>190</v>
+      </c>
+      <c r="AL9" s="100">
+        <v>43576</v>
+      </c>
+      <c r="AM9" s="101">
+        <f t="shared" ref="AM9" si="6">SUM(AJ9:AK9)</f>
+        <v>1584</v>
+      </c>
+      <c r="AN9" s="102">
+        <f>AM9/Z9*100</f>
+        <v>0.33980915768517883</v>
+      </c>
+      <c r="AO9" s="102">
+        <v>1.26</v>
+      </c>
+      <c r="AP9" s="102">
+        <f t="shared" ref="AP9" si="7">AO9-AN9</f>
+        <v>0.92019084231482118</v>
+      </c>
+      <c r="AQ9" s="103"/>
+    </row>
+    <row r="10" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26">
+        <v>2</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="71">
+        <v>29921</v>
+      </c>
+      <c r="D10" s="72">
+        <v>29921</v>
+      </c>
+      <c r="E10" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F10" s="59">
+        <v>815</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="31">
+        <f>G10-'Tháng 7_2026'!G10</f>
+        <v>-496</v>
+      </c>
+      <c r="I10" s="31">
+        <f>G10-'Thang 12'!Q11</f>
+        <v>-487</v>
+      </c>
+      <c r="J10" s="31">
+        <f t="shared" si="1"/>
+        <v>815</v>
+      </c>
+      <c r="K10" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="31">
+        <v>1297</v>
+      </c>
+      <c r="M10" s="30"/>
+      <c r="N10" s="53">
+        <f>M10-'Tháng 7_2026'!M10</f>
+        <v>-720</v>
+      </c>
+      <c r="O10" s="53">
+        <f>M10-'Thang 12'!AG11</f>
+        <v>-590</v>
+      </c>
+      <c r="P10" s="53">
+        <f t="shared" ref="P10:P15" si="8">L10-M10</f>
+        <v>1297</v>
+      </c>
+      <c r="Q10" s="70">
+        <f t="shared" ref="Q10:Q16" si="9">M10/L10*100</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="31">
+        <v>661</v>
+      </c>
+      <c r="S10" s="31"/>
+      <c r="T10" s="53">
+        <f>S10-'Tháng 7_2026'!S10</f>
+        <v>-390</v>
+      </c>
+      <c r="U10" s="53">
+        <f>S10-'Thang 12'!Y11</f>
+        <v>-350</v>
+      </c>
+      <c r="V10" s="53">
+        <f t="shared" si="3"/>
+        <v>661</v>
+      </c>
+      <c r="W10" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="107" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z10" s="106">
+        <v>173399</v>
+      </c>
+      <c r="AA10" s="93">
+        <v>94017</v>
+      </c>
+      <c r="AB10" s="93">
+        <v>94017</v>
+      </c>
+      <c r="AC10" s="93">
+        <f t="shared" ref="AC10:AC14" si="10">AA10-AB10</f>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="93">
+        <f t="shared" ref="AD10:AD14" si="11">AA10-AG10</f>
+        <v>-97632</v>
+      </c>
+      <c r="AE10" s="96">
+        <f t="shared" ref="AE10:AE13" si="12">AA10/Z10*100</f>
+        <v>54.220035871025786</v>
+      </c>
+      <c r="AF10" s="97">
+        <f t="shared" ref="AF10:AF13" si="13">Z10-AA10</f>
+        <v>79382</v>
+      </c>
+      <c r="AG10" s="103">
+        <v>191649</v>
+      </c>
+      <c r="AH10" s="94"/>
+      <c r="AI10" s="104"/>
+      <c r="AJ10" s="104"/>
+      <c r="AK10" s="104"/>
+      <c r="AL10" s="95"/>
+      <c r="AM10" s="95"/>
+      <c r="AN10" s="93"/>
+      <c r="AO10" s="93"/>
+      <c r="AP10" s="93"/>
+      <c r="AQ10" s="103"/>
+    </row>
+    <row r="11" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="26">
+        <v>3</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="71">
+        <v>25763</v>
+      </c>
+      <c r="D11" s="72">
+        <v>25763</v>
+      </c>
+      <c r="E11" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F11" s="59">
+        <v>652</v>
+      </c>
+      <c r="G11" s="30"/>
+      <c r="H11" s="31">
+        <f>G11-'Tháng 7_2026'!G11</f>
+        <v>-519</v>
+      </c>
+      <c r="I11" s="31">
+        <f>G11-'Thang 12'!Q12</f>
+        <v>-539</v>
+      </c>
+      <c r="J11" s="31">
+        <f t="shared" si="1"/>
+        <v>652</v>
+      </c>
+      <c r="K11" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="31">
+        <v>1117</v>
+      </c>
+      <c r="M11" s="30"/>
+      <c r="N11" s="53">
+        <f>M11-'Tháng 7_2026'!M11</f>
+        <v>-770</v>
+      </c>
+      <c r="O11" s="53">
+        <f>M11-'Thang 12'!AG12</f>
+        <v>-816</v>
+      </c>
+      <c r="P11" s="53">
+        <f t="shared" si="8"/>
+        <v>1117</v>
+      </c>
+      <c r="Q11" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="31">
+        <v>565</v>
+      </c>
+      <c r="S11" s="31"/>
+      <c r="T11" s="53">
+        <f>S11-'Tháng 7_2026'!S11</f>
+        <v>-434</v>
+      </c>
+      <c r="U11" s="53">
+        <f>S11-'Thang 12'!Y12</f>
+        <v>-397</v>
+      </c>
+      <c r="V11" s="53">
+        <f t="shared" si="3"/>
+        <v>565</v>
+      </c>
+      <c r="W11" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="28"/>
+      <c r="Y11" s="107" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z11" s="106">
+        <v>37255</v>
+      </c>
+      <c r="AA11" s="108">
+        <v>19221</v>
+      </c>
+      <c r="AB11" s="108">
+        <v>19221</v>
+      </c>
+      <c r="AC11" s="93">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="93">
+        <f t="shared" si="11"/>
+        <v>-16054</v>
+      </c>
+      <c r="AE11" s="96">
+        <f t="shared" si="12"/>
+        <v>51.593074755066439</v>
+      </c>
+      <c r="AF11" s="97">
+        <f t="shared" si="13"/>
+        <v>18034</v>
+      </c>
+      <c r="AG11" s="103">
+        <v>35275</v>
+      </c>
+      <c r="AH11" s="103"/>
+      <c r="AI11" s="103"/>
+      <c r="AJ11" s="103"/>
+      <c r="AK11" s="103"/>
+      <c r="AL11" s="103"/>
+      <c r="AM11" s="103"/>
+      <c r="AN11" s="103"/>
+      <c r="AO11" s="103"/>
+      <c r="AP11" s="103"/>
+      <c r="AQ11" s="103"/>
+    </row>
+    <row r="12" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="26">
         <v>4</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-    </row>
-    <row r="21" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-    </row>
-    <row r="22" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-    </row>
-    <row r="23" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B23" s="5"/>
-      <c r="R23" s="31"/>
-    </row>
-    <row r="24" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B24" s="5"/>
-      <c r="R24" s="31"/>
-    </row>
-    <row r="25" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B25" s="5" t="s">
+      <c r="B12" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="71">
+        <v>51742</v>
+      </c>
+      <c r="D12" s="72">
+        <v>51742</v>
+      </c>
+      <c r="E12" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F12" s="59">
+        <v>1151</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="31">
+        <f>G12-'Tháng 7_2026'!G12</f>
+        <v>-1096</v>
+      </c>
+      <c r="I12" s="31">
+        <f>G12-'Thang 12'!Q13</f>
+        <v>-1101</v>
+      </c>
+      <c r="J12" s="31">
+        <f t="shared" si="1"/>
+        <v>1151</v>
+      </c>
+      <c r="K12" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="31">
+        <v>2043</v>
+      </c>
+      <c r="M12" s="30"/>
+      <c r="N12" s="53">
+        <f>M12-'Tháng 7_2026'!M12</f>
+        <v>-1626</v>
+      </c>
+      <c r="O12" s="53">
+        <f>M12-'Thang 12'!AG13</f>
+        <v>-1451</v>
+      </c>
+      <c r="P12" s="53">
+        <f t="shared" si="8"/>
+        <v>2043</v>
+      </c>
+      <c r="Q12" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="31">
+        <v>978</v>
+      </c>
+      <c r="S12" s="31"/>
+      <c r="T12" s="53">
+        <f>S12-'Tháng 7_2026'!S12</f>
+        <v>-991</v>
+      </c>
+      <c r="U12" s="53">
+        <f>S12-'Thang 12'!Y13</f>
+        <v>-910</v>
+      </c>
+      <c r="V12" s="53">
+        <f t="shared" si="3"/>
+        <v>978</v>
+      </c>
+      <c r="W12" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="107" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z12" s="106">
+        <v>10639</v>
+      </c>
+      <c r="AA12" s="108">
+        <v>6448</v>
+      </c>
+      <c r="AB12" s="108">
+        <v>6448</v>
+      </c>
+      <c r="AC12" s="93">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="93">
+        <f t="shared" si="11"/>
+        <v>-6661</v>
+      </c>
+      <c r="AE12" s="96">
+        <f t="shared" si="12"/>
+        <v>60.607199924804966</v>
+      </c>
+      <c r="AF12" s="97">
+        <f t="shared" si="13"/>
+        <v>4191</v>
+      </c>
+      <c r="AG12" s="103">
+        <v>13109</v>
+      </c>
+      <c r="AH12" s="103"/>
+      <c r="AI12" s="103"/>
+      <c r="AJ12" s="103"/>
+      <c r="AK12" s="103"/>
+      <c r="AL12" s="103"/>
+      <c r="AM12" s="103"/>
+      <c r="AN12" s="103"/>
+      <c r="AO12" s="103"/>
+      <c r="AP12" s="103"/>
+      <c r="AQ12" s="103"/>
+    </row>
+    <row r="13" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="26">
         <v>5</v>
       </c>
-      <c r="R25" s="31"/>
+      <c r="B13" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="71">
+        <v>27773</v>
+      </c>
+      <c r="D13" s="72">
+        <v>27773</v>
+      </c>
+      <c r="E13" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F13" s="59">
+        <v>1206</v>
+      </c>
+      <c r="G13" s="30"/>
+      <c r="H13" s="31">
+        <f>G13-'Tháng 7_2026'!G13</f>
+        <v>-979</v>
+      </c>
+      <c r="I13" s="31">
+        <f>G13-'Thang 12'!Q14</f>
+        <v>-1008</v>
+      </c>
+      <c r="J13" s="31">
+        <f t="shared" si="1"/>
+        <v>1206</v>
+      </c>
+      <c r="K13" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="31">
+        <v>1204</v>
+      </c>
+      <c r="M13" s="30"/>
+      <c r="N13" s="53">
+        <f>M13-'Tháng 7_2026'!M13</f>
+        <v>-972</v>
+      </c>
+      <c r="O13" s="53">
+        <f>M13-'Thang 12'!AG14</f>
+        <v>-1007</v>
+      </c>
+      <c r="P13" s="53">
+        <f t="shared" si="8"/>
+        <v>1204</v>
+      </c>
+      <c r="Q13" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="31">
+        <v>1005</v>
+      </c>
+      <c r="S13" s="31"/>
+      <c r="T13" s="53">
+        <f>S13-'Tháng 7_2026'!S13</f>
+        <v>-864</v>
+      </c>
+      <c r="U13" s="53">
+        <f>S13-'Thang 12'!Y14</f>
+        <v>-914</v>
+      </c>
+      <c r="V13" s="53">
+        <f t="shared" si="3"/>
+        <v>1005</v>
+      </c>
+      <c r="W13" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="107" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z13" s="106">
+        <v>244851</v>
+      </c>
+      <c r="AA13" s="108">
+        <v>129490</v>
+      </c>
+      <c r="AB13" s="108">
+        <v>129490</v>
+      </c>
+      <c r="AC13" s="93">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="93">
+        <f t="shared" si="11"/>
+        <v>-153011</v>
+      </c>
+      <c r="AE13" s="96">
+        <f t="shared" si="12"/>
+        <v>52.88522407504972</v>
+      </c>
+      <c r="AF13" s="97">
+        <f t="shared" si="13"/>
+        <v>115361</v>
+      </c>
+      <c r="AG13" s="103">
+        <v>282501</v>
+      </c>
+      <c r="AH13" s="103"/>
+      <c r="AI13" s="103"/>
+      <c r="AJ13" s="103"/>
+      <c r="AK13" s="103"/>
+      <c r="AL13" s="103"/>
+      <c r="AM13" s="103"/>
+      <c r="AN13" s="103"/>
+      <c r="AO13" s="103"/>
+      <c r="AP13" s="103"/>
+      <c r="AQ13" s="103"/>
+    </row>
+    <row r="14" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="26">
+        <v>6</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="71">
+        <v>28987</v>
+      </c>
+      <c r="D14" s="72">
+        <v>28987</v>
+      </c>
+      <c r="E14" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F14" s="59">
+        <v>591</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="31">
+        <f>G14-'Tháng 7_2026'!G14</f>
+        <v>-524</v>
+      </c>
+      <c r="I14" s="31">
+        <f>G14-'Thang 12'!Q15</f>
+        <v>-464</v>
+      </c>
+      <c r="J14" s="31">
+        <f t="shared" si="1"/>
+        <v>591</v>
+      </c>
+      <c r="K14" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="31">
+        <v>1257</v>
+      </c>
+      <c r="M14" s="30"/>
+      <c r="N14" s="53">
+        <f>M14-'Tháng 7_2026'!M14</f>
+        <v>-1010</v>
+      </c>
+      <c r="O14" s="53">
+        <f>M14-'Thang 12'!AG15</f>
+        <v>-980</v>
+      </c>
+      <c r="P14" s="53">
+        <f t="shared" si="8"/>
+        <v>1257</v>
+      </c>
+      <c r="Q14" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="31">
+        <v>447</v>
+      </c>
+      <c r="S14" s="31"/>
+      <c r="T14" s="53">
+        <f>S14-'Tháng 7_2026'!S14</f>
+        <v>-417</v>
+      </c>
+      <c r="U14" s="53">
+        <f>S14-'Thang 12'!Y15</f>
+        <v>-372</v>
+      </c>
+      <c r="V14" s="53">
+        <f t="shared" si="3"/>
+        <v>447</v>
+      </c>
+      <c r="W14" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X14" s="28"/>
+      <c r="Y14" s="107" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z14" s="108"/>
+      <c r="AA14" s="108">
+        <v>142</v>
+      </c>
+      <c r="AB14" s="108">
+        <v>142</v>
+      </c>
+      <c r="AC14" s="93">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="93">
+        <f t="shared" si="11"/>
+        <v>-39</v>
+      </c>
+      <c r="AE14" s="96"/>
+      <c r="AF14" s="103"/>
+      <c r="AG14" s="103">
+        <v>181</v>
+      </c>
+      <c r="AH14" s="103"/>
+      <c r="AI14" s="103"/>
+      <c r="AJ14" s="103"/>
+      <c r="AK14" s="103"/>
+      <c r="AL14" s="103"/>
+      <c r="AM14" s="103"/>
+      <c r="AN14" s="103"/>
+      <c r="AO14" s="103"/>
+      <c r="AP14" s="103"/>
+      <c r="AQ14" s="103"/>
+    </row>
+    <row r="15" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="26">
+        <v>7</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="71">
+        <v>24726</v>
+      </c>
+      <c r="D15" s="72">
+        <v>24726</v>
+      </c>
+      <c r="E15" s="29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F15" s="59">
+        <v>541</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="31">
+        <f>G15-'Tháng 7_2026'!G15</f>
+        <v>-536</v>
+      </c>
+      <c r="I15" s="31">
+        <f>G15-'Thang 12'!Q16</f>
+        <v>-461</v>
+      </c>
+      <c r="J15" s="31">
+        <f t="shared" si="1"/>
+        <v>541</v>
+      </c>
+      <c r="K15" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="31">
+        <v>1072</v>
+      </c>
+      <c r="M15" s="30"/>
+      <c r="N15" s="53">
+        <f>M15-'Tháng 7_2026'!M15</f>
+        <v>-1068</v>
+      </c>
+      <c r="O15" s="53">
+        <f>M15-'Thang 12'!AG16</f>
+        <v>-1040</v>
+      </c>
+      <c r="P15" s="53">
+        <f t="shared" si="8"/>
+        <v>1072</v>
+      </c>
+      <c r="Q15" s="70">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="31">
+        <v>439</v>
+      </c>
+      <c r="S15" s="31"/>
+      <c r="T15" s="53">
+        <f>S15-'Tháng 7_2026'!S15</f>
+        <v>-441</v>
+      </c>
+      <c r="U15" s="53">
+        <f>S15-'Thang 12'!Y16</f>
+        <v>-383</v>
+      </c>
+      <c r="V15" s="53">
+        <f t="shared" si="3"/>
+        <v>439</v>
+      </c>
+      <c r="W15" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10"/>
+      <c r="AB15" s="10"/>
+      <c r="AC15" s="10"/>
+    </row>
+    <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="121"/>
+      <c r="C16" s="18">
+        <f>SUM(C9:C15)</f>
+        <v>228291</v>
+      </c>
+      <c r="D16" s="18">
+        <f>SUM(D9:D15)</f>
+        <v>228291</v>
+      </c>
+      <c r="E16" s="32">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F16" s="60">
+        <f>SUM(F9:F15)</f>
+        <v>6581</v>
+      </c>
+      <c r="G16" s="50">
+        <f>SUM(G9:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="55">
+        <f>SUM(H9:H15)</f>
+        <v>-5678</v>
+      </c>
+      <c r="I16" s="55">
+        <f>G16-'Thang 12'!Q17</f>
+        <v>-5712</v>
+      </c>
+      <c r="J16" s="55">
+        <f>SUM(J9:J15)</f>
+        <v>6581</v>
+      </c>
+      <c r="K16" s="57">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="18">
+        <f>SUM(L9:L15)</f>
+        <v>9852</v>
+      </c>
+      <c r="M16" s="18">
+        <f>SUM(M9:M15)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="56">
+        <f>SUM(N9:N15)</f>
+        <v>-7790</v>
+      </c>
+      <c r="O16" s="56">
+        <f>SUM(O9:O15)</f>
+        <v>-7554</v>
+      </c>
+      <c r="P16" s="18">
+        <f t="shared" ref="P16" si="14">SUM(P9:P15)</f>
+        <v>9852</v>
+      </c>
+      <c r="Q16" s="69">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="55">
+        <f>SUM(R9:R15)</f>
+        <v>5515</v>
+      </c>
+      <c r="S16" s="18">
+        <f>SUM(S9:S15)</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="56">
+        <f>SUM(T9:T15)</f>
+        <v>-4929</v>
+      </c>
+      <c r="U16" s="56">
+        <f>SUM(U9:U15)</f>
+        <v>-4771</v>
+      </c>
+      <c r="V16" s="56">
+        <f>SUM(V9:V15)</f>
+        <v>5515</v>
+      </c>
+      <c r="W16" s="57">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="37"/>
+      <c r="Y16" s="36"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="25"/>
+    </row>
+    <row r="17" spans="1:25" ht="9.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="11"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="19">
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D20:E20"/>
     <mergeCell ref="X7:X8"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
@@ -15245,1499 +16152,4 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="5.88671875" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" customWidth="1"/>
-    <col min="3" max="4" width="13.5546875" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="10.88671875" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="10" width="10.33203125" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="9.21875" customWidth="1"/>
-    <col min="13" max="13" width="11.109375" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="17" width="8.6640625" customWidth="1"/>
-    <col min="18" max="18" width="8" customWidth="1"/>
-    <col min="19" max="19" width="11.5546875" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="23" width="8.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.88671875" customWidth="1"/>
-    <col min="25" max="25" width="17" customWidth="1"/>
-    <col min="40" max="40" width="11.88671875" customWidth="1"/>
-    <col min="41" max="41" width="11.33203125" customWidth="1"/>
-    <col min="42" max="42" width="10.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="118"/>
-    </row>
-    <row r="2" spans="1:43" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="135"/>
-      <c r="Y2" s="118"/>
-    </row>
-    <row r="3" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="137"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-    </row>
-    <row r="4" spans="1:43" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="117"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="117"/>
-      <c r="O4" s="117"/>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="118"/>
-      <c r="X4" s="118"/>
-      <c r="Y4" s="118"/>
-    </row>
-    <row r="5" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="134" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
-      <c r="T5" s="135"/>
-      <c r="U5" s="135"/>
-      <c r="V5" s="135"/>
-      <c r="W5" s="135"/>
-      <c r="X5" s="135"/>
-      <c r="Y5" s="118"/>
-    </row>
-    <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y6" s="7"/>
-    </row>
-    <row r="7" spans="1:43" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="126" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="126" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="129" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="124" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="124" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="125"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="143" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y7" s="128" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z7" s="152" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA7" s="152"/>
-      <c r="AB7" s="152"/>
-      <c r="AC7" s="152"/>
-      <c r="AD7" s="152"/>
-      <c r="AE7" s="152"/>
-      <c r="AF7" s="152"/>
-      <c r="AG7" s="150" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH7" s="152" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI7" s="152"/>
-      <c r="AJ7" s="152"/>
-      <c r="AK7" s="152"/>
-      <c r="AL7" s="152"/>
-      <c r="AM7" s="152"/>
-      <c r="AN7" s="152"/>
-      <c r="AO7" s="152"/>
-      <c r="AP7" s="152"/>
-      <c r="AQ7" s="150"/>
-    </row>
-    <row r="8" spans="1:43" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="127"/>
-      <c r="C8" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="121" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="121" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="121" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="121" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="121" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="121" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="121" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="121" t="s">
-        <v>81</v>
-      </c>
-      <c r="N8" s="121" t="s">
-        <v>30</v>
-      </c>
-      <c r="O8" s="121" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" s="121" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q8" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="R8" s="121" t="s">
-        <v>33</v>
-      </c>
-      <c r="S8" s="121" t="s">
-        <v>81</v>
-      </c>
-      <c r="T8" s="121" t="s">
-        <v>30</v>
-      </c>
-      <c r="U8" s="121" t="s">
-        <v>46</v>
-      </c>
-      <c r="V8" s="121" t="s">
-        <v>34</v>
-      </c>
-      <c r="W8" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="X8" s="144"/>
-      <c r="Y8" s="128"/>
-      <c r="Z8" s="94" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA8" s="94" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB8" s="94" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC8" s="94" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD8" s="94" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE8" s="94" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF8" s="95" t="s">
-        <v>68</v>
-      </c>
-      <c r="AG8" s="151"/>
-      <c r="AH8" s="95" t="s">
-        <v>69</v>
-      </c>
-      <c r="AI8" s="105" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ8" s="105" t="s">
-        <v>71</v>
-      </c>
-      <c r="AK8" s="105" t="s">
-        <v>72</v>
-      </c>
-      <c r="AL8" s="96" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM8" s="96" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN8" s="94" t="s">
-        <v>67</v>
-      </c>
-      <c r="AO8" s="94" t="s">
-        <v>63</v>
-      </c>
-      <c r="AP8" s="94" t="s">
-        <v>75</v>
-      </c>
-      <c r="AQ8" s="151"/>
-    </row>
-    <row r="9" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26">
-        <v>1</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="71">
-        <v>39379</v>
-      </c>
-      <c r="D9" s="72">
-        <v>39379</v>
-      </c>
-      <c r="E9" s="29">
-        <f t="shared" ref="E9:E16" si="0">D9/C9*100</f>
-        <v>100</v>
-      </c>
-      <c r="F9" s="59">
-        <v>1625</v>
-      </c>
-      <c r="G9" s="30"/>
-      <c r="H9" s="31">
-        <f>G9-'Tháng 7_2025'!G9</f>
-        <v>-1528</v>
-      </c>
-      <c r="I9" s="31">
-        <f>G9-'Thang 12'!Q10</f>
-        <v>-1652</v>
-      </c>
-      <c r="J9" s="31">
-        <f t="shared" ref="J9:J15" si="1">F9-G9</f>
-        <v>1625</v>
-      </c>
-      <c r="K9" s="61">
-        <f t="shared" ref="K9:K16" si="2">G9/F9*100</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="31">
-        <v>1862</v>
-      </c>
-      <c r="M9" s="30"/>
-      <c r="N9" s="53">
-        <f>M9-'Tháng 7_2025'!M9</f>
-        <v>-1624</v>
-      </c>
-      <c r="O9" s="53">
-        <f>M9-'Thang 12'!AG10</f>
-        <v>-1670</v>
-      </c>
-      <c r="P9" s="53">
-        <f>L9-M9</f>
-        <v>1862</v>
-      </c>
-      <c r="Q9" s="70">
-        <f>M9/L9*100</f>
-        <v>0</v>
-      </c>
-      <c r="R9" s="31">
-        <v>1420</v>
-      </c>
-      <c r="S9" s="31"/>
-      <c r="T9" s="53">
-        <f>S9-'Tháng 7_2025'!S9</f>
-        <v>-1392</v>
-      </c>
-      <c r="U9" s="53">
-        <f>S9-'Thang 12'!Y10</f>
-        <v>-1445</v>
-      </c>
-      <c r="V9" s="53">
-        <f t="shared" ref="V9:V15" si="3">R9-S9</f>
-        <v>1420</v>
-      </c>
-      <c r="W9" s="61">
-        <f t="shared" ref="W9:W16" si="4">S9/R9*100</f>
-        <v>0</v>
-      </c>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="106" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z9" s="107">
-        <f>Z10+Z11+Z12+Z13</f>
-        <v>466144</v>
-      </c>
-      <c r="AA9" s="94">
-        <v>249318</v>
-      </c>
-      <c r="AB9" s="94">
-        <v>249318</v>
-      </c>
-      <c r="AC9" s="94">
-        <f>AA9-AB9</f>
-        <v>0</v>
-      </c>
-      <c r="AD9" s="94">
-        <f>AA9-AG9</f>
-        <v>-273397</v>
-      </c>
-      <c r="AE9" s="97">
-        <f>AA9/Z9*100</f>
-        <v>53.48518912610696</v>
-      </c>
-      <c r="AF9" s="98">
-        <f>Z9-AA9</f>
-        <v>216826</v>
-      </c>
-      <c r="AG9" s="104">
-        <v>522715</v>
-      </c>
-      <c r="AH9" s="99">
-        <f t="shared" ref="AH9" si="5">SUM(AI9:AL9)</f>
-        <v>48041</v>
-      </c>
-      <c r="AI9" s="100">
-        <v>2881</v>
-      </c>
-      <c r="AJ9" s="100">
-        <v>1394</v>
-      </c>
-      <c r="AK9" s="100">
-        <v>190</v>
-      </c>
-      <c r="AL9" s="101">
-        <v>43576</v>
-      </c>
-      <c r="AM9" s="102">
-        <f t="shared" ref="AM9" si="6">SUM(AJ9:AK9)</f>
-        <v>1584</v>
-      </c>
-      <c r="AN9" s="103">
-        <f>AM9/Z9*100</f>
-        <v>0.33980915768517883</v>
-      </c>
-      <c r="AO9" s="103">
-        <v>1.26</v>
-      </c>
-      <c r="AP9" s="103">
-        <f t="shared" ref="AP9" si="7">AO9-AN9</f>
-        <v>0.92019084231482118</v>
-      </c>
-      <c r="AQ9" s="104"/>
-    </row>
-    <row r="10" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26">
-        <v>2</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="71">
-        <v>29921</v>
-      </c>
-      <c r="D10" s="72">
-        <v>29921</v>
-      </c>
-      <c r="E10" s="29">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F10" s="59">
-        <v>815</v>
-      </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="31">
-        <f>G10-'Tháng 7_2025'!G10</f>
-        <v>-496</v>
-      </c>
-      <c r="I10" s="31">
-        <f>G10-'Thang 12'!Q11</f>
-        <v>-487</v>
-      </c>
-      <c r="J10" s="31">
-        <f t="shared" si="1"/>
-        <v>815</v>
-      </c>
-      <c r="K10" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="31">
-        <v>1297</v>
-      </c>
-      <c r="M10" s="30"/>
-      <c r="N10" s="53">
-        <f>M10-'Tháng 7_2025'!M10</f>
-        <v>-720</v>
-      </c>
-      <c r="O10" s="53">
-        <f>M10-'Thang 12'!AG11</f>
-        <v>-590</v>
-      </c>
-      <c r="P10" s="53">
-        <f t="shared" ref="P10:P15" si="8">L10-M10</f>
-        <v>1297</v>
-      </c>
-      <c r="Q10" s="70">
-        <f t="shared" ref="Q10:Q16" si="9">M10/L10*100</f>
-        <v>0</v>
-      </c>
-      <c r="R10" s="31">
-        <v>661</v>
-      </c>
-      <c r="S10" s="31"/>
-      <c r="T10" s="53">
-        <f>S10-'Tháng 7_2025'!S10</f>
-        <v>-390</v>
-      </c>
-      <c r="U10" s="53">
-        <f>S10-'Thang 12'!Y11</f>
-        <v>-350</v>
-      </c>
-      <c r="V10" s="53">
-        <f t="shared" si="3"/>
-        <v>661</v>
-      </c>
-      <c r="W10" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X10" s="28"/>
-      <c r="Y10" s="108" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z10" s="107">
-        <v>173399</v>
-      </c>
-      <c r="AA10" s="94">
-        <v>94017</v>
-      </c>
-      <c r="AB10" s="94">
-        <v>94017</v>
-      </c>
-      <c r="AC10" s="94">
-        <f t="shared" ref="AC10:AC14" si="10">AA10-AB10</f>
-        <v>0</v>
-      </c>
-      <c r="AD10" s="94">
-        <f t="shared" ref="AD10:AD14" si="11">AA10-AG10</f>
-        <v>-97632</v>
-      </c>
-      <c r="AE10" s="97">
-        <f t="shared" ref="AE10:AE13" si="12">AA10/Z10*100</f>
-        <v>54.220035871025786</v>
-      </c>
-      <c r="AF10" s="98">
-        <f t="shared" ref="AF10:AF13" si="13">Z10-AA10</f>
-        <v>79382</v>
-      </c>
-      <c r="AG10" s="104">
-        <v>191649</v>
-      </c>
-      <c r="AH10" s="95"/>
-      <c r="AI10" s="105"/>
-      <c r="AJ10" s="105"/>
-      <c r="AK10" s="105"/>
-      <c r="AL10" s="96"/>
-      <c r="AM10" s="96"/>
-      <c r="AN10" s="94"/>
-      <c r="AO10" s="94"/>
-      <c r="AP10" s="94"/>
-      <c r="AQ10" s="104"/>
-    </row>
-    <row r="11" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26">
-        <v>3</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="71">
-        <v>25763</v>
-      </c>
-      <c r="D11" s="72">
-        <v>25763</v>
-      </c>
-      <c r="E11" s="29">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F11" s="59">
-        <v>652</v>
-      </c>
-      <c r="G11" s="30"/>
-      <c r="H11" s="31">
-        <f>G11-'Tháng 7_2025'!G11</f>
-        <v>-519</v>
-      </c>
-      <c r="I11" s="31">
-        <f>G11-'Thang 12'!Q12</f>
-        <v>-539</v>
-      </c>
-      <c r="J11" s="31">
-        <f t="shared" si="1"/>
-        <v>652</v>
-      </c>
-      <c r="K11" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="31">
-        <v>1117</v>
-      </c>
-      <c r="M11" s="30"/>
-      <c r="N11" s="53">
-        <f>M11-'Tháng 7_2025'!M11</f>
-        <v>-770</v>
-      </c>
-      <c r="O11" s="53">
-        <f>M11-'Thang 12'!AG12</f>
-        <v>-816</v>
-      </c>
-      <c r="P11" s="53">
-        <f t="shared" si="8"/>
-        <v>1117</v>
-      </c>
-      <c r="Q11" s="70">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="31">
-        <v>565</v>
-      </c>
-      <c r="S11" s="31"/>
-      <c r="T11" s="53">
-        <f>S11-'Tháng 7_2025'!S11</f>
-        <v>-434</v>
-      </c>
-      <c r="U11" s="53">
-        <f>S11-'Thang 12'!Y12</f>
-        <v>-397</v>
-      </c>
-      <c r="V11" s="53">
-        <f t="shared" si="3"/>
-        <v>565</v>
-      </c>
-      <c r="W11" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X11" s="28"/>
-      <c r="Y11" s="108" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z11" s="107">
-        <v>37255</v>
-      </c>
-      <c r="AA11" s="109">
-        <v>19221</v>
-      </c>
-      <c r="AB11" s="109">
-        <v>19221</v>
-      </c>
-      <c r="AC11" s="94">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="94">
-        <f t="shared" si="11"/>
-        <v>-16054</v>
-      </c>
-      <c r="AE11" s="97">
-        <f t="shared" si="12"/>
-        <v>51.593074755066439</v>
-      </c>
-      <c r="AF11" s="98">
-        <f t="shared" si="13"/>
-        <v>18034</v>
-      </c>
-      <c r="AG11" s="104">
-        <v>35275</v>
-      </c>
-      <c r="AH11" s="104"/>
-      <c r="AI11" s="104"/>
-      <c r="AJ11" s="104"/>
-      <c r="AK11" s="104"/>
-      <c r="AL11" s="104"/>
-      <c r="AM11" s="104"/>
-      <c r="AN11" s="104"/>
-      <c r="AO11" s="104"/>
-      <c r="AP11" s="104"/>
-      <c r="AQ11" s="104"/>
-    </row>
-    <row r="12" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26">
-        <v>4</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="71">
-        <v>51742</v>
-      </c>
-      <c r="D12" s="72">
-        <v>51742</v>
-      </c>
-      <c r="E12" s="29">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F12" s="59">
-        <v>1151</v>
-      </c>
-      <c r="G12" s="30"/>
-      <c r="H12" s="31">
-        <f>G12-'Tháng 7_2025'!G12</f>
-        <v>-1096</v>
-      </c>
-      <c r="I12" s="31">
-        <f>G12-'Thang 12'!Q13</f>
-        <v>-1101</v>
-      </c>
-      <c r="J12" s="31">
-        <f t="shared" si="1"/>
-        <v>1151</v>
-      </c>
-      <c r="K12" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="31">
-        <v>2043</v>
-      </c>
-      <c r="M12" s="30"/>
-      <c r="N12" s="53">
-        <f>M12-'Tháng 7_2025'!M12</f>
-        <v>-1626</v>
-      </c>
-      <c r="O12" s="53">
-        <f>M12-'Thang 12'!AG13</f>
-        <v>-1451</v>
-      </c>
-      <c r="P12" s="53">
-        <f t="shared" si="8"/>
-        <v>2043</v>
-      </c>
-      <c r="Q12" s="70">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="31">
-        <v>978</v>
-      </c>
-      <c r="S12" s="31"/>
-      <c r="T12" s="53">
-        <f>S12-'Tháng 7_2025'!S12</f>
-        <v>-991</v>
-      </c>
-      <c r="U12" s="53">
-        <f>S12-'Thang 12'!Y13</f>
-        <v>-910</v>
-      </c>
-      <c r="V12" s="53">
-        <f t="shared" si="3"/>
-        <v>978</v>
-      </c>
-      <c r="W12" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X12" s="28"/>
-      <c r="Y12" s="108" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z12" s="107">
-        <v>10639</v>
-      </c>
-      <c r="AA12" s="109">
-        <v>6448</v>
-      </c>
-      <c r="AB12" s="109">
-        <v>6448</v>
-      </c>
-      <c r="AC12" s="94">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="94">
-        <f t="shared" si="11"/>
-        <v>-6661</v>
-      </c>
-      <c r="AE12" s="97">
-        <f t="shared" si="12"/>
-        <v>60.607199924804966</v>
-      </c>
-      <c r="AF12" s="98">
-        <f t="shared" si="13"/>
-        <v>4191</v>
-      </c>
-      <c r="AG12" s="104">
-        <v>13109</v>
-      </c>
-      <c r="AH12" s="104"/>
-      <c r="AI12" s="104"/>
-      <c r="AJ12" s="104"/>
-      <c r="AK12" s="104"/>
-      <c r="AL12" s="104"/>
-      <c r="AM12" s="104"/>
-      <c r="AN12" s="104"/>
-      <c r="AO12" s="104"/>
-      <c r="AP12" s="104"/>
-      <c r="AQ12" s="104"/>
-    </row>
-    <row r="13" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26">
-        <v>5</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="71">
-        <v>27773</v>
-      </c>
-      <c r="D13" s="72">
-        <v>27773</v>
-      </c>
-      <c r="E13" s="29">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F13" s="59">
-        <v>1206</v>
-      </c>
-      <c r="G13" s="30"/>
-      <c r="H13" s="31">
-        <f>G13-'Tháng 7_2025'!G13</f>
-        <v>-979</v>
-      </c>
-      <c r="I13" s="31">
-        <f>G13-'Thang 12'!Q14</f>
-        <v>-1008</v>
-      </c>
-      <c r="J13" s="31">
-        <f t="shared" si="1"/>
-        <v>1206</v>
-      </c>
-      <c r="K13" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="31">
-        <v>1204</v>
-      </c>
-      <c r="M13" s="30"/>
-      <c r="N13" s="53">
-        <f>M13-'Tháng 7_2025'!M13</f>
-        <v>-972</v>
-      </c>
-      <c r="O13" s="53">
-        <f>M13-'Thang 12'!AG14</f>
-        <v>-1007</v>
-      </c>
-      <c r="P13" s="53">
-        <f t="shared" si="8"/>
-        <v>1204</v>
-      </c>
-      <c r="Q13" s="70">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R13" s="31">
-        <v>1005</v>
-      </c>
-      <c r="S13" s="31"/>
-      <c r="T13" s="53">
-        <f>S13-'Tháng 7_2025'!S13</f>
-        <v>-864</v>
-      </c>
-      <c r="U13" s="53">
-        <f>S13-'Thang 12'!Y14</f>
-        <v>-914</v>
-      </c>
-      <c r="V13" s="53">
-        <f t="shared" si="3"/>
-        <v>1005</v>
-      </c>
-      <c r="W13" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X13" s="28"/>
-      <c r="Y13" s="108" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z13" s="107">
-        <v>244851</v>
-      </c>
-      <c r="AA13" s="109">
-        <v>129490</v>
-      </c>
-      <c r="AB13" s="109">
-        <v>129490</v>
-      </c>
-      <c r="AC13" s="94">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD13" s="94">
-        <f t="shared" si="11"/>
-        <v>-153011</v>
-      </c>
-      <c r="AE13" s="97">
-        <f t="shared" si="12"/>
-        <v>52.88522407504972</v>
-      </c>
-      <c r="AF13" s="98">
-        <f t="shared" si="13"/>
-        <v>115361</v>
-      </c>
-      <c r="AG13" s="104">
-        <v>282501</v>
-      </c>
-      <c r="AH13" s="104"/>
-      <c r="AI13" s="104"/>
-      <c r="AJ13" s="104"/>
-      <c r="AK13" s="104"/>
-      <c r="AL13" s="104"/>
-      <c r="AM13" s="104"/>
-      <c r="AN13" s="104"/>
-      <c r="AO13" s="104"/>
-      <c r="AP13" s="104"/>
-      <c r="AQ13" s="104"/>
-    </row>
-    <row r="14" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26">
-        <v>6</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="71">
-        <v>28987</v>
-      </c>
-      <c r="D14" s="72">
-        <v>28987</v>
-      </c>
-      <c r="E14" s="29">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F14" s="59">
-        <v>591</v>
-      </c>
-      <c r="G14" s="30"/>
-      <c r="H14" s="31">
-        <f>G14-'Tháng 7_2025'!G14</f>
-        <v>-524</v>
-      </c>
-      <c r="I14" s="31">
-        <f>G14-'Thang 12'!Q15</f>
-        <v>-464</v>
-      </c>
-      <c r="J14" s="31">
-        <f t="shared" si="1"/>
-        <v>591</v>
-      </c>
-      <c r="K14" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="31">
-        <v>1257</v>
-      </c>
-      <c r="M14" s="30"/>
-      <c r="N14" s="53">
-        <f>M14-'Tháng 7_2025'!M14</f>
-        <v>-1010</v>
-      </c>
-      <c r="O14" s="53">
-        <f>M14-'Thang 12'!AG15</f>
-        <v>-980</v>
-      </c>
-      <c r="P14" s="53">
-        <f t="shared" si="8"/>
-        <v>1257</v>
-      </c>
-      <c r="Q14" s="70">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="31">
-        <v>447</v>
-      </c>
-      <c r="S14" s="31"/>
-      <c r="T14" s="53">
-        <f>S14-'Tháng 7_2025'!S14</f>
-        <v>-417</v>
-      </c>
-      <c r="U14" s="53">
-        <f>S14-'Thang 12'!Y15</f>
-        <v>-372</v>
-      </c>
-      <c r="V14" s="53">
-        <f t="shared" si="3"/>
-        <v>447</v>
-      </c>
-      <c r="W14" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X14" s="28"/>
-      <c r="Y14" s="108" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z14" s="109"/>
-      <c r="AA14" s="109">
-        <v>142</v>
-      </c>
-      <c r="AB14" s="109">
-        <v>142</v>
-      </c>
-      <c r="AC14" s="94">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AD14" s="94">
-        <f t="shared" si="11"/>
-        <v>-39</v>
-      </c>
-      <c r="AE14" s="97"/>
-      <c r="AF14" s="104"/>
-      <c r="AG14" s="104">
-        <v>181</v>
-      </c>
-      <c r="AH14" s="104"/>
-      <c r="AI14" s="104"/>
-      <c r="AJ14" s="104"/>
-      <c r="AK14" s="104"/>
-      <c r="AL14" s="104"/>
-      <c r="AM14" s="104"/>
-      <c r="AN14" s="104"/>
-      <c r="AO14" s="104"/>
-      <c r="AP14" s="104"/>
-      <c r="AQ14" s="104"/>
-    </row>
-    <row r="15" spans="1:43" ht="18" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26">
-        <v>7</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="71">
-        <v>24726</v>
-      </c>
-      <c r="D15" s="72">
-        <v>24726</v>
-      </c>
-      <c r="E15" s="29">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F15" s="59">
-        <v>541</v>
-      </c>
-      <c r="G15" s="30"/>
-      <c r="H15" s="31">
-        <f>G15-'Tháng 7_2025'!G15</f>
-        <v>-536</v>
-      </c>
-      <c r="I15" s="31">
-        <f>G15-'Thang 12'!Q16</f>
-        <v>-461</v>
-      </c>
-      <c r="J15" s="31">
-        <f t="shared" si="1"/>
-        <v>541</v>
-      </c>
-      <c r="K15" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="31">
-        <v>1072</v>
-      </c>
-      <c r="M15" s="30"/>
-      <c r="N15" s="53">
-        <f>M15-'Tháng 7_2025'!M15</f>
-        <v>-1068</v>
-      </c>
-      <c r="O15" s="53">
-        <f>M15-'Thang 12'!AG16</f>
-        <v>-1040</v>
-      </c>
-      <c r="P15" s="53">
-        <f t="shared" si="8"/>
-        <v>1072</v>
-      </c>
-      <c r="Q15" s="70">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R15" s="31">
-        <v>439</v>
-      </c>
-      <c r="S15" s="31"/>
-      <c r="T15" s="53">
-        <f>S15-'Tháng 7_2025'!S15</f>
-        <v>-441</v>
-      </c>
-      <c r="U15" s="53">
-        <f>S15-'Thang 12'!Y16</f>
-        <v>-383</v>
-      </c>
-      <c r="V15" s="53">
-        <f t="shared" si="3"/>
-        <v>439</v>
-      </c>
-      <c r="W15" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X15" s="28"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="10"/>
-      <c r="AA15" s="10"/>
-      <c r="AB15" s="10"/>
-      <c r="AC15" s="10"/>
-    </row>
-    <row r="16" spans="1:43" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="141"/>
-      <c r="C16" s="18">
-        <f>SUM(C9:C15)</f>
-        <v>228291</v>
-      </c>
-      <c r="D16" s="18">
-        <f>SUM(D9:D15)</f>
-        <v>228291</v>
-      </c>
-      <c r="E16" s="32">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F16" s="60">
-        <f>SUM(F9:F15)</f>
-        <v>6581</v>
-      </c>
-      <c r="G16" s="50">
-        <f>SUM(G9:G15)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="55">
-        <f>SUM(H9:H15)</f>
-        <v>-5678</v>
-      </c>
-      <c r="I16" s="55">
-        <f>G16-'Thang 12'!Q17</f>
-        <v>-5712</v>
-      </c>
-      <c r="J16" s="55">
-        <f>SUM(J9:J15)</f>
-        <v>6581</v>
-      </c>
-      <c r="K16" s="57">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="18">
-        <f>SUM(L9:L15)</f>
-        <v>9852</v>
-      </c>
-      <c r="M16" s="18">
-        <f>SUM(M9:M15)</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="56">
-        <f>SUM(N9:N15)</f>
-        <v>-7790</v>
-      </c>
-      <c r="O16" s="56">
-        <f>SUM(O9:O15)</f>
-        <v>-7554</v>
-      </c>
-      <c r="P16" s="18">
-        <f t="shared" ref="P16" si="14">SUM(P9:P15)</f>
-        <v>9852</v>
-      </c>
-      <c r="Q16" s="69">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="55">
-        <f>SUM(R9:R15)</f>
-        <v>5515</v>
-      </c>
-      <c r="S16" s="18">
-        <f>SUM(S9:S15)</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="56">
-        <f>SUM(T9:T15)</f>
-        <v>-4929</v>
-      </c>
-      <c r="U16" s="56">
-        <f>SUM(U9:U15)</f>
-        <v>-4771</v>
-      </c>
-      <c r="V16" s="56">
-        <f>SUM(V9:V15)</f>
-        <v>5515</v>
-      </c>
-      <c r="W16" s="57">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X16" s="37"/>
-      <c r="Y16" s="36"/>
-      <c r="Z16" s="10"/>
-      <c r="AA16" s="25"/>
-    </row>
-    <row r="17" spans="1:25" ht="9.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11"/>
-      <c r="B17" s="119"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="15"/>
-      <c r="Y17" s="15"/>
-    </row>
-    <row r="18" spans="1:25" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="142" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="19"/>
-    </row>
-    <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.35">
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="119"/>
-      <c r="J19" s="119"/>
-      <c r="K19" s="119"/>
-      <c r="L19" s="119"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="80"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B20" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-    </row>
-    <row r="21" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="120"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-    </row>
-    <row r="22" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-    </row>
-    <row r="23" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B23" s="5"/>
-      <c r="R23" s="31"/>
-    </row>
-    <row r="24" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B24" s="5"/>
-      <c r="R24" s="31"/>
-    </row>
-    <row r="25" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="R25" s="31"/>
-    </row>
-  </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:X1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="H2:X2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AH7:AP7"/>
-    <mergeCell ref="AQ7:AQ8"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:K7"/>
-    <mergeCell ref="L7:Q7"/>
-    <mergeCell ref="R7:W7"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-</worksheet>
 </file>